--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{257639EF-80E3-4CCD-83D9-10B46D84FE01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B12006F-1F75-45C2-8CC1-BC74096B59AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -361,6 +361,8 @@
       <sheetName val="INVENTARIO NACIONAL 06-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 07-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 10-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 11-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 12-08-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -368,21 +370,21 @@
       <sheetData sheetId="2">
         <row r="4">
           <cell r="F4">
-            <v>1114.5999999999999</v>
+            <v>1163.2857142857142</v>
           </cell>
           <cell r="G4">
-            <v>-3.5273081924578342E-3</v>
+            <v>3.9998606724874541E-2</v>
           </cell>
           <cell r="H4" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="5">
           <cell r="F5">
-            <v>93.8</v>
+            <v>80.428571428571431</v>
           </cell>
           <cell r="G5">
-            <v>0.20326530612244897</v>
+            <v>3.1736776343190387E-2</v>
           </cell>
           <cell r="H5" t="str">
             <v>SUBIÓ</v>
@@ -390,10 +392,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>393.8</v>
+            <v>443.28571428571428</v>
           </cell>
           <cell r="G6">
-            <v>-0.2807305936073059</v>
+            <v>-0.1903457273320287</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -401,10 +403,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>104.6</v>
+            <v>103.28571428571429</v>
           </cell>
           <cell r="G7">
-            <v>6.9827986982798684E-2</v>
+            <v>5.6385734210002036E-2</v>
           </cell>
           <cell r="H7" t="str">
             <v>SUBIÓ</v>
@@ -412,10 +414,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>8.4</v>
+            <v>9.1428571428571423</v>
           </cell>
           <cell r="G8">
-            <v>-0.49645776566757494</v>
+            <v>-0.45192681977423133</v>
           </cell>
           <cell r="H8" t="str">
             <v>BAJO</v>
@@ -423,10 +425,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1301.2</v>
+            <v>1436.7142857142858</v>
           </cell>
           <cell r="G9">
-            <v>4.8581859028362651E-3</v>
+            <v>0.10950976852409022</v>
           </cell>
           <cell r="H9" t="str">
             <v>SUBIÓ</v>
@@ -434,10 +436,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>123.4</v>
+            <v>137.71428571428572</v>
           </cell>
           <cell r="G10">
-            <v>9.9702380952380043E-3</v>
+            <v>0.12712585034013602</v>
           </cell>
           <cell r="H10" t="str">
             <v>SUBIÓ</v>
@@ -445,10 +447,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>327</v>
+            <v>358.57142857142856</v>
           </cell>
           <cell r="G11">
-            <v>7.6623765339718597E-2</v>
+            <v>0.18057040236028543</v>
           </cell>
           <cell r="H11" t="str">
             <v>SUBIÓ</v>
@@ -456,10 +458,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>745.6</v>
+            <v>680.85714285714289</v>
           </cell>
           <cell r="G12">
-            <v>0.12628398791540785</v>
+            <v>2.8485110056106988E-2</v>
           </cell>
           <cell r="H12" t="str">
             <v>SUBIÓ</v>
@@ -467,65 +469,65 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>423.2</v>
+            <v>389.71428571428572</v>
           </cell>
           <cell r="G13">
-            <v>4.4352215367358339E-2</v>
+            <v>-3.8282188927169281E-2</v>
           </cell>
           <cell r="H13" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3133.8</v>
+            <v>3438.4285714285716</v>
           </cell>
           <cell r="G14">
-            <v>-3.5767331925427581E-2</v>
+            <v>5.7963225289556553E-2</v>
           </cell>
           <cell r="H14" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2087.4</v>
+            <v>2212.5714285714284</v>
           </cell>
           <cell r="G15">
-            <v>-4.1837756634952372E-2</v>
+            <v>1.5618666094379563E-2</v>
           </cell>
           <cell r="H15" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2021</v>
+            <v>2208.4285714285716</v>
           </cell>
           <cell r="G16">
-            <v>-6.5453169665377509E-2</v>
+            <v>2.121718033101927E-2</v>
           </cell>
           <cell r="H16" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2275.8000000000002</v>
+            <v>2580.4285714285716</v>
           </cell>
           <cell r="G17">
-            <v>-5.3596204374042888E-2</v>
+            <v>7.308524226279367E-2</v>
           </cell>
           <cell r="H17" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="18">
           <cell r="F18">
-            <v>62</v>
+            <v>45.571428571428569</v>
           </cell>
           <cell r="G18">
-            <v>-0.53431205189484454</v>
+            <v>-0.65770862800565766</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -533,10 +535,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>208.2</v>
+            <v>202.14285714285714</v>
           </cell>
           <cell r="G19">
-            <v>-7.8204870195210385E-2</v>
+            <v>-0.10502256849610447</v>
           </cell>
           <cell r="H19" t="str">
             <v>BAJO</v>
@@ -544,10 +546,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>125.6</v>
+            <v>120.57142857142857</v>
           </cell>
           <cell r="G20">
-            <v>-0.15082974800245852</v>
+            <v>-0.18482746509790149</v>
           </cell>
           <cell r="H20" t="str">
             <v>BAJO</v>
@@ -555,21 +557,21 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>484.4</v>
+            <v>489</v>
           </cell>
           <cell r="G21">
-            <v>-4.5025688930406815E-3</v>
+            <v>4.9509574964969882E-3</v>
           </cell>
           <cell r="H21" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="22">
           <cell r="F22">
-            <v>731</v>
+            <v>722.14285714285711</v>
           </cell>
           <cell r="G22">
-            <v>-8.2130015410079249E-2</v>
+            <v>-9.3251363669718756E-2</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -588,10 +590,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>80.400000000000006</v>
+            <v>83.142857142857139</v>
           </cell>
           <cell r="G24">
-            <v>0.63475046210720909</v>
+            <v>0.69052020068655917</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -599,10 +601,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>575.4</v>
+            <v>612.42857142857144</v>
           </cell>
           <cell r="G25">
-            <v>-0.15966542750929369</v>
+            <v>-0.10558758819512937</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -610,32 +612,32 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>882.6</v>
+            <v>1151.7142857142858</v>
           </cell>
           <cell r="G26">
-            <v>-0.20457170947523651</v>
+            <v>3.7962979218970405E-2</v>
           </cell>
           <cell r="H26" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="27">
           <cell r="F27">
-            <v>480.2</v>
+            <v>484</v>
           </cell>
           <cell r="G27">
-            <v>-5.609939759036231E-3</v>
+            <v>2.2590361445782303E-3</v>
           </cell>
           <cell r="H27" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="28">
           <cell r="F28">
-            <v>331.6</v>
+            <v>363.71428571428572</v>
           </cell>
           <cell r="G28">
-            <v>-9.5000620270437874E-2</v>
+            <v>-7.3546351923724496E-3</v>
           </cell>
           <cell r="H28" t="str">
             <v>BAJO</v>
@@ -643,10 +645,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>116.4</v>
+            <v>130.57142857142858</v>
           </cell>
           <cell r="G29">
-            <v>8.738853503184707E-2</v>
+            <v>0.21977555353351552</v>
           </cell>
           <cell r="H29" t="str">
             <v>SUBIÓ</v>
@@ -654,10 +656,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>102.6</v>
+            <v>107</v>
           </cell>
           <cell r="G30">
-            <v>-0.162759643916914</v>
+            <v>-0.12685459940652821</v>
           </cell>
           <cell r="H30" t="str">
             <v>BAJO</v>
@@ -665,10 +667,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>406.4</v>
+            <v>490.57142857142856</v>
           </cell>
           <cell r="G31">
-            <v>-0.48604276845251781</v>
+            <v>-0.37959465230102163</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -676,10 +678,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>631.6</v>
+            <v>645.57142857142856</v>
           </cell>
           <cell r="G32">
-            <v>-3.0612529649783671E-2</v>
+            <v>-9.1690087504234796E-3</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -687,21 +689,21 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>820</v>
+            <v>845.42857142857144</v>
           </cell>
           <cell r="G33">
-            <v>-2.6863739346207782E-2</v>
+            <v>3.3136568900944408E-3</v>
           </cell>
           <cell r="H33" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="34">
           <cell r="F34">
-            <v>494.6</v>
+            <v>544.57142857142856</v>
           </cell>
           <cell r="G34">
-            <v>-0.13586404066073698</v>
+            <v>-4.8556906879651529E-2</v>
           </cell>
           <cell r="H34" t="str">
             <v>BAJO</v>
@@ -709,10 +711,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>34.4</v>
+            <v>25</v>
           </cell>
           <cell r="G35">
-            <v>-0.83815226689478184</v>
+            <v>-0.88237810094097524</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -720,10 +722,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>647.4</v>
+            <v>647.14285714285711</v>
           </cell>
           <cell r="G36">
-            <v>1.2212726138490333</v>
+            <v>1.2203903395419302</v>
           </cell>
           <cell r="H36" t="str">
             <v>SUBIÓ</v>
@@ -731,10 +733,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>132.4</v>
+            <v>101.28571428571429</v>
           </cell>
           <cell r="G37">
-            <v>-0.64620429976922145</v>
+            <v>-0.72934705280144363</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -742,10 +744,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>285.60000000000002</v>
+            <v>311.57142857142856</v>
           </cell>
           <cell r="G38">
-            <v>4.6328059950041744E-2</v>
+            <v>0.14147734031164516</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -753,10 +755,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>574.79999999999995</v>
+            <v>557.42857142857144</v>
           </cell>
           <cell r="G39">
-            <v>0.36723970158936092</v>
+            <v>0.32591940441437672</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -764,10 +766,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>312.2</v>
+            <v>321.57142857142856</v>
           </cell>
           <cell r="G40">
-            <v>0.26676503135374396</v>
+            <v>0.30479000895821251</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -775,10 +777,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>250.4</v>
+            <v>259.42857142857144</v>
           </cell>
           <cell r="G41">
-            <v>-4.9387402933563473E-2</v>
+            <v>-1.5111549365216304E-2</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -786,10 +788,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>41</v>
+            <v>49.285714285714285</v>
           </cell>
           <cell r="G42">
-            <v>-0.17850637522768664</v>
+            <v>-1.2490241998438734E-2</v>
           </cell>
           <cell r="H42" t="str">
             <v>BAJO</v>
@@ -797,10 +799,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>90.4</v>
+            <v>102.14285714285714</v>
           </cell>
           <cell r="G43">
-            <v>0.13840870062965105</v>
+            <v>0.28628669555973496</v>
           </cell>
           <cell r="H43" t="str">
             <v>SUBIÓ</v>
@@ -808,10 +810,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>66.2</v>
+            <v>69</v>
           </cell>
           <cell r="G44">
-            <v>0.93156498673740051</v>
+            <v>1.0132625994694959</v>
           </cell>
           <cell r="H44" t="str">
             <v>SUBIÓ</v>
@@ -819,10 +821,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>43.2</v>
+            <v>55.285714285714285</v>
           </cell>
           <cell r="G45">
-            <v>0.15200000000000014</v>
+            <v>0.4742857142857142</v>
           </cell>
           <cell r="H45" t="str">
             <v>SUBIÓ</v>
@@ -841,10 +843,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>2</v>
+            <v>1.5714285714285714</v>
           </cell>
           <cell r="G47">
-            <v>-0.38888888888888895</v>
+            <v>-0.51984126984126988</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -856,6 +858,8 @@
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1112,15 +1116,15 @@
       </c>
       <c r="E2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1114.5999999999999</v>
+        <v>1163.2857142857142</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>-3.5273081924578342E-3</v>
+        <v>3.9998606724874541E-2</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H2">
         <v>1.36</v>
@@ -1141,11 +1145,11 @@
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>93.8</v>
+        <v>80.428571428571431</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>0.20326530612244897</v>
+        <v>3.1736776343190387E-2</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1170,11 +1174,11 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>393.8</v>
+        <v>443.28571428571428</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-0.2807305936073059</v>
+        <v>-0.1903457273320287</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1199,11 +1203,11 @@
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>104.6</v>
+        <v>103.28571428571429</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>6.9827986982798684E-2</v>
+        <v>5.6385734210002036E-2</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1228,11 +1232,11 @@
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>8.4</v>
+        <v>9.1428571428571423</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>-0.49645776566757494</v>
+        <v>-0.45192681977423133</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1257,11 +1261,11 @@
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1301.2</v>
+        <v>1436.7142857142858</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>4.8581859028362651E-3</v>
+        <v>0.10950976852409022</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1286,11 +1290,11 @@
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>123.4</v>
+        <v>137.71428571428572</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>9.9702380952380043E-3</v>
+        <v>0.12712585034013602</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1315,11 +1319,11 @@
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>327</v>
+        <v>358.57142857142856</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>7.6623765339718597E-2</v>
+        <v>0.18057040236028543</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1344,11 +1348,11 @@
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>745.6</v>
+        <v>680.85714285714289</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>0.12628398791540785</v>
+        <v>2.8485110056106988E-2</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1373,15 +1377,15 @@
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>423.2</v>
+        <v>389.71428571428572</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>4.4352215367358339E-2</v>
+        <v>-3.8282188927169281E-2</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H11">
         <v>1.0900000000000001</v>
@@ -1402,15 +1406,15 @@
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3133.8</v>
+        <v>3438.4285714285716</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-3.5767331925427581E-2</v>
+        <v>5.7963225289556553E-2</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H12">
         <v>1.1599999999999999</v>
@@ -1431,15 +1435,15 @@
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2087.4</v>
+        <v>2212.5714285714284</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-4.1837756634952372E-2</v>
+        <v>1.5618666094379563E-2</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H13">
         <v>1.1599999999999999</v>
@@ -1460,15 +1464,15 @@
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2021</v>
+        <v>2208.4285714285716</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-6.5453169665377509E-2</v>
+        <v>2.121718033101927E-2</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H14">
         <v>1.1599999999999999</v>
@@ -1489,15 +1493,15 @@
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2275.8000000000002</v>
+        <v>2580.4285714285716</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-5.3596204374042888E-2</v>
+        <v>7.308524226279367E-2</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H15">
         <v>1.1599999999999999</v>
@@ -1518,11 +1522,11 @@
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>62</v>
+        <v>45.571428571428569</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.53431205189484454</v>
+        <v>-0.65770862800565766</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1547,11 +1551,11 @@
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>208.2</v>
+        <v>202.14285714285714</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>-7.8204870195210385E-2</v>
+        <v>-0.10502256849610447</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1576,11 +1580,11 @@
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>125.6</v>
+        <v>120.57142857142857</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>-0.15082974800245852</v>
+        <v>-0.18482746509790149</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1605,15 +1609,15 @@
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>484.4</v>
+        <v>489</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>-4.5025688930406815E-3</v>
+        <v>4.9509574964969882E-3</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H19">
         <v>4.1500000000000004</v>
@@ -1634,11 +1638,11 @@
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>731</v>
+        <v>722.14285714285711</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-8.2130015410079249E-2</v>
+        <v>-9.3251363669718756E-2</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1692,11 +1696,11 @@
       </c>
       <c r="E22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>80.400000000000006</v>
+        <v>83.142857142857139</v>
       </c>
       <c r="F22" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>0.63475046210720909</v>
+        <v>0.69052020068655917</v>
       </c>
       <c r="G22" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1721,11 +1725,11 @@
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>575.4</v>
+        <v>612.42857142857144</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-0.15966542750929369</v>
+        <v>-0.10558758819512937</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1750,15 +1754,15 @@
       </c>
       <c r="E24" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>882.6</v>
+        <v>1151.7142857142858</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.20457170947523651</v>
+        <v>3.7962979218970405E-2</v>
       </c>
       <c r="G24" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H24">
         <v>1.63</v>
@@ -1779,15 +1783,15 @@
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>480.2</v>
+        <v>484</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-5.609939759036231E-3</v>
+        <v>2.2590361445782303E-3</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H25">
         <v>1.63</v>
@@ -1808,11 +1812,11 @@
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>331.6</v>
+        <v>363.71428571428572</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-9.5000620270437874E-2</v>
+        <v>-7.3546351923724496E-3</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1837,11 +1841,11 @@
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>116.4</v>
+        <v>130.57142857142858</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>8.738853503184707E-2</v>
+        <v>0.21977555353351552</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1866,11 +1870,11 @@
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>102.6</v>
+        <v>107</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>-0.162759643916914</v>
+        <v>-0.12685459940652821</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1895,11 +1899,11 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>406.4</v>
+        <v>490.57142857142856</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-0.48604276845251781</v>
+        <v>-0.37959465230102163</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1924,11 +1928,11 @@
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>631.6</v>
+        <v>645.57142857142856</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-3.0612529649783671E-2</v>
+        <v>-9.1690087504234796E-3</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1953,15 +1957,15 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>820</v>
+        <v>845.42857142857144</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-2.6863739346207782E-2</v>
+        <v>3.3136568900944408E-3</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H31">
         <v>1.1599999999999999</v>
@@ -1982,11 +1986,11 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>494.6</v>
+        <v>544.57142857142856</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-0.13586404066073698</v>
+        <v>-4.8556906879651529E-2</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2011,11 +2015,11 @@
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>34.4</v>
+        <v>25</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-0.83815226689478184</v>
+        <v>-0.88237810094097524</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2040,11 +2044,11 @@
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>647.4</v>
+        <v>647.14285714285711</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>1.2212726138490333</v>
+        <v>1.2203903395419302</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2069,11 +2073,11 @@
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>132.4</v>
+        <v>101.28571428571429</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.64620429976922145</v>
+        <v>-0.72934705280144363</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2098,11 +2102,11 @@
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>285.60000000000002</v>
+        <v>311.57142857142856</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>4.6328059950041744E-2</v>
+        <v>0.14147734031164516</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2127,11 +2131,11 @@
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>574.79999999999995</v>
+        <v>557.42857142857144</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.36723970158936092</v>
+        <v>0.32591940441437672</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2156,11 +2160,11 @@
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>312.2</v>
+        <v>321.57142857142856</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>0.26676503135374396</v>
+        <v>0.30479000895821251</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2185,11 +2189,11 @@
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>250.4</v>
+        <v>259.42857142857144</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-4.9387402933563473E-2</v>
+        <v>-1.5111549365216304E-2</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2214,11 +2218,11 @@
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>41</v>
+        <v>49.285714285714285</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>-0.17850637522768664</v>
+        <v>-1.2490241998438734E-2</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2243,11 +2247,11 @@
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>90.4</v>
+        <v>102.14285714285714</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>0.13840870062965105</v>
+        <v>0.28628669555973496</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2272,11 +2276,11 @@
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>66.2</v>
+        <v>69</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>0.93156498673740051</v>
+        <v>1.0132625994694959</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2301,11 +2305,11 @@
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>43.2</v>
+        <v>55.285714285714285</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>0.15200000000000014</v>
+        <v>0.4742857142857142</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2359,11 +2363,11 @@
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>2</v>
+        <v>1.5714285714285714</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.38888888888888895</v>
+        <v>-0.51984126984126988</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B12006F-1F75-45C2-8CC1-BC74096B59AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22721092-6B14-441E-AE7B-218B68497D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -370,10 +370,10 @@
       <sheetData sheetId="2">
         <row r="4">
           <cell r="F4">
-            <v>1163.2857142857142</v>
+            <v>1213.25</v>
           </cell>
           <cell r="G4">
-            <v>3.9998606724874541E-2</v>
+            <v>8.4667587776332986E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -381,10 +381,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>80.428571428571431</v>
+            <v>78.625</v>
           </cell>
           <cell r="G5">
-            <v>3.1736776343190387E-2</v>
+            <v>8.6005830903790326E-3</v>
           </cell>
           <cell r="H5" t="str">
             <v>SUBIÓ</v>
@@ -392,10 +392,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>443.28571428571428</v>
+            <v>470.875</v>
           </cell>
           <cell r="G6">
-            <v>-0.1903457273320287</v>
+            <v>-0.13995433789954337</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -403,10 +403,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>103.28571428571429</v>
+            <v>108.25</v>
           </cell>
           <cell r="G7">
-            <v>5.6385734210002036E-2</v>
+            <v>0.10715946071594606</v>
           </cell>
           <cell r="H7" t="str">
             <v>SUBIÓ</v>
@@ -414,10 +414,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>9.1428571428571423</v>
+            <v>9.375</v>
           </cell>
           <cell r="G8">
-            <v>-0.45192681977423133</v>
+            <v>-0.43801089918256131</v>
           </cell>
           <cell r="H8" t="str">
             <v>BAJO</v>
@@ -425,10 +425,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1436.7142857142858</v>
+            <v>1455.875</v>
           </cell>
           <cell r="G9">
-            <v>0.10950976852409022</v>
+            <v>0.12430672563886547</v>
           </cell>
           <cell r="H9" t="str">
             <v>SUBIÓ</v>
@@ -436,10 +436,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>137.71428571428572</v>
+            <v>144.75</v>
           </cell>
           <cell r="G10">
-            <v>0.12712585034013602</v>
+            <v>0.1847098214285714</v>
           </cell>
           <cell r="H10" t="str">
             <v>SUBIÓ</v>
@@ -447,10 +447,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>358.57142857142856</v>
+            <v>346</v>
           </cell>
           <cell r="G11">
-            <v>0.18057040236028543</v>
+            <v>0.13917988626159827</v>
           </cell>
           <cell r="H11" t="str">
             <v>SUBIÓ</v>
@@ -458,10 +458,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>680.85714285714289</v>
+            <v>725</v>
           </cell>
           <cell r="G12">
-            <v>2.8485110056106988E-2</v>
+            <v>9.5166163141993998E-2</v>
           </cell>
           <cell r="H12" t="str">
             <v>SUBIÓ</v>
@@ -469,10 +469,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>389.71428571428572</v>
+            <v>387.25</v>
           </cell>
           <cell r="G13">
-            <v>-3.8282188927169281E-2</v>
+            <v>-4.4363432417274251E-2</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -480,10 +480,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3438.4285714285716</v>
+            <v>3533.5</v>
           </cell>
           <cell r="G14">
-            <v>5.7963225289556553E-2</v>
+            <v>8.721556341869352E-2</v>
           </cell>
           <cell r="H14" t="str">
             <v>SUBIÓ</v>
@@ -491,10 +491,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2212.5714285714284</v>
+            <v>2248.5</v>
           </cell>
           <cell r="G15">
-            <v>1.5618666094379563E-2</v>
+            <v>3.2110665998998478E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>SUBIÓ</v>
@@ -502,10 +502,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2208.4285714285716</v>
+            <v>2218.375</v>
           </cell>
           <cell r="G16">
-            <v>2.121718033101927E-2</v>
+            <v>2.5816588195728851E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>SUBIÓ</v>
@@ -513,10 +513,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2580.4285714285716</v>
+            <v>2674.25</v>
           </cell>
           <cell r="G17">
-            <v>7.308524226279367E-2</v>
+            <v>0.11210139311570244</v>
           </cell>
           <cell r="H17" t="str">
             <v>SUBIÓ</v>
@@ -524,10 +524,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>45.571428571428569</v>
+            <v>43.5</v>
           </cell>
           <cell r="G18">
-            <v>-0.65770862800565766</v>
+            <v>-0.6732673267326732</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -535,10 +535,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>202.14285714285714</v>
+            <v>222.25</v>
           </cell>
           <cell r="G19">
-            <v>-0.10502256849610447</v>
+            <v>-1.5999195009056222E-2</v>
           </cell>
           <cell r="H19" t="str">
             <v>BAJO</v>
@@ -546,10 +546,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>120.57142857142857</v>
+            <v>129.75</v>
           </cell>
           <cell r="G20">
-            <v>-0.18482746509790149</v>
+            <v>-0.12277197295636144</v>
           </cell>
           <cell r="H20" t="str">
             <v>BAJO</v>
@@ -557,10 +557,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>489</v>
+            <v>528.25</v>
           </cell>
           <cell r="G21">
-            <v>4.9509574964969882E-3</v>
+            <v>8.5614198972442823E-2</v>
           </cell>
           <cell r="H21" t="str">
             <v>SUBIÓ</v>
@@ -568,10 +568,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>722.14285714285711</v>
+            <v>796.125</v>
           </cell>
           <cell r="G22">
-            <v>-9.3251363669718756E-2</v>
+            <v>-3.5671479938359507E-4</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -590,10 +590,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>83.142857142857139</v>
+            <v>72.75</v>
           </cell>
           <cell r="G24">
-            <v>0.69052020068655917</v>
+            <v>0.47920517560073939</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -601,10 +601,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>612.42857142857144</v>
+            <v>656.125</v>
           </cell>
           <cell r="G25">
-            <v>-0.10558758819512937</v>
+            <v>-4.1771773765268194E-2</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -612,10 +612,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>1151.7142857142858</v>
+            <v>1148.5</v>
           </cell>
           <cell r="G26">
-            <v>3.7962979218970405E-2</v>
+            <v>3.5066158698947358E-2</v>
           </cell>
           <cell r="H26" t="str">
             <v>SUBIÓ</v>
@@ -623,10 +623,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>484</v>
+            <v>520.625</v>
           </cell>
           <cell r="G27">
-            <v>2.2590361445782303E-3</v>
+            <v>7.8101468373493965E-2</v>
           </cell>
           <cell r="H27" t="str">
             <v>SUBIÓ</v>
@@ -634,21 +634,21 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>363.71428571428572</v>
+            <v>381</v>
           </cell>
           <cell r="G28">
-            <v>-7.3546351923724496E-3</v>
+            <v>3.9821362113881653E-2</v>
           </cell>
           <cell r="H28" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="29">
           <cell r="F29">
-            <v>130.57142857142858</v>
+            <v>136.125</v>
           </cell>
           <cell r="G29">
-            <v>0.21977555353351552</v>
+            <v>0.27165605095541401</v>
           </cell>
           <cell r="H29" t="str">
             <v>SUBIÓ</v>
@@ -656,10 +656,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>107</v>
+            <v>110.625</v>
           </cell>
           <cell r="G30">
-            <v>-0.12685459940652821</v>
+            <v>-9.7273738872403537E-2</v>
           </cell>
           <cell r="H30" t="str">
             <v>BAJO</v>
@@ -667,10 +667,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>490.57142857142856</v>
+            <v>617.375</v>
           </cell>
           <cell r="G31">
-            <v>-0.37959465230102163</v>
+            <v>-0.21923143251322141</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -678,21 +678,21 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>645.57142857142856</v>
+            <v>689.25</v>
           </cell>
           <cell r="G32">
-            <v>-9.1690087504234796E-3</v>
+            <v>5.7869401423189748E-2</v>
           </cell>
           <cell r="H32" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="33">
           <cell r="F33">
-            <v>845.42857142857144</v>
+            <v>911.75</v>
           </cell>
           <cell r="G33">
-            <v>3.3136568900944408E-3</v>
+            <v>8.2020714208652423E-2</v>
           </cell>
           <cell r="H33" t="str">
             <v>SUBIÓ</v>
@@ -700,21 +700,21 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>544.57142857142856</v>
+            <v>586</v>
           </cell>
           <cell r="G34">
-            <v>-4.8556906879651529E-2</v>
+            <v>2.3824650571791617E-2</v>
           </cell>
           <cell r="H34" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="35">
           <cell r="F35">
-            <v>25</v>
+            <v>21.875</v>
           </cell>
           <cell r="G35">
-            <v>-0.88237810094097524</v>
+            <v>-0.89708083832335328</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -722,10 +722,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>647.14285714285711</v>
+            <v>617.125</v>
           </cell>
           <cell r="G36">
-            <v>1.2203903395419302</v>
+            <v>1.1173970679975049</v>
           </cell>
           <cell r="H36" t="str">
             <v>SUBIÓ</v>
@@ -733,10 +733,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>101.28571428571429</v>
+            <v>88.625</v>
           </cell>
           <cell r="G37">
-            <v>-0.72934705280144363</v>
+            <v>-0.76317867120126326</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -744,10 +744,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>311.57142857142856</v>
+            <v>316.375</v>
           </cell>
           <cell r="G38">
-            <v>0.14147734031164516</v>
+            <v>0.15907577019150709</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -755,10 +755,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>557.42857142857144</v>
+            <v>565.375</v>
           </cell>
           <cell r="G39">
-            <v>0.32591940441437672</v>
+            <v>0.34482106173640381</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -766,10 +766,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>321.57142857142856</v>
+            <v>331.75</v>
           </cell>
           <cell r="G40">
-            <v>0.30479000895821251</v>
+            <v>0.3460900036886756</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -777,32 +777,32 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>259.42857142857144</v>
+            <v>268.125</v>
           </cell>
           <cell r="G41">
-            <v>-1.5111549365216304E-2</v>
+            <v>1.7903364969801494E-2</v>
           </cell>
           <cell r="H41" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="42">
           <cell r="F42">
-            <v>49.285714285714285</v>
+            <v>52.25</v>
           </cell>
           <cell r="G42">
-            <v>-1.2490241998438734E-2</v>
+            <v>4.6903460837887101E-2</v>
           </cell>
           <cell r="H42" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="43">
           <cell r="F43">
-            <v>102.14285714285714</v>
+            <v>103.625</v>
           </cell>
           <cell r="G43">
-            <v>0.28628669555973496</v>
+            <v>0.30495134516313693</v>
           </cell>
           <cell r="H43" t="str">
             <v>SUBIÓ</v>
@@ -810,10 +810,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>69</v>
+            <v>67.375</v>
           </cell>
           <cell r="G44">
-            <v>1.0132625994694959</v>
+            <v>0.96584880636604775</v>
           </cell>
           <cell r="H44" t="str">
             <v>SUBIÓ</v>
@@ -821,10 +821,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>55.285714285714285</v>
+            <v>55</v>
           </cell>
           <cell r="G45">
-            <v>0.4742857142857142</v>
+            <v>0.46666666666666656</v>
           </cell>
           <cell r="H45" t="str">
             <v>SUBIÓ</v>
@@ -843,10 +843,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>1.5714285714285714</v>
+            <v>1.625</v>
           </cell>
           <cell r="G47">
-            <v>-0.51984126984126988</v>
+            <v>-0.50347222222222232</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -1116,11 +1116,11 @@
       </c>
       <c r="E2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1163.2857142857142</v>
+        <v>1213.25</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>3.9998606724874541E-2</v>
+        <v>8.4667587776332986E-2</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1145,11 +1145,11 @@
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>80.428571428571431</v>
+        <v>78.625</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>3.1736776343190387E-2</v>
+        <v>8.6005830903790326E-3</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1174,11 +1174,11 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>443.28571428571428</v>
+        <v>470.875</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-0.1903457273320287</v>
+        <v>-0.13995433789954337</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1203,11 +1203,11 @@
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>103.28571428571429</v>
+        <v>108.25</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>5.6385734210002036E-2</v>
+        <v>0.10715946071594606</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1232,11 +1232,11 @@
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>9.1428571428571423</v>
+        <v>9.375</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>-0.45192681977423133</v>
+        <v>-0.43801089918256131</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1261,11 +1261,11 @@
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1436.7142857142858</v>
+        <v>1455.875</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>0.10950976852409022</v>
+        <v>0.12430672563886547</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1290,11 +1290,11 @@
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>137.71428571428572</v>
+        <v>144.75</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>0.12712585034013602</v>
+        <v>0.1847098214285714</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1319,11 +1319,11 @@
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>358.57142857142856</v>
+        <v>346</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>0.18057040236028543</v>
+        <v>0.13917988626159827</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1348,11 +1348,11 @@
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>680.85714285714289</v>
+        <v>725</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>2.8485110056106988E-2</v>
+        <v>9.5166163141993998E-2</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1377,11 +1377,11 @@
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>389.71428571428572</v>
+        <v>387.25</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-3.8282188927169281E-2</v>
+        <v>-4.4363432417274251E-2</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1406,11 +1406,11 @@
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3438.4285714285716</v>
+        <v>3533.5</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>5.7963225289556553E-2</v>
+        <v>8.721556341869352E-2</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1435,11 +1435,11 @@
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2212.5714285714284</v>
+        <v>2248.5</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>1.5618666094379563E-2</v>
+        <v>3.2110665998998478E-2</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1464,11 +1464,11 @@
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2208.4285714285716</v>
+        <v>2218.375</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>2.121718033101927E-2</v>
+        <v>2.5816588195728851E-2</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1493,11 +1493,11 @@
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2580.4285714285716</v>
+        <v>2674.25</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>7.308524226279367E-2</v>
+        <v>0.11210139311570244</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1522,11 +1522,11 @@
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>45.571428571428569</v>
+        <v>43.5</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.65770862800565766</v>
+        <v>-0.6732673267326732</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1551,11 +1551,11 @@
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>202.14285714285714</v>
+        <v>222.25</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>-0.10502256849610447</v>
+        <v>-1.5999195009056222E-2</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1580,11 +1580,11 @@
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>120.57142857142857</v>
+        <v>129.75</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>-0.18482746509790149</v>
+        <v>-0.12277197295636144</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1609,11 +1609,11 @@
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>489</v>
+        <v>528.25</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>4.9509574964969882E-3</v>
+        <v>8.5614198972442823E-2</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1638,11 +1638,11 @@
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>722.14285714285711</v>
+        <v>796.125</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-9.3251363669718756E-2</v>
+        <v>-3.5671479938359507E-4</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1696,11 +1696,11 @@
       </c>
       <c r="E22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>83.142857142857139</v>
+        <v>72.75</v>
       </c>
       <c r="F22" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>0.69052020068655917</v>
+        <v>0.47920517560073939</v>
       </c>
       <c r="G22" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1725,11 +1725,11 @@
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>612.42857142857144</v>
+        <v>656.125</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-0.10558758819512937</v>
+        <v>-4.1771773765268194E-2</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1754,11 +1754,11 @@
       </c>
       <c r="E24" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>1151.7142857142858</v>
+        <v>1148.5</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>3.7962979218970405E-2</v>
+        <v>3.5066158698947358E-2</v>
       </c>
       <c r="G24" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1783,11 +1783,11 @@
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>484</v>
+        <v>520.625</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>2.2590361445782303E-3</v>
+        <v>7.8101468373493965E-2</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1812,15 +1812,15 @@
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>363.71428571428572</v>
+        <v>381</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-7.3546351923724496E-3</v>
+        <v>3.9821362113881653E-2</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H26">
         <v>1.63</v>
@@ -1841,11 +1841,11 @@
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>130.57142857142858</v>
+        <v>136.125</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>0.21977555353351552</v>
+        <v>0.27165605095541401</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1870,11 +1870,11 @@
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>107</v>
+        <v>110.625</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>-0.12685459940652821</v>
+        <v>-9.7273738872403537E-2</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1899,11 +1899,11 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>490.57142857142856</v>
+        <v>617.375</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-0.37959465230102163</v>
+        <v>-0.21923143251322141</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1928,15 +1928,15 @@
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>645.57142857142856</v>
+        <v>689.25</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-9.1690087504234796E-3</v>
+        <v>5.7869401423189748E-2</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H30">
         <v>1.1599999999999999</v>
@@ -1957,11 +1957,11 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>845.42857142857144</v>
+        <v>911.75</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>3.3136568900944408E-3</v>
+        <v>8.2020714208652423E-2</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -1986,15 +1986,15 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>544.57142857142856</v>
+        <v>586</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-4.8556906879651529E-2</v>
+        <v>2.3824650571791617E-2</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H32">
         <v>1.1599999999999999</v>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>25</v>
+        <v>21.875</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-0.88237810094097524</v>
+        <v>-0.89708083832335328</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2044,11 +2044,11 @@
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>647.14285714285711</v>
+        <v>617.125</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>1.2203903395419302</v>
+        <v>1.1173970679975049</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2073,11 +2073,11 @@
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>101.28571428571429</v>
+        <v>88.625</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.72934705280144363</v>
+        <v>-0.76317867120126326</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2102,11 +2102,11 @@
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>311.57142857142856</v>
+        <v>316.375</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>0.14147734031164516</v>
+        <v>0.15907577019150709</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2131,11 +2131,11 @@
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>557.42857142857144</v>
+        <v>565.375</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.32591940441437672</v>
+        <v>0.34482106173640381</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2160,11 +2160,11 @@
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>321.57142857142856</v>
+        <v>331.75</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>0.30479000895821251</v>
+        <v>0.3460900036886756</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2189,15 +2189,15 @@
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>259.42857142857144</v>
+        <v>268.125</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-1.5111549365216304E-2</v>
+        <v>1.7903364969801494E-2</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H39">
         <v>0.81</v>
@@ -2218,15 +2218,15 @@
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>49.285714285714285</v>
+        <v>52.25</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>-1.2490241998438734E-2</v>
+        <v>4.6903460837887101E-2</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H40">
         <v>2.62</v>
@@ -2247,11 +2247,11 @@
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>102.14285714285714</v>
+        <v>103.625</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>0.28628669555973496</v>
+        <v>0.30495134516313693</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2276,11 +2276,11 @@
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>69</v>
+        <v>67.375</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>1.0132625994694959</v>
+        <v>0.96584880636604775</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2305,11 +2305,11 @@
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>55.285714285714285</v>
+        <v>55</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>0.4742857142857142</v>
+        <v>0.46666666666666656</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2363,11 +2363,11 @@
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>1.5714285714285714</v>
+        <v>1.625</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.51984126984126988</v>
+        <v>-0.50347222222222232</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22721092-6B14-441E-AE7B-218B68497D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC642946-D14B-4B44-99DF-B44118C967AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -353,9 +353,6 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="VINCULO VTS BY SKU JULIO"/>
-      <sheetName val="VINCULO VTS BY SKU OPEN"/>
-      <sheetName val="DESV. VTS BY SKU"/>
       <sheetName val="INVENTARIO NACIONAL 04-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 05-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 06-08-26"/>
@@ -363,496 +360,16 @@
       <sheetName val="INVENTARIO NACIONAL 10-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 11-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 12-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 13-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 14-08-26"/>
+      <sheetName val="VINCULO VTS BY SKU JULIO"/>
+      <sheetName val="VINCULO VTS BY SKU OPEN"/>
+      <sheetName val="DESV. VTS BY SKU"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="4">
-          <cell r="F4">
-            <v>1213.25</v>
-          </cell>
-          <cell r="G4">
-            <v>8.4667587776332986E-2</v>
-          </cell>
-          <cell r="H4" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="F5">
-            <v>78.625</v>
-          </cell>
-          <cell r="G5">
-            <v>8.6005830903790326E-3</v>
-          </cell>
-          <cell r="H5" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="F6">
-            <v>470.875</v>
-          </cell>
-          <cell r="G6">
-            <v>-0.13995433789954337</v>
-          </cell>
-          <cell r="H6" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="F7">
-            <v>108.25</v>
-          </cell>
-          <cell r="G7">
-            <v>0.10715946071594606</v>
-          </cell>
-          <cell r="H7" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="F8">
-            <v>9.375</v>
-          </cell>
-          <cell r="G8">
-            <v>-0.43801089918256131</v>
-          </cell>
-          <cell r="H8" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="F9">
-            <v>1455.875</v>
-          </cell>
-          <cell r="G9">
-            <v>0.12430672563886547</v>
-          </cell>
-          <cell r="H9" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="F10">
-            <v>144.75</v>
-          </cell>
-          <cell r="G10">
-            <v>0.1847098214285714</v>
-          </cell>
-          <cell r="H10" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="F11">
-            <v>346</v>
-          </cell>
-          <cell r="G11">
-            <v>0.13917988626159827</v>
-          </cell>
-          <cell r="H11" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="F12">
-            <v>725</v>
-          </cell>
-          <cell r="G12">
-            <v>9.5166163141993998E-2</v>
-          </cell>
-          <cell r="H12" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="F13">
-            <v>387.25</v>
-          </cell>
-          <cell r="G13">
-            <v>-4.4363432417274251E-2</v>
-          </cell>
-          <cell r="H13" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="F14">
-            <v>3533.5</v>
-          </cell>
-          <cell r="G14">
-            <v>8.721556341869352E-2</v>
-          </cell>
-          <cell r="H14" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="F15">
-            <v>2248.5</v>
-          </cell>
-          <cell r="G15">
-            <v>3.2110665998998478E-2</v>
-          </cell>
-          <cell r="H15" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="F16">
-            <v>2218.375</v>
-          </cell>
-          <cell r="G16">
-            <v>2.5816588195728851E-2</v>
-          </cell>
-          <cell r="H16" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="F17">
-            <v>2674.25</v>
-          </cell>
-          <cell r="G17">
-            <v>0.11210139311570244</v>
-          </cell>
-          <cell r="H17" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="F18">
-            <v>43.5</v>
-          </cell>
-          <cell r="G18">
-            <v>-0.6732673267326732</v>
-          </cell>
-          <cell r="H18" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="F19">
-            <v>222.25</v>
-          </cell>
-          <cell r="G19">
-            <v>-1.5999195009056222E-2</v>
-          </cell>
-          <cell r="H19" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="F20">
-            <v>129.75</v>
-          </cell>
-          <cell r="G20">
-            <v>-0.12277197295636144</v>
-          </cell>
-          <cell r="H20" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="F21">
-            <v>528.25</v>
-          </cell>
-          <cell r="G21">
-            <v>8.5614198972442823E-2</v>
-          </cell>
-          <cell r="H21" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="F22">
-            <v>796.125</v>
-          </cell>
-          <cell r="G22">
-            <v>-3.5671479938359507E-4</v>
-          </cell>
-          <cell r="H22" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="F23">
-            <v>0</v>
-          </cell>
-          <cell r="G23">
-            <v>-1</v>
-          </cell>
-          <cell r="H23" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="F24">
-            <v>72.75</v>
-          </cell>
-          <cell r="G24">
-            <v>0.47920517560073939</v>
-          </cell>
-          <cell r="H24" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="F25">
-            <v>656.125</v>
-          </cell>
-          <cell r="G25">
-            <v>-4.1771773765268194E-2</v>
-          </cell>
-          <cell r="H25" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="F26">
-            <v>1148.5</v>
-          </cell>
-          <cell r="G26">
-            <v>3.5066158698947358E-2</v>
-          </cell>
-          <cell r="H26" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="F27">
-            <v>520.625</v>
-          </cell>
-          <cell r="G27">
-            <v>7.8101468373493965E-2</v>
-          </cell>
-          <cell r="H27" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="F28">
-            <v>381</v>
-          </cell>
-          <cell r="G28">
-            <v>3.9821362113881653E-2</v>
-          </cell>
-          <cell r="H28" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="F29">
-            <v>136.125</v>
-          </cell>
-          <cell r="G29">
-            <v>0.27165605095541401</v>
-          </cell>
-          <cell r="H29" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="F30">
-            <v>110.625</v>
-          </cell>
-          <cell r="G30">
-            <v>-9.7273738872403537E-2</v>
-          </cell>
-          <cell r="H30" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="F31">
-            <v>617.375</v>
-          </cell>
-          <cell r="G31">
-            <v>-0.21923143251322141</v>
-          </cell>
-          <cell r="H31" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="F32">
-            <v>689.25</v>
-          </cell>
-          <cell r="G32">
-            <v>5.7869401423189748E-2</v>
-          </cell>
-          <cell r="H32" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="F33">
-            <v>911.75</v>
-          </cell>
-          <cell r="G33">
-            <v>8.2020714208652423E-2</v>
-          </cell>
-          <cell r="H33" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="F34">
-            <v>586</v>
-          </cell>
-          <cell r="G34">
-            <v>2.3824650571791617E-2</v>
-          </cell>
-          <cell r="H34" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="F35">
-            <v>21.875</v>
-          </cell>
-          <cell r="G35">
-            <v>-0.89708083832335328</v>
-          </cell>
-          <cell r="H35" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="F36">
-            <v>617.125</v>
-          </cell>
-          <cell r="G36">
-            <v>1.1173970679975049</v>
-          </cell>
-          <cell r="H36" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="F37">
-            <v>88.625</v>
-          </cell>
-          <cell r="G37">
-            <v>-0.76317867120126326</v>
-          </cell>
-          <cell r="H37" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="F38">
-            <v>316.375</v>
-          </cell>
-          <cell r="G38">
-            <v>0.15907577019150709</v>
-          </cell>
-          <cell r="H38" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="F39">
-            <v>565.375</v>
-          </cell>
-          <cell r="G39">
-            <v>0.34482106173640381</v>
-          </cell>
-          <cell r="H39" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="F40">
-            <v>331.75</v>
-          </cell>
-          <cell r="G40">
-            <v>0.3460900036886756</v>
-          </cell>
-          <cell r="H40" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="F41">
-            <v>268.125</v>
-          </cell>
-          <cell r="G41">
-            <v>1.7903364969801494E-2</v>
-          </cell>
-          <cell r="H41" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="F42">
-            <v>52.25</v>
-          </cell>
-          <cell r="G42">
-            <v>4.6903460837887101E-2</v>
-          </cell>
-          <cell r="H42" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="F43">
-            <v>103.625</v>
-          </cell>
-          <cell r="G43">
-            <v>0.30495134516313693</v>
-          </cell>
-          <cell r="H43" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="F44">
-            <v>67.375</v>
-          </cell>
-          <cell r="G44">
-            <v>0.96584880636604775</v>
-          </cell>
-          <cell r="H44" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="F45">
-            <v>55</v>
-          </cell>
-          <cell r="G45">
-            <v>0.46666666666666656</v>
-          </cell>
-          <cell r="H45" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="F46">
-            <v>0</v>
-          </cell>
-          <cell r="G46">
-            <v>-1</v>
-          </cell>
-          <cell r="H46" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="F47">
-            <v>1.625</v>
-          </cell>
-          <cell r="G47">
-            <v>-0.50347222222222232</v>
-          </cell>
-          <cell r="H47" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
@@ -860,6 +377,493 @@
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
       <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11">
+        <row r="4">
+          <cell r="F4">
+            <v>1189.2222222222222</v>
+          </cell>
+          <cell r="G4">
+            <v>6.3186317006213022E-2</v>
+          </cell>
+          <cell r="H4" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="F5">
+            <v>87.666666666666671</v>
+          </cell>
+          <cell r="G5">
+            <v>0.12458697764820226</v>
+          </cell>
+          <cell r="H5" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="F6">
+            <v>467.44444444444446</v>
+          </cell>
+          <cell r="G6">
+            <v>-0.14622019279553522</v>
+          </cell>
+          <cell r="H6" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="F7">
+            <v>107.44444444444444</v>
+          </cell>
+          <cell r="G7">
+            <v>9.8920398780928842E-2</v>
+          </cell>
+          <cell r="H7" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="F8">
+            <v>10</v>
+          </cell>
+          <cell r="G8">
+            <v>-0.40054495912806543</v>
+          </cell>
+          <cell r="H8" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="F9">
+            <v>1468.1111111111111</v>
+          </cell>
+          <cell r="G9">
+            <v>0.13375612343598853</v>
+          </cell>
+          <cell r="H9" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="F10">
+            <v>151.22222222222223</v>
+          </cell>
+          <cell r="G10">
+            <v>0.23768187830687837</v>
+          </cell>
+          <cell r="H10" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="F11">
+            <v>343.77777777777777</v>
+          </cell>
+          <cell r="G11">
+            <v>0.13186338089061822</v>
+          </cell>
+          <cell r="H11" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="F12">
+            <v>757.11111111111109</v>
+          </cell>
+          <cell r="G12">
+            <v>0.1436723732796239</v>
+          </cell>
+          <cell r="H12" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="F13">
+            <v>362</v>
+          </cell>
+          <cell r="G13">
+            <v>-0.10667414469994396</v>
+          </cell>
+          <cell r="H13" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="F14">
+            <v>3589.3333333333335</v>
+          </cell>
+          <cell r="G14">
+            <v>0.10439481032899312</v>
+          </cell>
+          <cell r="H14" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="F15">
+            <v>2294.6666666666665</v>
+          </cell>
+          <cell r="G15">
+            <v>5.3302175485450354E-2</v>
+          </cell>
+          <cell r="H15" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="F16">
+            <v>2267.1111111111113</v>
+          </cell>
+          <cell r="G16">
+            <v>4.8353044485548446E-2</v>
+          </cell>
+          <cell r="H16" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="F17">
+            <v>2711.8888888888887</v>
+          </cell>
+          <cell r="G17">
+            <v>0.12775372957215203</v>
+          </cell>
+          <cell r="H17" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="F18">
+            <v>39.333333333333336</v>
+          </cell>
+          <cell r="G18">
+            <v>-0.70456355980425622</v>
+          </cell>
+          <cell r="H18" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="F19">
+            <v>243.77777777777777</v>
+          </cell>
+          <cell r="G19">
+            <v>7.931396882896169E-2</v>
+          </cell>
+          <cell r="H19" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="F20">
+            <v>139.11111111111111</v>
+          </cell>
+          <cell r="G20">
+            <v>-5.9482346513692552E-2</v>
+          </cell>
+          <cell r="H20" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="F21">
+            <v>519.88888888888891</v>
+          </cell>
+          <cell r="G21">
+            <v>6.8431158856193885E-2</v>
+          </cell>
+          <cell r="H21" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="F22">
+            <v>800.88888888888891</v>
+          </cell>
+          <cell r="G22">
+            <v>5.6249960365022389E-3</v>
+          </cell>
+          <cell r="H22" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="F23">
+            <v>0</v>
+          </cell>
+          <cell r="G23">
+            <v>-1</v>
+          </cell>
+          <cell r="H23" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="F24">
+            <v>64.666666666666671</v>
+          </cell>
+          <cell r="G24">
+            <v>0.31484904497843513</v>
+          </cell>
+          <cell r="H24" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="F25">
+            <v>684.11111111111109</v>
+          </cell>
+          <cell r="G25">
+            <v>-8.9986428276400687E-4</v>
+          </cell>
+          <cell r="H25" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="F26">
+            <v>1194.6666666666667</v>
+          </cell>
+          <cell r="G26">
+            <v>7.6673084538391389E-2</v>
+          </cell>
+          <cell r="H26" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="F27">
+            <v>514.55555555555554</v>
+          </cell>
+          <cell r="G27">
+            <v>6.5532965194109671E-2</v>
+          </cell>
+          <cell r="H27" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="F28">
+            <v>376.22222222222223</v>
+          </cell>
+          <cell r="G28">
+            <v>2.678189913024287E-2</v>
+          </cell>
+          <cell r="H28" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="F29">
+            <v>129.33333333333334</v>
+          </cell>
+          <cell r="G29">
+            <v>0.20820948336871914</v>
+          </cell>
+          <cell r="H29" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="F30">
+            <v>116.44444444444444</v>
+          </cell>
+          <cell r="G30">
+            <v>-4.9785690735245636E-2</v>
+          </cell>
+          <cell r="H30" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="F31">
+            <v>630</v>
+          </cell>
+          <cell r="G31">
+            <v>-0.20326511841802719</v>
+          </cell>
+          <cell r="H31" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="F32">
+            <v>694.66666666666663</v>
+          </cell>
+          <cell r="G32">
+            <v>6.6182968234035577E-2</v>
+          </cell>
+          <cell r="H32" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="F33">
+            <v>909.33333333333337</v>
+          </cell>
+          <cell r="G33">
+            <v>7.9152731326644465E-2</v>
+          </cell>
+          <cell r="H33" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="F34">
+            <v>610.66666666666663</v>
+          </cell>
+          <cell r="G34">
+            <v>6.6920796272765593E-2</v>
+          </cell>
+          <cell r="H34" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="F35">
+            <v>19.444444444444443</v>
+          </cell>
+          <cell r="G35">
+            <v>-0.90851630073186962</v>
+          </cell>
+          <cell r="H35" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="F36">
+            <v>583.44444444444446</v>
+          </cell>
+          <cell r="G36">
+            <v>1.0018368337145631</v>
+          </cell>
+          <cell r="H36" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="F37">
+            <v>78.777777777777771</v>
+          </cell>
+          <cell r="G37">
+            <v>-0.78949215217890067</v>
+          </cell>
+          <cell r="H37" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="F38">
+            <v>302.22222222222223</v>
+          </cell>
+          <cell r="G38">
+            <v>0.10722546026459434</v>
+          </cell>
+          <cell r="H38" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="F39">
+            <v>539.66666666666663</v>
+          </cell>
+          <cell r="G39">
+            <v>0.28367030669982318</v>
+          </cell>
+          <cell r="H39" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="F40">
+            <v>320.11111111111109</v>
+          </cell>
+          <cell r="G40">
+            <v>0.29886470756998218</v>
+          </cell>
+          <cell r="H40" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="F41">
+            <v>266</v>
+          </cell>
+          <cell r="G41">
+            <v>9.8360655737703695E-3</v>
+          </cell>
+          <cell r="H41" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="F42">
+            <v>48.555555555555557</v>
+          </cell>
+          <cell r="G42">
+            <v>-2.7120016191054308E-2</v>
+          </cell>
+          <cell r="H42" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="F43">
+            <v>100.22222222222223</v>
+          </cell>
+          <cell r="G43">
+            <v>0.26210010812185991</v>
+          </cell>
+          <cell r="H43" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="F44">
+            <v>60.666666666666664</v>
+          </cell>
+          <cell r="G44">
+            <v>0.77011494252873547</v>
+          </cell>
+          <cell r="H44" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="F45">
+            <v>51.888888888888886</v>
+          </cell>
+          <cell r="G45">
+            <v>0.38370370370370366</v>
+          </cell>
+          <cell r="H45" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="F46">
+            <v>0</v>
+          </cell>
+          <cell r="G46">
+            <v>-1</v>
+          </cell>
+          <cell r="H46" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="F47">
+            <v>2.2222222222222223</v>
+          </cell>
+          <cell r="G47">
+            <v>-0.32098765432098764</v>
+          </cell>
+          <cell r="H47" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1116,11 +1120,11 @@
       </c>
       <c r="E2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1213.25</v>
+        <v>1189.2222222222222</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>8.4667587776332986E-2</v>
+        <v>6.3186317006213022E-2</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1145,11 +1149,11 @@
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>78.625</v>
+        <v>87.666666666666671</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>8.6005830903790326E-3</v>
+        <v>0.12458697764820226</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1174,11 +1178,11 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>470.875</v>
+        <v>467.44444444444446</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-0.13995433789954337</v>
+        <v>-0.14622019279553522</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1203,11 +1207,11 @@
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>108.25</v>
+        <v>107.44444444444444</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>0.10715946071594606</v>
+        <v>9.8920398780928842E-2</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1232,11 +1236,11 @@
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>9.375</v>
+        <v>10</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>-0.43801089918256131</v>
+        <v>-0.40054495912806543</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1261,11 +1265,11 @@
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1455.875</v>
+        <v>1468.1111111111111</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>0.12430672563886547</v>
+        <v>0.13375612343598853</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1290,11 +1294,11 @@
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>144.75</v>
+        <v>151.22222222222223</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>0.1847098214285714</v>
+        <v>0.23768187830687837</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1319,11 +1323,11 @@
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>346</v>
+        <v>343.77777777777777</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>0.13917988626159827</v>
+        <v>0.13186338089061822</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1348,11 +1352,11 @@
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>725</v>
+        <v>757.11111111111109</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>9.5166163141993998E-2</v>
+        <v>0.1436723732796239</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1377,11 +1381,11 @@
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>387.25</v>
+        <v>362</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-4.4363432417274251E-2</v>
+        <v>-0.10667414469994396</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1406,11 +1410,11 @@
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3533.5</v>
+        <v>3589.3333333333335</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>8.721556341869352E-2</v>
+        <v>0.10439481032899312</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1435,11 +1439,11 @@
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2248.5</v>
+        <v>2294.6666666666665</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>3.2110665998998478E-2</v>
+        <v>5.3302175485450354E-2</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1464,11 +1468,11 @@
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2218.375</v>
+        <v>2267.1111111111113</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>2.5816588195728851E-2</v>
+        <v>4.8353044485548446E-2</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1493,11 +1497,11 @@
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2674.25</v>
+        <v>2711.8888888888887</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>0.11210139311570244</v>
+        <v>0.12775372957215203</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1522,11 +1526,11 @@
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>43.5</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.6732673267326732</v>
+        <v>-0.70456355980425622</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1551,15 +1555,15 @@
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>222.25</v>
+        <v>243.77777777777777</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>-1.5999195009056222E-2</v>
+        <v>7.931396882896169E-2</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H17">
         <v>3.68</v>
@@ -1580,11 +1584,11 @@
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>129.75</v>
+        <v>139.11111111111111</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>-0.12277197295636144</v>
+        <v>-5.9482346513692552E-2</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1609,11 +1613,11 @@
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>528.25</v>
+        <v>519.88888888888891</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>8.5614198972442823E-2</v>
+        <v>6.8431158856193885E-2</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1638,15 +1642,15 @@
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>796.125</v>
+        <v>800.88888888888891</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-3.5671479938359507E-4</v>
+        <v>5.6249960365022389E-3</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H20">
         <v>4.1500000000000004</v>
@@ -1696,11 +1700,11 @@
       </c>
       <c r="E22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>72.75</v>
+        <v>64.666666666666671</v>
       </c>
       <c r="F22" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>0.47920517560073939</v>
+        <v>0.31484904497843513</v>
       </c>
       <c r="G22" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1725,11 +1729,11 @@
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>656.125</v>
+        <v>684.11111111111109</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-4.1771773765268194E-2</v>
+        <v>-8.9986428276400687E-4</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1754,11 +1758,11 @@
       </c>
       <c r="E24" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>1148.5</v>
+        <v>1194.6666666666667</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>3.5066158698947358E-2</v>
+        <v>7.6673084538391389E-2</v>
       </c>
       <c r="G24" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1783,11 +1787,11 @@
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>520.625</v>
+        <v>514.55555555555554</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>7.8101468373493965E-2</v>
+        <v>6.5532965194109671E-2</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1812,11 +1816,11 @@
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>381</v>
+        <v>376.22222222222223</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>3.9821362113881653E-2</v>
+        <v>2.678189913024287E-2</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1841,11 +1845,11 @@
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>136.125</v>
+        <v>129.33333333333334</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>0.27165605095541401</v>
+        <v>0.20820948336871914</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1870,11 +1874,11 @@
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>110.625</v>
+        <v>116.44444444444444</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>-9.7273738872403537E-2</v>
+        <v>-4.9785690735245636E-2</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1899,11 +1903,11 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>617.375</v>
+        <v>630</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-0.21923143251322141</v>
+        <v>-0.20326511841802719</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1928,11 +1932,11 @@
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>689.25</v>
+        <v>694.66666666666663</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>5.7869401423189748E-2</v>
+        <v>6.6182968234035577E-2</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1957,11 +1961,11 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>911.75</v>
+        <v>909.33333333333337</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>8.2020714208652423E-2</v>
+        <v>7.9152731326644465E-2</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -1986,11 +1990,11 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>586</v>
+        <v>610.66666666666663</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>2.3824650571791617E-2</v>
+        <v>6.6920796272765593E-2</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2015,11 +2019,11 @@
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>21.875</v>
+        <v>19.444444444444443</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-0.89708083832335328</v>
+        <v>-0.90851630073186962</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2044,11 +2048,11 @@
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>617.125</v>
+        <v>583.44444444444446</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>1.1173970679975049</v>
+        <v>1.0018368337145631</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2073,11 +2077,11 @@
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>88.625</v>
+        <v>78.777777777777771</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.76317867120126326</v>
+        <v>-0.78949215217890067</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2102,11 +2106,11 @@
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>316.375</v>
+        <v>302.22222222222223</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>0.15907577019150709</v>
+        <v>0.10722546026459434</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2131,11 +2135,11 @@
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>565.375</v>
+        <v>539.66666666666663</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.34482106173640381</v>
+        <v>0.28367030669982318</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2160,11 +2164,11 @@
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>331.75</v>
+        <v>320.11111111111109</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>0.3460900036886756</v>
+        <v>0.29886470756998218</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2189,11 +2193,11 @@
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>268.125</v>
+        <v>266</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>1.7903364969801494E-2</v>
+        <v>9.8360655737703695E-3</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2218,15 +2222,15 @@
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>52.25</v>
+        <v>48.555555555555557</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>4.6903460837887101E-2</v>
+        <v>-2.7120016191054308E-2</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H40">
         <v>2.62</v>
@@ -2247,11 +2251,11 @@
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>103.625</v>
+        <v>100.22222222222223</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>0.30495134516313693</v>
+        <v>0.26210010812185991</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2276,11 +2280,11 @@
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>67.375</v>
+        <v>60.666666666666664</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>0.96584880636604775</v>
+        <v>0.77011494252873547</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2305,11 +2309,11 @@
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>55</v>
+        <v>51.888888888888886</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>0.46666666666666656</v>
+        <v>0.38370370370370366</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2363,11 +2367,11 @@
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>1.625</v>
+        <v>2.2222222222222223</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.50347222222222232</v>
+        <v>-0.32098765432098764</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC642946-D14B-4B44-99DF-B44118C967AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926CA52C-5E1E-4B4F-B4AE-C80CDFEECD76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -362,6 +362,7 @@
       <sheetName val="INVENTARIO NACIONAL 12-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 13-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 14-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 17-08-26"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -378,13 +379,14 @@
       <sheetData sheetId="8"/>
       <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
-      <sheetData sheetId="11">
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12">
         <row r="4">
           <cell r="F4">
-            <v>1189.2222222222222</v>
+            <v>1175.5999999999999</v>
           </cell>
           <cell r="G4">
-            <v>6.3186317006213022E-2</v>
+            <v>5.1007802340702124E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -392,10 +394,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>87.666666666666671</v>
+            <v>82.3</v>
           </cell>
           <cell r="G5">
-            <v>0.12458697764820226</v>
+            <v>5.5743440233236186E-2</v>
           </cell>
           <cell r="H5" t="str">
             <v>SUBIÓ</v>
@@ -403,10 +405,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>467.44444444444446</v>
+            <v>463.4</v>
           </cell>
           <cell r="G6">
-            <v>-0.14622019279553522</v>
+            <v>-0.15360730593607308</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -414,10 +416,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>107.44444444444444</v>
+            <v>100.4</v>
           </cell>
           <cell r="G7">
-            <v>9.8920398780928842E-2</v>
+            <v>2.6871222687122387E-2</v>
           </cell>
           <cell r="H7" t="str">
             <v>SUBIÓ</v>
@@ -425,10 +427,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>10</v>
+            <v>9</v>
           </cell>
           <cell r="G8">
-            <v>-0.40054495912806543</v>
+            <v>-0.46049046321525888</v>
           </cell>
           <cell r="H8" t="str">
             <v>BAJO</v>
@@ -436,10 +438,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1468.1111111111111</v>
+            <v>1443.7</v>
           </cell>
           <cell r="G9">
-            <v>0.13375612343598853</v>
+            <v>0.11490452120190953</v>
           </cell>
           <cell r="H9" t="str">
             <v>SUBIÓ</v>
@@ -447,10 +449,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>151.22222222222223</v>
+            <v>144.1</v>
           </cell>
           <cell r="G10">
-            <v>0.23768187830687837</v>
+            <v>0.17938988095238084</v>
           </cell>
           <cell r="H10" t="str">
             <v>SUBIÓ</v>
@@ -458,10 +460,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>343.77777777777777</v>
+            <v>315.7</v>
           </cell>
           <cell r="G11">
-            <v>0.13186338089061822</v>
+            <v>3.9419335528284805E-2</v>
           </cell>
           <cell r="H11" t="str">
             <v>SUBIÓ</v>
@@ -469,10 +471,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>757.11111111111109</v>
+            <v>718</v>
           </cell>
           <cell r="G12">
-            <v>0.1436723732796239</v>
+            <v>8.4592145015105702E-2</v>
           </cell>
           <cell r="H12" t="str">
             <v>SUBIÓ</v>
@@ -480,10 +482,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>362</v>
+            <v>342.2</v>
           </cell>
           <cell r="G13">
-            <v>-0.10667414469994396</v>
+            <v>-0.15553561413348294</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -491,10 +493,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3589.3333333333335</v>
+            <v>3651</v>
           </cell>
           <cell r="G14">
-            <v>0.10439481032899312</v>
+            <v>0.12336890393141364</v>
           </cell>
           <cell r="H14" t="str">
             <v>SUBIÓ</v>
@@ -502,10 +504,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2294.6666666666665</v>
+            <v>2408</v>
           </cell>
           <cell r="G15">
-            <v>5.3302175485450354E-2</v>
+            <v>0.1053246536471375</v>
           </cell>
           <cell r="H15" t="str">
             <v>SUBIÓ</v>
@@ -513,10 +515,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2267.1111111111113</v>
+            <v>2329.1999999999998</v>
           </cell>
           <cell r="G16">
-            <v>4.8353044485548446E-2</v>
+            <v>7.7064065915587676E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>SUBIÓ</v>
@@ -524,10 +526,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2711.8888888888887</v>
+            <v>2794.6</v>
           </cell>
           <cell r="G17">
-            <v>0.12775372957215203</v>
+            <v>0.16214959454095235</v>
           </cell>
           <cell r="H17" t="str">
             <v>SUBIÓ</v>
@@ -535,10 +537,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>39.333333333333336</v>
+            <v>35.5</v>
           </cell>
           <cell r="G18">
-            <v>-0.70456355980425622</v>
+            <v>-0.73335609423011272</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -546,10 +548,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>243.77777777777777</v>
+            <v>238.4</v>
           </cell>
           <cell r="G19">
-            <v>7.931396882896169E-2</v>
+            <v>5.5504125578587304E-2</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -557,10 +559,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>139.11111111111111</v>
+            <v>129.80000000000001</v>
           </cell>
           <cell r="G20">
-            <v>-5.9482346513692552E-2</v>
+            <v>-0.12243392747387816</v>
           </cell>
           <cell r="H20" t="str">
             <v>BAJO</v>
@@ -568,10 +570,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>519.88888888888891</v>
+            <v>500.3</v>
           </cell>
           <cell r="G21">
-            <v>6.8431158856193885E-2</v>
+            <v>2.8173750583839308E-2</v>
           </cell>
           <cell r="H21" t="str">
             <v>SUBIÓ</v>
@@ -579,32 +581,32 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>800.88888888888891</v>
+            <v>776.3</v>
           </cell>
           <cell r="G22">
-            <v>5.6249960365022389E-3</v>
+            <v>-2.5249700359568528E-2</v>
           </cell>
           <cell r="H22" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="23">
           <cell r="F23">
-            <v>0</v>
+            <v>10</v>
           </cell>
           <cell r="G23">
-            <v>-1</v>
+            <v>1</v>
           </cell>
           <cell r="H23" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="24">
           <cell r="F24">
-            <v>64.666666666666671</v>
+            <v>150</v>
           </cell>
           <cell r="G24">
-            <v>0.31484904497843513</v>
+            <v>2.0499075785582255</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -612,10 +614,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>684.11111111111109</v>
+            <v>678.2</v>
           </cell>
           <cell r="G25">
-            <v>-8.9986428276400687E-4</v>
+            <v>-9.532660647902258E-3</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -623,21 +625,21 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>1194.6666666666667</v>
+            <v>1105.2</v>
           </cell>
           <cell r="G26">
-            <v>7.6673084538391389E-2</v>
+            <v>-3.9572323952314914E-3</v>
           </cell>
           <cell r="H26" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="27">
           <cell r="F27">
-            <v>514.55555555555554</v>
+            <v>493.2</v>
           </cell>
           <cell r="G27">
-            <v>6.5532965194109671E-2</v>
+            <v>2.1310240963855254E-2</v>
           </cell>
           <cell r="H27" t="str">
             <v>SUBIÓ</v>
@@ -645,21 +647,21 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>376.22222222222223</v>
+            <v>339.1</v>
           </cell>
           <cell r="G28">
-            <v>2.678189913024287E-2</v>
+            <v>-7.4531695819377242E-2</v>
           </cell>
           <cell r="H28" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="29">
           <cell r="F29">
-            <v>129.33333333333334</v>
+            <v>132.6</v>
           </cell>
           <cell r="G29">
-            <v>0.20820948336871914</v>
+            <v>0.23872611464968152</v>
           </cell>
           <cell r="H29" t="str">
             <v>SUBIÓ</v>
@@ -667,10 +669,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>116.44444444444444</v>
+            <v>119.2</v>
           </cell>
           <cell r="G30">
-            <v>-4.9785690735245636E-2</v>
+            <v>-2.7299703264094921E-2</v>
           </cell>
           <cell r="H30" t="str">
             <v>BAJO</v>
@@ -678,10 +680,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>630</v>
+            <v>614.5</v>
           </cell>
           <cell r="G31">
-            <v>-0.20326511841802719</v>
+            <v>-0.22286732582202806</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -689,10 +691,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>694.66666666666663</v>
+            <v>671.5</v>
           </cell>
           <cell r="G32">
-            <v>6.6182968234035577E-2</v>
+            <v>3.0626482489186646E-2</v>
           </cell>
           <cell r="H32" t="str">
             <v>SUBIÓ</v>
@@ -700,21 +702,21 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>909.33333333333337</v>
+            <v>831.6</v>
           </cell>
           <cell r="G33">
-            <v>7.9152731326644465E-2</v>
+            <v>-1.3097421512568763E-2</v>
           </cell>
           <cell r="H33" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="34">
           <cell r="F34">
-            <v>610.66666666666663</v>
+            <v>581.79999999999995</v>
           </cell>
           <cell r="G34">
-            <v>6.6920796272765593E-2</v>
+            <v>1.6486658195679738E-2</v>
           </cell>
           <cell r="H34" t="str">
             <v>SUBIÓ</v>
@@ -722,10 +724,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>19.444444444444443</v>
+            <v>17.5</v>
           </cell>
           <cell r="G35">
-            <v>-0.90851630073186962</v>
+            <v>-0.91766467065868262</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -733,10 +735,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>583.44444444444446</v>
+            <v>570.1</v>
           </cell>
           <cell r="G36">
-            <v>1.0018368337145631</v>
+            <v>0.95605115408608876</v>
           </cell>
           <cell r="H36" t="str">
             <v>SUBIÓ</v>
@@ -744,10 +746,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>78.777777777777771</v>
+            <v>70.900000000000006</v>
           </cell>
           <cell r="G37">
-            <v>-0.78949215217890067</v>
+            <v>-0.81054293696101054</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -755,10 +757,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>302.22222222222223</v>
+            <v>303.60000000000002</v>
           </cell>
           <cell r="G38">
-            <v>0.10722546026459434</v>
+            <v>0.11227310574521243</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -766,10 +768,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>539.66666666666663</v>
+            <v>528.5</v>
           </cell>
           <cell r="G39">
-            <v>0.28367030669982318</v>
+            <v>0.25710887663531179</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -777,10 +779,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>320.11111111111109</v>
+            <v>322.3</v>
           </cell>
           <cell r="G40">
-            <v>0.29886470756998218</v>
+            <v>0.30774621910734035</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -788,10 +790,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>266</v>
+            <v>273.39999999999998</v>
           </cell>
           <cell r="G41">
-            <v>9.8360655737703695E-3</v>
+            <v>3.7929249352890215E-2</v>
           </cell>
           <cell r="H41" t="str">
             <v>SUBIÓ</v>
@@ -799,10 +801,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>48.555555555555557</v>
+            <v>44.6</v>
           </cell>
           <cell r="G42">
-            <v>-2.7120016191054308E-2</v>
+            <v>-0.10637522768670304</v>
           </cell>
           <cell r="H42" t="str">
             <v>BAJO</v>
@@ -810,10 +812,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>100.22222222222223</v>
+            <v>93.3</v>
           </cell>
           <cell r="G43">
-            <v>0.26210010812185991</v>
+            <v>0.17492844876931879</v>
           </cell>
           <cell r="H43" t="str">
             <v>SUBIÓ</v>
@@ -821,10 +823,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>60.666666666666664</v>
+            <v>54.6</v>
           </cell>
           <cell r="G44">
-            <v>0.77011494252873547</v>
+            <v>0.59310344827586214</v>
           </cell>
           <cell r="H44" t="str">
             <v>SUBIÓ</v>
@@ -832,10 +834,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>51.888888888888886</v>
+            <v>46.7</v>
           </cell>
           <cell r="G45">
-            <v>0.38370370370370366</v>
+            <v>0.2453333333333334</v>
           </cell>
           <cell r="H45" t="str">
             <v>SUBIÓ</v>
@@ -854,10 +856,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>2.2222222222222223</v>
+            <v>2.4</v>
           </cell>
           <cell r="G47">
-            <v>-0.32098765432098764</v>
+            <v>-0.26666666666666672</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -1120,11 +1122,11 @@
       </c>
       <c r="E2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1189.2222222222222</v>
+        <v>1175.5999999999999</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>6.3186317006213022E-2</v>
+        <v>5.1007802340702124E-2</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1149,11 +1151,11 @@
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>87.666666666666671</v>
+        <v>82.3</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>0.12458697764820226</v>
+        <v>5.5743440233236186E-2</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1178,11 +1180,11 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>467.44444444444446</v>
+        <v>463.4</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-0.14622019279553522</v>
+        <v>-0.15360730593607308</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1207,11 +1209,11 @@
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>107.44444444444444</v>
+        <v>100.4</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>9.8920398780928842E-2</v>
+        <v>2.6871222687122387E-2</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1236,11 +1238,11 @@
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>-0.40054495912806543</v>
+        <v>-0.46049046321525888</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1265,11 +1267,11 @@
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1468.1111111111111</v>
+        <v>1443.7</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>0.13375612343598853</v>
+        <v>0.11490452120190953</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1294,11 +1296,11 @@
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>151.22222222222223</v>
+        <v>144.1</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>0.23768187830687837</v>
+        <v>0.17938988095238084</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1323,11 +1325,11 @@
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>343.77777777777777</v>
+        <v>315.7</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>0.13186338089061822</v>
+        <v>3.9419335528284805E-2</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1352,11 +1354,11 @@
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>757.11111111111109</v>
+        <v>718</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>0.1436723732796239</v>
+        <v>8.4592145015105702E-2</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1381,11 +1383,11 @@
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>362</v>
+        <v>342.2</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.10667414469994396</v>
+        <v>-0.15553561413348294</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1410,11 +1412,11 @@
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3589.3333333333335</v>
+        <v>3651</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>0.10439481032899312</v>
+        <v>0.12336890393141364</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1439,11 +1441,11 @@
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2294.6666666666665</v>
+        <v>2408</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>5.3302175485450354E-2</v>
+        <v>0.1053246536471375</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1468,11 +1470,11 @@
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2267.1111111111113</v>
+        <v>2329.1999999999998</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>4.8353044485548446E-2</v>
+        <v>7.7064065915587676E-2</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1497,11 +1499,11 @@
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2711.8888888888887</v>
+        <v>2794.6</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>0.12775372957215203</v>
+        <v>0.16214959454095235</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1526,11 +1528,11 @@
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>39.333333333333336</v>
+        <v>35.5</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.70456355980425622</v>
+        <v>-0.73335609423011272</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1555,11 +1557,11 @@
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>243.77777777777777</v>
+        <v>238.4</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>7.931396882896169E-2</v>
+        <v>5.5504125578587304E-2</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1584,11 +1586,11 @@
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>139.11111111111111</v>
+        <v>129.80000000000001</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>-5.9482346513692552E-2</v>
+        <v>-0.12243392747387816</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1613,11 +1615,11 @@
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>519.88888888888891</v>
+        <v>500.3</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>6.8431158856193885E-2</v>
+        <v>2.8173750583839308E-2</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1642,15 +1644,15 @@
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>800.88888888888891</v>
+        <v>776.3</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>5.6249960365022389E-3</v>
+        <v>-2.5249700359568528E-2</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H20">
         <v>4.1500000000000004</v>
@@ -1671,15 +1673,15 @@
       </c>
       <c r="E21" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F21" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G21" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H21">
         <v>4.1500000000000004</v>
@@ -1700,11 +1702,11 @@
       </c>
       <c r="E22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>64.666666666666671</v>
+        <v>150</v>
       </c>
       <c r="F22" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>0.31484904497843513</v>
+        <v>2.0499075785582255</v>
       </c>
       <c r="G22" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1729,11 +1731,11 @@
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>684.11111111111109</v>
+        <v>678.2</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-8.9986428276400687E-4</v>
+        <v>-9.532660647902258E-3</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1758,15 +1760,15 @@
       </c>
       <c r="E24" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>1194.6666666666667</v>
+        <v>1105.2</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>7.6673084538391389E-2</v>
+        <v>-3.9572323952314914E-3</v>
       </c>
       <c r="G24" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H24">
         <v>1.63</v>
@@ -1787,11 +1789,11 @@
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>514.55555555555554</v>
+        <v>493.2</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>6.5532965194109671E-2</v>
+        <v>2.1310240963855254E-2</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1816,15 +1818,15 @@
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>376.22222222222223</v>
+        <v>339.1</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>2.678189913024287E-2</v>
+        <v>-7.4531695819377242E-2</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H26">
         <v>1.63</v>
@@ -1845,11 +1847,11 @@
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>129.33333333333334</v>
+        <v>132.6</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>0.20820948336871914</v>
+        <v>0.23872611464968152</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1874,11 +1876,11 @@
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>116.44444444444444</v>
+        <v>119.2</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>-4.9785690735245636E-2</v>
+        <v>-2.7299703264094921E-2</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1903,11 +1905,11 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>630</v>
+        <v>614.5</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-0.20326511841802719</v>
+        <v>-0.22286732582202806</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1932,11 +1934,11 @@
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>694.66666666666663</v>
+        <v>671.5</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>6.6182968234035577E-2</v>
+        <v>3.0626482489186646E-2</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1961,15 +1963,15 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>909.33333333333337</v>
+        <v>831.6</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>7.9152731326644465E-2</v>
+        <v>-1.3097421512568763E-2</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H31">
         <v>1.1599999999999999</v>
@@ -1990,11 +1992,11 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>610.66666666666663</v>
+        <v>581.79999999999995</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>6.6920796272765593E-2</v>
+        <v>1.6486658195679738E-2</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2019,11 +2021,11 @@
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>19.444444444444443</v>
+        <v>17.5</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-0.90851630073186962</v>
+        <v>-0.91766467065868262</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2048,11 +2050,11 @@
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>583.44444444444446</v>
+        <v>570.1</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>1.0018368337145631</v>
+        <v>0.95605115408608876</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2077,11 +2079,11 @@
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>78.777777777777771</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.78949215217890067</v>
+        <v>-0.81054293696101054</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2106,11 +2108,11 @@
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>302.22222222222223</v>
+        <v>303.60000000000002</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>0.10722546026459434</v>
+        <v>0.11227310574521243</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2135,11 +2137,11 @@
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>539.66666666666663</v>
+        <v>528.5</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.28367030669982318</v>
+        <v>0.25710887663531179</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2164,11 +2166,11 @@
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>320.11111111111109</v>
+        <v>322.3</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>0.29886470756998218</v>
+        <v>0.30774621910734035</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2193,11 +2195,11 @@
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>266</v>
+        <v>273.39999999999998</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>9.8360655737703695E-3</v>
+        <v>3.7929249352890215E-2</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2222,11 +2224,11 @@
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>48.555555555555557</v>
+        <v>44.6</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>-2.7120016191054308E-2</v>
+        <v>-0.10637522768670304</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2251,11 +2253,11 @@
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>100.22222222222223</v>
+        <v>93.3</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>0.26210010812185991</v>
+        <v>0.17492844876931879</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2280,11 +2282,11 @@
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>60.666666666666664</v>
+        <v>54.6</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>0.77011494252873547</v>
+        <v>0.59310344827586214</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2309,11 +2311,11 @@
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>51.888888888888886</v>
+        <v>46.7</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>0.38370370370370366</v>
+        <v>0.2453333333333334</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2367,11 +2369,11 @@
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>2.2222222222222223</v>
+        <v>2.4</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.32098765432098764</v>
+        <v>-0.26666666666666672</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926CA52C-5E1E-4B4F-B4AE-C80CDFEECD76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA3B847-93B4-4176-97AC-F1DC71A1244A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -363,6 +363,7 @@
       <sheetName val="INVENTARIO NACIONAL 13-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 14-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 17-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 18-08-26"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -380,13 +381,14 @@
       <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
-      <sheetData sheetId="12">
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13">
         <row r="4">
           <cell r="F4">
-            <v>1175.5999999999999</v>
+            <v>1294.4000000000001</v>
           </cell>
           <cell r="G4">
-            <v>5.1007802340702124E-2</v>
+            <v>0.15721716514954509</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -394,10 +396,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>82.3</v>
+            <v>90.3</v>
           </cell>
           <cell r="G5">
-            <v>5.5743440233236186E-2</v>
+            <v>0.15836734693877541</v>
           </cell>
           <cell r="H5" t="str">
             <v>SUBIÓ</v>
@@ -405,10 +407,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>463.4</v>
+            <v>527.9</v>
           </cell>
           <cell r="G6">
-            <v>-0.15360730593607308</v>
+            <v>-3.5799086757990928E-2</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -416,10 +418,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>100.4</v>
+            <v>106.1</v>
           </cell>
           <cell r="G7">
-            <v>2.6871222687122387E-2</v>
+            <v>8.5169688516968822E-2</v>
           </cell>
           <cell r="H7" t="str">
             <v>SUBIÓ</v>
@@ -427,10 +429,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>9</v>
+            <v>10.5</v>
           </cell>
           <cell r="G8">
-            <v>-0.46049046321525888</v>
+            <v>-0.3705722070844687</v>
           </cell>
           <cell r="H8" t="str">
             <v>BAJO</v>
@@ -438,10 +440,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1443.7</v>
+            <v>1594.8</v>
           </cell>
           <cell r="G9">
-            <v>0.11490452120190953</v>
+            <v>0.23159224936815481</v>
           </cell>
           <cell r="H9" t="str">
             <v>SUBIÓ</v>
@@ -449,10 +451,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>144.1</v>
+            <v>153.69999999999999</v>
           </cell>
           <cell r="G10">
-            <v>0.17938988095238084</v>
+            <v>0.25796130952380936</v>
           </cell>
           <cell r="H10" t="str">
             <v>SUBIÓ</v>
@@ -460,10 +462,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>315.7</v>
+            <v>340.3</v>
           </cell>
           <cell r="G11">
-            <v>3.9419335528284805E-2</v>
+            <v>0.12041304998503444</v>
           </cell>
           <cell r="H11" t="str">
             <v>SUBIÓ</v>
@@ -471,10 +473,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>718</v>
+            <v>762.5</v>
           </cell>
           <cell r="G12">
-            <v>8.4592145015105702E-2</v>
+            <v>0.15181268882175236</v>
           </cell>
           <cell r="H12" t="str">
             <v>SUBIÓ</v>
@@ -482,10 +484,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>342.2</v>
+            <v>354.2</v>
           </cell>
           <cell r="G13">
-            <v>-0.15553561413348294</v>
+            <v>-0.1259226023555805</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -493,10 +495,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3651</v>
+            <v>3991.1</v>
           </cell>
           <cell r="G14">
-            <v>0.12336890393141364</v>
+            <v>0.22801359421546552</v>
           </cell>
           <cell r="H14" t="str">
             <v>SUBIÓ</v>
@@ -504,10 +506,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2408</v>
+            <v>2634.2</v>
           </cell>
           <cell r="G15">
-            <v>0.1053246536471375</v>
+            <v>0.20915539976631603</v>
           </cell>
           <cell r="H15" t="str">
             <v>SUBIÓ</v>
@@ -515,10 +517,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2329.1999999999998</v>
+            <v>2542</v>
           </cell>
           <cell r="G16">
-            <v>7.7064065915587676E-2</v>
+            <v>0.17546662182613093</v>
           </cell>
           <cell r="H16" t="str">
             <v>SUBIÓ</v>
@@ -526,10 +528,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2794.6</v>
+            <v>3037.3</v>
           </cell>
           <cell r="G17">
-            <v>0.16214959454095235</v>
+            <v>0.26307770825851096</v>
           </cell>
           <cell r="H17" t="str">
             <v>SUBIÓ</v>
@@ -537,10 +539,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>35.5</v>
+            <v>36.5</v>
           </cell>
           <cell r="G18">
-            <v>-0.73335609423011272</v>
+            <v>-0.7258449982929327</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -548,10 +550,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>238.4</v>
+            <v>252.3</v>
           </cell>
           <cell r="G19">
-            <v>5.5504125578587304E-2</v>
+            <v>0.11704568323606357</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -559,10 +561,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>129.80000000000001</v>
+            <v>139.1</v>
           </cell>
           <cell r="G20">
-            <v>-0.12243392747387816</v>
+            <v>-5.9557467732022196E-2</v>
           </cell>
           <cell r="H20" t="str">
             <v>BAJO</v>
@@ -570,10 +572,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>500.3</v>
+            <v>533.6</v>
           </cell>
           <cell r="G21">
-            <v>2.8173750583839308E-2</v>
+            <v>9.66090611863617E-2</v>
           </cell>
           <cell r="H21" t="str">
             <v>SUBIÓ</v>
@@ -581,13 +583,13 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>776.3</v>
+            <v>837.3</v>
           </cell>
           <cell r="G22">
-            <v>-2.5249700359568528E-2</v>
+            <v>5.134410136407741E-2</v>
           </cell>
           <cell r="H22" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="23">
@@ -603,10 +605,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>150</v>
+            <v>168.2</v>
           </cell>
           <cell r="G24">
-            <v>2.0499075785582255</v>
+            <v>2.4199630314232903</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -614,32 +616,32 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>678.2</v>
+            <v>743.4</v>
           </cell>
           <cell r="G25">
-            <v>-9.532660647902258E-3</v>
+            <v>8.5687732342007328E-2</v>
           </cell>
           <cell r="H25" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="26">
           <cell r="F26">
-            <v>1105.2</v>
+            <v>1210.7</v>
           </cell>
           <cell r="G26">
-            <v>-3.9572323952314914E-3</v>
+            <v>9.1122854450862434E-2</v>
           </cell>
           <cell r="H26" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="27">
           <cell r="F27">
-            <v>493.2</v>
+            <v>531.1</v>
           </cell>
           <cell r="G27">
-            <v>2.1310240963855254E-2</v>
+            <v>9.9792921686747027E-2</v>
           </cell>
           <cell r="H27" t="str">
             <v>SUBIÓ</v>
@@ -647,32 +649,32 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>339.1</v>
+            <v>373</v>
           </cell>
           <cell r="G28">
-            <v>-7.4531695819377242E-2</v>
+            <v>1.7987842699416889E-2</v>
           </cell>
           <cell r="H28" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="29">
           <cell r="F29">
-            <v>132.6</v>
+            <v>4.7</v>
           </cell>
           <cell r="G29">
-            <v>0.23872611464968152</v>
+            <v>-0.95609341825902339</v>
           </cell>
           <cell r="H29" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="30">
           <cell r="F30">
-            <v>119.2</v>
+            <v>4.5999999999999996</v>
           </cell>
           <cell r="G30">
-            <v>-2.7299703264094921E-2</v>
+            <v>-0.9624629080118694</v>
           </cell>
           <cell r="H30" t="str">
             <v>BAJO</v>
@@ -680,10 +682,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>614.5</v>
+            <v>142.4</v>
           </cell>
           <cell r="G31">
-            <v>-0.22286732582202806</v>
+            <v>-0.81991262359163031</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -691,21 +693,21 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>671.5</v>
+            <v>135.69999999999999</v>
           </cell>
           <cell r="G32">
-            <v>3.0626482489186646E-2</v>
+            <v>-0.79172596623412861</v>
           </cell>
           <cell r="H32" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="33">
           <cell r="F33">
-            <v>831.6</v>
+            <v>642.20000000000005</v>
           </cell>
           <cell r="G33">
-            <v>-1.3097421512568763E-2</v>
+            <v>-0.23786816269284705</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -713,10 +715,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>581.79999999999995</v>
+            <v>716.8</v>
           </cell>
           <cell r="G34">
-            <v>1.6486658195679738E-2</v>
+            <v>0.25235069885641659</v>
           </cell>
           <cell r="H34" t="str">
             <v>SUBIÓ</v>
@@ -724,21 +726,21 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>17.5</v>
+            <v>894.1</v>
           </cell>
           <cell r="G35">
-            <v>-0.91766467065868262</v>
+            <v>3.2066295979469635</v>
           </cell>
           <cell r="H35" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="36">
           <cell r="F36">
-            <v>570.1</v>
+            <v>631.1</v>
           </cell>
           <cell r="G36">
-            <v>0.95605115408608876</v>
+            <v>1.1653462258265752</v>
           </cell>
           <cell r="H36" t="str">
             <v>SUBIÓ</v>
@@ -746,10 +748,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>70.900000000000006</v>
+            <v>19.100000000000001</v>
           </cell>
           <cell r="G37">
-            <v>-0.81054293696101054</v>
+            <v>-0.94896149641685901</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -757,10 +759,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>303.60000000000002</v>
+            <v>608.6</v>
           </cell>
           <cell r="G38">
-            <v>0.11227310574521243</v>
+            <v>1.2296752706078271</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -768,21 +770,21 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>528.5</v>
+            <v>71.2</v>
           </cell>
           <cell r="G39">
-            <v>0.25710887663531179</v>
+            <v>-0.83064115039463726</v>
           </cell>
           <cell r="H39" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="40">
           <cell r="F40">
-            <v>322.3</v>
+            <v>344.7</v>
           </cell>
           <cell r="G40">
-            <v>0.30774621910734035</v>
+            <v>0.3986351899668017</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -790,10 +792,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>273.39999999999998</v>
+            <v>585.1</v>
           </cell>
           <cell r="G41">
-            <v>3.7929249352890215E-2</v>
+            <v>1.2212597066436581</v>
           </cell>
           <cell r="H41" t="str">
             <v>SUBIÓ</v>
@@ -801,21 +803,21 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>44.6</v>
+            <v>357.5</v>
           </cell>
           <cell r="G42">
-            <v>-0.10637522768670304</v>
+            <v>6.1630236794171225</v>
           </cell>
           <cell r="H42" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="43">
           <cell r="F43">
-            <v>93.3</v>
+            <v>310.7</v>
           </cell>
           <cell r="G43">
-            <v>0.17492844876931879</v>
+            <v>2.9126502575844304</v>
           </cell>
           <cell r="H43" t="str">
             <v>SUBIÓ</v>
@@ -823,10 +825,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>54.6</v>
+            <v>50.6</v>
           </cell>
           <cell r="G44">
-            <v>0.59310344827586214</v>
+            <v>0.47639257294429704</v>
           </cell>
           <cell r="H44" t="str">
             <v>SUBIÓ</v>
@@ -834,10 +836,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>46.7</v>
+            <v>102.1</v>
           </cell>
           <cell r="G45">
-            <v>0.2453333333333334</v>
+            <v>1.7226666666666666</v>
           </cell>
           <cell r="H45" t="str">
             <v>SUBIÓ</v>
@@ -845,24 +847,24 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>0</v>
+            <v>61.2</v>
           </cell>
           <cell r="G46">
-            <v>-1</v>
+            <v>73.8</v>
           </cell>
           <cell r="H46" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="47">
           <cell r="F47">
-            <v>2.4</v>
+            <v>47.6</v>
           </cell>
           <cell r="G47">
-            <v>-0.26666666666666672</v>
+            <v>13.544444444444444</v>
           </cell>
           <cell r="H47" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
       </sheetData>
@@ -1122,11 +1124,11 @@
       </c>
       <c r="E2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1175.5999999999999</v>
+        <v>1294.4000000000001</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>5.1007802340702124E-2</v>
+        <v>0.15721716514954509</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1151,11 +1153,11 @@
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>82.3</v>
+        <v>90.3</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>5.5743440233236186E-2</v>
+        <v>0.15836734693877541</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1180,11 +1182,11 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>463.4</v>
+        <v>527.9</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-0.15360730593607308</v>
+        <v>-3.5799086757990928E-2</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1209,11 +1211,11 @@
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>100.4</v>
+        <v>106.1</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>2.6871222687122387E-2</v>
+        <v>8.5169688516968822E-2</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1238,11 +1240,11 @@
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>-0.46049046321525888</v>
+        <v>-0.3705722070844687</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1267,11 +1269,11 @@
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1443.7</v>
+        <v>1594.8</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>0.11490452120190953</v>
+        <v>0.23159224936815481</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1296,11 +1298,11 @@
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>144.1</v>
+        <v>153.69999999999999</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>0.17938988095238084</v>
+        <v>0.25796130952380936</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1325,11 +1327,11 @@
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>315.7</v>
+        <v>340.3</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>3.9419335528284805E-2</v>
+        <v>0.12041304998503444</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1354,11 +1356,11 @@
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>718</v>
+        <v>762.5</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>8.4592145015105702E-2</v>
+        <v>0.15181268882175236</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1383,11 +1385,11 @@
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>342.2</v>
+        <v>354.2</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.15553561413348294</v>
+        <v>-0.1259226023555805</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1412,11 +1414,11 @@
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3651</v>
+        <v>3991.1</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>0.12336890393141364</v>
+        <v>0.22801359421546552</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1441,11 +1443,11 @@
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2408</v>
+        <v>2634.2</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>0.1053246536471375</v>
+        <v>0.20915539976631603</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1470,11 +1472,11 @@
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2329.1999999999998</v>
+        <v>2542</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>7.7064065915587676E-2</v>
+        <v>0.17546662182613093</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1499,11 +1501,11 @@
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2794.6</v>
+        <v>3037.3</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>0.16214959454095235</v>
+        <v>0.26307770825851096</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1528,11 +1530,11 @@
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>35.5</v>
+        <v>36.5</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.73335609423011272</v>
+        <v>-0.7258449982929327</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1557,11 +1559,11 @@
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>238.4</v>
+        <v>252.3</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>5.5504125578587304E-2</v>
+        <v>0.11704568323606357</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1586,11 +1588,11 @@
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>129.80000000000001</v>
+        <v>139.1</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>-0.12243392747387816</v>
+        <v>-5.9557467732022196E-2</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1615,11 +1617,11 @@
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>500.3</v>
+        <v>533.6</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>2.8173750583839308E-2</v>
+        <v>9.66090611863617E-2</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1644,15 +1646,15 @@
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>776.3</v>
+        <v>837.3</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-2.5249700359568528E-2</v>
+        <v>5.134410136407741E-2</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H20">
         <v>4.1500000000000004</v>
@@ -1702,11 +1704,11 @@
       </c>
       <c r="E22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>150</v>
+        <v>168.2</v>
       </c>
       <c r="F22" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>2.0499075785582255</v>
+        <v>2.4199630314232903</v>
       </c>
       <c r="G22" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1731,15 +1733,15 @@
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>678.2</v>
+        <v>743.4</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-9.532660647902258E-3</v>
+        <v>8.5687732342007328E-2</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H23">
         <v>1.63</v>
@@ -1760,15 +1762,15 @@
       </c>
       <c r="E24" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>1105.2</v>
+        <v>1210.7</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-3.9572323952314914E-3</v>
+        <v>9.1122854450862434E-2</v>
       </c>
       <c r="G24" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H24">
         <v>1.63</v>
@@ -1789,11 +1791,11 @@
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>493.2</v>
+        <v>531.1</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>2.1310240963855254E-2</v>
+        <v>9.9792921686747027E-2</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1818,15 +1820,15 @@
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>339.1</v>
+        <v>373</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-7.4531695819377242E-2</v>
+        <v>1.7987842699416889E-2</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H26">
         <v>1.63</v>
@@ -1847,15 +1849,15 @@
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>132.6</v>
+        <v>4.7</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>0.23872611464968152</v>
+        <v>-0.95609341825902339</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H27">
         <v>6.15</v>
@@ -1876,11 +1878,11 @@
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>119.2</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>-2.7299703264094921E-2</v>
+        <v>-0.9624629080118694</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1905,11 +1907,11 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>614.5</v>
+        <v>142.4</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-0.22286732582202806</v>
+        <v>-0.81991262359163031</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1934,15 +1936,15 @@
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>671.5</v>
+        <v>135.69999999999999</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>3.0626482489186646E-2</v>
+        <v>-0.79172596623412861</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H30">
         <v>1.1599999999999999</v>
@@ -1963,11 +1965,11 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>831.6</v>
+        <v>642.20000000000005</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-1.3097421512568763E-2</v>
+        <v>-0.23786816269284705</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -1992,11 +1994,11 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>581.79999999999995</v>
+        <v>716.8</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>1.6486658195679738E-2</v>
+        <v>0.25235069885641659</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2021,15 +2023,15 @@
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>17.5</v>
+        <v>894.1</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-0.91766467065868262</v>
+        <v>3.2066295979469635</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H33">
         <v>1.1599999999999999</v>
@@ -2050,11 +2052,11 @@
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>570.1</v>
+        <v>631.1</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>0.95605115408608876</v>
+        <v>1.1653462258265752</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2079,11 +2081,11 @@
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>70.900000000000006</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.81054293696101054</v>
+        <v>-0.94896149641685901</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2108,11 +2110,11 @@
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>303.60000000000002</v>
+        <v>608.6</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>0.11227310574521243</v>
+        <v>1.2296752706078271</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2137,15 +2139,15 @@
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>528.5</v>
+        <v>71.2</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.25710887663531179</v>
+        <v>-0.83064115039463726</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H37">
         <v>0.81</v>
@@ -2166,11 +2168,11 @@
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>322.3</v>
+        <v>344.7</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>0.30774621910734035</v>
+        <v>0.3986351899668017</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2195,11 +2197,11 @@
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>273.39999999999998</v>
+        <v>585.1</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>3.7929249352890215E-2</v>
+        <v>1.2212597066436581</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2224,15 +2226,15 @@
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>44.6</v>
+        <v>357.5</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>-0.10637522768670304</v>
+        <v>6.1630236794171225</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H40">
         <v>2.62</v>
@@ -2253,11 +2255,11 @@
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>93.3</v>
+        <v>310.7</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>0.17492844876931879</v>
+        <v>2.9126502575844304</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2282,11 +2284,11 @@
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>54.6</v>
+        <v>50.6</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>0.59310344827586214</v>
+        <v>0.47639257294429704</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2311,11 +2313,11 @@
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>46.7</v>
+        <v>102.1</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>0.2453333333333334</v>
+        <v>1.7226666666666666</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2340,15 +2342,15 @@
       </c>
       <c r="E44" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>0</v>
+        <v>61.2</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-1</v>
+        <v>73.8</v>
       </c>
       <c r="G44" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H44">
         <v>18</v>
@@ -2369,15 +2371,15 @@
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>2.4</v>
+        <v>47.6</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.26666666666666672</v>
+        <v>13.544444444444444</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H45">
         <v>18</v>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA3B847-93B4-4176-97AC-F1DC71A1244A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{780BAC07-CE9D-4E65-8C47-34D5C560C194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -364,6 +364,7 @@
       <sheetName val="INVENTARIO NACIONAL 14-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 17-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 18-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 19-08-26"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -382,13 +383,14 @@
       <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
-      <sheetData sheetId="13">
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14">
         <row r="4">
           <cell r="F4">
-            <v>1294.4000000000001</v>
+            <v>1162.0833333333333</v>
           </cell>
           <cell r="G4">
-            <v>0.15721716514954509</v>
+            <v>3.8923656263545769E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -396,10 +398,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>90.3</v>
+            <v>83.083333333333329</v>
           </cell>
           <cell r="G5">
-            <v>0.15836734693877541</v>
+            <v>6.5792031098153458E-2</v>
           </cell>
           <cell r="H5" t="str">
             <v>SUBIÓ</v>
@@ -407,10 +409,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>527.9</v>
+            <v>466.08333333333331</v>
           </cell>
           <cell r="G6">
-            <v>-3.5799086757990928E-2</v>
+            <v>-0.14870624048706249</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -418,21 +420,21 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>106.1</v>
+            <v>90.833333333333329</v>
           </cell>
           <cell r="G7">
-            <v>8.5169688516968822E-2</v>
+            <v>-7.0974740430807315E-2</v>
           </cell>
           <cell r="H7" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="8">
           <cell r="F8">
-            <v>10.5</v>
+            <v>9.4166666666666661</v>
           </cell>
           <cell r="G8">
-            <v>-0.3705722070844687</v>
+            <v>-0.43551316984559496</v>
           </cell>
           <cell r="H8" t="str">
             <v>BAJO</v>
@@ -440,10 +442,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1594.8</v>
+            <v>1397.25</v>
           </cell>
           <cell r="G9">
-            <v>0.23159224936815481</v>
+            <v>7.9033277169334282E-2</v>
           </cell>
           <cell r="H9" t="str">
             <v>SUBIÓ</v>
@@ -451,10 +453,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>153.69999999999999</v>
+            <v>138.41666666666666</v>
           </cell>
           <cell r="G10">
-            <v>0.25796130952380936</v>
+            <v>0.13287450396825373</v>
           </cell>
           <cell r="H10" t="str">
             <v>SUBIÓ</v>
@@ -462,10 +464,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>340.3</v>
+            <v>307.58333333333331</v>
           </cell>
           <cell r="G11">
-            <v>0.12041304998503444</v>
+            <v>1.269579966078016E-2</v>
           </cell>
           <cell r="H11" t="str">
             <v>SUBIÓ</v>
@@ -473,10 +475,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>762.5</v>
+            <v>712.66666666666663</v>
           </cell>
           <cell r="G12">
-            <v>0.15181268882175236</v>
+            <v>7.6535750251762291E-2</v>
           </cell>
           <cell r="H12" t="str">
             <v>SUBIÓ</v>
@@ -484,10 +486,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>354.2</v>
+            <v>334.41666666666669</v>
           </cell>
           <cell r="G13">
-            <v>-0.1259226023555805</v>
+            <v>-0.17474294260609458</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -495,10 +497,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3991.1</v>
+            <v>3611.25</v>
           </cell>
           <cell r="G14">
-            <v>0.22801359421546552</v>
+            <v>0.11113830575796135</v>
           </cell>
           <cell r="H14" t="str">
             <v>SUBIÓ</v>
@@ -506,10 +508,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2634.2</v>
+            <v>2375.9166666666665</v>
           </cell>
           <cell r="G15">
-            <v>0.20915539976631603</v>
+            <v>9.0597702108718536E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>SUBIÓ</v>
@@ -517,10 +519,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2542</v>
+            <v>2293.6666666666665</v>
           </cell>
           <cell r="G16">
-            <v>0.17546662182613093</v>
+            <v>6.0632812062104025E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>SUBIÓ</v>
@@ -528,10 +530,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>3037.3</v>
+            <v>2765.5833333333335</v>
           </cell>
           <cell r="G17">
-            <v>0.26307770825851096</v>
+            <v>0.15008285604471094</v>
           </cell>
           <cell r="H17" t="str">
             <v>SUBIÓ</v>
@@ -539,10 +541,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>36.5</v>
+            <v>32.083333333333336</v>
           </cell>
           <cell r="G18">
-            <v>-0.7258449982929327</v>
+            <v>-0.75901900534881073</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -550,10 +552,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>252.3</v>
+            <v>230.33333333333334</v>
           </cell>
           <cell r="G19">
-            <v>0.11704568323606357</v>
+            <v>1.9789360703025505E-2</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -561,10 +563,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>139.1</v>
+            <v>131.41666666666666</v>
           </cell>
           <cell r="G20">
-            <v>-5.9557467732022196E-2</v>
+            <v>-0.11150379020692491</v>
           </cell>
           <cell r="H20" t="str">
             <v>BAJO</v>
@@ -572,10 +574,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>533.6</v>
+            <v>500.41666666666669</v>
           </cell>
           <cell r="G21">
-            <v>9.66090611863617E-2</v>
+            <v>2.8413513934298695E-2</v>
           </cell>
           <cell r="H21" t="str">
             <v>SUBIÓ</v>
@@ -583,21 +585,21 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>837.3</v>
+            <v>784.41666666666663</v>
           </cell>
           <cell r="G22">
-            <v>5.134410136407741E-2</v>
+            <v>-1.5058120731312963E-2</v>
           </cell>
           <cell r="H22" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="23">
           <cell r="F23">
-            <v>10</v>
+            <v>8.3333333333333339</v>
           </cell>
           <cell r="G23">
-            <v>1</v>
+            <v>0.66666666666666674</v>
           </cell>
           <cell r="H23" t="str">
             <v>SUBIÓ</v>
@@ -605,10 +607,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>168.2</v>
+            <v>142</v>
           </cell>
           <cell r="G24">
-            <v>2.4199630314232903</v>
+            <v>1.8872458410351203</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -616,32 +618,32 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>743.4</v>
+            <v>663.58333333333337</v>
           </cell>
           <cell r="G25">
-            <v>8.5687732342007328E-2</v>
+            <v>-3.0879359178615617E-2</v>
           </cell>
           <cell r="H25" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="26">
           <cell r="F26">
-            <v>1210.7</v>
+            <v>1083.3333333333333</v>
           </cell>
           <cell r="G26">
-            <v>9.1122854450862434E-2</v>
+            <v>-2.3664195103300423E-2</v>
           </cell>
           <cell r="H26" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="27">
           <cell r="F27">
-            <v>531.1</v>
+            <v>493.5</v>
           </cell>
           <cell r="G27">
-            <v>9.9792921686747027E-2</v>
+            <v>2.1931475903614439E-2</v>
           </cell>
           <cell r="H27" t="str">
             <v>SUBIÓ</v>
@@ -649,43 +651,43 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>373</v>
+            <v>358.16666666666669</v>
           </cell>
           <cell r="G28">
-            <v>1.7987842699416889E-2</v>
+            <v>-2.2495141214903036E-2</v>
           </cell>
           <cell r="H28" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="29">
           <cell r="F29">
-            <v>4.7</v>
+            <v>131.75</v>
           </cell>
           <cell r="G29">
-            <v>-0.95609341825902339</v>
+            <v>0.23078556263269645</v>
           </cell>
           <cell r="H29" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="30">
           <cell r="F30">
-            <v>4.5999999999999996</v>
+            <v>127.58333333333333</v>
           </cell>
           <cell r="G30">
-            <v>-0.9624629080118694</v>
+            <v>4.1110286844708188E-2</v>
           </cell>
           <cell r="H30" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="31">
           <cell r="F31">
-            <v>142.4</v>
+            <v>587.75</v>
           </cell>
           <cell r="G31">
-            <v>-0.81991262359163031</v>
+            <v>-0.25669694182570713</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -693,21 +695,21 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>135.69999999999999</v>
+            <v>655.41666666666663</v>
           </cell>
           <cell r="G32">
-            <v>-0.79172596623412861</v>
+            <v>5.9415841123668933E-3</v>
           </cell>
           <cell r="H32" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="33">
           <cell r="F33">
-            <v>642.20000000000005</v>
+            <v>818.75</v>
           </cell>
           <cell r="G33">
-            <v>-0.23786816269284705</v>
+            <v>-2.8347178767936132E-2</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -715,32 +717,32 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>716.8</v>
+            <v>570.5</v>
           </cell>
           <cell r="G34">
-            <v>0.25235069885641659</v>
+            <v>-3.2560355781449113E-3</v>
           </cell>
           <cell r="H34" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="35">
           <cell r="F35">
-            <v>894.1</v>
+            <v>24.833333333333332</v>
           </cell>
           <cell r="G35">
-            <v>3.2066295979469635</v>
+            <v>-0.88316224693470202</v>
           </cell>
           <cell r="H35" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="36">
           <cell r="F36">
-            <v>631.1</v>
+            <v>571.75</v>
           </cell>
           <cell r="G36">
-            <v>1.1653462258265752</v>
+            <v>0.96171241422333131</v>
           </cell>
           <cell r="H36" t="str">
             <v>SUBIÓ</v>
@@ -748,10 +750,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>19.100000000000001</v>
+            <v>59.333333333333336</v>
           </cell>
           <cell r="G37">
-            <v>-0.94896149641685901</v>
+            <v>-0.84145107089355842</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -759,10 +761,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>608.6</v>
+            <v>299.83333333333331</v>
           </cell>
           <cell r="G38">
-            <v>1.2296752706078271</v>
+            <v>9.847349431029695E-2</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -770,21 +772,21 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>71.2</v>
+            <v>519.75</v>
           </cell>
           <cell r="G39">
-            <v>-0.83064115039463726</v>
+            <v>0.23629581576386638</v>
           </cell>
           <cell r="H39" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="40">
           <cell r="F40">
-            <v>344.7</v>
+            <v>313.16666666666669</v>
           </cell>
           <cell r="G40">
-            <v>0.3986351899668017</v>
+            <v>0.27068732325095302</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -792,10 +794,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>585.1</v>
+            <v>276.16666666666669</v>
           </cell>
           <cell r="G41">
-            <v>1.2212597066436581</v>
+            <v>4.8432556801840665E-2</v>
           </cell>
           <cell r="H41" t="str">
             <v>SUBIÓ</v>
@@ -803,21 +805,21 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>357.5</v>
+            <v>46.166666666666664</v>
           </cell>
           <cell r="G42">
-            <v>6.1630236794171225</v>
+            <v>-7.4984820886460191E-2</v>
           </cell>
           <cell r="H42" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="43">
           <cell r="F43">
-            <v>310.7</v>
+            <v>89.666666666666671</v>
           </cell>
           <cell r="G43">
-            <v>2.9126502575844304</v>
+            <v>0.12917382178973491</v>
           </cell>
           <cell r="H43" t="str">
             <v>SUBIÓ</v>
@@ -825,10 +827,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>50.6</v>
+            <v>51</v>
           </cell>
           <cell r="G44">
-            <v>0.47639257294429704</v>
+            <v>0.48806366047745353</v>
           </cell>
           <cell r="H44" t="str">
             <v>SUBIÓ</v>
@@ -836,10 +838,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>102.1</v>
+            <v>43</v>
           </cell>
           <cell r="G45">
-            <v>1.7226666666666666</v>
+            <v>0.14666666666666672</v>
           </cell>
           <cell r="H45" t="str">
             <v>SUBIÓ</v>
@@ -847,24 +849,24 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>61.2</v>
+            <v>0</v>
           </cell>
           <cell r="G46">
-            <v>73.8</v>
+            <v>-1</v>
           </cell>
           <cell r="H46" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="47">
           <cell r="F47">
-            <v>47.6</v>
+            <v>2.1666666666666665</v>
           </cell>
           <cell r="G47">
-            <v>13.544444444444444</v>
+            <v>-0.33796296296296302</v>
           </cell>
           <cell r="H47" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
       </sheetData>
@@ -1124,11 +1126,11 @@
       </c>
       <c r="E2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1294.4000000000001</v>
+        <v>1162.0833333333333</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>0.15721716514954509</v>
+        <v>3.8923656263545769E-2</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1153,11 +1155,11 @@
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>90.3</v>
+        <v>83.083333333333329</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>0.15836734693877541</v>
+        <v>6.5792031098153458E-2</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1182,11 +1184,11 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>527.9</v>
+        <v>466.08333333333331</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-3.5799086757990928E-2</v>
+        <v>-0.14870624048706249</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1211,15 +1213,15 @@
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>106.1</v>
+        <v>90.833333333333329</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>8.5169688516968822E-2</v>
+        <v>-7.0974740430807315E-2</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H5">
         <v>3.61</v>
@@ -1240,11 +1242,11 @@
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>10.5</v>
+        <v>9.4166666666666661</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>-0.3705722070844687</v>
+        <v>-0.43551316984559496</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1269,11 +1271,11 @@
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1594.8</v>
+        <v>1397.25</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>0.23159224936815481</v>
+        <v>7.9033277169334282E-2</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1298,11 +1300,11 @@
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>153.69999999999999</v>
+        <v>138.41666666666666</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>0.25796130952380936</v>
+        <v>0.13287450396825373</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1327,11 +1329,11 @@
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>340.3</v>
+        <v>307.58333333333331</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>0.12041304998503444</v>
+        <v>1.269579966078016E-2</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1356,11 +1358,11 @@
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>762.5</v>
+        <v>712.66666666666663</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>0.15181268882175236</v>
+        <v>7.6535750251762291E-2</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1385,11 +1387,11 @@
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>354.2</v>
+        <v>334.41666666666669</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.1259226023555805</v>
+        <v>-0.17474294260609458</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1414,11 +1416,11 @@
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3991.1</v>
+        <v>3611.25</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>0.22801359421546552</v>
+        <v>0.11113830575796135</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1443,11 +1445,11 @@
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2634.2</v>
+        <v>2375.9166666666665</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>0.20915539976631603</v>
+        <v>9.0597702108718536E-2</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1472,11 +1474,11 @@
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2542</v>
+        <v>2293.6666666666665</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>0.17546662182613093</v>
+        <v>6.0632812062104025E-2</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1501,11 +1503,11 @@
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>3037.3</v>
+        <v>2765.5833333333335</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>0.26307770825851096</v>
+        <v>0.15008285604471094</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1530,11 +1532,11 @@
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>36.5</v>
+        <v>32.083333333333336</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.7258449982929327</v>
+        <v>-0.75901900534881073</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1559,11 +1561,11 @@
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>252.3</v>
+        <v>230.33333333333334</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>0.11704568323606357</v>
+        <v>1.9789360703025505E-2</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1588,11 +1590,11 @@
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>139.1</v>
+        <v>131.41666666666666</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>-5.9557467732022196E-2</v>
+        <v>-0.11150379020692491</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1617,11 +1619,11 @@
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>533.6</v>
+        <v>500.41666666666669</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>9.66090611863617E-2</v>
+        <v>2.8413513934298695E-2</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1646,15 +1648,15 @@
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>837.3</v>
+        <v>784.41666666666663</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>5.134410136407741E-2</v>
+        <v>-1.5058120731312963E-2</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H20">
         <v>4.1500000000000004</v>
@@ -1675,11 +1677,11 @@
       </c>
       <c r="E21" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>10</v>
+        <v>8.3333333333333339</v>
       </c>
       <c r="F21" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>1</v>
+        <v>0.66666666666666674</v>
       </c>
       <c r="G21" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
@@ -1704,11 +1706,11 @@
       </c>
       <c r="E22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>168.2</v>
+        <v>142</v>
       </c>
       <c r="F22" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>2.4199630314232903</v>
+        <v>1.8872458410351203</v>
       </c>
       <c r="G22" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1733,15 +1735,15 @@
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>743.4</v>
+        <v>663.58333333333337</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>8.5687732342007328E-2</v>
+        <v>-3.0879359178615617E-2</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H23">
         <v>1.63</v>
@@ -1762,15 +1764,15 @@
       </c>
       <c r="E24" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>1210.7</v>
+        <v>1083.3333333333333</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>9.1122854450862434E-2</v>
+        <v>-2.3664195103300423E-2</v>
       </c>
       <c r="G24" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H24">
         <v>1.63</v>
@@ -1791,11 +1793,11 @@
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>531.1</v>
+        <v>493.5</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>9.9792921686747027E-2</v>
+        <v>2.1931475903614439E-2</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1820,15 +1822,15 @@
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>373</v>
+        <v>358.16666666666669</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>1.7987842699416889E-2</v>
+        <v>-2.2495141214903036E-2</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H26">
         <v>1.63</v>
@@ -1849,15 +1851,15 @@
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>4.7</v>
+        <v>131.75</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>-0.95609341825902339</v>
+        <v>0.23078556263269645</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H27">
         <v>6.15</v>
@@ -1878,15 +1880,15 @@
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>4.5999999999999996</v>
+        <v>127.58333333333333</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>-0.9624629080118694</v>
+        <v>4.1110286844708188E-2</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H28">
         <v>6.15</v>
@@ -1907,11 +1909,11 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>142.4</v>
+        <v>587.75</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-0.81991262359163031</v>
+        <v>-0.25669694182570713</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1936,15 +1938,15 @@
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>135.69999999999999</v>
+        <v>655.41666666666663</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-0.79172596623412861</v>
+        <v>5.9415841123668933E-3</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H30">
         <v>1.1599999999999999</v>
@@ -1965,11 +1967,11 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>642.20000000000005</v>
+        <v>818.75</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-0.23786816269284705</v>
+        <v>-2.8347178767936132E-2</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -1994,15 +1996,15 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>716.8</v>
+        <v>570.5</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>0.25235069885641659</v>
+        <v>-3.2560355781449113E-3</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H32">
         <v>1.1599999999999999</v>
@@ -2023,15 +2025,15 @@
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>894.1</v>
+        <v>24.833333333333332</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>3.2066295979469635</v>
+        <v>-0.88316224693470202</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H33">
         <v>1.1599999999999999</v>
@@ -2052,11 +2054,11 @@
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>631.1</v>
+        <v>571.75</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>1.1653462258265752</v>
+        <v>0.96171241422333131</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2081,11 +2083,11 @@
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>19.100000000000001</v>
+        <v>59.333333333333336</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.94896149641685901</v>
+        <v>-0.84145107089355842</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2110,11 +2112,11 @@
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>608.6</v>
+        <v>299.83333333333331</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>1.2296752706078271</v>
+        <v>9.847349431029695E-2</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2139,15 +2141,15 @@
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>71.2</v>
+        <v>519.75</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>-0.83064115039463726</v>
+        <v>0.23629581576386638</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H37">
         <v>0.81</v>
@@ -2168,11 +2170,11 @@
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>344.7</v>
+        <v>313.16666666666669</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>0.3986351899668017</v>
+        <v>0.27068732325095302</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2197,11 +2199,11 @@
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>585.1</v>
+        <v>276.16666666666669</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>1.2212597066436581</v>
+        <v>4.8432556801840665E-2</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2226,15 +2228,15 @@
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>357.5</v>
+        <v>46.166666666666664</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>6.1630236794171225</v>
+        <v>-7.4984820886460191E-2</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H40">
         <v>2.62</v>
@@ -2255,11 +2257,11 @@
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>310.7</v>
+        <v>89.666666666666671</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>2.9126502575844304</v>
+        <v>0.12917382178973491</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2284,11 +2286,11 @@
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>50.6</v>
+        <v>51</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>0.47639257294429704</v>
+        <v>0.48806366047745353</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2313,11 +2315,11 @@
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>102.1</v>
+        <v>43</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>1.7226666666666666</v>
+        <v>0.14666666666666672</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2342,15 +2344,15 @@
       </c>
       <c r="E44" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>61.2</v>
+        <v>0</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>73.8</v>
+        <v>-1</v>
       </c>
       <c r="G44" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H44">
         <v>18</v>
@@ -2371,15 +2373,15 @@
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>47.6</v>
+        <v>2.1666666666666665</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>13.544444444444444</v>
+        <v>-0.33796296296296302</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H45">
         <v>18</v>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{780BAC07-CE9D-4E65-8C47-34D5C560C194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE263C90-282C-4B8F-83E6-69308900AA74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -365,6 +365,8 @@
       <sheetName val="INVENTARIO NACIONAL 17-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 18-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 19-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 19-08-26-2"/>
+      <sheetName val="INVENTARIO NACIONAL 20-08-26"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -384,13 +386,15 @@
       <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
       <sheetData sheetId="13"/>
-      <sheetData sheetId="14">
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16">
         <row r="4">
           <cell r="F4">
-            <v>1162.0833333333333</v>
+            <v>1148.6923076923076</v>
           </cell>
           <cell r="G4">
-            <v>3.8923656263545769E-2</v>
+            <v>2.6951835550665271E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -398,10 +402,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>83.083333333333329</v>
+            <v>83.307692307692307</v>
           </cell>
           <cell r="G5">
-            <v>6.5792031098153458E-2</v>
+            <v>6.8670105404799342E-2</v>
           </cell>
           <cell r="H5" t="str">
             <v>SUBIÓ</v>
@@ -409,10 +413,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>466.08333333333331</v>
+            <v>466.84615384615387</v>
           </cell>
           <cell r="G6">
-            <v>-0.14870624048706249</v>
+            <v>-0.14731296101159108</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -420,10 +424,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>90.833333333333329</v>
+            <v>90.84615384615384</v>
           </cell>
           <cell r="G7">
-            <v>-7.0974740430807315E-2</v>
+            <v>-7.0843614776669228E-2</v>
           </cell>
           <cell r="H7" t="str">
             <v>BAJO</v>
@@ -431,10 +435,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>9.4166666666666661</v>
+            <v>10.076923076923077</v>
           </cell>
           <cell r="G8">
-            <v>-0.43551316984559496</v>
+            <v>-0.39593376650597367</v>
           </cell>
           <cell r="H8" t="str">
             <v>BAJO</v>
@@ -442,10 +446,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1397.25</v>
+            <v>1362.4615384615386</v>
           </cell>
           <cell r="G9">
-            <v>7.9033277169334282E-2</v>
+            <v>5.2167714341261107E-2</v>
           </cell>
           <cell r="H9" t="str">
             <v>SUBIÓ</v>
@@ -453,10 +457,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>138.41666666666666</v>
+            <v>140.07692307692307</v>
           </cell>
           <cell r="G10">
-            <v>0.13287450396825373</v>
+            <v>0.14646291208791196</v>
           </cell>
           <cell r="H10" t="str">
             <v>SUBIÓ</v>
@@ -464,10 +468,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>307.58333333333331</v>
+            <v>324.53846153846155</v>
           </cell>
           <cell r="G11">
-            <v>1.269579966078016E-2</v>
+            <v>6.8519328621094555E-2</v>
           </cell>
           <cell r="H11" t="str">
             <v>SUBIÓ</v>
@@ -475,10 +479,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>712.66666666666663</v>
+            <v>728.30769230769226</v>
           </cell>
           <cell r="G12">
-            <v>7.6535750251762291E-2</v>
+            <v>0.10016267720195215</v>
           </cell>
           <cell r="H12" t="str">
             <v>SUBIÓ</v>
@@ -486,10 +490,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>334.41666666666669</v>
+            <v>344.61538461538464</v>
           </cell>
           <cell r="G13">
-            <v>-0.17474294260609458</v>
+            <v>-0.14957504637818708</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -497,10 +501,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3611.25</v>
+            <v>3577.3076923076924</v>
           </cell>
           <cell r="G14">
-            <v>0.11113830575796135</v>
+            <v>0.10069466484062084</v>
           </cell>
           <cell r="H14" t="str">
             <v>SUBIÓ</v>
@@ -508,10 +512,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2375.9166666666665</v>
+            <v>2352.7692307692309</v>
           </cell>
           <cell r="G15">
-            <v>9.0597702108718536E-2</v>
+            <v>7.9972522886894604E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>SUBIÓ</v>
@@ -519,10 +523,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2293.6666666666665</v>
+            <v>2278.6153846153848</v>
           </cell>
           <cell r="G16">
-            <v>6.0632812062104025E-2</v>
+            <v>5.3672827928755273E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>SUBIÓ</v>
@@ -530,10 +534,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2765.5833333333335</v>
+            <v>2733.2307692307691</v>
           </cell>
           <cell r="G17">
-            <v>0.15008285604471094</v>
+            <v>0.13662886647405492</v>
           </cell>
           <cell r="H17" t="str">
             <v>SUBIÓ</v>
@@ -541,10 +545,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>32.083333333333336</v>
+            <v>30.153846153846153</v>
           </cell>
           <cell r="G18">
-            <v>-0.75901900534881073</v>
+            <v>-0.77351156866349768</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -552,10 +556,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>230.33333333333334</v>
+            <v>232.92307692307693</v>
           </cell>
           <cell r="G19">
-            <v>1.9789360703025505E-2</v>
+            <v>3.1255321454556784E-2</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -563,10 +567,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>131.41666666666666</v>
+            <v>136.23076923076923</v>
           </cell>
           <cell r="G20">
-            <v>-0.11150379020692491</v>
+            <v>-7.895607772682145E-2</v>
           </cell>
           <cell r="H20" t="str">
             <v>BAJO</v>
@@ -574,10 +578,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>500.41666666666669</v>
+            <v>504.07692307692309</v>
           </cell>
           <cell r="G21">
-            <v>2.8413513934298695E-2</v>
+            <v>3.5935759709697201E-2</v>
           </cell>
           <cell r="H21" t="str">
             <v>SUBIÓ</v>
@@ -585,10 +589,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>784.41666666666663</v>
+            <v>782.46153846153845</v>
           </cell>
           <cell r="G22">
-            <v>-1.5058120731312963E-2</v>
+            <v>-1.7513050273737396E-2</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -596,10 +600,10 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>8.3333333333333339</v>
+            <v>7.6923076923076925</v>
           </cell>
           <cell r="G23">
-            <v>0.66666666666666674</v>
+            <v>0.53846153846153855</v>
           </cell>
           <cell r="H23" t="str">
             <v>SUBIÓ</v>
@@ -607,10 +611,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>142</v>
+            <v>131.07692307692307</v>
           </cell>
           <cell r="G24">
-            <v>1.8872458410351203</v>
+            <v>1.6651500071093417</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -618,10 +622,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>663.58333333333337</v>
+            <v>640.92307692307691</v>
           </cell>
           <cell r="G25">
-            <v>-3.0879359178615617E-2</v>
+            <v>-6.3973201519670009E-2</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -629,10 +633,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>1083.3333333333333</v>
+            <v>1064.3076923076924</v>
           </cell>
           <cell r="G26">
-            <v>-2.3664195103300423E-2</v>
+            <v>-4.0810731605864792E-2</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -640,10 +644,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>493.5</v>
+            <v>502.07692307692309</v>
           </cell>
           <cell r="G27">
-            <v>2.1931475903614439E-2</v>
+            <v>3.9692423540315103E-2</v>
           </cell>
           <cell r="H27" t="str">
             <v>SUBIÓ</v>
@@ -651,10 +655,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>358.16666666666669</v>
+            <v>356.07692307692309</v>
           </cell>
           <cell r="G28">
-            <v>-2.2495141214903036E-2</v>
+            <v>-2.8198448369643025E-2</v>
           </cell>
           <cell r="H28" t="str">
             <v>BAJO</v>
@@ -662,10 +666,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>131.75</v>
+            <v>127.69230769230769</v>
           </cell>
           <cell r="G29">
-            <v>0.23078556263269645</v>
+            <v>0.19287930752898896</v>
           </cell>
           <cell r="H29" t="str">
             <v>SUBIÓ</v>
@@ -673,10 +677,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>127.58333333333333</v>
+            <v>130.38461538461539</v>
           </cell>
           <cell r="G30">
-            <v>4.1110286844708188E-2</v>
+            <v>6.3969413375941642E-2</v>
           </cell>
           <cell r="H30" t="str">
             <v>SUBIÓ</v>
@@ -684,10 +688,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>587.75</v>
+            <v>609.69230769230774</v>
           </cell>
           <cell r="G31">
-            <v>-0.25669694182570713</v>
+            <v>-0.22894741496718962</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -695,10 +699,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>655.41666666666663</v>
+            <v>652.23076923076928</v>
           </cell>
           <cell r="G32">
-            <v>5.9415841123668933E-3</v>
+            <v>1.0518294319048493E-3</v>
           </cell>
           <cell r="H32" t="str">
             <v>SUBIÓ</v>
@@ -706,10 +710,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>818.75</v>
+            <v>830.61538461538464</v>
           </cell>
           <cell r="G33">
-            <v>-2.8347178767936132E-2</v>
+            <v>-1.4265915333991686E-2</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -717,21 +721,21 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>570.5</v>
+            <v>575.30769230769226</v>
           </cell>
           <cell r="G34">
-            <v>-3.2560355781449113E-3</v>
+            <v>5.1436809696021601E-3</v>
           </cell>
           <cell r="H34" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="35">
           <cell r="F35">
-            <v>24.833333333333332</v>
+            <v>48.769230769230766</v>
           </cell>
           <cell r="G35">
-            <v>-0.88316224693470202</v>
+            <v>-0.77054681845101003</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -739,10 +743,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>571.75</v>
+            <v>563.38461538461536</v>
           </cell>
           <cell r="G36">
-            <v>0.96171241422333131</v>
+            <v>0.93301022121982813</v>
           </cell>
           <cell r="H36" t="str">
             <v>SUBIÓ</v>
@@ -750,10 +754,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>59.333333333333336</v>
+            <v>54.769230769230766</v>
           </cell>
           <cell r="G37">
-            <v>-0.84145107089355842</v>
+            <v>-0.85364714236328476</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -761,10 +765,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>299.83333333333331</v>
+            <v>296.38461538461536</v>
           </cell>
           <cell r="G38">
-            <v>9.847349431029695E-2</v>
+            <v>8.5838724140139488E-2</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -772,10 +776,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>519.75</v>
+            <v>509.30769230769232</v>
           </cell>
           <cell r="G39">
-            <v>0.23629581576386638</v>
+            <v>0.2114573716909105</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -783,10 +787,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>313.16666666666669</v>
+            <v>303.30769230769232</v>
           </cell>
           <cell r="G40">
-            <v>0.27068732325095302</v>
+            <v>0.23068410748233692</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -794,10 +798,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>276.16666666666669</v>
+            <v>271.84615384615387</v>
           </cell>
           <cell r="G41">
-            <v>4.8432556801840665E-2</v>
+            <v>3.2030264817149989E-2</v>
           </cell>
           <cell r="H41" t="str">
             <v>SUBIÓ</v>
@@ -805,10 +809,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>46.166666666666664</v>
+            <v>46.153846153846153</v>
           </cell>
           <cell r="G42">
-            <v>-7.4984820886460191E-2</v>
+            <v>-7.5241698192517803E-2</v>
           </cell>
           <cell r="H42" t="str">
             <v>BAJO</v>
@@ -816,10 +820,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>89.666666666666671</v>
+            <v>93.307692307692307</v>
           </cell>
           <cell r="G43">
-            <v>0.12917382178973491</v>
+            <v>0.17502531812777944</v>
           </cell>
           <cell r="H43" t="str">
             <v>SUBIÓ</v>
@@ -827,10 +831,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>51</v>
+            <v>51.384615384615387</v>
           </cell>
           <cell r="G44">
-            <v>0.48806366047745353</v>
+            <v>0.49928586002856568</v>
           </cell>
           <cell r="H44" t="str">
             <v>SUBIÓ</v>
@@ -838,10 +842,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>43</v>
+            <v>40.92307692307692</v>
           </cell>
           <cell r="G45">
-            <v>0.14666666666666672</v>
+            <v>9.1282051282051135E-2</v>
           </cell>
           <cell r="H45" t="str">
             <v>SUBIÓ</v>
@@ -860,10 +864,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>2.1666666666666665</v>
+            <v>2.0769230769230771</v>
           </cell>
           <cell r="G47">
-            <v>-0.33796296296296302</v>
+            <v>-0.36538461538461542</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -1126,11 +1130,11 @@
       </c>
       <c r="E2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1162.0833333333333</v>
+        <v>1148.6923076923076</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>3.8923656263545769E-2</v>
+        <v>2.6951835550665271E-2</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1155,11 +1159,11 @@
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>83.083333333333329</v>
+        <v>83.307692307692307</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>6.5792031098153458E-2</v>
+        <v>6.8670105404799342E-2</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1184,11 +1188,11 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>466.08333333333331</v>
+        <v>466.84615384615387</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-0.14870624048706249</v>
+        <v>-0.14731296101159108</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1213,11 +1217,11 @@
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>90.833333333333329</v>
+        <v>90.84615384615384</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>-7.0974740430807315E-2</v>
+        <v>-7.0843614776669228E-2</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1242,11 +1246,11 @@
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>9.4166666666666661</v>
+        <v>10.076923076923077</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>-0.43551316984559496</v>
+        <v>-0.39593376650597367</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1271,11 +1275,11 @@
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1397.25</v>
+        <v>1362.4615384615386</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>7.9033277169334282E-2</v>
+        <v>5.2167714341261107E-2</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1300,11 +1304,11 @@
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>138.41666666666666</v>
+        <v>140.07692307692307</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>0.13287450396825373</v>
+        <v>0.14646291208791196</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1329,11 +1333,11 @@
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>307.58333333333331</v>
+        <v>324.53846153846155</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>1.269579966078016E-2</v>
+        <v>6.8519328621094555E-2</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1358,11 +1362,11 @@
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>712.66666666666663</v>
+        <v>728.30769230769226</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>7.6535750251762291E-2</v>
+        <v>0.10016267720195215</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1387,11 +1391,11 @@
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>334.41666666666669</v>
+        <v>344.61538461538464</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.17474294260609458</v>
+        <v>-0.14957504637818708</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1416,11 +1420,11 @@
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3611.25</v>
+        <v>3577.3076923076924</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>0.11113830575796135</v>
+        <v>0.10069466484062084</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1445,11 +1449,11 @@
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2375.9166666666665</v>
+        <v>2352.7692307692309</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>9.0597702108718536E-2</v>
+        <v>7.9972522886894604E-2</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1474,11 +1478,11 @@
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2293.6666666666665</v>
+        <v>2278.6153846153848</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>6.0632812062104025E-2</v>
+        <v>5.3672827928755273E-2</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1503,11 +1507,11 @@
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2765.5833333333335</v>
+        <v>2733.2307692307691</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>0.15008285604471094</v>
+        <v>0.13662886647405492</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1532,11 +1536,11 @@
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>32.083333333333336</v>
+        <v>30.153846153846153</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.75901900534881073</v>
+        <v>-0.77351156866349768</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1561,11 +1565,11 @@
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>230.33333333333334</v>
+        <v>232.92307692307693</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>1.9789360703025505E-2</v>
+        <v>3.1255321454556784E-2</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1590,11 +1594,11 @@
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>131.41666666666666</v>
+        <v>136.23076923076923</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>-0.11150379020692491</v>
+        <v>-7.895607772682145E-2</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1619,11 +1623,11 @@
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>500.41666666666669</v>
+        <v>504.07692307692309</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>2.8413513934298695E-2</v>
+        <v>3.5935759709697201E-2</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1648,11 +1652,11 @@
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>784.41666666666663</v>
+        <v>782.46153846153845</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-1.5058120731312963E-2</v>
+        <v>-1.7513050273737396E-2</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1677,11 +1681,11 @@
       </c>
       <c r="E21" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>8.3333333333333339</v>
+        <v>7.6923076923076925</v>
       </c>
       <c r="F21" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>0.66666666666666674</v>
+        <v>0.53846153846153855</v>
       </c>
       <c r="G21" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
@@ -1706,11 +1710,11 @@
       </c>
       <c r="E22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>142</v>
+        <v>131.07692307692307</v>
       </c>
       <c r="F22" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>1.8872458410351203</v>
+        <v>1.6651500071093417</v>
       </c>
       <c r="G22" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1735,11 +1739,11 @@
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>663.58333333333337</v>
+        <v>640.92307692307691</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-3.0879359178615617E-2</v>
+        <v>-6.3973201519670009E-2</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1764,11 +1768,11 @@
       </c>
       <c r="E24" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>1083.3333333333333</v>
+        <v>1064.3076923076924</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-2.3664195103300423E-2</v>
+        <v>-4.0810731605864792E-2</v>
       </c>
       <c r="G24" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1793,11 +1797,11 @@
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>493.5</v>
+        <v>502.07692307692309</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>2.1931475903614439E-2</v>
+        <v>3.9692423540315103E-2</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1822,11 +1826,11 @@
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>358.16666666666669</v>
+        <v>356.07692307692309</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-2.2495141214903036E-2</v>
+        <v>-2.8198448369643025E-2</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1851,11 +1855,11 @@
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>131.75</v>
+        <v>127.69230769230769</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>0.23078556263269645</v>
+        <v>0.19287930752898896</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1880,11 +1884,11 @@
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>127.58333333333333</v>
+        <v>130.38461538461539</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>4.1110286844708188E-2</v>
+        <v>6.3969413375941642E-2</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1909,11 +1913,11 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>587.75</v>
+        <v>609.69230769230774</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-0.25669694182570713</v>
+        <v>-0.22894741496718962</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1938,11 +1942,11 @@
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>655.41666666666663</v>
+        <v>652.23076923076928</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>5.9415841123668933E-3</v>
+        <v>1.0518294319048493E-3</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1967,11 +1971,11 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>818.75</v>
+        <v>830.61538461538464</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-2.8347178767936132E-2</v>
+        <v>-1.4265915333991686E-2</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -1996,15 +2000,15 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>570.5</v>
+        <v>575.30769230769226</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-3.2560355781449113E-3</v>
+        <v>5.1436809696021601E-3</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H32">
         <v>1.1599999999999999</v>
@@ -2025,11 +2029,11 @@
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>24.833333333333332</v>
+        <v>48.769230769230766</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-0.88316224693470202</v>
+        <v>-0.77054681845101003</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2054,11 +2058,11 @@
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>571.75</v>
+        <v>563.38461538461536</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>0.96171241422333131</v>
+        <v>0.93301022121982813</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2083,11 +2087,11 @@
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>59.333333333333336</v>
+        <v>54.769230769230766</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.84145107089355842</v>
+        <v>-0.85364714236328476</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2112,11 +2116,11 @@
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>299.83333333333331</v>
+        <v>296.38461538461536</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>9.847349431029695E-2</v>
+        <v>8.5838724140139488E-2</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2141,11 +2145,11 @@
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>519.75</v>
+        <v>509.30769230769232</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.23629581576386638</v>
+        <v>0.2114573716909105</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2170,11 +2174,11 @@
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>313.16666666666669</v>
+        <v>303.30769230769232</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>0.27068732325095302</v>
+        <v>0.23068410748233692</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2199,11 +2203,11 @@
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>276.16666666666669</v>
+        <v>271.84615384615387</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>4.8432556801840665E-2</v>
+        <v>3.2030264817149989E-2</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2228,11 +2232,11 @@
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>46.166666666666664</v>
+        <v>46.153846153846153</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>-7.4984820886460191E-2</v>
+        <v>-7.5241698192517803E-2</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2257,11 +2261,11 @@
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>89.666666666666671</v>
+        <v>93.307692307692307</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>0.12917382178973491</v>
+        <v>0.17502531812777944</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2286,11 +2290,11 @@
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>51</v>
+        <v>51.384615384615387</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>0.48806366047745353</v>
+        <v>0.49928586002856568</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2315,11 +2319,11 @@
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>43</v>
+        <v>40.92307692307692</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>0.14666666666666672</v>
+        <v>9.1282051282051135E-2</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2373,11 +2377,11 @@
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>2.1666666666666665</v>
+        <v>2.0769230769230771</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.33796296296296302</v>
+        <v>-0.36538461538461542</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE263C90-282C-4B8F-83E6-69308900AA74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE4FE7FA-5BC4-4D78-9967-16C5395E4FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   <externalReferences>
     <externalReference r:id="rId3"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -367,6 +367,9 @@
       <sheetName val="INVENTARIO NACIONAL 19-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 19-08-26-2"/>
       <sheetName val="INVENTARIO NACIONAL 20-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 20-08-26-2"/>
+      <sheetName val="INVENTARIO NACIONAL 21-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 24-08-26"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -388,13 +391,16 @@
       <sheetData sheetId="13"/>
       <sheetData sheetId="14"/>
       <sheetData sheetId="15"/>
-      <sheetData sheetId="16">
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19">
         <row r="4">
           <cell r="F4">
-            <v>1148.6923076923076</v>
+            <v>1170.7333333333333</v>
           </cell>
           <cell r="G4">
-            <v>2.6951835550665271E-2</v>
+            <v>4.6656913740789063E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -402,10 +408,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>83.307692307692307</v>
+            <v>81.466666666666669</v>
           </cell>
           <cell r="G5">
-            <v>6.8670105404799342E-2</v>
+            <v>4.5053449951409252E-2</v>
           </cell>
           <cell r="H5" t="str">
             <v>SUBIÓ</v>
@@ -413,10 +419,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>466.84615384615387</v>
+            <v>491.4</v>
           </cell>
           <cell r="G6">
-            <v>-0.14731296101159108</v>
+            <v>-0.10246575342465758</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -424,10 +430,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>90.84615384615384</v>
+            <v>95.066666666666663</v>
           </cell>
           <cell r="G7">
-            <v>-7.0843614776669228E-2</v>
+            <v>-2.7677049434371548E-2</v>
           </cell>
           <cell r="H7" t="str">
             <v>BAJO</v>
@@ -435,10 +441,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>10.076923076923077</v>
+            <v>11.866666666666667</v>
           </cell>
           <cell r="G8">
-            <v>-0.39593376650597367</v>
+            <v>-0.28864668483197098</v>
           </cell>
           <cell r="H8" t="str">
             <v>BAJO</v>
@@ -446,10 +452,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1362.4615384615386</v>
+            <v>1399.9333333333334</v>
           </cell>
           <cell r="G9">
-            <v>5.2167714341261107E-2</v>
+            <v>8.1105494711223525E-2</v>
           </cell>
           <cell r="H9" t="str">
             <v>SUBIÓ</v>
@@ -457,10 +463,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>140.07692307692307</v>
+            <v>149.4</v>
           </cell>
           <cell r="G10">
-            <v>0.14646291208791196</v>
+            <v>0.22276785714285707</v>
           </cell>
           <cell r="H10" t="str">
             <v>SUBIÓ</v>
@@ -468,10 +474,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>324.53846153846155</v>
+            <v>320.93333333333334</v>
           </cell>
           <cell r="G11">
-            <v>6.8519328621094555E-2</v>
+            <v>5.6649705676943052E-2</v>
           </cell>
           <cell r="H11" t="str">
             <v>SUBIÓ</v>
@@ -479,10 +485,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>728.30769230769226</v>
+            <v>720.2</v>
           </cell>
           <cell r="G12">
-            <v>0.10016267720195215</v>
+            <v>8.7915407854984862E-2</v>
           </cell>
           <cell r="H12" t="str">
             <v>SUBIÓ</v>
@@ -490,10 +496,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>344.61538461538464</v>
+            <v>339.4</v>
           </cell>
           <cell r="G13">
-            <v>-0.14957504637818708</v>
+            <v>-0.1624453168816602</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -501,10 +507,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3577.3076923076924</v>
+            <v>3515.8</v>
           </cell>
           <cell r="G14">
-            <v>0.10069466484062084</v>
+            <v>8.1769485741458148E-2</v>
           </cell>
           <cell r="H14" t="str">
             <v>SUBIÓ</v>
@@ -512,10 +518,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2352.7692307692309</v>
+            <v>2287.9333333333334</v>
           </cell>
           <cell r="G15">
-            <v>7.9972522886894604E-2</v>
+            <v>5.0211428253491341E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>SUBIÓ</v>
@@ -523,10 +529,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2278.6153846153848</v>
+            <v>2236.6</v>
           </cell>
           <cell r="G16">
-            <v>5.3672827928755273E-2</v>
+            <v>3.424415671767278E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>SUBIÓ</v>
@@ -534,10 +540,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2733.2307692307691</v>
+            <v>2663.0666666666666</v>
           </cell>
           <cell r="G17">
-            <v>0.13662886647405492</v>
+            <v>0.10745074318406656</v>
           </cell>
           <cell r="H17" t="str">
             <v>SUBIÓ</v>
@@ -545,10 +551,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>30.153846153846153</v>
+            <v>26.4</v>
           </cell>
           <cell r="G18">
-            <v>-0.77351156866349768</v>
+            <v>-0.80170706725844998</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -556,10 +562,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>232.92307692307693</v>
+            <v>234.66666666666666</v>
           </cell>
           <cell r="G19">
-            <v>3.1255321454556784E-2</v>
+            <v>3.8974978198161869E-2</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -567,10 +573,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>136.23076923076923</v>
+            <v>132.66666666666666</v>
           </cell>
           <cell r="G20">
-            <v>-7.895607772682145E-2</v>
+            <v>-0.10305265314484746</v>
           </cell>
           <cell r="H20" t="str">
             <v>BAJO</v>
@@ -578,10 +584,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>504.07692307692309</v>
+            <v>498.33333333333331</v>
           </cell>
           <cell r="G21">
-            <v>3.5935759709697201E-2</v>
+            <v>2.4132025533240009E-2</v>
           </cell>
           <cell r="H21" t="str">
             <v>SUBIÓ</v>
@@ -589,10 +595,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>782.46153846153845</v>
+            <v>780.4666666666667</v>
           </cell>
           <cell r="G22">
-            <v>-1.7513050273737396E-2</v>
+            <v>-2.0017883301942319E-2</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -600,10 +606,10 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>7.6923076923076925</v>
+            <v>6.666666666666667</v>
           </cell>
           <cell r="G23">
-            <v>0.53846153846153855</v>
+            <v>0.33333333333333348</v>
           </cell>
           <cell r="H23" t="str">
             <v>SUBIÓ</v>
@@ -611,10 +617,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>131.07692307692307</v>
+            <v>120.26666666666667</v>
           </cell>
           <cell r="G24">
-            <v>1.6651500071093417</v>
+            <v>1.4453481207640175</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -622,32 +628,32 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>640.92307692307691</v>
+            <v>696.73333333333335</v>
           </cell>
           <cell r="G25">
-            <v>-6.3973201519670009E-2</v>
+            <v>1.7534076827757206E-2</v>
           </cell>
           <cell r="H25" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="26">
           <cell r="F26">
-            <v>1064.3076923076924</v>
+            <v>1211.7333333333333</v>
           </cell>
           <cell r="G26">
-            <v>-4.0810731605864792E-2</v>
+            <v>9.2054128603225482E-2</v>
           </cell>
           <cell r="H26" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="27">
           <cell r="F27">
-            <v>502.07692307692309</v>
+            <v>510.86666666666667</v>
           </cell>
           <cell r="G27">
-            <v>3.9692423540315103E-2</v>
+            <v>5.7894076305220921E-2</v>
           </cell>
           <cell r="H27" t="str">
             <v>SUBIÓ</v>
@@ -655,10 +661,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>356.07692307692309</v>
+            <v>357.4</v>
           </cell>
           <cell r="G28">
-            <v>-2.8198448369643025E-2</v>
+            <v>-2.45875201587894E-2</v>
           </cell>
           <cell r="H28" t="str">
             <v>BAJO</v>
@@ -666,10 +672,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>127.69230769230769</v>
+            <v>118.86666666666666</v>
           </cell>
           <cell r="G29">
-            <v>0.19287930752898896</v>
+            <v>0.11043170559094118</v>
           </cell>
           <cell r="H29" t="str">
             <v>SUBIÓ</v>
@@ -677,10 +683,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>130.38461538461539</v>
+            <v>132.93333333333334</v>
           </cell>
           <cell r="G30">
-            <v>6.3969413375941642E-2</v>
+            <v>8.4767556874381755E-2</v>
           </cell>
           <cell r="H30" t="str">
             <v>SUBIÓ</v>
@@ -688,10 +694,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>609.69230769230774</v>
+            <v>593.13333333333333</v>
           </cell>
           <cell r="G31">
-            <v>-0.22894741496718962</v>
+            <v>-0.24988886334023153</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -699,21 +705,21 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>652.23076923076928</v>
+            <v>634.4666666666667</v>
           </cell>
           <cell r="G32">
-            <v>1.0518294319048493E-3</v>
+            <v>-2.621273429142823E-2</v>
           </cell>
           <cell r="H32" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="33">
           <cell r="F33">
-            <v>830.61538461538464</v>
+            <v>841.6</v>
           </cell>
           <cell r="G33">
-            <v>-1.4265915333991686E-2</v>
+            <v>-1.2299061387419652E-3</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -721,21 +727,21 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>575.30769230769226</v>
+            <v>560.66666666666663</v>
           </cell>
           <cell r="G34">
-            <v>5.1436809696021601E-3</v>
+            <v>-2.0436255823803595E-2</v>
           </cell>
           <cell r="H34" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="35">
           <cell r="F35">
-            <v>48.769230769230766</v>
+            <v>78.733333333333334</v>
           </cell>
           <cell r="G35">
-            <v>-0.77054681845101003</v>
+            <v>-0.62956943256344444</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -743,10 +749,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>563.38461538461536</v>
+            <v>509.86666666666667</v>
           </cell>
           <cell r="G36">
-            <v>0.93301022121982813</v>
+            <v>0.74938656685381577</v>
           </cell>
           <cell r="H36" t="str">
             <v>SUBIÓ</v>
@@ -754,10 +760,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>54.769230769230766</v>
+            <v>47.466666666666669</v>
           </cell>
           <cell r="G37">
-            <v>-0.85364714236328476</v>
+            <v>-0.87316085671484678</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -765,10 +771,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>296.38461538461536</v>
+            <v>286.53333333333336</v>
           </cell>
           <cell r="G38">
-            <v>8.5838724140139488E-2</v>
+            <v>4.9747432694976501E-2</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -776,10 +782,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>509.30769230769232</v>
+            <v>476.6</v>
           </cell>
           <cell r="G39">
-            <v>0.2114573716909105</v>
+            <v>0.13365769272353756</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -787,10 +793,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>303.30769230769232</v>
+            <v>284.06666666666666</v>
           </cell>
           <cell r="G40">
-            <v>0.23068410748233692</v>
+            <v>0.1526128120004917</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -798,21 +804,21 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>271.84615384615387</v>
+            <v>252.2</v>
           </cell>
           <cell r="G41">
-            <v>3.2030264817149989E-2</v>
+            <v>-4.255392579810191E-2</v>
           </cell>
           <cell r="H41" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="42">
           <cell r="F42">
-            <v>46.153846153846153</v>
+            <v>44</v>
           </cell>
           <cell r="G42">
-            <v>-7.5241698192517803E-2</v>
+            <v>-0.11839708561020035</v>
           </cell>
           <cell r="H42" t="str">
             <v>BAJO</v>
@@ -820,10 +826,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>93.307692307692307</v>
+            <v>85.4</v>
           </cell>
           <cell r="G43">
-            <v>0.17502531812777944</v>
+            <v>7.5443617630223336E-2</v>
           </cell>
           <cell r="H43" t="str">
             <v>SUBIÓ</v>
@@ -831,10 +837,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>51.384615384615387</v>
+            <v>48</v>
           </cell>
           <cell r="G44">
-            <v>0.49928586002856568</v>
+            <v>0.40053050397877987</v>
           </cell>
           <cell r="H44" t="str">
             <v>SUBIÓ</v>
@@ -842,10 +848,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>40.92307692307692</v>
+            <v>39.799999999999997</v>
           </cell>
           <cell r="G45">
-            <v>9.1282051282051135E-2</v>
+            <v>6.133333333333324E-2</v>
           </cell>
           <cell r="H45" t="str">
             <v>SUBIÓ</v>
@@ -853,10 +859,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>0</v>
+            <v>0.13333333333333333</v>
           </cell>
           <cell r="G46">
-            <v>-1</v>
+            <v>-0.83703703703703702</v>
           </cell>
           <cell r="H46" t="str">
             <v>BAJO</v>
@@ -864,10 +870,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>2.0769230769230771</v>
+            <v>2.8</v>
           </cell>
           <cell r="G47">
-            <v>-0.36538461538461542</v>
+            <v>-0.1444444444444446</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -1130,11 +1136,11 @@
       </c>
       <c r="E2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1148.6923076923076</v>
+        <v>1170.7333333333333</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>2.6951835550665271E-2</v>
+        <v>4.6656913740789063E-2</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1159,11 +1165,11 @@
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>83.307692307692307</v>
+        <v>81.466666666666669</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>6.8670105404799342E-2</v>
+        <v>4.5053449951409252E-2</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1188,11 +1194,11 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>466.84615384615387</v>
+        <v>491.4</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-0.14731296101159108</v>
+        <v>-0.10246575342465758</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1217,11 +1223,11 @@
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>90.84615384615384</v>
+        <v>95.066666666666663</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>-7.0843614776669228E-2</v>
+        <v>-2.7677049434371548E-2</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1246,11 +1252,11 @@
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>10.076923076923077</v>
+        <v>11.866666666666667</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>-0.39593376650597367</v>
+        <v>-0.28864668483197098</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1275,11 +1281,11 @@
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1362.4615384615386</v>
+        <v>1399.9333333333334</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>5.2167714341261107E-2</v>
+        <v>8.1105494711223525E-2</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1304,11 +1310,11 @@
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>140.07692307692307</v>
+        <v>149.4</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>0.14646291208791196</v>
+        <v>0.22276785714285707</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1333,11 +1339,11 @@
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>324.53846153846155</v>
+        <v>320.93333333333334</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>6.8519328621094555E-2</v>
+        <v>5.6649705676943052E-2</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1362,11 +1368,11 @@
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>728.30769230769226</v>
+        <v>720.2</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>0.10016267720195215</v>
+        <v>8.7915407854984862E-2</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1391,11 +1397,11 @@
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>344.61538461538464</v>
+        <v>339.4</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.14957504637818708</v>
+        <v>-0.1624453168816602</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1420,11 +1426,11 @@
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3577.3076923076924</v>
+        <v>3515.8</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>0.10069466484062084</v>
+        <v>8.1769485741458148E-2</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1449,11 +1455,11 @@
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2352.7692307692309</v>
+        <v>2287.9333333333334</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>7.9972522886894604E-2</v>
+        <v>5.0211428253491341E-2</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1478,11 +1484,11 @@
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2278.6153846153848</v>
+        <v>2236.6</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>5.3672827928755273E-2</v>
+        <v>3.424415671767278E-2</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1507,11 +1513,11 @@
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2733.2307692307691</v>
+        <v>2663.0666666666666</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>0.13662886647405492</v>
+        <v>0.10745074318406656</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1536,11 +1542,11 @@
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>30.153846153846153</v>
+        <v>26.4</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.77351156866349768</v>
+        <v>-0.80170706725844998</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1565,11 +1571,11 @@
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>232.92307692307693</v>
+        <v>234.66666666666666</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>3.1255321454556784E-2</v>
+        <v>3.8974978198161869E-2</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1594,11 +1600,11 @@
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>136.23076923076923</v>
+        <v>132.66666666666666</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>-7.895607772682145E-2</v>
+        <v>-0.10305265314484746</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1623,11 +1629,11 @@
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>504.07692307692309</v>
+        <v>498.33333333333331</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>3.5935759709697201E-2</v>
+        <v>2.4132025533240009E-2</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1652,11 +1658,11 @@
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>782.46153846153845</v>
+        <v>780.4666666666667</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-1.7513050273737396E-2</v>
+        <v>-2.0017883301942319E-2</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1681,11 +1687,11 @@
       </c>
       <c r="E21" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>7.6923076923076925</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="F21" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>0.53846153846153855</v>
+        <v>0.33333333333333348</v>
       </c>
       <c r="G21" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
@@ -1710,11 +1716,11 @@
       </c>
       <c r="E22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>131.07692307692307</v>
+        <v>120.26666666666667</v>
       </c>
       <c r="F22" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>1.6651500071093417</v>
+        <v>1.4453481207640175</v>
       </c>
       <c r="G22" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1739,15 +1745,15 @@
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>640.92307692307691</v>
+        <v>696.73333333333335</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-6.3973201519670009E-2</v>
+        <v>1.7534076827757206E-2</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H23">
         <v>1.63</v>
@@ -1768,15 +1774,15 @@
       </c>
       <c r="E24" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>1064.3076923076924</v>
+        <v>1211.7333333333333</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-4.0810731605864792E-2</v>
+        <v>9.2054128603225482E-2</v>
       </c>
       <c r="G24" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H24">
         <v>1.63</v>
@@ -1797,11 +1803,11 @@
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>502.07692307692309</v>
+        <v>510.86666666666667</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>3.9692423540315103E-2</v>
+        <v>5.7894076305220921E-2</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1826,11 +1832,11 @@
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>356.07692307692309</v>
+        <v>357.4</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-2.8198448369643025E-2</v>
+        <v>-2.45875201587894E-2</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1855,11 +1861,11 @@
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>127.69230769230769</v>
+        <v>118.86666666666666</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>0.19287930752898896</v>
+        <v>0.11043170559094118</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1884,11 +1890,11 @@
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>130.38461538461539</v>
+        <v>132.93333333333334</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>6.3969413375941642E-2</v>
+        <v>8.4767556874381755E-2</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1913,11 +1919,11 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>609.69230769230774</v>
+        <v>593.13333333333333</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-0.22894741496718962</v>
+        <v>-0.24988886334023153</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1942,15 +1948,15 @@
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>652.23076923076928</v>
+        <v>634.4666666666667</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>1.0518294319048493E-3</v>
+        <v>-2.621273429142823E-2</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H30">
         <v>1.1599999999999999</v>
@@ -1971,11 +1977,11 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>830.61538461538464</v>
+        <v>841.6</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-1.4265915333991686E-2</v>
+        <v>-1.2299061387419652E-3</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2000,15 +2006,15 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>575.30769230769226</v>
+        <v>560.66666666666663</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>5.1436809696021601E-3</v>
+        <v>-2.0436255823803595E-2</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H32">
         <v>1.1599999999999999</v>
@@ -2029,11 +2035,11 @@
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>48.769230769230766</v>
+        <v>78.733333333333334</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-0.77054681845101003</v>
+        <v>-0.62956943256344444</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2058,11 +2064,11 @@
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>563.38461538461536</v>
+        <v>509.86666666666667</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>0.93301022121982813</v>
+        <v>0.74938656685381577</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2087,11 +2093,11 @@
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>54.769230769230766</v>
+        <v>47.466666666666669</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.85364714236328476</v>
+        <v>-0.87316085671484678</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2116,11 +2122,11 @@
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>296.38461538461536</v>
+        <v>286.53333333333336</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>8.5838724140139488E-2</v>
+        <v>4.9747432694976501E-2</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2145,11 +2151,11 @@
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>509.30769230769232</v>
+        <v>476.6</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.2114573716909105</v>
+        <v>0.13365769272353756</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2174,11 +2180,11 @@
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>303.30769230769232</v>
+        <v>284.06666666666666</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>0.23068410748233692</v>
+        <v>0.1526128120004917</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2203,15 +2209,15 @@
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>271.84615384615387</v>
+        <v>252.2</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>3.2030264817149989E-2</v>
+        <v>-4.255392579810191E-2</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H39">
         <v>0.81</v>
@@ -2232,11 +2238,11 @@
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>46.153846153846153</v>
+        <v>44</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>-7.5241698192517803E-2</v>
+        <v>-0.11839708561020035</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2261,11 +2267,11 @@
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>93.307692307692307</v>
+        <v>85.4</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>0.17502531812777944</v>
+        <v>7.5443617630223336E-2</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2290,11 +2296,11 @@
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>51.384615384615387</v>
+        <v>48</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>0.49928586002856568</v>
+        <v>0.40053050397877987</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2319,11 +2325,11 @@
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>40.92307692307692</v>
+        <v>39.799999999999997</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>9.1282051282051135E-2</v>
+        <v>6.133333333333324E-2</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2348,11 +2354,11 @@
       </c>
       <c r="E44" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>0</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-1</v>
+        <v>-0.83703703703703702</v>
       </c>
       <c r="G44" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
@@ -2377,11 +2383,11 @@
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>2.0769230769230771</v>
+        <v>2.8</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.36538461538461542</v>
+        <v>-0.1444444444444446</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE4FE7FA-5BC4-4D78-9967-16C5395E4FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A18A7A0-0335-480C-A56C-FFBD8EB44A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -370,6 +370,7 @@
       <sheetName val="INVENTARIO NACIONAL 20-08-26-2"/>
       <sheetName val="INVENTARIO NACIONAL 21-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 24-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 25-08-26"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -394,13 +395,14 @@
       <sheetData sheetId="16"/>
       <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
-      <sheetData sheetId="19">
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20">
         <row r="4">
           <cell r="F4">
-            <v>1170.7333333333333</v>
+            <v>1168.4375</v>
           </cell>
           <cell r="G4">
-            <v>4.6656913740789063E-2</v>
+            <v>4.4604396944083247E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -408,21 +410,21 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>81.466666666666669</v>
+            <v>76.9375</v>
           </cell>
           <cell r="G5">
-            <v>4.5053449951409252E-2</v>
+            <v>-1.3046647230320674E-2</v>
           </cell>
           <cell r="H5" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="6">
           <cell r="F6">
-            <v>491.4</v>
+            <v>492.125</v>
           </cell>
           <cell r="G6">
-            <v>-0.10246575342465758</v>
+            <v>-0.10114155251141554</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -430,10 +432,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>95.066666666666663</v>
+            <v>89.3125</v>
           </cell>
           <cell r="G7">
-            <v>-2.7677049434371548E-2</v>
+            <v>-8.6529521152952094E-2</v>
           </cell>
           <cell r="H7" t="str">
             <v>BAJO</v>
@@ -441,10 +443,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>11.866666666666667</v>
+            <v>10.9375</v>
           </cell>
           <cell r="G8">
-            <v>-0.28864668483197098</v>
+            <v>-0.3443460490463216</v>
           </cell>
           <cell r="H8" t="str">
             <v>BAJO</v>
@@ -452,10 +454,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1399.9333333333334</v>
+            <v>1422.8125</v>
           </cell>
           <cell r="G9">
-            <v>8.1105494711223525E-2</v>
+            <v>9.8774045212018935E-2</v>
           </cell>
           <cell r="H9" t="str">
             <v>SUBIÓ</v>
@@ -463,10 +465,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>149.4</v>
+            <v>144.8125</v>
           </cell>
           <cell r="G10">
-            <v>0.22276785714285707</v>
+            <v>0.18522135416666652</v>
           </cell>
           <cell r="H10" t="str">
             <v>SUBIÓ</v>
@@ -474,10 +476,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>320.93333333333334</v>
+            <v>313.25</v>
           </cell>
           <cell r="G11">
-            <v>5.6649705676943052E-2</v>
+            <v>3.1352888356779296E-2</v>
           </cell>
           <cell r="H11" t="str">
             <v>SUBIÓ</v>
@@ -485,10 +487,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>720.2</v>
+            <v>713.625</v>
           </cell>
           <cell r="G12">
-            <v>8.7915407854984862E-2</v>
+            <v>7.79833836858006E-2</v>
           </cell>
           <cell r="H12" t="str">
             <v>SUBIÓ</v>
@@ -496,10 +498,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>339.4</v>
+            <v>331.375</v>
           </cell>
           <cell r="G13">
-            <v>-0.1624453168816602</v>
+            <v>-0.18224901850813235</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -507,10 +509,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3515.8</v>
+            <v>3495.4375</v>
           </cell>
           <cell r="G14">
-            <v>8.1769485741458148E-2</v>
+            <v>7.5504188752604895E-2</v>
           </cell>
           <cell r="H14" t="str">
             <v>SUBIÓ</v>
@@ -518,10 +520,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2287.9333333333334</v>
+            <v>2279.5625</v>
           </cell>
           <cell r="G15">
-            <v>5.0211428253491341E-2</v>
+            <v>4.6369032715740222E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>SUBIÓ</v>
@@ -529,10 +531,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2236.6</v>
+            <v>2222.9375</v>
           </cell>
           <cell r="G16">
-            <v>3.424415671767278E-2</v>
+            <v>2.7926370438876802E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>SUBIÓ</v>
@@ -540,10 +542,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2663.0666666666666</v>
+            <v>2633.875</v>
           </cell>
           <cell r="G17">
-            <v>0.10745074318406656</v>
+            <v>9.5311229986957402E-2</v>
           </cell>
           <cell r="H17" t="str">
             <v>SUBIÓ</v>
@@ -551,10 +553,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>26.4</v>
+            <v>21.25</v>
           </cell>
           <cell r="G18">
-            <v>-0.80170706725844998</v>
+            <v>-0.84038921133492661</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -562,21 +564,21 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>234.66666666666666</v>
+            <v>225.6875</v>
           </cell>
           <cell r="G19">
-            <v>3.8974978198161869E-2</v>
+            <v>-7.7983497685651937E-4</v>
           </cell>
           <cell r="H19" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="20">
           <cell r="F20">
-            <v>132.66666666666666</v>
+            <v>130.375</v>
           </cell>
           <cell r="G20">
-            <v>-0.10305265314484746</v>
+            <v>-0.11854640442532272</v>
           </cell>
           <cell r="H20" t="str">
             <v>BAJO</v>
@@ -584,10 +586,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>498.33333333333331</v>
+            <v>489.75</v>
           </cell>
           <cell r="G21">
-            <v>2.4132025533240009E-2</v>
+            <v>6.4922933208781952E-3</v>
           </cell>
           <cell r="H21" t="str">
             <v>SUBIÓ</v>
@@ -595,10 +597,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>780.4666666666667</v>
+            <v>773.375</v>
           </cell>
           <cell r="G22">
-            <v>-2.0017883301942319E-2</v>
+            <v>-2.8922435934021995E-2</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -606,21 +608,21 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>6.666666666666667</v>
+            <v>0</v>
           </cell>
           <cell r="G23">
-            <v>0.33333333333333348</v>
+            <v>-1</v>
           </cell>
           <cell r="H23" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="24">
           <cell r="F24">
-            <v>120.26666666666667</v>
+            <v>77.25</v>
           </cell>
           <cell r="G24">
-            <v>1.4453481207640175</v>
+            <v>0.57070240295748609</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -628,10 +630,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>696.73333333333335</v>
+            <v>718</v>
           </cell>
           <cell r="G25">
-            <v>1.7534076827757206E-2</v>
+            <v>4.8592671269251264E-2</v>
           </cell>
           <cell r="H25" t="str">
             <v>SUBIÓ</v>
@@ -639,10 +641,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>1211.7333333333333</v>
+            <v>1191.375</v>
           </cell>
           <cell r="G26">
-            <v>9.2054128603225482E-2</v>
+            <v>7.3706525746589646E-2</v>
           </cell>
           <cell r="H26" t="str">
             <v>SUBIÓ</v>
@@ -650,10 +652,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>510.86666666666667</v>
+            <v>508.3125</v>
           </cell>
           <cell r="G27">
-            <v>5.7894076305220921E-2</v>
+            <v>5.2604951054216809E-2</v>
           </cell>
           <cell r="H27" t="str">
             <v>SUBIÓ</v>
@@ -661,21 +663,21 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>357.4</v>
+            <v>373.9375</v>
           </cell>
           <cell r="G28">
-            <v>-2.45875201587894E-2</v>
+            <v>2.0546458255799482E-2</v>
           </cell>
           <cell r="H28" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="29">
           <cell r="F29">
-            <v>118.86666666666666</v>
+            <v>114.1875</v>
           </cell>
           <cell r="G29">
-            <v>0.11043170559094118</v>
+            <v>6.6719745222930005E-2</v>
           </cell>
           <cell r="H29" t="str">
             <v>SUBIÓ</v>
@@ -683,10 +685,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>132.93333333333334</v>
+            <v>131.4375</v>
           </cell>
           <cell r="G30">
-            <v>8.4767556874381755E-2</v>
+            <v>7.2561201780415363E-2</v>
           </cell>
           <cell r="H30" t="str">
             <v>SUBIÓ</v>
@@ -694,10 +696,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>593.13333333333333</v>
+            <v>596.6875</v>
           </cell>
           <cell r="G31">
-            <v>-0.24988886334023153</v>
+            <v>-0.24539405610485165</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -705,10 +707,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>634.4666666666667</v>
+            <v>623.5625</v>
           </cell>
           <cell r="G32">
-            <v>-2.621273429142823E-2</v>
+            <v>-4.2948583786800554E-2</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -716,10 +718,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>841.6</v>
+            <v>827.9375</v>
           </cell>
           <cell r="G33">
-            <v>-1.2299061387419652E-3</v>
+            <v>-1.7443899018232845E-2</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -727,10 +729,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>560.66666666666663</v>
+            <v>557.1875</v>
           </cell>
           <cell r="G34">
-            <v>-2.0436255823803595E-2</v>
+            <v>-2.6514850698856396E-2</v>
           </cell>
           <cell r="H34" t="str">
             <v>BAJO</v>
@@ -738,10 +740,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>78.733333333333334</v>
+            <v>87</v>
           </cell>
           <cell r="G35">
-            <v>-0.62956943256344444</v>
+            <v>-0.59067579127459369</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -749,10 +751,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>509.86666666666667</v>
+            <v>496.5625</v>
           </cell>
           <cell r="G36">
-            <v>0.74938656685381577</v>
+            <v>0.70373908296943233</v>
           </cell>
           <cell r="H36" t="str">
             <v>SUBIÓ</v>
@@ -760,10 +762,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>47.466666666666669</v>
+            <v>41.5625</v>
           </cell>
           <cell r="G37">
-            <v>-0.87316085671484678</v>
+            <v>-0.88893781124741889</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -771,10 +773,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>286.53333333333336</v>
+            <v>287.125</v>
           </cell>
           <cell r="G38">
-            <v>4.9747432694976501E-2</v>
+            <v>5.1915070774354755E-2</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -782,10 +784,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>476.6</v>
+            <v>482.6875</v>
           </cell>
           <cell r="G39">
-            <v>0.13365769272353756</v>
+            <v>0.14813763650124323</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -793,10 +795,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>284.06666666666666</v>
+            <v>284.6875</v>
           </cell>
           <cell r="G40">
-            <v>0.1526128120004917</v>
+            <v>0.15513187015861307</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -804,10 +806,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>252.2</v>
+            <v>256.375</v>
           </cell>
           <cell r="G41">
-            <v>-4.255392579810191E-2</v>
+            <v>-2.6704055220017398E-2</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -815,10 +817,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>44</v>
+            <v>47.1875</v>
           </cell>
           <cell r="G42">
-            <v>-0.11839708561020035</v>
+            <v>-5.4530965391621056E-2</v>
           </cell>
           <cell r="H42" t="str">
             <v>BAJO</v>
@@ -826,10 +828,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>85.4</v>
+            <v>92.25</v>
           </cell>
           <cell r="G43">
-            <v>7.5443617630223336E-2</v>
+            <v>0.16170578133943914</v>
           </cell>
           <cell r="H43" t="str">
             <v>SUBIÓ</v>
@@ -837,10 +839,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>48</v>
+            <v>49.3125</v>
           </cell>
           <cell r="G44">
-            <v>0.40053050397877987</v>
+            <v>0.43882625994694968</v>
           </cell>
           <cell r="H44" t="str">
             <v>SUBIÓ</v>
@@ -848,10 +850,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>39.799999999999997</v>
+            <v>42.1875</v>
           </cell>
           <cell r="G45">
-            <v>6.133333333333324E-2</v>
+            <v>0.125</v>
           </cell>
           <cell r="H45" t="str">
             <v>SUBIÓ</v>
@@ -859,10 +861,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>0.13333333333333333</v>
+            <v>0.5</v>
           </cell>
           <cell r="G46">
-            <v>-0.83703703703703702</v>
+            <v>-0.38888888888888895</v>
           </cell>
           <cell r="H46" t="str">
             <v>BAJO</v>
@@ -870,10 +872,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>2.8</v>
+            <v>2.625</v>
           </cell>
           <cell r="G47">
-            <v>-0.1444444444444446</v>
+            <v>-0.19791666666666674</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -1136,11 +1138,11 @@
       </c>
       <c r="E2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1170.7333333333333</v>
+        <v>1168.4375</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>4.6656913740789063E-2</v>
+        <v>4.4604396944083247E-2</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1165,15 +1167,15 @@
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>81.466666666666669</v>
+        <v>76.9375</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>4.5053449951409252E-2</v>
+        <v>-1.3046647230320674E-2</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H3">
         <v>1.59</v>
@@ -1194,11 +1196,11 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>491.4</v>
+        <v>492.125</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-0.10246575342465758</v>
+        <v>-0.10114155251141554</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1223,11 +1225,11 @@
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>95.066666666666663</v>
+        <v>89.3125</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>-2.7677049434371548E-2</v>
+        <v>-8.6529521152952094E-2</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1252,11 +1254,11 @@
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>11.866666666666667</v>
+        <v>10.9375</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>-0.28864668483197098</v>
+        <v>-0.3443460490463216</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1281,11 +1283,11 @@
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1399.9333333333334</v>
+        <v>1422.8125</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>8.1105494711223525E-2</v>
+        <v>9.8774045212018935E-2</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1310,11 +1312,11 @@
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>149.4</v>
+        <v>144.8125</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>0.22276785714285707</v>
+        <v>0.18522135416666652</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1339,11 +1341,11 @@
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>320.93333333333334</v>
+        <v>313.25</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>5.6649705676943052E-2</v>
+        <v>3.1352888356779296E-2</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1368,11 +1370,11 @@
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>720.2</v>
+        <v>713.625</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>8.7915407854984862E-2</v>
+        <v>7.79833836858006E-2</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1397,11 +1399,11 @@
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>339.4</v>
+        <v>331.375</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.1624453168816602</v>
+        <v>-0.18224901850813235</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1426,11 +1428,11 @@
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3515.8</v>
+        <v>3495.4375</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>8.1769485741458148E-2</v>
+        <v>7.5504188752604895E-2</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1455,11 +1457,11 @@
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2287.9333333333334</v>
+        <v>2279.5625</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>5.0211428253491341E-2</v>
+        <v>4.6369032715740222E-2</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1484,11 +1486,11 @@
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2236.6</v>
+        <v>2222.9375</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>3.424415671767278E-2</v>
+        <v>2.7926370438876802E-2</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1513,11 +1515,11 @@
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2663.0666666666666</v>
+        <v>2633.875</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>0.10745074318406656</v>
+        <v>9.5311229986957402E-2</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1542,11 +1544,11 @@
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>26.4</v>
+        <v>21.25</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.80170706725844998</v>
+        <v>-0.84038921133492661</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1571,15 +1573,15 @@
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>234.66666666666666</v>
+        <v>225.6875</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>3.8974978198161869E-2</v>
+        <v>-7.7983497685651937E-4</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H17">
         <v>3.68</v>
@@ -1600,11 +1602,11 @@
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>132.66666666666666</v>
+        <v>130.375</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>-0.10305265314484746</v>
+        <v>-0.11854640442532272</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1629,11 +1631,11 @@
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>498.33333333333331</v>
+        <v>489.75</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>2.4132025533240009E-2</v>
+        <v>6.4922933208781952E-3</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1658,11 +1660,11 @@
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>780.4666666666667</v>
+        <v>773.375</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-2.0017883301942319E-2</v>
+        <v>-2.8922435934021995E-2</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1687,15 +1689,15 @@
       </c>
       <c r="E21" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>6.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="F21" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>0.33333333333333348</v>
+        <v>-1</v>
       </c>
       <c r="G21" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H21">
         <v>4.1500000000000004</v>
@@ -1716,11 +1718,11 @@
       </c>
       <c r="E22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>120.26666666666667</v>
+        <v>77.25</v>
       </c>
       <c r="F22" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>1.4453481207640175</v>
+        <v>0.57070240295748609</v>
       </c>
       <c r="G22" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1745,11 +1747,11 @@
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>696.73333333333335</v>
+        <v>718</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>1.7534076827757206E-2</v>
+        <v>4.8592671269251264E-2</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1774,11 +1776,11 @@
       </c>
       <c r="E24" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>1211.7333333333333</v>
+        <v>1191.375</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>9.2054128603225482E-2</v>
+        <v>7.3706525746589646E-2</v>
       </c>
       <c r="G24" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1803,11 +1805,11 @@
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>510.86666666666667</v>
+        <v>508.3125</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>5.7894076305220921E-2</v>
+        <v>5.2604951054216809E-2</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1832,15 +1834,15 @@
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>357.4</v>
+        <v>373.9375</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-2.45875201587894E-2</v>
+        <v>2.0546458255799482E-2</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H26">
         <v>1.63</v>
@@ -1861,11 +1863,11 @@
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>118.86666666666666</v>
+        <v>114.1875</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>0.11043170559094118</v>
+        <v>6.6719745222930005E-2</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1890,11 +1892,11 @@
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>132.93333333333334</v>
+        <v>131.4375</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>8.4767556874381755E-2</v>
+        <v>7.2561201780415363E-2</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1919,11 +1921,11 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>593.13333333333333</v>
+        <v>596.6875</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-0.24988886334023153</v>
+        <v>-0.24539405610485165</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1948,11 +1950,11 @@
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>634.4666666666667</v>
+        <v>623.5625</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-2.621273429142823E-2</v>
+        <v>-4.2948583786800554E-2</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1977,11 +1979,11 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>841.6</v>
+        <v>827.9375</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-1.2299061387419652E-3</v>
+        <v>-1.7443899018232845E-2</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2006,11 +2008,11 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>560.66666666666663</v>
+        <v>557.1875</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-2.0436255823803595E-2</v>
+        <v>-2.6514850698856396E-2</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2035,11 +2037,11 @@
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>78.733333333333334</v>
+        <v>87</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-0.62956943256344444</v>
+        <v>-0.59067579127459369</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2064,11 +2066,11 @@
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>509.86666666666667</v>
+        <v>496.5625</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>0.74938656685381577</v>
+        <v>0.70373908296943233</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2093,11 +2095,11 @@
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>47.466666666666669</v>
+        <v>41.5625</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.87316085671484678</v>
+        <v>-0.88893781124741889</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2122,11 +2124,11 @@
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>286.53333333333336</v>
+        <v>287.125</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>4.9747432694976501E-2</v>
+        <v>5.1915070774354755E-2</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2151,11 +2153,11 @@
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>476.6</v>
+        <v>482.6875</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.13365769272353756</v>
+        <v>0.14813763650124323</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2180,11 +2182,11 @@
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>284.06666666666666</v>
+        <v>284.6875</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>0.1526128120004917</v>
+        <v>0.15513187015861307</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2209,11 +2211,11 @@
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>252.2</v>
+        <v>256.375</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-4.255392579810191E-2</v>
+        <v>-2.6704055220017398E-2</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2238,11 +2240,11 @@
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>44</v>
+        <v>47.1875</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>-0.11839708561020035</v>
+        <v>-5.4530965391621056E-2</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2267,11 +2269,11 @@
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>85.4</v>
+        <v>92.25</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>7.5443617630223336E-2</v>
+        <v>0.16170578133943914</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2296,11 +2298,11 @@
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>48</v>
+        <v>49.3125</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>0.40053050397877987</v>
+        <v>0.43882625994694968</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2325,11 +2327,11 @@
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>39.799999999999997</v>
+        <v>42.1875</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>6.133333333333324E-2</v>
+        <v>0.125</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2354,11 +2356,11 @@
       </c>
       <c r="E44" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>0.13333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-0.83703703703703702</v>
+        <v>-0.38888888888888895</v>
       </c>
       <c r="G44" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
@@ -2383,11 +2385,11 @@
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>2.8</v>
+        <v>2.625</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.1444444444444446</v>
+        <v>-0.19791666666666674</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A18A7A0-0335-480C-A56C-FFBD8EB44A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8747C699-81BC-491B-931C-3FECFC60E2DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -371,6 +371,7 @@
       <sheetName val="INVENTARIO NACIONAL 21-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 24-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 25-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 25-08-26-2"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -396,13 +397,14 @@
       <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
-      <sheetData sheetId="20">
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21">
         <row r="4">
           <cell r="F4">
-            <v>1168.4375</v>
+            <v>1164.8235294117646</v>
           </cell>
           <cell r="G4">
-            <v>4.4604396944083247E-2</v>
+            <v>4.1373441444197967E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -410,10 +412,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>76.9375</v>
+            <v>72.882352941176464</v>
           </cell>
           <cell r="G5">
-            <v>-1.3046647230320674E-2</v>
+            <v>-6.5066026410564248E-2</v>
           </cell>
           <cell r="H5" t="str">
             <v>BAJO</v>
@@ -421,10 +423,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>492.125</v>
+            <v>485</v>
           </cell>
           <cell r="G6">
-            <v>-0.10114155251141554</v>
+            <v>-0.11415525114155256</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -432,10 +434,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>89.3125</v>
+            <v>87.411764705882348</v>
           </cell>
           <cell r="G7">
-            <v>-8.6529521152952094E-2</v>
+            <v>-0.10596986353816285</v>
           </cell>
           <cell r="H7" t="str">
             <v>BAJO</v>
@@ -443,10 +445,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>10.9375</v>
+            <v>11.176470588235293</v>
           </cell>
           <cell r="G8">
-            <v>-0.3443460490463216</v>
+            <v>-0.33002083667254378</v>
           </cell>
           <cell r="H8" t="str">
             <v>BAJO</v>
@@ -454,10 +456,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1422.8125</v>
+            <v>1418.1764705882354</v>
           </cell>
           <cell r="G9">
-            <v>9.8774045212018935E-2</v>
+            <v>9.5193848390240587E-2</v>
           </cell>
           <cell r="H9" t="str">
             <v>SUBIÓ</v>
@@ -465,10 +467,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>144.8125</v>
+            <v>143</v>
           </cell>
           <cell r="G10">
-            <v>0.18522135416666652</v>
+            <v>0.17038690476190466</v>
           </cell>
           <cell r="H10" t="str">
             <v>SUBIÓ</v>
@@ -476,10 +478,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>313.25</v>
+            <v>314</v>
           </cell>
           <cell r="G11">
-            <v>3.1352888356779296E-2</v>
+            <v>3.3822208919485064E-2</v>
           </cell>
           <cell r="H11" t="str">
             <v>SUBIÓ</v>
@@ -487,10 +489,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>713.625</v>
+            <v>723.47058823529414</v>
           </cell>
           <cell r="G12">
-            <v>7.79833836858006E-2</v>
+            <v>9.2855873467211802E-2</v>
           </cell>
           <cell r="H12" t="str">
             <v>SUBIÓ</v>
@@ -498,10 +500,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>331.375</v>
+            <v>342</v>
           </cell>
           <cell r="G13">
-            <v>-0.18224901850813235</v>
+            <v>-0.15602916432978131</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -509,10 +511,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3495.4375</v>
+            <v>3471.294117647059</v>
           </cell>
           <cell r="G14">
-            <v>7.5504188752604895E-2</v>
+            <v>6.807555961784173E-2</v>
           </cell>
           <cell r="H14" t="str">
             <v>SUBIÓ</v>
@@ -520,10 +522,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2279.5625</v>
+            <v>2253.4705882352941</v>
           </cell>
           <cell r="G15">
-            <v>4.6369032715740222E-2</v>
+            <v>3.4392274686539714E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>SUBIÓ</v>
@@ -531,10 +533,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2222.9375</v>
+            <v>2207.3529411764707</v>
           </cell>
           <cell r="G16">
-            <v>2.7926370438876802E-2</v>
+            <v>2.0719789513249376E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>SUBIÓ</v>
@@ -542,10 +544,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2633.875</v>
+            <v>2617.3529411764707</v>
           </cell>
           <cell r="G17">
-            <v>9.5311229986957402E-2</v>
+            <v>8.8440442052102108E-2</v>
           </cell>
           <cell r="H17" t="str">
             <v>SUBIÓ</v>
@@ -553,10 +555,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>21.25</v>
+            <v>18.882352941176471</v>
           </cell>
           <cell r="G18">
-            <v>-0.84038921133492661</v>
+            <v>-0.85817283553913204</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -564,21 +566,21 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>225.6875</v>
+            <v>227.05882352941177</v>
           </cell>
           <cell r="G19">
-            <v>-7.7983497685651937E-4</v>
+            <v>5.2916316456146362E-3</v>
           </cell>
           <cell r="H19" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="20">
           <cell r="F20">
-            <v>130.375</v>
+            <v>130.94117647058823</v>
           </cell>
           <cell r="G20">
-            <v>-0.11854640442532272</v>
+            <v>-0.1147185364619111</v>
           </cell>
           <cell r="H20" t="str">
             <v>BAJO</v>
@@ -586,10 +588,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>489.75</v>
+            <v>499.05882352941177</v>
           </cell>
           <cell r="G21">
-            <v>6.4922933208781952E-3</v>
+            <v>2.5622990905843857E-2</v>
           </cell>
           <cell r="H21" t="str">
             <v>SUBIÓ</v>
@@ -597,10 +599,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>773.375</v>
+            <v>788.52941176470586</v>
           </cell>
           <cell r="G22">
-            <v>-2.8922435934021995E-2</v>
+            <v>-9.8940095414913332E-3</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -619,10 +621,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>77.25</v>
+            <v>73.882352941176464</v>
           </cell>
           <cell r="G24">
-            <v>0.57070240295748609</v>
+            <v>0.50222898771338476</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -630,10 +632,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>718</v>
+            <v>705.70588235294122</v>
           </cell>
           <cell r="G25">
-            <v>4.8592671269251264E-2</v>
+            <v>3.0637905719908876E-2</v>
           </cell>
           <cell r="H25" t="str">
             <v>SUBIÓ</v>
@@ -641,10 +643,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>1191.375</v>
+            <v>1158</v>
           </cell>
           <cell r="G26">
-            <v>7.3706525746589646E-2</v>
+            <v>4.3627872680349178E-2</v>
           </cell>
           <cell r="H26" t="str">
             <v>SUBIÓ</v>
@@ -652,10 +654,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>508.3125</v>
+            <v>507.29411764705884</v>
           </cell>
           <cell r="G27">
-            <v>5.2604951054216809E-2</v>
+            <v>5.0496102055279879E-2</v>
           </cell>
           <cell r="H27" t="str">
             <v>SUBIÓ</v>
@@ -663,10 +665,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>373.9375</v>
+            <v>384.58823529411762</v>
           </cell>
           <cell r="G28">
-            <v>2.0546458255799482E-2</v>
+            <v>4.9614337733604685E-2</v>
           </cell>
           <cell r="H28" t="str">
             <v>SUBIÓ</v>
@@ -674,10 +676,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>114.1875</v>
+            <v>113.70588235294117</v>
           </cell>
           <cell r="G29">
-            <v>6.6719745222930005E-2</v>
+            <v>6.2220557012613975E-2</v>
           </cell>
           <cell r="H29" t="str">
             <v>SUBIÓ</v>
@@ -685,10 +687,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>131.4375</v>
+            <v>130.47058823529412</v>
           </cell>
           <cell r="G30">
-            <v>7.2561201780415363E-2</v>
+            <v>6.4670972246465341E-2</v>
           </cell>
           <cell r="H30" t="str">
             <v>SUBIÓ</v>
@@ -696,10 +698,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>596.6875</v>
+            <v>608.41176470588232</v>
           </cell>
           <cell r="G31">
-            <v>-0.24539405610485165</v>
+            <v>-0.23056686459361864</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -707,10 +709,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>623.5625</v>
+            <v>619.76470588235293</v>
           </cell>
           <cell r="G32">
-            <v>-4.2948583786800554E-2</v>
+            <v>-4.8777485041735402E-2</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -718,10 +720,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>827.9375</v>
+            <v>821.82352941176475</v>
           </cell>
           <cell r="G33">
-            <v>-1.7443899018232845E-2</v>
+            <v>-2.4699663013333484E-2</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -729,10 +731,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>557.1875</v>
+            <v>553</v>
           </cell>
           <cell r="G34">
-            <v>-2.6514850698856396E-2</v>
+            <v>-3.3831003811944149E-2</v>
           </cell>
           <cell r="H34" t="str">
             <v>BAJO</v>
@@ -740,10 +742,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>87</v>
+            <v>106.88235294117646</v>
           </cell>
           <cell r="G35">
-            <v>-0.59067579127459369</v>
+            <v>-0.49713178684647508</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -751,10 +753,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>496.5625</v>
+            <v>500.52941176470586</v>
           </cell>
           <cell r="G36">
-            <v>0.70373908296943233</v>
+            <v>0.71734982202487974</v>
           </cell>
           <cell r="H36" t="str">
             <v>SUBIÓ</v>
@@ -762,10 +764,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>41.5625</v>
+            <v>38.705882352941174</v>
           </cell>
           <cell r="G37">
-            <v>-0.88893781124741889</v>
+            <v>-0.89657118768799882</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -773,10 +775,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>287.125</v>
+            <v>286.94117647058823</v>
           </cell>
           <cell r="G38">
-            <v>5.1915070774354755E-2</v>
+            <v>5.1241612381838664E-2</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -784,10 +786,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>482.6875</v>
+            <v>475.1764705882353</v>
           </cell>
           <cell r="G39">
-            <v>0.14813763650124323</v>
+            <v>0.13027163508932604</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -795,10 +797,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>284.6875</v>
+            <v>275.94117647058823</v>
           </cell>
           <cell r="G40">
-            <v>0.15513187015861307</v>
+            <v>0.11964328335539309</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -806,10 +808,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>256.375</v>
+            <v>252.70588235294119</v>
           </cell>
           <cell r="G41">
-            <v>-2.6704055220017398E-2</v>
+            <v>-4.0633406080292422E-2</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -817,10 +819,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>47.1875</v>
+            <v>48.647058823529413</v>
           </cell>
           <cell r="G42">
-            <v>-5.4530965391621056E-2</v>
+            <v>-2.5286617379192022E-2</v>
           </cell>
           <cell r="H42" t="str">
             <v>BAJO</v>
@@ -828,10 +830,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>92.25</v>
+            <v>92.82352941176471</v>
           </cell>
           <cell r="G43">
-            <v>0.16170578133943914</v>
+            <v>0.16892824674231455</v>
           </cell>
           <cell r="H43" t="str">
             <v>SUBIÓ</v>
@@ -839,10 +841,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>49.3125</v>
+            <v>49.647058823529413</v>
           </cell>
           <cell r="G44">
-            <v>0.43882625994694968</v>
+            <v>0.44858792323295371</v>
           </cell>
           <cell r="H44" t="str">
             <v>SUBIÓ</v>
@@ -850,10 +852,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>42.1875</v>
+            <v>42.176470588235297</v>
           </cell>
           <cell r="G45">
-            <v>0.125</v>
+            <v>0.12470588235294122</v>
           </cell>
           <cell r="H45" t="str">
             <v>SUBIÓ</v>
@@ -861,10 +863,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>0.5</v>
+            <v>0.52941176470588236</v>
           </cell>
           <cell r="G46">
-            <v>-0.38888888888888895</v>
+            <v>-0.35294117647058831</v>
           </cell>
           <cell r="H46" t="str">
             <v>BAJO</v>
@@ -872,10 +874,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>2.625</v>
+            <v>2.5882352941176472</v>
           </cell>
           <cell r="G47">
-            <v>-0.19791666666666674</v>
+            <v>-0.20915032679738566</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -1138,11 +1140,11 @@
       </c>
       <c r="E2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1168.4375</v>
+        <v>1164.8235294117646</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>4.4604396944083247E-2</v>
+        <v>4.1373441444197967E-2</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1167,11 +1169,11 @@
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>76.9375</v>
+        <v>72.882352941176464</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-1.3046647230320674E-2</v>
+        <v>-6.5066026410564248E-2</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1196,11 +1198,11 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>492.125</v>
+        <v>485</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-0.10114155251141554</v>
+        <v>-0.11415525114155256</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1225,11 +1227,11 @@
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>89.3125</v>
+        <v>87.411764705882348</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>-8.6529521152952094E-2</v>
+        <v>-0.10596986353816285</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1254,11 +1256,11 @@
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>10.9375</v>
+        <v>11.176470588235293</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>-0.3443460490463216</v>
+        <v>-0.33002083667254378</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1283,11 +1285,11 @@
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1422.8125</v>
+        <v>1418.1764705882354</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>9.8774045212018935E-2</v>
+        <v>9.5193848390240587E-2</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1312,11 +1314,11 @@
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>144.8125</v>
+        <v>143</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>0.18522135416666652</v>
+        <v>0.17038690476190466</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1341,11 +1343,11 @@
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>313.25</v>
+        <v>314</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>3.1352888356779296E-2</v>
+        <v>3.3822208919485064E-2</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1370,11 +1372,11 @@
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>713.625</v>
+        <v>723.47058823529414</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>7.79833836858006E-2</v>
+        <v>9.2855873467211802E-2</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1399,11 +1401,11 @@
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>331.375</v>
+        <v>342</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.18224901850813235</v>
+        <v>-0.15602916432978131</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1428,11 +1430,11 @@
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3495.4375</v>
+        <v>3471.294117647059</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>7.5504188752604895E-2</v>
+        <v>6.807555961784173E-2</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1457,11 +1459,11 @@
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2279.5625</v>
+        <v>2253.4705882352941</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>4.6369032715740222E-2</v>
+        <v>3.4392274686539714E-2</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1486,11 +1488,11 @@
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2222.9375</v>
+        <v>2207.3529411764707</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>2.7926370438876802E-2</v>
+        <v>2.0719789513249376E-2</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1515,11 +1517,11 @@
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2633.875</v>
+        <v>2617.3529411764707</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>9.5311229986957402E-2</v>
+        <v>8.8440442052102108E-2</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1544,11 +1546,11 @@
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>21.25</v>
+        <v>18.882352941176471</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.84038921133492661</v>
+        <v>-0.85817283553913204</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1573,15 +1575,15 @@
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>225.6875</v>
+        <v>227.05882352941177</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>-7.7983497685651937E-4</v>
+        <v>5.2916316456146362E-3</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H17">
         <v>3.68</v>
@@ -1602,11 +1604,11 @@
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>130.375</v>
+        <v>130.94117647058823</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>-0.11854640442532272</v>
+        <v>-0.1147185364619111</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1631,11 +1633,11 @@
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>489.75</v>
+        <v>499.05882352941177</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>6.4922933208781952E-3</v>
+        <v>2.5622990905843857E-2</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1660,11 +1662,11 @@
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>773.375</v>
+        <v>788.52941176470586</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-2.8922435934021995E-2</v>
+        <v>-9.8940095414913332E-3</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1718,11 +1720,11 @@
       </c>
       <c r="E22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>77.25</v>
+        <v>73.882352941176464</v>
       </c>
       <c r="F22" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>0.57070240295748609</v>
+        <v>0.50222898771338476</v>
       </c>
       <c r="G22" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1747,11 +1749,11 @@
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>718</v>
+        <v>705.70588235294122</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>4.8592671269251264E-2</v>
+        <v>3.0637905719908876E-2</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1776,11 +1778,11 @@
       </c>
       <c r="E24" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>1191.375</v>
+        <v>1158</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>7.3706525746589646E-2</v>
+        <v>4.3627872680349178E-2</v>
       </c>
       <c r="G24" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1805,11 +1807,11 @@
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>508.3125</v>
+        <v>507.29411764705884</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>5.2604951054216809E-2</v>
+        <v>5.0496102055279879E-2</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1834,11 +1836,11 @@
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>373.9375</v>
+        <v>384.58823529411762</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>2.0546458255799482E-2</v>
+        <v>4.9614337733604685E-2</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1863,11 +1865,11 @@
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>114.1875</v>
+        <v>113.70588235294117</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>6.6719745222930005E-2</v>
+        <v>6.2220557012613975E-2</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1892,11 +1894,11 @@
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>131.4375</v>
+        <v>130.47058823529412</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>7.2561201780415363E-2</v>
+        <v>6.4670972246465341E-2</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1921,11 +1923,11 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>596.6875</v>
+        <v>608.41176470588232</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-0.24539405610485165</v>
+        <v>-0.23056686459361864</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1950,11 +1952,11 @@
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>623.5625</v>
+        <v>619.76470588235293</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-4.2948583786800554E-2</v>
+        <v>-4.8777485041735402E-2</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1979,11 +1981,11 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>827.9375</v>
+        <v>821.82352941176475</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-1.7443899018232845E-2</v>
+        <v>-2.4699663013333484E-2</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2008,11 +2010,11 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>557.1875</v>
+        <v>553</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-2.6514850698856396E-2</v>
+        <v>-3.3831003811944149E-2</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2037,11 +2039,11 @@
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>87</v>
+        <v>106.88235294117646</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-0.59067579127459369</v>
+        <v>-0.49713178684647508</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2066,11 +2068,11 @@
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>496.5625</v>
+        <v>500.52941176470586</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>0.70373908296943233</v>
+        <v>0.71734982202487974</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2095,11 +2097,11 @@
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>41.5625</v>
+        <v>38.705882352941174</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.88893781124741889</v>
+        <v>-0.89657118768799882</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2124,11 +2126,11 @@
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>287.125</v>
+        <v>286.94117647058823</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>5.1915070774354755E-2</v>
+        <v>5.1241612381838664E-2</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2153,11 +2155,11 @@
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>482.6875</v>
+        <v>475.1764705882353</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.14813763650124323</v>
+        <v>0.13027163508932604</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2182,11 +2184,11 @@
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>284.6875</v>
+        <v>275.94117647058823</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>0.15513187015861307</v>
+        <v>0.11964328335539309</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2211,11 +2213,11 @@
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>256.375</v>
+        <v>252.70588235294119</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-2.6704055220017398E-2</v>
+        <v>-4.0633406080292422E-2</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2240,11 +2242,11 @@
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>47.1875</v>
+        <v>48.647058823529413</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>-5.4530965391621056E-2</v>
+        <v>-2.5286617379192022E-2</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2269,11 +2271,11 @@
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>92.25</v>
+        <v>92.82352941176471</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>0.16170578133943914</v>
+        <v>0.16892824674231455</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2298,11 +2300,11 @@
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>49.3125</v>
+        <v>49.647058823529413</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>0.43882625994694968</v>
+        <v>0.44858792323295371</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2327,11 +2329,11 @@
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>42.1875</v>
+        <v>42.176470588235297</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>0.125</v>
+        <v>0.12470588235294122</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2356,11 +2358,11 @@
       </c>
       <c r="E44" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>0.5</v>
+        <v>0.52941176470588236</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-0.38888888888888895</v>
+        <v>-0.35294117647058831</v>
       </c>
       <c r="G44" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
@@ -2385,11 +2387,11 @@
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>2.625</v>
+        <v>2.5882352941176472</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.19791666666666674</v>
+        <v>-0.20915032679738566</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8747C699-81BC-491B-931C-3FECFC60E2DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08DAE008-4E32-4A59-B05D-1343527EBC8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -372,6 +372,8 @@
       <sheetName val="INVENTARIO NACIONAL 24-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 25-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 25-08-26-2"/>
+      <sheetName val="INVENTARIO NACIONAL 27-08-26"/>
+      <sheetName val="Hoja1"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -398,13 +400,15 @@
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
-      <sheetData sheetId="21">
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23">
         <row r="4">
           <cell r="F4">
-            <v>1164.8235294117646</v>
+            <v>1185.0555555555557</v>
           </cell>
           <cell r="G4">
-            <v>4.1373441444197967E-2</v>
+            <v>5.9461241150122968E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -412,10 +416,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>72.882352941176464</v>
+            <v>71.944444444444443</v>
           </cell>
           <cell r="G5">
-            <v>-6.5066026410564248E-2</v>
+            <v>-7.7097505668934252E-2</v>
           </cell>
           <cell r="H5" t="str">
             <v>BAJO</v>
@@ -423,10 +427,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>485</v>
+            <v>492</v>
           </cell>
           <cell r="G6">
-            <v>-0.11415525114155256</v>
+            <v>-0.10136986301369866</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -434,10 +438,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>87.411764705882348</v>
+            <v>85.722222222222229</v>
           </cell>
           <cell r="G7">
-            <v>-0.10596986353816285</v>
+            <v>-0.12325016788057219</v>
           </cell>
           <cell r="H7" t="str">
             <v>BAJO</v>
@@ -445,10 +449,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>11.176470588235293</v>
+            <v>11</v>
           </cell>
           <cell r="G8">
-            <v>-0.33002083667254378</v>
+            <v>-0.34059945504087197</v>
           </cell>
           <cell r="H8" t="str">
             <v>BAJO</v>
@@ -456,10 +460,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1418.1764705882354</v>
+            <v>1434.8333333333333</v>
           </cell>
           <cell r="G9">
-            <v>9.5193848390240587E-2</v>
+            <v>0.10805719367218924</v>
           </cell>
           <cell r="H9" t="str">
             <v>SUBIÓ</v>
@@ -467,10 +471,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>143</v>
+            <v>143.94444444444446</v>
           </cell>
           <cell r="G10">
-            <v>0.17038690476190466</v>
+            <v>0.17811673280423279</v>
           </cell>
           <cell r="H10" t="str">
             <v>SUBIÓ</v>
@@ -478,10 +482,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>314</v>
+            <v>321.77777777777777</v>
           </cell>
           <cell r="G11">
-            <v>3.3822208919485064E-2</v>
+            <v>5.9429977717915472E-2</v>
           </cell>
           <cell r="H11" t="str">
             <v>SUBIÓ</v>
@@ -489,10 +493,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>723.47058823529414</v>
+            <v>748</v>
           </cell>
           <cell r="G12">
-            <v>9.2855873467211802E-2</v>
+            <v>0.1299093655589123</v>
           </cell>
           <cell r="H12" t="str">
             <v>SUBIÓ</v>
@@ -500,10 +504,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>342</v>
+            <v>353</v>
           </cell>
           <cell r="G13">
-            <v>-0.15602916432978131</v>
+            <v>-0.12888390353337076</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -511,10 +515,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3471.294117647059</v>
+            <v>3477.7777777777778</v>
           </cell>
           <cell r="G14">
-            <v>6.807555961784173E-2</v>
+            <v>7.0070504064434269E-2</v>
           </cell>
           <cell r="H14" t="str">
             <v>SUBIÓ</v>
@@ -522,10 +526,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2253.4705882352941</v>
+            <v>2268.0555555555557</v>
           </cell>
           <cell r="G15">
-            <v>3.4392274686539714E-2</v>
+            <v>4.1087093603368041E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>SUBIÓ</v>
@@ -533,10 +537,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2207.3529411764707</v>
+            <v>2204.9444444444443</v>
           </cell>
           <cell r="G16">
-            <v>2.0719789513249376E-2</v>
+            <v>1.9606057209050398E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>SUBIÓ</v>
@@ -544,10 +548,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2617.3529411764707</v>
+            <v>2637</v>
           </cell>
           <cell r="G17">
-            <v>8.8440442052102108E-2</v>
+            <v>9.661077821673647E-2</v>
           </cell>
           <cell r="H17" t="str">
             <v>SUBIÓ</v>
@@ -555,10 +559,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>18.882352941176471</v>
+            <v>17.833333333333332</v>
           </cell>
           <cell r="G18">
-            <v>-0.85817283553913204</v>
+            <v>-0.86605212245362462</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -566,10 +570,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>227.05882352941177</v>
+            <v>228.88888888888889</v>
           </cell>
           <cell r="G19">
-            <v>5.2916316456146362E-3</v>
+            <v>1.3394154871313235E-2</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -577,10 +581,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>130.94117647058823</v>
+            <v>135.33333333333334</v>
           </cell>
           <cell r="G20">
-            <v>-0.1147185364619111</v>
+            <v>-8.5023560745748794E-2</v>
           </cell>
           <cell r="H20" t="str">
             <v>BAJO</v>
@@ -588,10 +592,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>499.05882352941177</v>
+            <v>510.66666666666669</v>
           </cell>
           <cell r="G21">
-            <v>2.5622990905843857E-2</v>
+            <v>4.9478436867507414E-2</v>
           </cell>
           <cell r="H21" t="str">
             <v>SUBIÓ</v>
@@ -599,13 +603,13 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>788.52941176470586</v>
+            <v>811.55555555555554</v>
           </cell>
           <cell r="G22">
-            <v>-9.8940095414913332E-3</v>
+            <v>1.9018447704024943E-2</v>
           </cell>
           <cell r="H22" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="23">
@@ -621,10 +625,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>73.882352941176464</v>
+            <v>69.666666666666671</v>
           </cell>
           <cell r="G24">
-            <v>0.50222898771338476</v>
+            <v>0.41651263093037594</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -632,10 +636,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>705.70588235294122</v>
+            <v>709.16666666666663</v>
           </cell>
           <cell r="G25">
-            <v>3.0637905719908876E-2</v>
+            <v>3.5692157904053667E-2</v>
           </cell>
           <cell r="H25" t="str">
             <v>SUBIÓ</v>
@@ -643,10 +647,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>1158</v>
+            <v>1162.1666666666667</v>
           </cell>
           <cell r="G26">
-            <v>4.3627872680349178E-2</v>
+            <v>4.7383010391490288E-2</v>
           </cell>
           <cell r="H26" t="str">
             <v>SUBIÓ</v>
@@ -654,10 +658,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>507.29411764705884</v>
+            <v>516.11111111111109</v>
           </cell>
           <cell r="G27">
-            <v>5.0496102055279879E-2</v>
+            <v>6.8754183400267621E-2</v>
           </cell>
           <cell r="H27" t="str">
             <v>SUBIÓ</v>
@@ -665,10 +669,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>384.58823529411762</v>
+            <v>395.72222222222223</v>
           </cell>
           <cell r="G28">
-            <v>4.9614337733604685E-2</v>
+            <v>8.0001102703000759E-2</v>
           </cell>
           <cell r="H28" t="str">
             <v>SUBIÓ</v>
@@ -676,10 +680,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>113.70588235294117</v>
+            <v>114.77777777777777</v>
           </cell>
           <cell r="G29">
-            <v>6.2220557012613975E-2</v>
+            <v>7.2234017456947353E-2</v>
           </cell>
           <cell r="H29" t="str">
             <v>SUBIÓ</v>
@@ -687,10 +691,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>130.47058823529412</v>
+            <v>134.38888888888889</v>
           </cell>
           <cell r="G30">
-            <v>6.4670972246465341E-2</v>
+            <v>9.6645235740191238E-2</v>
           </cell>
           <cell r="H30" t="str">
             <v>SUBIÓ</v>
@@ -698,10 +702,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>608.41176470588232</v>
+            <v>637.22222222222217</v>
           </cell>
           <cell r="G31">
-            <v>-0.23056686459361864</v>
+            <v>-0.19413147339107339</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -709,10 +713,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>619.76470588235293</v>
+            <v>631.38888888888891</v>
           </cell>
           <cell r="G32">
-            <v>-4.8777485041735402E-2</v>
+            <v>-3.0936545587026854E-2</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -720,10 +724,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>821.82352941176475</v>
+            <v>841.33333333333337</v>
           </cell>
           <cell r="G33">
-            <v>-2.4699663013333484E-2</v>
+            <v>-1.5463732153773169E-3</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -731,10 +735,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>553</v>
+            <v>570.16666666666663</v>
           </cell>
           <cell r="G34">
-            <v>-3.3831003811944149E-2</v>
+            <v>-3.8384159254554184E-3</v>
           </cell>
           <cell r="H34" t="str">
             <v>BAJO</v>
@@ -742,10 +746,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>106.88235294117646</v>
+            <v>134.55555555555554</v>
           </cell>
           <cell r="G35">
-            <v>-0.49713178684647508</v>
+            <v>-0.36693280106453763</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -753,10 +757,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>500.52941176470586</v>
+            <v>525.55555555555554</v>
           </cell>
           <cell r="G36">
-            <v>0.71734982202487974</v>
+            <v>0.80321619186248006</v>
           </cell>
           <cell r="H36" t="str">
             <v>SUBIÓ</v>
@@ -764,10 +768,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>38.705882352941174</v>
+            <v>38.055555555555557</v>
           </cell>
           <cell r="G37">
-            <v>-0.89657118768799882</v>
+            <v>-0.89830897337274118</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -775,10 +779,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>286.94117647058823</v>
+            <v>302.55555555555554</v>
           </cell>
           <cell r="G38">
-            <v>5.1241612381838664E-2</v>
+            <v>0.10844666481635667</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -786,10 +790,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>475.1764705882353</v>
+            <v>539.55555555555554</v>
           </cell>
           <cell r="G39">
-            <v>0.13027163508932604</v>
+            <v>0.28340601386336051</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -797,10 +801,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>275.94117647058823</v>
+            <v>316.16666666666669</v>
           </cell>
           <cell r="G40">
-            <v>0.11964328335539309</v>
+            <v>0.28285995327677371</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -808,32 +812,32 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>252.70588235294119</v>
+            <v>293.38888888888891</v>
           </cell>
           <cell r="G41">
-            <v>-4.0633406080292422E-2</v>
+            <v>0.11381459112261516</v>
           </cell>
           <cell r="H41" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="42">
           <cell r="F42">
-            <v>48.647058823529413</v>
+            <v>60.833333333333336</v>
           </cell>
           <cell r="G42">
-            <v>-2.5286617379192022E-2</v>
+            <v>0.21888281724347314</v>
           </cell>
           <cell r="H42" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="43">
           <cell r="F43">
-            <v>92.82352941176471</v>
+            <v>109.16666666666667</v>
           </cell>
           <cell r="G43">
-            <v>0.16892824674231455</v>
+            <v>0.37473764548750244</v>
           </cell>
           <cell r="H43" t="str">
             <v>SUBIÓ</v>
@@ -841,10 +845,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>49.647058823529413</v>
+            <v>51.777777777777779</v>
           </cell>
           <cell r="G44">
-            <v>0.44858792323295371</v>
+            <v>0.5107574417919245</v>
           </cell>
           <cell r="H44" t="str">
             <v>SUBIÓ</v>
@@ -852,10 +856,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>42.176470588235297</v>
+            <v>57.5</v>
           </cell>
           <cell r="G45">
-            <v>0.12470588235294122</v>
+            <v>0.53333333333333344</v>
           </cell>
           <cell r="H45" t="str">
             <v>SUBIÓ</v>
@@ -863,10 +867,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>0.52941176470588236</v>
+            <v>0.5</v>
           </cell>
           <cell r="G46">
-            <v>-0.35294117647058831</v>
+            <v>-0.38888888888888895</v>
           </cell>
           <cell r="H46" t="str">
             <v>BAJO</v>
@@ -874,10 +878,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>2.5882352941176472</v>
+            <v>2.4444444444444446</v>
           </cell>
           <cell r="G47">
-            <v>-0.20915032679738566</v>
+            <v>-0.25308641975308643</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -1140,11 +1144,11 @@
       </c>
       <c r="E2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1164.8235294117646</v>
+        <v>1185.0555555555557</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>4.1373441444197967E-2</v>
+        <v>5.9461241150122968E-2</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1169,11 +1173,11 @@
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>72.882352941176464</v>
+        <v>71.944444444444443</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-6.5066026410564248E-2</v>
+        <v>-7.7097505668934252E-2</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1198,11 +1202,11 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-0.11415525114155256</v>
+        <v>-0.10136986301369866</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1227,11 +1231,11 @@
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>87.411764705882348</v>
+        <v>85.722222222222229</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>-0.10596986353816285</v>
+        <v>-0.12325016788057219</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1256,11 +1260,11 @@
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>11.176470588235293</v>
+        <v>11</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>-0.33002083667254378</v>
+        <v>-0.34059945504087197</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1285,11 +1289,11 @@
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1418.1764705882354</v>
+        <v>1434.8333333333333</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>9.5193848390240587E-2</v>
+        <v>0.10805719367218924</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1314,11 +1318,11 @@
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>143</v>
+        <v>143.94444444444446</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>0.17038690476190466</v>
+        <v>0.17811673280423279</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1343,11 +1347,11 @@
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>314</v>
+        <v>321.77777777777777</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>3.3822208919485064E-2</v>
+        <v>5.9429977717915472E-2</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1372,11 +1376,11 @@
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>723.47058823529414</v>
+        <v>748</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>9.2855873467211802E-2</v>
+        <v>0.1299093655589123</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1401,11 +1405,11 @@
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.15602916432978131</v>
+        <v>-0.12888390353337076</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1430,11 +1434,11 @@
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3471.294117647059</v>
+        <v>3477.7777777777778</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>6.807555961784173E-2</v>
+        <v>7.0070504064434269E-2</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1459,11 +1463,11 @@
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2253.4705882352941</v>
+        <v>2268.0555555555557</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>3.4392274686539714E-2</v>
+        <v>4.1087093603368041E-2</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1488,11 +1492,11 @@
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2207.3529411764707</v>
+        <v>2204.9444444444443</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>2.0719789513249376E-2</v>
+        <v>1.9606057209050398E-2</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1517,11 +1521,11 @@
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2617.3529411764707</v>
+        <v>2637</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>8.8440442052102108E-2</v>
+        <v>9.661077821673647E-2</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1546,11 +1550,11 @@
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>18.882352941176471</v>
+        <v>17.833333333333332</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.85817283553913204</v>
+        <v>-0.86605212245362462</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1575,11 +1579,11 @@
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>227.05882352941177</v>
+        <v>228.88888888888889</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>5.2916316456146362E-3</v>
+        <v>1.3394154871313235E-2</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1604,11 +1608,11 @@
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>130.94117647058823</v>
+        <v>135.33333333333334</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>-0.1147185364619111</v>
+        <v>-8.5023560745748794E-2</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1633,11 +1637,11 @@
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>499.05882352941177</v>
+        <v>510.66666666666669</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>2.5622990905843857E-2</v>
+        <v>4.9478436867507414E-2</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1662,15 +1666,15 @@
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>788.52941176470586</v>
+        <v>811.55555555555554</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-9.8940095414913332E-3</v>
+        <v>1.9018447704024943E-2</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H20">
         <v>4.1500000000000004</v>
@@ -1720,11 +1724,11 @@
       </c>
       <c r="E22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>73.882352941176464</v>
+        <v>69.666666666666671</v>
       </c>
       <c r="F22" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>0.50222898771338476</v>
+        <v>0.41651263093037594</v>
       </c>
       <c r="G22" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1749,11 +1753,11 @@
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>705.70588235294122</v>
+        <v>709.16666666666663</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>3.0637905719908876E-2</v>
+        <v>3.5692157904053667E-2</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1778,11 +1782,11 @@
       </c>
       <c r="E24" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>1158</v>
+        <v>1162.1666666666667</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>4.3627872680349178E-2</v>
+        <v>4.7383010391490288E-2</v>
       </c>
       <c r="G24" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1807,11 +1811,11 @@
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>507.29411764705884</v>
+        <v>516.11111111111109</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>5.0496102055279879E-2</v>
+        <v>6.8754183400267621E-2</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1836,11 +1840,11 @@
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>384.58823529411762</v>
+        <v>395.72222222222223</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>4.9614337733604685E-2</v>
+        <v>8.0001102703000759E-2</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1865,11 +1869,11 @@
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>113.70588235294117</v>
+        <v>114.77777777777777</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>6.2220557012613975E-2</v>
+        <v>7.2234017456947353E-2</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1894,11 +1898,11 @@
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>130.47058823529412</v>
+        <v>134.38888888888889</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>6.4670972246465341E-2</v>
+        <v>9.6645235740191238E-2</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1923,11 +1927,11 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>608.41176470588232</v>
+        <v>637.22222222222217</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-0.23056686459361864</v>
+        <v>-0.19413147339107339</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1952,11 +1956,11 @@
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>619.76470588235293</v>
+        <v>631.38888888888891</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-4.8777485041735402E-2</v>
+        <v>-3.0936545587026854E-2</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1981,11 +1985,11 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>821.82352941176475</v>
+        <v>841.33333333333337</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-2.4699663013333484E-2</v>
+        <v>-1.5463732153773169E-3</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2010,11 +2014,11 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>553</v>
+        <v>570.16666666666663</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-3.3831003811944149E-2</v>
+        <v>-3.8384159254554184E-3</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2039,11 +2043,11 @@
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>106.88235294117646</v>
+        <v>134.55555555555554</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-0.49713178684647508</v>
+        <v>-0.36693280106453763</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2068,11 +2072,11 @@
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>500.52941176470586</v>
+        <v>525.55555555555554</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>0.71734982202487974</v>
+        <v>0.80321619186248006</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2097,11 +2101,11 @@
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>38.705882352941174</v>
+        <v>38.055555555555557</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.89657118768799882</v>
+        <v>-0.89830897337274118</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2126,11 +2130,11 @@
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>286.94117647058823</v>
+        <v>302.55555555555554</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>5.1241612381838664E-2</v>
+        <v>0.10844666481635667</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2155,11 +2159,11 @@
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>475.1764705882353</v>
+        <v>539.55555555555554</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.13027163508932604</v>
+        <v>0.28340601386336051</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2184,11 +2188,11 @@
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>275.94117647058823</v>
+        <v>316.16666666666669</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>0.11964328335539309</v>
+        <v>0.28285995327677371</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2213,15 +2217,15 @@
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>252.70588235294119</v>
+        <v>293.38888888888891</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-4.0633406080292422E-2</v>
+        <v>0.11381459112261516</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H39">
         <v>0.81</v>
@@ -2242,15 +2246,15 @@
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>48.647058823529413</v>
+        <v>60.833333333333336</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>-2.5286617379192022E-2</v>
+        <v>0.21888281724347314</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H40">
         <v>2.62</v>
@@ -2271,11 +2275,11 @@
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>92.82352941176471</v>
+        <v>109.16666666666667</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>0.16892824674231455</v>
+        <v>0.37473764548750244</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2300,11 +2304,11 @@
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>49.647058823529413</v>
+        <v>51.777777777777779</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>0.44858792323295371</v>
+        <v>0.5107574417919245</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2329,11 +2333,11 @@
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>42.176470588235297</v>
+        <v>57.5</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>0.12470588235294122</v>
+        <v>0.53333333333333344</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2358,11 +2362,11 @@
       </c>
       <c r="E44" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>0.52941176470588236</v>
+        <v>0.5</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-0.35294117647058831</v>
+        <v>-0.38888888888888895</v>
       </c>
       <c r="G44" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
@@ -2387,11 +2391,11 @@
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>2.5882352941176472</v>
+        <v>2.4444444444444446</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.20915032679738566</v>
+        <v>-0.25308641975308643</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08DAE008-4E32-4A59-B05D-1343527EBC8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6073A664-C6FD-4FC9-83AA-F63386C99D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   <externalReferences>
     <externalReference r:id="rId3"/>
   </externalReferences>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -373,6 +373,7 @@
       <sheetName val="INVENTARIO NACIONAL 25-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 25-08-26-2"/>
       <sheetName val="INVENTARIO NACIONAL 27-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 28-08-26"/>
       <sheetName val="Hoja1"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -402,13 +403,14 @@
       <sheetData sheetId="20"/>
       <sheetData sheetId="21"/>
       <sheetData sheetId="22"/>
-      <sheetData sheetId="23">
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24">
         <row r="4">
           <cell r="F4">
-            <v>1185.0555555555557</v>
+            <v>1171.2105263157894</v>
           </cell>
           <cell r="G4">
-            <v>5.9461241150122968E-2</v>
+            <v>4.7083532954623086E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -416,10 +418,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>71.944444444444443</v>
+            <v>72.21052631578948</v>
           </cell>
           <cell r="G5">
-            <v>-7.7097505668934252E-2</v>
+            <v>-7.3684210526315685E-2</v>
           </cell>
           <cell r="H5" t="str">
             <v>BAJO</v>
@@ -427,10 +429,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>492</v>
+            <v>493.26315789473682</v>
           </cell>
           <cell r="G6">
-            <v>-0.10136986301369866</v>
+            <v>-9.9062725306416799E-2</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -438,10 +440,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>85.722222222222229</v>
+            <v>87.21052631578948</v>
           </cell>
           <cell r="G7">
-            <v>-0.12325016788057219</v>
+            <v>-0.1080280897501773</v>
           </cell>
           <cell r="H7" t="str">
             <v>BAJO</v>
@@ -449,10 +451,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>11</v>
+            <v>11.526315789473685</v>
           </cell>
           <cell r="G8">
-            <v>-0.34059945504087197</v>
+            <v>-0.30904918973182272</v>
           </cell>
           <cell r="H8" t="str">
             <v>BAJO</v>
@@ -460,10 +462,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1434.8333333333333</v>
+            <v>1437.6315789473683</v>
           </cell>
           <cell r="G9">
-            <v>0.10805719367218924</v>
+            <v>0.11021815279563674</v>
           </cell>
           <cell r="H9" t="str">
             <v>SUBIÓ</v>
@@ -471,10 +473,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>143.94444444444446</v>
+            <v>142.15789473684211</v>
           </cell>
           <cell r="G10">
-            <v>0.17811673280423279</v>
+            <v>0.16349467418546371</v>
           </cell>
           <cell r="H10" t="str">
             <v>SUBIÓ</v>
@@ -482,10 +484,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>321.77777777777777</v>
+            <v>327.05263157894734</v>
           </cell>
           <cell r="G11">
-            <v>5.9429977717915472E-2</v>
+            <v>7.6797050993241633E-2</v>
           </cell>
           <cell r="H11" t="str">
             <v>SUBIÓ</v>
@@ -493,10 +495,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>748</v>
+            <v>747.47368421052636</v>
           </cell>
           <cell r="G12">
-            <v>0.1299093655589123</v>
+            <v>0.12911432660200362</v>
           </cell>
           <cell r="H12" t="str">
             <v>SUBIÓ</v>
@@ -504,10 +506,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>353</v>
+            <v>348.42105263157896</v>
           </cell>
           <cell r="G13">
-            <v>-0.12888390353337076</v>
+            <v>-0.1401836053959914</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -515,10 +517,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3477.7777777777778</v>
+            <v>3459.7368421052633</v>
           </cell>
           <cell r="G14">
-            <v>7.0070504064434269E-2</v>
+            <v>6.4519524570506581E-2</v>
           </cell>
           <cell r="H14" t="str">
             <v>SUBIÓ</v>
@@ -526,10 +528,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2268.0555555555557</v>
+            <v>2253.6315789473683</v>
           </cell>
           <cell r="G15">
-            <v>4.1087093603368041E-2</v>
+            <v>3.4466172943625972E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>SUBIÓ</v>
@@ -537,10 +539,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2204.9444444444443</v>
+            <v>2191.6315789473683</v>
           </cell>
           <cell r="G16">
-            <v>1.9606057209050398E-2</v>
+            <v>1.3449948226881281E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>SUBIÓ</v>
@@ -548,10 +550,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2637</v>
+            <v>2625</v>
           </cell>
           <cell r="G17">
-            <v>9.661077821673647E-2</v>
+            <v>9.1620513014384786E-2</v>
           </cell>
           <cell r="H17" t="str">
             <v>SUBIÓ</v>
@@ -559,10 +561,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>17.833333333333332</v>
+            <v>15.052631578947368</v>
           </cell>
           <cell r="G18">
-            <v>-0.86605212245362462</v>
+            <v>-0.8869382401035022</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -570,10 +572,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>228.88888888888889</v>
+            <v>231.26315789473685</v>
           </cell>
           <cell r="G19">
-            <v>1.3394154871313235E-2</v>
+            <v>2.3906112635180277E-2</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -581,10 +583,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>135.33333333333334</v>
+            <v>135.05263157894737</v>
           </cell>
           <cell r="G20">
-            <v>-8.5023560745748794E-2</v>
+            <v>-8.6921359945653864E-2</v>
           </cell>
           <cell r="H20" t="str">
             <v>BAJO</v>
@@ -592,10 +594,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>510.66666666666669</v>
+            <v>504.57894736842104</v>
           </cell>
           <cell r="G21">
-            <v>4.9478436867507414E-2</v>
+            <v>3.69674770766244E-2</v>
           </cell>
           <cell r="H21" t="str">
             <v>SUBIÓ</v>
@@ -603,10 +605,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>811.55555555555554</v>
+            <v>797.63157894736844</v>
           </cell>
           <cell r="G22">
-            <v>1.9018447704024943E-2</v>
+            <v>1.5350001051370743E-3</v>
           </cell>
           <cell r="H22" t="str">
             <v>SUBIÓ</v>
@@ -625,10 +627,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>69.666666666666671</v>
+            <v>67.05263157894737</v>
           </cell>
           <cell r="G24">
-            <v>0.41651263093037594</v>
+            <v>0.36336219476602793</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -636,10 +638,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>709.16666666666663</v>
+            <v>712.78947368421052</v>
           </cell>
           <cell r="G25">
-            <v>3.5692157904053667E-2</v>
+            <v>4.0983033792659995E-2</v>
           </cell>
           <cell r="H25" t="str">
             <v>SUBIÓ</v>
@@ -647,10 +649,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>1162.1666666666667</v>
+            <v>1181.8421052631579</v>
           </cell>
           <cell r="G26">
-            <v>4.7383010391490288E-2</v>
+            <v>6.5115165941152631E-2</v>
           </cell>
           <cell r="H26" t="str">
             <v>SUBIÓ</v>
@@ -658,10 +660,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>516.11111111111109</v>
+            <v>512.26315789473688</v>
           </cell>
           <cell r="G27">
-            <v>6.8754183400267621E-2</v>
+            <v>6.0785906785034927E-2</v>
           </cell>
           <cell r="H27" t="str">
             <v>SUBIÓ</v>
@@ -669,10 +671,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>395.72222222222223</v>
+            <v>397.42105263157896</v>
           </cell>
           <cell r="G28">
-            <v>8.0001102703000759E-2</v>
+            <v>8.4637533543572285E-2</v>
           </cell>
           <cell r="H28" t="str">
             <v>SUBIÓ</v>
@@ -680,10 +682,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>114.77777777777777</v>
+            <v>115.57894736842105</v>
           </cell>
           <cell r="G29">
-            <v>7.2234017456947353E-2</v>
+            <v>7.9718404290982203E-2</v>
           </cell>
           <cell r="H29" t="str">
             <v>SUBIÓ</v>
@@ -691,10 +693,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>134.38888888888889</v>
+            <v>132.15789473684211</v>
           </cell>
           <cell r="G30">
-            <v>9.6645235740191238E-2</v>
+            <v>7.8439793846634354E-2</v>
           </cell>
           <cell r="H30" t="str">
             <v>SUBIÓ</v>
@@ -702,10 +704,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>637.22222222222217</v>
+            <v>645.84210526315792</v>
           </cell>
           <cell r="G31">
-            <v>-0.19413147339107339</v>
+            <v>-0.18323026467064418</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -713,10 +715,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>631.38888888888891</v>
+            <v>629.84210526315792</v>
           </cell>
           <cell r="G32">
-            <v>-3.0936545587026854E-2</v>
+            <v>-3.3310568174307553E-2</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -724,10 +726,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>841.33333333333337</v>
+            <v>836.52631578947364</v>
           </cell>
           <cell r="G33">
-            <v>-1.5463732153773169E-3</v>
+            <v>-7.2511086757783838E-3</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -735,10 +737,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>570.16666666666663</v>
+            <v>568.84210526315792</v>
           </cell>
           <cell r="G34">
-            <v>-3.8384159254554184E-3</v>
+            <v>-6.1526115160837058E-3</v>
           </cell>
           <cell r="H34" t="str">
             <v>BAJO</v>
@@ -746,10 +748,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>134.55555555555554</v>
+            <v>135.10526315789474</v>
           </cell>
           <cell r="G35">
-            <v>-0.36693280106453763</v>
+            <v>-0.36434649497996485</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -757,10 +759,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>525.55555555555554</v>
+            <v>524.0526315789474</v>
           </cell>
           <cell r="G36">
-            <v>0.80321619186248006</v>
+            <v>0.79805955937879647</v>
           </cell>
           <cell r="H36" t="str">
             <v>SUBIÓ</v>
@@ -768,10 +770,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>38.055555555555557</v>
+            <v>59.05263157894737</v>
           </cell>
           <cell r="G37">
-            <v>-0.89830897337274118</v>
+            <v>-0.84220115453214595</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -779,10 +781,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>302.55555555555554</v>
+            <v>300.63157894736844</v>
           </cell>
           <cell r="G38">
-            <v>0.10844666481635667</v>
+            <v>0.10139795784214911</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -790,10 +792,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>539.55555555555554</v>
+            <v>531.0526315789474</v>
           </cell>
           <cell r="G39">
-            <v>0.28340601386336051</v>
+            <v>0.26318065679931268</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -801,10 +803,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>316.16666666666669</v>
+            <v>310.10526315789474</v>
           </cell>
           <cell r="G40">
-            <v>0.28285995327677371</v>
+            <v>0.25826554582694272</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -812,10 +814,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>293.38888888888891</v>
+            <v>290.78947368421052</v>
           </cell>
           <cell r="G41">
-            <v>0.11381459112261516</v>
+            <v>0.10394623314109253</v>
           </cell>
           <cell r="H41" t="str">
             <v>SUBIÓ</v>
@@ -823,10 +825,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>60.833333333333336</v>
+            <v>58.736842105263158</v>
           </cell>
           <cell r="G42">
-            <v>0.21888281724347314</v>
+            <v>0.17687661777394315</v>
           </cell>
           <cell r="H42" t="str">
             <v>SUBIÓ</v>
@@ -834,10 +836,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>109.16666666666667</v>
+            <v>107.68421052631579</v>
           </cell>
           <cell r="G43">
-            <v>0.37473764548750244</v>
+            <v>0.35606905070346162</v>
           </cell>
           <cell r="H43" t="str">
             <v>SUBIÓ</v>
@@ -845,10 +847,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>51.777777777777779</v>
+            <v>51.10526315789474</v>
           </cell>
           <cell r="G44">
-            <v>0.5107574417919245</v>
+            <v>0.49113499930196847</v>
           </cell>
           <cell r="H44" t="str">
             <v>SUBIÓ</v>
@@ -856,10 +858,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>57.5</v>
+            <v>56.789473684210527</v>
           </cell>
           <cell r="G45">
-            <v>0.53333333333333344</v>
+            <v>0.51438596491228084</v>
           </cell>
           <cell r="H45" t="str">
             <v>SUBIÓ</v>
@@ -867,10 +869,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>0.5</v>
+            <v>0.47368421052631576</v>
           </cell>
           <cell r="G46">
-            <v>-0.38888888888888895</v>
+            <v>-0.42105263157894746</v>
           </cell>
           <cell r="H46" t="str">
             <v>BAJO</v>
@@ -878,10 +880,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>2.4444444444444446</v>
+            <v>2.4736842105263159</v>
           </cell>
           <cell r="G47">
-            <v>-0.25308641975308643</v>
+            <v>-0.24415204678362579</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -1144,11 +1146,11 @@
       </c>
       <c r="E2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1185.0555555555557</v>
+        <v>1171.2105263157894</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>5.9461241150122968E-2</v>
+        <v>4.7083532954623086E-2</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1173,11 +1175,11 @@
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>71.944444444444443</v>
+        <v>72.21052631578948</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-7.7097505668934252E-2</v>
+        <v>-7.3684210526315685E-2</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1202,11 +1204,11 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>492</v>
+        <v>493.26315789473682</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-0.10136986301369866</v>
+        <v>-9.9062725306416799E-2</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1231,11 +1233,11 @@
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>85.722222222222229</v>
+        <v>87.21052631578948</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>-0.12325016788057219</v>
+        <v>-0.1080280897501773</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1260,11 +1262,11 @@
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>11</v>
+        <v>11.526315789473685</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>-0.34059945504087197</v>
+        <v>-0.30904918973182272</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1289,11 +1291,11 @@
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1434.8333333333333</v>
+        <v>1437.6315789473683</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>0.10805719367218924</v>
+        <v>0.11021815279563674</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1318,11 +1320,11 @@
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>143.94444444444446</v>
+        <v>142.15789473684211</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>0.17811673280423279</v>
+        <v>0.16349467418546371</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1347,11 +1349,11 @@
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>321.77777777777777</v>
+        <v>327.05263157894734</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>5.9429977717915472E-2</v>
+        <v>7.6797050993241633E-2</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1376,11 +1378,11 @@
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>748</v>
+        <v>747.47368421052636</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>0.1299093655589123</v>
+        <v>0.12911432660200362</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1405,11 +1407,11 @@
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>353</v>
+        <v>348.42105263157896</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.12888390353337076</v>
+        <v>-0.1401836053959914</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1434,11 +1436,11 @@
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3477.7777777777778</v>
+        <v>3459.7368421052633</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>7.0070504064434269E-2</v>
+        <v>6.4519524570506581E-2</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1463,11 +1465,11 @@
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2268.0555555555557</v>
+        <v>2253.6315789473683</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>4.1087093603368041E-2</v>
+        <v>3.4466172943625972E-2</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1492,11 +1494,11 @@
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2204.9444444444443</v>
+        <v>2191.6315789473683</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>1.9606057209050398E-2</v>
+        <v>1.3449948226881281E-2</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1521,11 +1523,11 @@
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2637</v>
+        <v>2625</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>9.661077821673647E-2</v>
+        <v>9.1620513014384786E-2</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1550,11 +1552,11 @@
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>17.833333333333332</v>
+        <v>15.052631578947368</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.86605212245362462</v>
+        <v>-0.8869382401035022</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1579,11 +1581,11 @@
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>228.88888888888889</v>
+        <v>231.26315789473685</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>1.3394154871313235E-2</v>
+        <v>2.3906112635180277E-2</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1608,11 +1610,11 @@
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>135.33333333333334</v>
+        <v>135.05263157894737</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>-8.5023560745748794E-2</v>
+        <v>-8.6921359945653864E-2</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1637,11 +1639,11 @@
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>510.66666666666669</v>
+        <v>504.57894736842104</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>4.9478436867507414E-2</v>
+        <v>3.69674770766244E-2</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1666,11 +1668,11 @@
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>811.55555555555554</v>
+        <v>797.63157894736844</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>1.9018447704024943E-2</v>
+        <v>1.5350001051370743E-3</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1724,11 +1726,11 @@
       </c>
       <c r="E22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>69.666666666666671</v>
+        <v>67.05263157894737</v>
       </c>
       <c r="F22" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>0.41651263093037594</v>
+        <v>0.36336219476602793</v>
       </c>
       <c r="G22" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1753,11 +1755,11 @@
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>709.16666666666663</v>
+        <v>712.78947368421052</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>3.5692157904053667E-2</v>
+        <v>4.0983033792659995E-2</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1782,11 +1784,11 @@
       </c>
       <c r="E24" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>1162.1666666666667</v>
+        <v>1181.8421052631579</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>4.7383010391490288E-2</v>
+        <v>6.5115165941152631E-2</v>
       </c>
       <c r="G24" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1811,11 +1813,11 @@
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>516.11111111111109</v>
+        <v>512.26315789473688</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>6.8754183400267621E-2</v>
+        <v>6.0785906785034927E-2</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1840,11 +1842,11 @@
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>395.72222222222223</v>
+        <v>397.42105263157896</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>8.0001102703000759E-2</v>
+        <v>8.4637533543572285E-2</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1869,11 +1871,11 @@
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>114.77777777777777</v>
+        <v>115.57894736842105</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>7.2234017456947353E-2</v>
+        <v>7.9718404290982203E-2</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1898,11 +1900,11 @@
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>134.38888888888889</v>
+        <v>132.15789473684211</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>9.6645235740191238E-2</v>
+        <v>7.8439793846634354E-2</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1927,11 +1929,11 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>637.22222222222217</v>
+        <v>645.84210526315792</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-0.19413147339107339</v>
+        <v>-0.18323026467064418</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1956,11 +1958,11 @@
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>631.38888888888891</v>
+        <v>629.84210526315792</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-3.0936545587026854E-2</v>
+        <v>-3.3310568174307553E-2</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1985,11 +1987,11 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>841.33333333333337</v>
+        <v>836.52631578947364</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-1.5463732153773169E-3</v>
+        <v>-7.2511086757783838E-3</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2014,11 +2016,11 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>570.16666666666663</v>
+        <v>568.84210526315792</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-3.8384159254554184E-3</v>
+        <v>-6.1526115160837058E-3</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2043,11 +2045,11 @@
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>134.55555555555554</v>
+        <v>135.10526315789474</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-0.36693280106453763</v>
+        <v>-0.36434649497996485</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2072,11 +2074,11 @@
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>525.55555555555554</v>
+        <v>524.0526315789474</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>0.80321619186248006</v>
+        <v>0.79805955937879647</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2101,11 +2103,11 @@
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>38.055555555555557</v>
+        <v>59.05263157894737</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.89830897337274118</v>
+        <v>-0.84220115453214595</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2130,11 +2132,11 @@
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>302.55555555555554</v>
+        <v>300.63157894736844</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>0.10844666481635667</v>
+        <v>0.10139795784214911</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2159,11 +2161,11 @@
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>539.55555555555554</v>
+        <v>531.0526315789474</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.28340601386336051</v>
+        <v>0.26318065679931268</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2188,11 +2190,11 @@
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>316.16666666666669</v>
+        <v>310.10526315789474</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>0.28285995327677371</v>
+        <v>0.25826554582694272</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2217,11 +2219,11 @@
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>293.38888888888891</v>
+        <v>290.78947368421052</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>0.11381459112261516</v>
+        <v>0.10394623314109253</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2246,11 +2248,11 @@
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>60.833333333333336</v>
+        <v>58.736842105263158</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>0.21888281724347314</v>
+        <v>0.17687661777394315</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2275,11 +2277,11 @@
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>109.16666666666667</v>
+        <v>107.68421052631579</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>0.37473764548750244</v>
+        <v>0.35606905070346162</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2304,11 +2306,11 @@
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>51.777777777777779</v>
+        <v>51.10526315789474</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>0.5107574417919245</v>
+        <v>0.49113499930196847</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2333,11 +2335,11 @@
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>57.5</v>
+        <v>56.789473684210527</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>0.53333333333333344</v>
+        <v>0.51438596491228084</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2362,11 +2364,11 @@
       </c>
       <c r="E44" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>0.5</v>
+        <v>0.47368421052631576</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-0.38888888888888895</v>
+        <v>-0.42105263157894746</v>
       </c>
       <c r="G44" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
@@ -2391,11 +2393,11 @@
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>2.4444444444444446</v>
+        <v>2.4736842105263159</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.25308641975308643</v>
+        <v>-0.24415204678362579</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6073A664-C6FD-4FC9-83AA-F63386C99D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54ACBD84-45E9-4331-83EB-2E885FD64AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -374,7 +374,8 @@
       <sheetName val="INVENTARIO NACIONAL 25-08-26-2"/>
       <sheetName val="INVENTARIO NACIONAL 27-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 28-08-26"/>
-      <sheetName val="Hoja1"/>
+      <sheetName val="INVENTARIO NACIONAL 31-08-26"/>
+      <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -404,13 +405,14 @@
       <sheetData sheetId="21"/>
       <sheetData sheetId="22"/>
       <sheetData sheetId="23"/>
-      <sheetData sheetId="24">
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25">
         <row r="4">
           <cell r="F4">
-            <v>1171.2105263157894</v>
+            <v>1147.25</v>
           </cell>
           <cell r="G4">
-            <v>4.7083532954623086E-2</v>
+            <v>2.5662386215864696E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -418,10 +420,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>72.21052631578948</v>
+            <v>75.05</v>
           </cell>
           <cell r="G5">
-            <v>-7.3684210526315685E-2</v>
+            <v>-3.7259475218658911E-2</v>
           </cell>
           <cell r="H5" t="str">
             <v>BAJO</v>
@@ -429,10 +431,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>493.26315789473682</v>
+            <v>485.15</v>
           </cell>
           <cell r="G6">
-            <v>-9.9062725306416799E-2</v>
+            <v>-0.1138812785388128</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -440,10 +442,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>87.21052631578948</v>
+            <v>88.25</v>
           </cell>
           <cell r="G7">
-            <v>-0.1080280897501773</v>
+            <v>-9.7396559739655886E-2</v>
           </cell>
           <cell r="H7" t="str">
             <v>BAJO</v>
@@ -451,10 +453,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>11.526315789473685</v>
+            <v>12.2</v>
           </cell>
           <cell r="G8">
-            <v>-0.30904918973182272</v>
+            <v>-0.26866485013623986</v>
           </cell>
           <cell r="H8" t="str">
             <v>BAJO</v>
@@ -462,10 +464,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1437.6315789473683</v>
+            <v>1415.3</v>
           </cell>
           <cell r="G9">
-            <v>0.11021815279563674</v>
+            <v>9.2972479640550221E-2</v>
           </cell>
           <cell r="H9" t="str">
             <v>SUBIÓ</v>
@@ -473,10 +475,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>142.15789473684211</v>
+            <v>139.85</v>
           </cell>
           <cell r="G10">
-            <v>0.16349467418546371</v>
+            <v>0.14460565476190457</v>
           </cell>
           <cell r="H10" t="str">
             <v>SUBIÓ</v>
@@ -484,10 +486,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>327.05263157894734</v>
+            <v>321.85000000000002</v>
           </cell>
           <cell r="G11">
-            <v>7.6797050993241633E-2</v>
+            <v>5.9667764142472324E-2</v>
           </cell>
           <cell r="H11" t="str">
             <v>SUBIÓ</v>
@@ -495,10 +497,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>747.47368421052636</v>
+            <v>747.6</v>
           </cell>
           <cell r="G12">
-            <v>0.12911432660200362</v>
+            <v>0.12930513595166171</v>
           </cell>
           <cell r="H12" t="str">
             <v>SUBIÓ</v>
@@ -506,10 +508,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>348.42105263157896</v>
+            <v>350.65</v>
           </cell>
           <cell r="G13">
-            <v>-0.1401836053959914</v>
+            <v>-0.13468311833987667</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -517,10 +519,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3459.7368421052633</v>
+            <v>3402.95</v>
           </cell>
           <cell r="G14">
-            <v>6.4519524570506581E-2</v>
+            <v>4.7046894449028542E-2</v>
           </cell>
           <cell r="H14" t="str">
             <v>SUBIÓ</v>
@@ -528,10 +530,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2253.6315789473683</v>
+            <v>2219.3000000000002</v>
           </cell>
           <cell r="G15">
-            <v>3.4466172943625972E-2</v>
+            <v>1.8707227507928748E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>SUBIÓ</v>
@@ -539,21 +541,21 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2191.6315789473683</v>
+            <v>2148.15</v>
           </cell>
           <cell r="G16">
-            <v>1.3449948226881281E-2</v>
+            <v>-6.6567176727760913E-3</v>
           </cell>
           <cell r="H16" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2625</v>
+            <v>2573.25</v>
           </cell>
           <cell r="G17">
-            <v>9.1620513014384786E-2</v>
+            <v>7.0099994329244186E-2</v>
           </cell>
           <cell r="H17" t="str">
             <v>SUBIÓ</v>
@@ -561,10 +563,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>15.052631578947368</v>
+            <v>9.6999999999999993</v>
           </cell>
           <cell r="G18">
-            <v>-0.8869382401035022</v>
+            <v>-0.92714236940935468</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -572,10 +574,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>231.26315789473685</v>
+            <v>232.75</v>
           </cell>
           <cell r="G19">
-            <v>2.3906112635180277E-2</v>
+            <v>3.0489031998389926E-2</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -583,10 +585,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>135.05263157894737</v>
+            <v>135.55000000000001</v>
           </cell>
           <cell r="G20">
-            <v>-8.6921359945653864E-2</v>
+            <v>-8.3558696988321968E-2</v>
           </cell>
           <cell r="H20" t="str">
             <v>BAJO</v>
@@ -594,10 +596,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>504.57894736842104</v>
+            <v>496.35</v>
           </cell>
           <cell r="G21">
-            <v>3.69674770766244E-2</v>
+            <v>2.0056048575432195E-2</v>
           </cell>
           <cell r="H21" t="str">
             <v>SUBIÓ</v>
@@ -605,13 +607,13 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>797.63157894736844</v>
+            <v>785</v>
           </cell>
           <cell r="G22">
-            <v>1.5350001051370743E-3</v>
+            <v>-1.4325666343245169E-2</v>
           </cell>
           <cell r="H22" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="23">
@@ -627,10 +629,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>67.05263157894737</v>
+            <v>63.7</v>
           </cell>
           <cell r="G24">
-            <v>0.36336219476602793</v>
+            <v>0.29519408502772659</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -638,10 +640,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>712.78947368421052</v>
+            <v>709.65</v>
           </cell>
           <cell r="G25">
-            <v>4.0983033792659995E-2</v>
+            <v>3.6398035050451361E-2</v>
           </cell>
           <cell r="H25" t="str">
             <v>SUBIÓ</v>
@@ -649,10 +651,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>1181.8421052631579</v>
+            <v>1162.95</v>
           </cell>
           <cell r="G26">
-            <v>6.5115165941152631E-2</v>
+            <v>4.8088976281184914E-2</v>
           </cell>
           <cell r="H26" t="str">
             <v>SUBIÓ</v>
@@ -660,10 +662,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>512.26315789473688</v>
+            <v>510.25</v>
           </cell>
           <cell r="G27">
-            <v>6.0785906785034927E-2</v>
+            <v>5.6617093373493965E-2</v>
           </cell>
           <cell r="H27" t="str">
             <v>SUBIÓ</v>
@@ -671,10 +673,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>397.42105263157896</v>
+            <v>400.6</v>
           </cell>
           <cell r="G28">
-            <v>8.4637533543572285E-2</v>
+            <v>9.3313484679320213E-2</v>
           </cell>
           <cell r="H28" t="str">
             <v>SUBIÓ</v>
@@ -682,10 +684,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>115.57894736842105</v>
+            <v>118.4</v>
           </cell>
           <cell r="G29">
-            <v>7.9718404290982203E-2</v>
+            <v>0.10607218683651798</v>
           </cell>
           <cell r="H29" t="str">
             <v>SUBIÓ</v>
@@ -693,10 +695,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>132.15789473684211</v>
+            <v>134.25</v>
           </cell>
           <cell r="G30">
-            <v>7.8439793846634354E-2</v>
+            <v>9.5511869436201824E-2</v>
           </cell>
           <cell r="H30" t="str">
             <v>SUBIÓ</v>
@@ -704,10 +706,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>645.84210526315792</v>
+            <v>641.1</v>
           </cell>
           <cell r="G31">
-            <v>-0.18323026467064418</v>
+            <v>-0.18922740859967813</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -715,10 +717,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>629.84210526315792</v>
+            <v>620.1</v>
           </cell>
           <cell r="G32">
-            <v>-3.3310568174307553E-2</v>
+            <v>-4.8262871494349047E-2</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -726,10 +728,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>836.52631578947364</v>
+            <v>828.85</v>
           </cell>
           <cell r="G33">
-            <v>-7.2511086757783838E-3</v>
+            <v>-1.6360988240371133E-2</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -737,10 +739,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>568.84210526315792</v>
+            <v>564.35</v>
           </cell>
           <cell r="G34">
-            <v>-6.1526115160837058E-3</v>
+            <v>-1.4000952986022885E-2</v>
           </cell>
           <cell r="H34" t="str">
             <v>BAJO</v>
@@ -748,10 +750,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>135.10526315789474</v>
+            <v>136.44999999999999</v>
           </cell>
           <cell r="G35">
-            <v>-0.36434649497996485</v>
+            <v>-0.35801967493584264</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -759,10 +761,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>524.0526315789474</v>
+            <v>529</v>
           </cell>
           <cell r="G36">
-            <v>0.79805955937879647</v>
+            <v>0.81503431066749843</v>
           </cell>
           <cell r="H36" t="str">
             <v>SUBIÓ</v>
@@ -770,10 +772,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>59.05263157894737</v>
+            <v>78.849999999999994</v>
           </cell>
           <cell r="G37">
-            <v>-0.84220115453214595</v>
+            <v>-0.78929916190938909</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -781,10 +783,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>300.63157894736844</v>
+            <v>296.45</v>
           </cell>
           <cell r="G38">
-            <v>0.10139795784214911</v>
+            <v>8.6078268109908374E-2</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -792,10 +794,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>531.0526315789474</v>
+            <v>524.6</v>
           </cell>
           <cell r="G39">
-            <v>0.26318065679931268</v>
+            <v>0.24783219807546764</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -803,10 +805,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>310.10526315789474</v>
+            <v>307.7</v>
           </cell>
           <cell r="G40">
-            <v>0.25826554582694272</v>
+            <v>0.24850608631501281</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -814,10 +816,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>290.78947368421052</v>
+            <v>291.2</v>
           </cell>
           <cell r="G41">
-            <v>0.10394623314109253</v>
+            <v>0.1055047454702327</v>
           </cell>
           <cell r="H41" t="str">
             <v>SUBIÓ</v>
@@ -825,10 +827,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>58.736842105263158</v>
+            <v>56.3</v>
           </cell>
           <cell r="G42">
-            <v>0.17687661777394315</v>
+            <v>0.12805100182149354</v>
           </cell>
           <cell r="H42" t="str">
             <v>SUBIÓ</v>
@@ -836,10 +838,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>107.68421052631579</v>
+            <v>104.55</v>
           </cell>
           <cell r="G43">
-            <v>0.35606905070346162</v>
+            <v>0.31659988551803098</v>
           </cell>
           <cell r="H43" t="str">
             <v>SUBIÓ</v>
@@ -847,10 +849,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>51.10526315789474</v>
+            <v>49.2</v>
           </cell>
           <cell r="G44">
-            <v>0.49113499930196847</v>
+            <v>0.43554376657824934</v>
           </cell>
           <cell r="H44" t="str">
             <v>SUBIÓ</v>
@@ -858,10 +860,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>56.789473684210527</v>
+            <v>54.4</v>
           </cell>
           <cell r="G45">
-            <v>0.51438596491228084</v>
+            <v>0.45066666666666655</v>
           </cell>
           <cell r="H45" t="str">
             <v>SUBIÓ</v>
@@ -869,10 +871,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>0.47368421052631576</v>
+            <v>0.45</v>
           </cell>
           <cell r="G46">
-            <v>-0.42105263157894746</v>
+            <v>-0.45000000000000007</v>
           </cell>
           <cell r="H46" t="str">
             <v>BAJO</v>
@@ -880,10 +882,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>2.4736842105263159</v>
+            <v>2.35</v>
           </cell>
           <cell r="G47">
-            <v>-0.24415204678362579</v>
+            <v>-0.28194444444444444</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -1146,11 +1148,11 @@
       </c>
       <c r="E2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1171.2105263157894</v>
+        <v>1147.25</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>4.7083532954623086E-2</v>
+        <v>2.5662386215864696E-2</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1175,11 +1177,11 @@
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>72.21052631578948</v>
+        <v>75.05</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-7.3684210526315685E-2</v>
+        <v>-3.7259475218658911E-2</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1204,11 +1206,11 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>493.26315789473682</v>
+        <v>485.15</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-9.9062725306416799E-2</v>
+        <v>-0.1138812785388128</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1233,11 +1235,11 @@
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>87.21052631578948</v>
+        <v>88.25</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>-0.1080280897501773</v>
+        <v>-9.7396559739655886E-2</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1262,11 +1264,11 @@
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>11.526315789473685</v>
+        <v>12.2</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>-0.30904918973182272</v>
+        <v>-0.26866485013623986</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1291,11 +1293,11 @@
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1437.6315789473683</v>
+        <v>1415.3</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>0.11021815279563674</v>
+        <v>9.2972479640550221E-2</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1320,11 +1322,11 @@
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>142.15789473684211</v>
+        <v>139.85</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>0.16349467418546371</v>
+        <v>0.14460565476190457</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1349,11 +1351,11 @@
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>327.05263157894734</v>
+        <v>321.85000000000002</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>7.6797050993241633E-2</v>
+        <v>5.9667764142472324E-2</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1378,11 +1380,11 @@
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>747.47368421052636</v>
+        <v>747.6</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>0.12911432660200362</v>
+        <v>0.12930513595166171</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1407,11 +1409,11 @@
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>348.42105263157896</v>
+        <v>350.65</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.1401836053959914</v>
+        <v>-0.13468311833987667</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1436,11 +1438,11 @@
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3459.7368421052633</v>
+        <v>3402.95</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>6.4519524570506581E-2</v>
+        <v>4.7046894449028542E-2</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1465,11 +1467,11 @@
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2253.6315789473683</v>
+        <v>2219.3000000000002</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>3.4466172943625972E-2</v>
+        <v>1.8707227507928748E-2</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1494,15 +1496,15 @@
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2191.6315789473683</v>
+        <v>2148.15</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>1.3449948226881281E-2</v>
+        <v>-6.6567176727760913E-3</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H14">
         <v>1.1599999999999999</v>
@@ -1523,11 +1525,11 @@
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2625</v>
+        <v>2573.25</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>9.1620513014384786E-2</v>
+        <v>7.0099994329244186E-2</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1552,11 +1554,11 @@
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>15.052631578947368</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.8869382401035022</v>
+        <v>-0.92714236940935468</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1581,11 +1583,11 @@
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>231.26315789473685</v>
+        <v>232.75</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>2.3906112635180277E-2</v>
+        <v>3.0489031998389926E-2</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1610,11 +1612,11 @@
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>135.05263157894737</v>
+        <v>135.55000000000001</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>-8.6921359945653864E-2</v>
+        <v>-8.3558696988321968E-2</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1639,11 +1641,11 @@
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>504.57894736842104</v>
+        <v>496.35</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>3.69674770766244E-2</v>
+        <v>2.0056048575432195E-2</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1668,15 +1670,15 @@
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>797.63157894736844</v>
+        <v>785</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>1.5350001051370743E-3</v>
+        <v>-1.4325666343245169E-2</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H20">
         <v>4.1500000000000004</v>
@@ -1726,11 +1728,11 @@
       </c>
       <c r="E22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>67.05263157894737</v>
+        <v>63.7</v>
       </c>
       <c r="F22" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>0.36336219476602793</v>
+        <v>0.29519408502772659</v>
       </c>
       <c r="G22" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1755,11 +1757,11 @@
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>712.78947368421052</v>
+        <v>709.65</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>4.0983033792659995E-2</v>
+        <v>3.6398035050451361E-2</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1784,11 +1786,11 @@
       </c>
       <c r="E24" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>1181.8421052631579</v>
+        <v>1162.95</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>6.5115165941152631E-2</v>
+        <v>4.8088976281184914E-2</v>
       </c>
       <c r="G24" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1813,11 +1815,11 @@
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>512.26315789473688</v>
+        <v>510.25</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>6.0785906785034927E-2</v>
+        <v>5.6617093373493965E-2</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1842,11 +1844,11 @@
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>397.42105263157896</v>
+        <v>400.6</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>8.4637533543572285E-2</v>
+        <v>9.3313484679320213E-2</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1871,11 +1873,11 @@
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>115.57894736842105</v>
+        <v>118.4</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>7.9718404290982203E-2</v>
+        <v>0.10607218683651798</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1900,11 +1902,11 @@
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>132.15789473684211</v>
+        <v>134.25</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>7.8439793846634354E-2</v>
+        <v>9.5511869436201824E-2</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1929,11 +1931,11 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>645.84210526315792</v>
+        <v>641.1</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-0.18323026467064418</v>
+        <v>-0.18922740859967813</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1958,11 +1960,11 @@
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>629.84210526315792</v>
+        <v>620.1</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-3.3310568174307553E-2</v>
+        <v>-4.8262871494349047E-2</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1987,11 +1989,11 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>836.52631578947364</v>
+        <v>828.85</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-7.2511086757783838E-3</v>
+        <v>-1.6360988240371133E-2</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2016,11 +2018,11 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>568.84210526315792</v>
+        <v>564.35</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-6.1526115160837058E-3</v>
+        <v>-1.4000952986022885E-2</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2045,11 +2047,11 @@
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>135.10526315789474</v>
+        <v>136.44999999999999</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-0.36434649497996485</v>
+        <v>-0.35801967493584264</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2074,11 +2076,11 @@
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>524.0526315789474</v>
+        <v>529</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>0.79805955937879647</v>
+        <v>0.81503431066749843</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2103,11 +2105,11 @@
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>59.05263157894737</v>
+        <v>78.849999999999994</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.84220115453214595</v>
+        <v>-0.78929916190938909</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2132,11 +2134,11 @@
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>300.63157894736844</v>
+        <v>296.45</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>0.10139795784214911</v>
+        <v>8.6078268109908374E-2</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2161,11 +2163,11 @@
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>531.0526315789474</v>
+        <v>524.6</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.26318065679931268</v>
+        <v>0.24783219807546764</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2190,11 +2192,11 @@
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>310.10526315789474</v>
+        <v>307.7</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>0.25826554582694272</v>
+        <v>0.24850608631501281</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2219,11 +2221,11 @@
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>290.78947368421052</v>
+        <v>291.2</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>0.10394623314109253</v>
+        <v>0.1055047454702327</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2248,11 +2250,11 @@
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>58.736842105263158</v>
+        <v>56.3</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>0.17687661777394315</v>
+        <v>0.12805100182149354</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2277,11 +2279,11 @@
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>107.68421052631579</v>
+        <v>104.55</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>0.35606905070346162</v>
+        <v>0.31659988551803098</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2306,11 +2308,11 @@
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>51.10526315789474</v>
+        <v>49.2</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>0.49113499930196847</v>
+        <v>0.43554376657824934</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2335,11 +2337,11 @@
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>56.789473684210527</v>
+        <v>54.4</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>0.51438596491228084</v>
+        <v>0.45066666666666655</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2364,11 +2366,11 @@
       </c>
       <c r="E44" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>0.47368421052631576</v>
+        <v>0.45</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-0.42105263157894746</v>
+        <v>-0.45000000000000007</v>
       </c>
       <c r="G44" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
@@ -2393,11 +2395,11 @@
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>2.4736842105263159</v>
+        <v>2.35</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.24415204678362579</v>
+        <v>-0.28194444444444444</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54ACBD84-45E9-4331-83EB-2E885FD64AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80104FE7-9FE3-431F-B6C7-624F6886D5C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -375,6 +375,7 @@
       <sheetName val="INVENTARIO NACIONAL 27-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 28-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 31-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL CIERRE"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -406,13 +407,14 @@
       <sheetData sheetId="22"/>
       <sheetData sheetId="23"/>
       <sheetData sheetId="24"/>
-      <sheetData sheetId="25">
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26">
         <row r="4">
           <cell r="F4">
-            <v>1147.25</v>
+            <v>1188.0952380952381</v>
           </cell>
           <cell r="G4">
-            <v>2.5662386215864696E-2</v>
+            <v>6.2178772679422956E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -420,10 +422,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>75.05</v>
+            <v>76.38095238095238</v>
           </cell>
           <cell r="G5">
-            <v>-3.7259475218658911E-2</v>
+            <v>-2.0186033597112352E-2</v>
           </cell>
           <cell r="H5" t="str">
             <v>BAJO</v>
@@ -431,10 +433,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>485.15</v>
+            <v>509.47619047619048</v>
           </cell>
           <cell r="G6">
-            <v>-0.1138812785388128</v>
+            <v>-6.9449880408784526E-2</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -442,21 +444,21 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>88.25</v>
+            <v>98</v>
           </cell>
           <cell r="G7">
-            <v>-9.7396559739655886E-2</v>
+            <v>2.3245002324501218E-3</v>
           </cell>
           <cell r="H7" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="8">
           <cell r="F8">
-            <v>12.2</v>
+            <v>11.952380952380953</v>
           </cell>
           <cell r="G8">
-            <v>-0.26866485013623986</v>
+            <v>-0.2835084987673544</v>
           </cell>
           <cell r="H8" t="str">
             <v>BAJO</v>
@@ -464,10 +466,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1415.3</v>
+            <v>1460.3333333333333</v>
           </cell>
           <cell r="G9">
-            <v>9.2972479640550221E-2</v>
+            <v>0.12774969577833928</v>
           </cell>
           <cell r="H9" t="str">
             <v>SUBIÓ</v>
@@ -475,10 +477,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>139.85</v>
+            <v>150.38095238095238</v>
           </cell>
           <cell r="G10">
-            <v>0.14460565476190457</v>
+            <v>0.2307964852607709</v>
           </cell>
           <cell r="H10" t="str">
             <v>SUBIÓ</v>
@@ -486,10 +488,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>321.85000000000002</v>
+            <v>343.57142857142856</v>
           </cell>
           <cell r="G11">
-            <v>5.9667764142472324E-2</v>
+            <v>0.13118399110617007</v>
           </cell>
           <cell r="H11" t="str">
             <v>SUBIÓ</v>
@@ -497,10 +499,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>747.6</v>
+            <v>766.19047619047615</v>
           </cell>
           <cell r="G12">
-            <v>0.12930513595166171</v>
+            <v>0.15738742626960134</v>
           </cell>
           <cell r="H12" t="str">
             <v>SUBIÓ</v>
@@ -508,10 +510,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>350.65</v>
+            <v>362.8095238095238</v>
           </cell>
           <cell r="G13">
-            <v>-0.13468311833987667</v>
+            <v>-0.10467644152445055</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -519,10 +521,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3402.95</v>
+            <v>3521.5238095238096</v>
           </cell>
           <cell r="G14">
-            <v>4.7046894449028542E-2</v>
+            <v>8.3530633271196475E-2</v>
           </cell>
           <cell r="H14" t="str">
             <v>SUBIÓ</v>
@@ -530,10 +532,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2219.3000000000002</v>
+            <v>2305</v>
           </cell>
           <cell r="G15">
-            <v>1.8707227507928748E-2</v>
+            <v>5.8045401435486532E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>SUBIÓ</v>
@@ -541,21 +543,21 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2148.15</v>
+            <v>2266.4761904761904</v>
           </cell>
           <cell r="G16">
-            <v>-6.6567176727760913E-3</v>
+            <v>4.8059445738948048E-2</v>
           </cell>
           <cell r="H16" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2573.25</v>
+            <v>2674</v>
           </cell>
           <cell r="G17">
-            <v>7.0099994329244186E-2</v>
+            <v>0.11199742925732004</v>
           </cell>
           <cell r="H17" t="str">
             <v>SUBIÓ</v>
@@ -563,10 +565,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>9.6999999999999993</v>
+            <v>11.666666666666666</v>
           </cell>
           <cell r="G18">
-            <v>-0.92714236940935468</v>
+            <v>-0.91237054739956758</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -574,10 +576,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>232.75</v>
+            <v>242</v>
           </cell>
           <cell r="G19">
-            <v>3.0489031998389926E-2</v>
+            <v>7.1442946266854435E-2</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -585,10 +587,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>135.55000000000001</v>
+            <v>142.1904761904762</v>
           </cell>
           <cell r="G20">
-            <v>-8.3558696988321968E-2</v>
+            <v>-3.8663037433781078E-2</v>
           </cell>
           <cell r="H20" t="str">
             <v>BAJO</v>
@@ -596,10 +598,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>496.35</v>
+            <v>513.09523809523807</v>
           </cell>
           <cell r="G21">
-            <v>2.0056048575432195E-2</v>
+            <v>5.4469429060741481E-2</v>
           </cell>
           <cell r="H21" t="str">
             <v>SUBIÓ</v>
@@ -607,13 +609,13 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>785</v>
+            <v>811.38095238095241</v>
           </cell>
           <cell r="G22">
-            <v>-1.4325666343245169E-2</v>
+            <v>1.8799209655895988E-2</v>
           </cell>
           <cell r="H22" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="23">
@@ -629,10 +631,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>63.7</v>
+            <v>74.952380952380949</v>
           </cell>
           <cell r="G24">
-            <v>0.29519408502772659</v>
+            <v>0.52398556465099899</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -640,10 +642,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>709.65</v>
+            <v>787.95238095238096</v>
           </cell>
           <cell r="G25">
-            <v>3.6398035050451361E-2</v>
+            <v>0.15075360999418352</v>
           </cell>
           <cell r="H25" t="str">
             <v>SUBIÓ</v>
@@ -651,10 +653,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>1162.95</v>
+            <v>1273.7142857142858</v>
           </cell>
           <cell r="G26">
-            <v>4.8088976281184914E-2</v>
+            <v>0.14791341140118353</v>
           </cell>
           <cell r="H26" t="str">
             <v>SUBIÓ</v>
@@ -662,10 +664,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>510.25</v>
+            <v>529.19047619047615</v>
           </cell>
           <cell r="G27">
-            <v>5.6617093373493965E-2</v>
+            <v>9.5838711990820169E-2</v>
           </cell>
           <cell r="H27" t="str">
             <v>SUBIÓ</v>
@@ -673,10 +675,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>400.6</v>
+            <v>401.85714285714283</v>
           </cell>
           <cell r="G28">
-            <v>9.3313484679320213E-2</v>
+            <v>9.6744466301593057E-2</v>
           </cell>
           <cell r="H28" t="str">
             <v>SUBIÓ</v>
@@ -684,10 +686,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>118.4</v>
+            <v>127.85714285714286</v>
           </cell>
           <cell r="G29">
-            <v>0.10607218683651798</v>
+            <v>0.19441916894146205</v>
           </cell>
           <cell r="H29" t="str">
             <v>SUBIÓ</v>
@@ -695,10 +697,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>134.25</v>
+            <v>143.33333333333334</v>
           </cell>
           <cell r="G30">
-            <v>9.5511869436201824E-2</v>
+            <v>0.16963402571711184</v>
           </cell>
           <cell r="H30" t="str">
             <v>SUBIÓ</v>
@@ -706,10 +708,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>641.1</v>
+            <v>652.19047619047615</v>
           </cell>
           <cell r="G31">
-            <v>-0.18922740859967813</v>
+            <v>-0.17520174314839765</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -717,10 +719,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>620.1</v>
+            <v>629.04761904761904</v>
           </cell>
           <cell r="G32">
-            <v>-4.8262871494349047E-2</v>
+            <v>-3.4529955417355929E-2</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -728,32 +730,32 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>828.85</v>
+            <v>852.19047619047615</v>
           </cell>
           <cell r="G33">
-            <v>-1.6360988240371133E-2</v>
+            <v>1.1338357761920159E-2</v>
           </cell>
           <cell r="H33" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="34">
           <cell r="F34">
-            <v>564.35</v>
+            <v>579</v>
           </cell>
           <cell r="G34">
-            <v>-1.4000952986022885E-2</v>
+            <v>1.1594663278271966E-2</v>
           </cell>
           <cell r="H34" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="35">
           <cell r="F35">
-            <v>136.44999999999999</v>
+            <v>137.14285714285714</v>
           </cell>
           <cell r="G35">
-            <v>-0.35801967493584264</v>
+            <v>-0.3547598680190639</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -761,10 +763,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>529</v>
+            <v>554.42857142857144</v>
           </cell>
           <cell r="G36">
-            <v>0.81503431066749843</v>
+            <v>0.90228143659210436</v>
           </cell>
           <cell r="H36" t="str">
             <v>SUBIÓ</v>
@@ -772,10 +774,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>78.849999999999994</v>
+            <v>132.8095238095238</v>
           </cell>
           <cell r="G37">
-            <v>-0.78929916190938909</v>
+            <v>-0.64510998131792507</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -783,10 +785,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>296.45</v>
+            <v>296.14285714285717</v>
           </cell>
           <cell r="G38">
-            <v>8.6078268109908374E-2</v>
+            <v>8.4953015344356064E-2</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -794,10 +796,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>524.6</v>
+            <v>528.71428571428567</v>
           </cell>
           <cell r="G39">
-            <v>0.24783219807546764</v>
+            <v>0.25761858424848993</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -805,10 +807,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>307.7</v>
+            <v>305.57142857142856</v>
           </cell>
           <cell r="G40">
-            <v>0.24850608631501281</v>
+            <v>0.2398693154871685</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -816,10 +818,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>291.2</v>
+            <v>289.90476190476193</v>
           </cell>
           <cell r="G41">
-            <v>0.1055047454702327</v>
+            <v>0.10058753440979484</v>
           </cell>
           <cell r="H41" t="str">
             <v>SUBIÓ</v>
@@ -827,10 +829,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>56.3</v>
+            <v>57.714285714285715</v>
           </cell>
           <cell r="G42">
-            <v>0.12805100182149354</v>
+            <v>0.15638823835545157</v>
           </cell>
           <cell r="H42" t="str">
             <v>SUBIÓ</v>
@@ -838,10 +840,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>104.55</v>
+            <v>104.71428571428571</v>
           </cell>
           <cell r="G43">
-            <v>0.31659988551803098</v>
+            <v>0.31866873824515496</v>
           </cell>
           <cell r="H43" t="str">
             <v>SUBIÓ</v>
@@ -849,10 +851,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>49.2</v>
+            <v>49.333333333333336</v>
           </cell>
           <cell r="G44">
-            <v>0.43554376657824934</v>
+            <v>0.43943412908930157</v>
           </cell>
           <cell r="H44" t="str">
             <v>SUBIÓ</v>
@@ -860,10 +862,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>54.4</v>
+            <v>55.333333333333336</v>
           </cell>
           <cell r="G45">
-            <v>0.45066666666666655</v>
+            <v>0.47555555555555551</v>
           </cell>
           <cell r="H45" t="str">
             <v>SUBIÓ</v>
@@ -871,10 +873,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>0.45</v>
+            <v>0.42857142857142855</v>
           </cell>
           <cell r="G46">
-            <v>-0.45000000000000007</v>
+            <v>-0.47619047619047628</v>
           </cell>
           <cell r="H46" t="str">
             <v>BAJO</v>
@@ -882,10 +884,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>2.35</v>
+            <v>2.4761904761904763</v>
           </cell>
           <cell r="G47">
-            <v>-0.28194444444444444</v>
+            <v>-0.24338624338624337</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -1147,15 +1149,15 @@
         <v>1118.5454545454545</v>
       </c>
       <c r="E2" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1147.25</v>
+        <f>'[1]DESV. VTS BY SKU'!F4</f>
+        <v>1188.0952380952381</v>
       </c>
       <c r="F2" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>2.5662386215864696E-2</v>
+        <f>'[1]DESV. VTS BY SKU'!G4</f>
+        <v>6.2178772679422956E-2</v>
       </c>
       <c r="G2" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
+        <f>'[1]DESV. VTS BY SKU'!H4</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H2">
@@ -1176,15 +1178,15 @@
         <v>77.954545454545453</v>
       </c>
       <c r="E3" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>75.05</v>
+        <f>'[1]DESV. VTS BY SKU'!F5</f>
+        <v>76.38095238095238</v>
       </c>
       <c r="F3" s="7">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-3.7259475218658911E-2</v>
+        <f>'[1]DESV. VTS BY SKU'!G5</f>
+        <v>-2.0186033597112352E-2</v>
       </c>
       <c r="G3" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
+        <f>'[1]DESV. VTS BY SKU'!H5</f>
         <v>BAJO</v>
       </c>
       <c r="H3">
@@ -1205,15 +1207,15 @@
         <v>547.5</v>
       </c>
       <c r="E4" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>485.15</v>
+        <f>'[1]DESV. VTS BY SKU'!F6</f>
+        <v>509.47619047619048</v>
       </c>
       <c r="F4" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-0.1138812785388128</v>
+        <f>'[1]DESV. VTS BY SKU'!G6</f>
+        <v>-6.9449880408784526E-2</v>
       </c>
       <c r="G4" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
+        <f>'[1]DESV. VTS BY SKU'!H6</f>
         <v>BAJO</v>
       </c>
       <c r="H4">
@@ -1234,16 +1236,16 @@
         <v>97.772727272727266</v>
       </c>
       <c r="E5" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>88.25</v>
+        <f>'[1]DESV. VTS BY SKU'!F7</f>
+        <v>98</v>
       </c>
       <c r="F5" s="7">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>-9.7396559739655886E-2</v>
+        <f>'[1]DESV. VTS BY SKU'!G7</f>
+        <v>2.3245002324501218E-3</v>
       </c>
       <c r="G5" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
-        <v>BAJO</v>
+        <f>'[1]DESV. VTS BY SKU'!H7</f>
+        <v>SUBIÓ</v>
       </c>
       <c r="H5">
         <v>3.61</v>
@@ -1263,15 +1265,15 @@
         <v>16.681818181818183</v>
       </c>
       <c r="E6" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>12.2</v>
+        <f>'[1]DESV. VTS BY SKU'!F8</f>
+        <v>11.952380952380953</v>
       </c>
       <c r="F6" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>-0.26866485013623986</v>
+        <f>'[1]DESV. VTS BY SKU'!G8</f>
+        <v>-0.2835084987673544</v>
       </c>
       <c r="G6" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
+        <f>'[1]DESV. VTS BY SKU'!H8</f>
         <v>BAJO</v>
       </c>
       <c r="H6">
@@ -1292,15 +1294,15 @@
         <v>1294.909090909091</v>
       </c>
       <c r="E7" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1415.3</v>
+        <f>'[1]DESV. VTS BY SKU'!F9</f>
+        <v>1460.3333333333333</v>
       </c>
       <c r="F7" s="7">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>9.2972479640550221E-2</v>
+        <f>'[1]DESV. VTS BY SKU'!G9</f>
+        <v>0.12774969577833928</v>
       </c>
       <c r="G7" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
+        <f>'[1]DESV. VTS BY SKU'!H9</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H7">
@@ -1321,15 +1323,15 @@
         <v>122.18181818181819</v>
       </c>
       <c r="E8" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>139.85</v>
+        <f>'[1]DESV. VTS BY SKU'!F10</f>
+        <v>150.38095238095238</v>
       </c>
       <c r="F8" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>0.14460565476190457</v>
+        <f>'[1]DESV. VTS BY SKU'!G10</f>
+        <v>0.2307964852607709</v>
       </c>
       <c r="G8" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
+        <f>'[1]DESV. VTS BY SKU'!H10</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H8">
@@ -1350,15 +1352,15 @@
         <v>303.72727272727275</v>
       </c>
       <c r="E9" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>321.85000000000002</v>
+        <f>'[1]DESV. VTS BY SKU'!F11</f>
+        <v>343.57142857142856</v>
       </c>
       <c r="F9" s="7">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>5.9667764142472324E-2</v>
+        <f>'[1]DESV. VTS BY SKU'!G11</f>
+        <v>0.13118399110617007</v>
       </c>
       <c r="G9" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
+        <f>'[1]DESV. VTS BY SKU'!H11</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H9">
@@ -1379,15 +1381,15 @@
         <v>662</v>
       </c>
       <c r="E10" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>747.6</v>
+        <f>'[1]DESV. VTS BY SKU'!F12</f>
+        <v>766.19047619047615</v>
       </c>
       <c r="F10" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>0.12930513595166171</v>
+        <f>'[1]DESV. VTS BY SKU'!G12</f>
+        <v>0.15738742626960134</v>
       </c>
       <c r="G10" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
+        <f>'[1]DESV. VTS BY SKU'!H12</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H10">
@@ -1408,15 +1410,15 @@
         <v>405.22727272727275</v>
       </c>
       <c r="E11" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>350.65</v>
+        <f>'[1]DESV. VTS BY SKU'!F13</f>
+        <v>362.8095238095238</v>
       </c>
       <c r="F11" s="7">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.13468311833987667</v>
+        <f>'[1]DESV. VTS BY SKU'!G13</f>
+        <v>-0.10467644152445055</v>
       </c>
       <c r="G11" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
+        <f>'[1]DESV. VTS BY SKU'!H13</f>
         <v>BAJO</v>
       </c>
       <c r="H11">
@@ -1437,15 +1439,15 @@
         <v>3250.0454545454545</v>
       </c>
       <c r="E12" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3402.95</v>
+        <f>'[1]DESV. VTS BY SKU'!F14</f>
+        <v>3521.5238095238096</v>
       </c>
       <c r="F12" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>4.7046894449028542E-2</v>
+        <f>'[1]DESV. VTS BY SKU'!G14</f>
+        <v>8.3530633271196475E-2</v>
       </c>
       <c r="G12" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
+        <f>'[1]DESV. VTS BY SKU'!H14</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H12">
@@ -1466,15 +1468,15 @@
         <v>2178.5454545454545</v>
       </c>
       <c r="E13" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2219.3000000000002</v>
+        <f>'[1]DESV. VTS BY SKU'!F15</f>
+        <v>2305</v>
       </c>
       <c r="F13" s="7">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>1.8707227507928748E-2</v>
+        <f>'[1]DESV. VTS BY SKU'!G15</f>
+        <v>5.8045401435486532E-2</v>
       </c>
       <c r="G13" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
+        <f>'[1]DESV. VTS BY SKU'!H15</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H13">
@@ -1495,16 +1497,16 @@
         <v>2162.5454545454545</v>
       </c>
       <c r="E14" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2148.15</v>
+        <f>'[1]DESV. VTS BY SKU'!F16</f>
+        <v>2266.4761904761904</v>
       </c>
       <c r="F14" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-6.6567176727760913E-3</v>
+        <f>'[1]DESV. VTS BY SKU'!G16</f>
+        <v>4.8059445738948048E-2</v>
       </c>
       <c r="G14" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
-        <v>BAJO</v>
+        <f>'[1]DESV. VTS BY SKU'!H16</f>
+        <v>SUBIÓ</v>
       </c>
       <c r="H14">
         <v>1.1599999999999999</v>
@@ -1524,15 +1526,15 @@
         <v>2404.681818181818</v>
       </c>
       <c r="E15" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2573.25</v>
+        <f>'[1]DESV. VTS BY SKU'!F17</f>
+        <v>2674</v>
       </c>
       <c r="F15" s="7">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>7.0099994329244186E-2</v>
+        <f>'[1]DESV. VTS BY SKU'!G17</f>
+        <v>0.11199742925732004</v>
       </c>
       <c r="G15" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
+        <f>'[1]DESV. VTS BY SKU'!H17</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H15">
@@ -1553,15 +1555,15 @@
         <v>133.13636363636363</v>
       </c>
       <c r="E16" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>9.6999999999999993</v>
+        <f>'[1]DESV. VTS BY SKU'!F18</f>
+        <v>11.666666666666666</v>
       </c>
       <c r="F16" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.92714236940935468</v>
+        <f>'[1]DESV. VTS BY SKU'!G18</f>
+        <v>-0.91237054739956758</v>
       </c>
       <c r="G16" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
+        <f>'[1]DESV. VTS BY SKU'!H18</f>
         <v>BAJO</v>
       </c>
       <c r="H16">
@@ -1582,15 +1584,15 @@
         <v>225.86363636363637</v>
       </c>
       <c r="E17" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>232.75</v>
+        <f>'[1]DESV. VTS BY SKU'!F19</f>
+        <v>242</v>
       </c>
       <c r="F17" s="7">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>3.0489031998389926E-2</v>
+        <f>'[1]DESV. VTS BY SKU'!G19</f>
+        <v>7.1442946266854435E-2</v>
       </c>
       <c r="G17" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
+        <f>'[1]DESV. VTS BY SKU'!H19</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H17">
@@ -1611,15 +1613,15 @@
         <v>147.90909090909091</v>
       </c>
       <c r="E18" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>135.55000000000001</v>
+        <f>'[1]DESV. VTS BY SKU'!F20</f>
+        <v>142.1904761904762</v>
       </c>
       <c r="F18" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>-8.3558696988321968E-2</v>
+        <f>'[1]DESV. VTS BY SKU'!G20</f>
+        <v>-3.8663037433781078E-2</v>
       </c>
       <c r="G18" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
+        <f>'[1]DESV. VTS BY SKU'!H20</f>
         <v>BAJO</v>
       </c>
       <c r="H18">
@@ -1640,15 +1642,15 @@
         <v>486.59090909090907</v>
       </c>
       <c r="E19" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>496.35</v>
+        <f>'[1]DESV. VTS BY SKU'!F21</f>
+        <v>513.09523809523807</v>
       </c>
       <c r="F19" s="7">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>2.0056048575432195E-2</v>
+        <f>'[1]DESV. VTS BY SKU'!G21</f>
+        <v>5.4469429060741481E-2</v>
       </c>
       <c r="G19" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
+        <f>'[1]DESV. VTS BY SKU'!H21</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H19">
@@ -1669,16 +1671,16 @@
         <v>796.40909090909088</v>
       </c>
       <c r="E20" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>785</v>
+        <f>'[1]DESV. VTS BY SKU'!F22</f>
+        <v>811.38095238095241</v>
       </c>
       <c r="F20" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-1.4325666343245169E-2</v>
+        <f>'[1]DESV. VTS BY SKU'!G22</f>
+        <v>1.8799209655895988E-2</v>
       </c>
       <c r="G20" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
-        <v>BAJO</v>
+        <f>'[1]DESV. VTS BY SKU'!H22</f>
+        <v>SUBIÓ</v>
       </c>
       <c r="H20">
         <v>4.1500000000000004</v>
@@ -1698,15 +1700,15 @@
         <v>5</v>
       </c>
       <c r="E21" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
+        <f>'[1]DESV. VTS BY SKU'!F23</f>
         <v>0</v>
       </c>
       <c r="F21" s="7">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
+        <f>'[1]DESV. VTS BY SKU'!G23</f>
         <v>-1</v>
       </c>
       <c r="G21" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
+        <f>'[1]DESV. VTS BY SKU'!H23</f>
         <v>BAJO</v>
       </c>
       <c r="H21">
@@ -1727,15 +1729,15 @@
         <v>49.18181818181818</v>
       </c>
       <c r="E22" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>63.7</v>
+        <f>'[1]DESV. VTS BY SKU'!F24</f>
+        <v>74.952380952380949</v>
       </c>
       <c r="F22" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>0.29519408502772659</v>
+        <f>'[1]DESV. VTS BY SKU'!G24</f>
+        <v>0.52398556465099899</v>
       </c>
       <c r="G22" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
+        <f>'[1]DESV. VTS BY SKU'!H24</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H22">
@@ -1756,15 +1758,15 @@
         <v>684.72727272727275</v>
       </c>
       <c r="E23" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>709.65</v>
+        <f>'[1]DESV. VTS BY SKU'!F25</f>
+        <v>787.95238095238096</v>
       </c>
       <c r="F23" s="7">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>3.6398035050451361E-2</v>
+        <f>'[1]DESV. VTS BY SKU'!G25</f>
+        <v>0.15075360999418352</v>
       </c>
       <c r="G23" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
+        <f>'[1]DESV. VTS BY SKU'!H25</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H23">
@@ -1785,15 +1787,15 @@
         <v>1109.590909090909</v>
       </c>
       <c r="E24" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>1162.95</v>
+        <f>'[1]DESV. VTS BY SKU'!F26</f>
+        <v>1273.7142857142858</v>
       </c>
       <c r="F24" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>4.8088976281184914E-2</v>
+        <f>'[1]DESV. VTS BY SKU'!G26</f>
+        <v>0.14791341140118353</v>
       </c>
       <c r="G24" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
+        <f>'[1]DESV. VTS BY SKU'!H26</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H24">
@@ -1814,15 +1816,15 @@
         <v>482.90909090909093</v>
       </c>
       <c r="E25" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>510.25</v>
+        <f>'[1]DESV. VTS BY SKU'!F27</f>
+        <v>529.19047619047615</v>
       </c>
       <c r="F25" s="7">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>5.6617093373493965E-2</v>
+        <f>'[1]DESV. VTS BY SKU'!G27</f>
+        <v>9.5838711990820169E-2</v>
       </c>
       <c r="G25" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
+        <f>'[1]DESV. VTS BY SKU'!H27</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H25">
@@ -1843,15 +1845,15 @@
         <v>366.40909090909093</v>
       </c>
       <c r="E26" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>400.6</v>
+        <f>'[1]DESV. VTS BY SKU'!F28</f>
+        <v>401.85714285714283</v>
       </c>
       <c r="F26" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>9.3313484679320213E-2</v>
+        <f>'[1]DESV. VTS BY SKU'!G28</f>
+        <v>9.6744466301593057E-2</v>
       </c>
       <c r="G26" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
+        <f>'[1]DESV. VTS BY SKU'!H28</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H26">
@@ -1872,15 +1874,15 @@
         <v>107.04545454545455</v>
       </c>
       <c r="E27" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>118.4</v>
+        <f>'[1]DESV. VTS BY SKU'!F29</f>
+        <v>127.85714285714286</v>
       </c>
       <c r="F27" s="7">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>0.10607218683651798</v>
+        <f>'[1]DESV. VTS BY SKU'!G29</f>
+        <v>0.19441916894146205</v>
       </c>
       <c r="G27" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
+        <f>'[1]DESV. VTS BY SKU'!H29</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H27">
@@ -1901,15 +1903,15 @@
         <v>122.54545454545455</v>
       </c>
       <c r="E28" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>134.25</v>
+        <f>'[1]DESV. VTS BY SKU'!F30</f>
+        <v>143.33333333333334</v>
       </c>
       <c r="F28" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>9.5511869436201824E-2</v>
+        <f>'[1]DESV. VTS BY SKU'!G30</f>
+        <v>0.16963402571711184</v>
       </c>
       <c r="G28" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
+        <f>'[1]DESV. VTS BY SKU'!H30</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H28">
@@ -1930,15 +1932,15 @@
         <v>790.72727272727275</v>
       </c>
       <c r="E29" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>641.1</v>
+        <f>'[1]DESV. VTS BY SKU'!F31</f>
+        <v>652.19047619047615</v>
       </c>
       <c r="F29" s="7">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-0.18922740859967813</v>
+        <f>'[1]DESV. VTS BY SKU'!G31</f>
+        <v>-0.17520174314839765</v>
       </c>
       <c r="G29" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
+        <f>'[1]DESV. VTS BY SKU'!H31</f>
         <v>BAJO</v>
       </c>
       <c r="H29">
@@ -1959,15 +1961,15 @@
         <v>651.5454545454545</v>
       </c>
       <c r="E30" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>620.1</v>
+        <f>'[1]DESV. VTS BY SKU'!F32</f>
+        <v>629.04761904761904</v>
       </c>
       <c r="F30" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-4.8262871494349047E-2</v>
+        <f>'[1]DESV. VTS BY SKU'!G32</f>
+        <v>-3.4529955417355929E-2</v>
       </c>
       <c r="G30" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
+        <f>'[1]DESV. VTS BY SKU'!H32</f>
         <v>BAJO</v>
       </c>
       <c r="H30">
@@ -1988,16 +1990,16 @@
         <v>842.63636363636363</v>
       </c>
       <c r="E31" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>828.85</v>
+        <f>'[1]DESV. VTS BY SKU'!F33</f>
+        <v>852.19047619047615</v>
       </c>
       <c r="F31" s="7">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-1.6360988240371133E-2</v>
+        <f>'[1]DESV. VTS BY SKU'!G33</f>
+        <v>1.1338357761920159E-2</v>
       </c>
       <c r="G31" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
-        <v>BAJO</v>
+        <f>'[1]DESV. VTS BY SKU'!H33</f>
+        <v>SUBIÓ</v>
       </c>
       <c r="H31">
         <v>1.1599999999999999</v>
@@ -2017,16 +2019,16 @@
         <v>572.36363636363637</v>
       </c>
       <c r="E32" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>564.35</v>
+        <f>'[1]DESV. VTS BY SKU'!F34</f>
+        <v>579</v>
       </c>
       <c r="F32" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-1.4000952986022885E-2</v>
+        <f>'[1]DESV. VTS BY SKU'!G34</f>
+        <v>1.1594663278271966E-2</v>
       </c>
       <c r="G32" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
-        <v>BAJO</v>
+        <f>'[1]DESV. VTS BY SKU'!H34</f>
+        <v>SUBIÓ</v>
       </c>
       <c r="H32">
         <v>1.1599999999999999</v>
@@ -2046,15 +2048,15 @@
         <v>212.54545454545453</v>
       </c>
       <c r="E33" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>136.44999999999999</v>
+        <f>'[1]DESV. VTS BY SKU'!F35</f>
+        <v>137.14285714285714</v>
       </c>
       <c r="F33" s="7">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-0.35801967493584264</v>
+        <f>'[1]DESV. VTS BY SKU'!G35</f>
+        <v>-0.3547598680190639</v>
       </c>
       <c r="G33" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
+        <f>'[1]DESV. VTS BY SKU'!H35</f>
         <v>BAJO</v>
       </c>
       <c r="H33">
@@ -2075,15 +2077,15 @@
         <v>291.45454545454544</v>
       </c>
       <c r="E34" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>529</v>
+        <f>'[1]DESV. VTS BY SKU'!F36</f>
+        <v>554.42857142857144</v>
       </c>
       <c r="F34" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>0.81503431066749843</v>
+        <f>'[1]DESV. VTS BY SKU'!G36</f>
+        <v>0.90228143659210436</v>
       </c>
       <c r="G34" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
+        <f>'[1]DESV. VTS BY SKU'!H36</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H34">
@@ -2104,15 +2106,15 @@
         <v>374.22727272727275</v>
       </c>
       <c r="E35" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>78.849999999999994</v>
+        <f>'[1]DESV. VTS BY SKU'!F37</f>
+        <v>132.8095238095238</v>
       </c>
       <c r="F35" s="7">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.78929916190938909</v>
+        <f>'[1]DESV. VTS BY SKU'!G37</f>
+        <v>-0.64510998131792507</v>
       </c>
       <c r="G35" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
+        <f>'[1]DESV. VTS BY SKU'!H37</f>
         <v>BAJO</v>
       </c>
       <c r="H35">
@@ -2133,15 +2135,15 @@
         <v>272.95454545454544</v>
       </c>
       <c r="E36" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>296.45</v>
+        <f>'[1]DESV. VTS BY SKU'!F38</f>
+        <v>296.14285714285717</v>
       </c>
       <c r="F36" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>8.6078268109908374E-2</v>
+        <f>'[1]DESV. VTS BY SKU'!G38</f>
+        <v>8.4953015344356064E-2</v>
       </c>
       <c r="G36" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
+        <f>'[1]DESV. VTS BY SKU'!H38</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H36">
@@ -2162,15 +2164,15 @@
         <v>420.40909090909093</v>
       </c>
       <c r="E37" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>524.6</v>
+        <f>'[1]DESV. VTS BY SKU'!F39</f>
+        <v>528.71428571428567</v>
       </c>
       <c r="F37" s="7">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.24783219807546764</v>
+        <f>'[1]DESV. VTS BY SKU'!G39</f>
+        <v>0.25761858424848993</v>
       </c>
       <c r="G37" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
+        <f>'[1]DESV. VTS BY SKU'!H39</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H37">
@@ -2191,15 +2193,15 @@
         <v>246.45454545454547</v>
       </c>
       <c r="E38" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>307.7</v>
+        <f>'[1]DESV. VTS BY SKU'!F40</f>
+        <v>305.57142857142856</v>
       </c>
       <c r="F38" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>0.24850608631501281</v>
+        <f>'[1]DESV. VTS BY SKU'!G40</f>
+        <v>0.2398693154871685</v>
       </c>
       <c r="G38" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
+        <f>'[1]DESV. VTS BY SKU'!H40</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H38">
@@ -2220,15 +2222,15 @@
         <v>263.40909090909093</v>
       </c>
       <c r="E39" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>291.2</v>
+        <f>'[1]DESV. VTS BY SKU'!F41</f>
+        <v>289.90476190476193</v>
       </c>
       <c r="F39" s="7">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>0.1055047454702327</v>
+        <f>'[1]DESV. VTS BY SKU'!G41</f>
+        <v>0.10058753440979484</v>
       </c>
       <c r="G39" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
+        <f>'[1]DESV. VTS BY SKU'!H41</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H39">
@@ -2249,15 +2251,15 @@
         <v>49.909090909090907</v>
       </c>
       <c r="E40" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>56.3</v>
+        <f>'[1]DESV. VTS BY SKU'!F42</f>
+        <v>57.714285714285715</v>
       </c>
       <c r="F40" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>0.12805100182149354</v>
+        <f>'[1]DESV. VTS BY SKU'!G42</f>
+        <v>0.15638823835545157</v>
       </c>
       <c r="G40" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
+        <f>'[1]DESV. VTS BY SKU'!H42</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H40">
@@ -2278,15 +2280,15 @@
         <v>79.409090909090907</v>
       </c>
       <c r="E41" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>104.55</v>
+        <f>'[1]DESV. VTS BY SKU'!F43</f>
+        <v>104.71428571428571</v>
       </c>
       <c r="F41" s="7">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>0.31659988551803098</v>
+        <f>'[1]DESV. VTS BY SKU'!G43</f>
+        <v>0.31866873824515496</v>
       </c>
       <c r="G41" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
+        <f>'[1]DESV. VTS BY SKU'!H43</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H41">
@@ -2307,15 +2309,15 @@
         <v>34.272727272727273</v>
       </c>
       <c r="E42" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>49.2</v>
+        <f>'[1]DESV. VTS BY SKU'!F44</f>
+        <v>49.333333333333336</v>
       </c>
       <c r="F42" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>0.43554376657824934</v>
+        <f>'[1]DESV. VTS BY SKU'!G44</f>
+        <v>0.43943412908930157</v>
       </c>
       <c r="G42" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
+        <f>'[1]DESV. VTS BY SKU'!H44</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H42">
@@ -2336,15 +2338,15 @@
         <v>37.5</v>
       </c>
       <c r="E43" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>54.4</v>
+        <f>'[1]DESV. VTS BY SKU'!F45</f>
+        <v>55.333333333333336</v>
       </c>
       <c r="F43" s="7">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>0.45066666666666655</v>
+        <f>'[1]DESV. VTS BY SKU'!G45</f>
+        <v>0.47555555555555551</v>
       </c>
       <c r="G43" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
+        <f>'[1]DESV. VTS BY SKU'!H45</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H43">
@@ -2365,15 +2367,15 @@
         <v>0.81818181818181823</v>
       </c>
       <c r="E44" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>0.45</v>
+        <f>'[1]DESV. VTS BY SKU'!F46</f>
+        <v>0.42857142857142855</v>
       </c>
       <c r="F44" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-0.45000000000000007</v>
+        <f>'[1]DESV. VTS BY SKU'!G46</f>
+        <v>-0.47619047619047628</v>
       </c>
       <c r="G44" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
+        <f>'[1]DESV. VTS BY SKU'!H46</f>
         <v>BAJO</v>
       </c>
       <c r="H44">
@@ -2394,15 +2396,15 @@
         <v>3.2727272727272729</v>
       </c>
       <c r="E45" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>2.35</v>
+        <f>'[1]DESV. VTS BY SKU'!F47</f>
+        <v>2.4761904761904763</v>
       </c>
       <c r="F45" s="7">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.28194444444444444</v>
+        <f>'[1]DESV. VTS BY SKU'!G47</f>
+        <v>-0.24338624338624337</v>
       </c>
       <c r="G45" s="8" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
+        <f>'[1]DESV. VTS BY SKU'!H47</f>
         <v>BAJO</v>
       </c>
       <c r="H45">

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80104FE7-9FE3-431F-B6C7-624F6886D5C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0594D04-A4EC-4121-8DE8-47AD5FDB08C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="64">
   <si>
     <t>REFERENCIA INTERNA</t>
   </si>
@@ -91,9 +91,6 @@
     <t>Cremigurt Griego 150g</t>
   </si>
   <si>
-    <t>Cremigurt Light 150g</t>
-  </si>
-  <si>
     <t>Cremigurt Natural 700g</t>
   </si>
   <si>
@@ -106,9 +103,6 @@
     <t>Cremigurt Griego 700g</t>
   </si>
   <si>
-    <t>Cremigurt Light 700g</t>
-  </si>
-  <si>
     <t>Griego Mykonos 700g</t>
   </si>
   <si>
@@ -193,9 +187,6 @@
     <t>Tevia Tropical Punch 1.5 L</t>
   </si>
   <si>
-    <t>Not in source</t>
-  </si>
-  <si>
     <t>PRECIO UNITARIO</t>
   </si>
   <si>
@@ -220,7 +211,22 @@
     <t>PROMD VTA DIA AGOSTO</t>
   </si>
   <si>
-    <t>PROMD VTA DIA JULIO</t>
+    <t>Cremigurt Power Piña Colada 150g</t>
+  </si>
+  <si>
+    <t>Cremigurt Power Dulce de Leche 150g</t>
+  </si>
+  <si>
+    <t>Cremigurt Griego Mango 150g</t>
+  </si>
+  <si>
+    <t>Cremigurt Griego Ciruela 150g</t>
+  </si>
+  <si>
+    <t>Cremigurt Griego Mora 150g</t>
+  </si>
+  <si>
+    <t>PROMD VTA DIA SEPTIEMBRE</t>
   </si>
 </sst>
 </file>
@@ -316,9 +322,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -328,6 +331,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -353,31 +359,11 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="INVENTARIO NACIONAL 04-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 05-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 06-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 07-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 10-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 11-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 12-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 13-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 14-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 17-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 18-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 19-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 19-08-26-2"/>
-      <sheetName val="INVENTARIO NACIONAL 20-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 20-08-26-2"/>
-      <sheetName val="INVENTARIO NACIONAL 21-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 24-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 25-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 25-08-26-2"/>
-      <sheetName val="INVENTARIO NACIONAL 27-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 28-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 31-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL CIERRE"/>
+      <sheetName val="INVENTARIO NACIONAL INICIO"/>
+      <sheetName val="INVENTARIO NACIONAL 02-09-2026"/>
+      <sheetName val="INVENTARIO NACIONAL 03-09-26"/>
       <sheetName val="CCC"/>
-      <sheetName val="VINCULO VTS BY SKU JULIO"/>
+      <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
     </sheetNames>
@@ -388,44 +374,24 @@
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26">
+      <sheetData sheetId="6">
         <row r="4">
           <cell r="F4">
-            <v>1188.0952380952381</v>
+            <v>750.5</v>
           </cell>
           <cell r="G4">
-            <v>6.2178772679422956E-2</v>
+            <v>-0.36831663326653308</v>
           </cell>
           <cell r="H4" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="5">
           <cell r="F5">
-            <v>76.38095238095238</v>
+            <v>67.5</v>
           </cell>
           <cell r="G5">
-            <v>-2.0186033597112352E-2</v>
+            <v>-0.11627182044887774</v>
           </cell>
           <cell r="H5" t="str">
             <v>BAJO</v>
@@ -433,10 +399,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>509.47619047619048</v>
+            <v>236.5</v>
           </cell>
           <cell r="G6">
-            <v>-6.9449880408784526E-2</v>
+            <v>-0.53579773810636511</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -444,21 +410,21 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>98</v>
+            <v>85.5</v>
           </cell>
           <cell r="G7">
-            <v>2.3245002324501218E-3</v>
+            <v>-0.12755102040816324</v>
           </cell>
           <cell r="H7" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="8">
           <cell r="F8">
-            <v>11.952380952380953</v>
+            <v>5.5</v>
           </cell>
           <cell r="G8">
-            <v>-0.2835084987673544</v>
+            <v>-0.53984063745019917</v>
           </cell>
           <cell r="H8" t="str">
             <v>BAJO</v>
@@ -466,54 +432,54 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1460.3333333333333</v>
+            <v>785</v>
           </cell>
           <cell r="G9">
-            <v>0.12774969577833928</v>
+            <v>-0.46245149509244465</v>
           </cell>
           <cell r="H9" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="10">
           <cell r="F10">
-            <v>150.38095238095238</v>
+            <v>90.5</v>
           </cell>
           <cell r="G10">
-            <v>0.2307964852607709</v>
+            <v>-0.39819506016466122</v>
           </cell>
           <cell r="H10" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="11">
           <cell r="F11">
-            <v>343.57142857142856</v>
+            <v>181</v>
           </cell>
           <cell r="G11">
-            <v>0.13118399110617007</v>
+            <v>-0.47318087318087321</v>
           </cell>
           <cell r="H11" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="12">
           <cell r="F12">
-            <v>766.19047619047615</v>
+            <v>569.5</v>
           </cell>
           <cell r="G12">
-            <v>0.15738742626960134</v>
+            <v>-0.25671224362958356</v>
           </cell>
           <cell r="H12" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="13">
           <cell r="F13">
-            <v>362.8095238095238</v>
+            <v>228</v>
           </cell>
           <cell r="G13">
-            <v>-0.10467644152445055</v>
+            <v>-0.37157107231920194</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -521,65 +487,65 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3521.5238095238096</v>
+            <v>2041</v>
           </cell>
           <cell r="G14">
-            <v>8.3530633271196475E-2</v>
+            <v>-0.42042135439203809</v>
           </cell>
           <cell r="H14" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2305</v>
+            <v>1292</v>
           </cell>
           <cell r="G15">
-            <v>5.8045401435486532E-2</v>
+            <v>-0.4394793926247289</v>
           </cell>
           <cell r="H15" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2266.4761904761904</v>
+            <v>1316</v>
           </cell>
           <cell r="G16">
-            <v>4.8059445738948048E-2</v>
+            <v>-0.41936297167829228</v>
           </cell>
           <cell r="H16" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2674</v>
+            <v>1592</v>
           </cell>
           <cell r="G17">
-            <v>0.11199742925732004</v>
+            <v>-0.40463724756918473</v>
           </cell>
           <cell r="H17" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="18">
           <cell r="F18">
-            <v>11.666666666666666</v>
+            <v>528</v>
           </cell>
           <cell r="G18">
-            <v>-0.91237054739956758</v>
+            <v>0.35666218034993258</v>
           </cell>
           <cell r="H18" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="19">
           <cell r="F19">
-            <v>242</v>
+            <v>683</v>
           </cell>
           <cell r="G19">
-            <v>7.1442946266854435E-2</v>
+            <v>0.59437527790128941</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -587,43 +553,43 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>142.1904761904762</v>
+            <v>695.5</v>
           </cell>
           <cell r="G20">
-            <v>-3.8663037433781078E-2</v>
+            <v>0.7798562027784548</v>
           </cell>
           <cell r="H20" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="21">
           <cell r="F21">
-            <v>513.09523809523807</v>
+            <v>189.5</v>
           </cell>
           <cell r="G21">
-            <v>5.4469429060741481E-2</v>
+            <v>-0.21694214876033058</v>
           </cell>
           <cell r="H21" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="22">
           <cell r="F22">
-            <v>811.38095238095241</v>
+            <v>99.5</v>
           </cell>
           <cell r="G22">
-            <v>1.8799209655895988E-2</v>
+            <v>-0.30023442732752859</v>
           </cell>
           <cell r="H22" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="23">
           <cell r="F23">
-            <v>0</v>
+            <v>380</v>
           </cell>
           <cell r="G23">
-            <v>-1</v>
+            <v>-0.25939675174013921</v>
           </cell>
           <cell r="H23" t="str">
             <v>BAJO</v>
@@ -631,87 +597,87 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>74.952380952380949</v>
+            <v>628</v>
           </cell>
           <cell r="G24">
-            <v>0.52398556465099899</v>
+            <v>-0.22601091613357593</v>
           </cell>
           <cell r="H24" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="25">
           <cell r="F25">
-            <v>787.95238095238096</v>
+            <v>10</v>
           </cell>
           <cell r="G25">
-            <v>0.15075360999418352</v>
+            <v>-0.8665819567979669</v>
           </cell>
           <cell r="H25" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="26">
           <cell r="F26">
-            <v>1273.7142857142858</v>
+            <v>343.5</v>
           </cell>
           <cell r="G26">
-            <v>0.14791341140118353</v>
+            <v>-0.56405995044418922</v>
           </cell>
           <cell r="H26" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="27">
           <cell r="F27">
-            <v>529.19047619047615</v>
+            <v>309</v>
           </cell>
           <cell r="G27">
-            <v>9.5838711990820169E-2</v>
+            <v>-0.7574024226110363</v>
           </cell>
           <cell r="H27" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="28">
           <cell r="F28">
-            <v>401.85714285714283</v>
+            <v>388.5</v>
           </cell>
           <cell r="G28">
-            <v>9.6744466301593057E-2</v>
+            <v>-0.26585980383334828</v>
           </cell>
           <cell r="H28" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="29">
           <cell r="F29">
-            <v>127.85714285714286</v>
+            <v>236.5</v>
           </cell>
           <cell r="G29">
-            <v>0.19441916894146205</v>
+            <v>-0.41148240312833273</v>
           </cell>
           <cell r="H29" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="30">
           <cell r="F30">
-            <v>143.33333333333334</v>
+            <v>41</v>
           </cell>
           <cell r="G30">
-            <v>0.16963402571711184</v>
+            <v>-0.46120150187734676</v>
           </cell>
           <cell r="H30" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="31">
           <cell r="F31">
-            <v>652.19047619047615</v>
+            <v>70</v>
           </cell>
           <cell r="G31">
-            <v>-0.17520174314839765</v>
+            <v>-2.9062087186261687E-2</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -719,10 +685,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>629.04761904761904</v>
+            <v>99</v>
           </cell>
           <cell r="G32">
-            <v>-3.4529955417355929E-2</v>
+            <v>-0.22569832402234635</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -730,32 +696,32 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>852.19047619047615</v>
+            <v>66.5</v>
           </cell>
           <cell r="G33">
-            <v>1.1338357761920159E-2</v>
+            <v>-0.53604651162790695</v>
           </cell>
           <cell r="H33" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="34">
           <cell r="F34">
-            <v>579</v>
+            <v>398.5</v>
           </cell>
           <cell r="G34">
-            <v>1.1594663278271966E-2</v>
+            <v>-0.38898218457943923</v>
           </cell>
           <cell r="H34" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="35">
           <cell r="F35">
-            <v>137.14285714285714</v>
+            <v>327</v>
           </cell>
           <cell r="G35">
-            <v>-0.3547598680190639</v>
+            <v>-0.48016654049962149</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -763,21 +729,21 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>554.42857142857144</v>
+            <v>522.5</v>
           </cell>
           <cell r="G36">
-            <v>0.90228143659210436</v>
+            <v>-0.38687416182387124</v>
           </cell>
           <cell r="H36" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="37">
           <cell r="F37">
-            <v>132.8095238095238</v>
+            <v>309.5</v>
           </cell>
           <cell r="G37">
-            <v>-0.64510998131792507</v>
+            <v>-0.4654576856649395</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -785,10 +751,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>296.14285714285717</v>
+            <v>4.5</v>
           </cell>
           <cell r="G38">
-            <v>8.4953015344356064E-2</v>
+            <v>0.81730769230769229</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -796,10 +762,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>528.71428571428567</v>
+            <v>2</v>
           </cell>
           <cell r="G39">
-            <v>0.25761858424848993</v>
+            <v>3.666666666666667</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -807,32 +773,32 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>305.57142857142856</v>
+            <v>119</v>
           </cell>
           <cell r="G40">
-            <v>0.2398693154871685</v>
+            <v>-0.1322916666666667</v>
           </cell>
           <cell r="H40" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="41">
           <cell r="F41">
-            <v>289.90476190476193</v>
+            <v>259</v>
           </cell>
           <cell r="G41">
-            <v>0.10058753440979484</v>
+            <v>-0.53285235763978356</v>
           </cell>
           <cell r="H41" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="42">
           <cell r="F42">
-            <v>57.714285714285715</v>
+            <v>407.5</v>
           </cell>
           <cell r="G42">
-            <v>0.15638823835545157</v>
+            <v>2.0683040516314093</v>
           </cell>
           <cell r="H42" t="str">
             <v>SUBIÓ</v>
@@ -840,43 +806,43 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>104.71428571428571</v>
+            <v>117.5</v>
           </cell>
           <cell r="G43">
-            <v>0.31866873824515496</v>
+            <v>-0.60323203087313071</v>
           </cell>
           <cell r="H43" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="44">
           <cell r="F44">
-            <v>49.333333333333336</v>
+            <v>230</v>
           </cell>
           <cell r="G44">
-            <v>0.43943412908930157</v>
+            <v>-0.56498243717914076</v>
           </cell>
           <cell r="H44" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="45">
           <cell r="F45">
-            <v>55.333333333333336</v>
+            <v>119</v>
           </cell>
           <cell r="G45">
-            <v>0.47555555555555551</v>
+            <v>-0.61056568489948571</v>
           </cell>
           <cell r="H45" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="46">
           <cell r="F46">
-            <v>0.42857142857142855</v>
+            <v>144.5</v>
           </cell>
           <cell r="G46">
-            <v>-0.47619047619047628</v>
+            <v>-0.50156044678055189</v>
           </cell>
           <cell r="H46" t="str">
             <v>BAJO</v>
@@ -884,12 +850,45 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>2.4761904761904763</v>
+            <v>35</v>
           </cell>
           <cell r="G47">
-            <v>-0.24338624338624337</v>
+            <v>-0.39356435643564358</v>
           </cell>
           <cell r="H47" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="F48">
+            <v>51.5</v>
+          </cell>
+          <cell r="G48">
+            <v>-0.50818553888130968</v>
+          </cell>
+          <cell r="H48" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="F49">
+            <v>14</v>
+          </cell>
+          <cell r="G49">
+            <v>-0.71621621621621623</v>
+          </cell>
+          <cell r="H49" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="F50">
+            <v>17.5</v>
+          </cell>
+          <cell r="G50">
+            <v>-0.68373493975903621</v>
+          </cell>
+          <cell r="H50" t="str">
             <v>BAJO</v>
           </cell>
         </row>
@@ -1097,7 +1096,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.7109375" customWidth="1"/>
@@ -1116,23 +1115,23 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="C1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>53</v>
+      <c r="H1" s="3" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -1142,23 +1141,23 @@
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" s="5">
-        <v>1118.5454545454545</v>
-      </c>
-      <c r="E2" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F4</f>
+      <c r="C2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="4">
         <v>1188.0952380952381</v>
       </c>
-      <c r="F2" s="6">
-        <f>'[1]DESV. VTS BY SKU'!G4</f>
-        <v>6.2178772679422956E-2</v>
-      </c>
-      <c r="G2" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H4</f>
-        <v>SUBIÓ</v>
+      <c r="E2" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
+        <v>750.5</v>
+      </c>
+      <c r="F2" s="5">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
+        <v>-0.36831663326653308</v>
+      </c>
+      <c r="G2" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
+        <v>BAJO</v>
       </c>
       <c r="H2">
         <v>1.36</v>
@@ -1171,22 +1170,22 @@
       <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="5">
-        <v>77.954545454545453</v>
-      </c>
-      <c r="E3" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F5</f>
+      <c r="C3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="4">
         <v>76.38095238095238</v>
       </c>
-      <c r="F3" s="7">
-        <f>'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-2.0186033597112352E-2</v>
-      </c>
-      <c r="G3" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H5</f>
+      <c r="E3" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
+        <v>67.5</v>
+      </c>
+      <c r="F3" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
+        <v>-0.11627182044887774</v>
+      </c>
+      <c r="G3" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
         <v>BAJO</v>
       </c>
       <c r="H3">
@@ -1200,22 +1199,22 @@
       <c r="B4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" s="5">
-        <v>547.5</v>
-      </c>
-      <c r="E4" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F6</f>
+      <c r="C4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="4">
         <v>509.47619047619048</v>
       </c>
-      <c r="F4" s="6">
-        <f>'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-6.9449880408784526E-2</v>
-      </c>
-      <c r="G4" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H6</f>
+      <c r="E4" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
+        <v>236.5</v>
+      </c>
+      <c r="F4" s="5">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
+        <v>-0.53579773810636511</v>
+      </c>
+      <c r="G4" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
         <v>BAJO</v>
       </c>
       <c r="H4">
@@ -1229,23 +1228,23 @@
       <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D5" s="5">
-        <v>97.772727272727266</v>
-      </c>
-      <c r="E5" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F7</f>
+      <c r="C5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="4">
         <v>98</v>
       </c>
-      <c r="F5" s="7">
-        <f>'[1]DESV. VTS BY SKU'!G7</f>
-        <v>2.3245002324501218E-3</v>
-      </c>
-      <c r="G5" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H7</f>
-        <v>SUBIÓ</v>
+      <c r="E5" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
+        <v>85.5</v>
+      </c>
+      <c r="F5" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
+        <v>-0.12755102040816324</v>
+      </c>
+      <c r="G5" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
+        <v>BAJO</v>
       </c>
       <c r="H5">
         <v>3.61</v>
@@ -1258,22 +1257,22 @@
       <c r="B6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="5">
-        <v>16.681818181818183</v>
-      </c>
-      <c r="E6" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F8</f>
+      <c r="C6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="4">
         <v>11.952380952380953</v>
       </c>
-      <c r="F6" s="6">
-        <f>'[1]DESV. VTS BY SKU'!G8</f>
-        <v>-0.2835084987673544</v>
-      </c>
-      <c r="G6" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H8</f>
+      <c r="E6" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
+        <v>5.5</v>
+      </c>
+      <c r="F6" s="5">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
+        <v>-0.53984063745019917</v>
+      </c>
+      <c r="G6" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
         <v>BAJO</v>
       </c>
       <c r="H6">
@@ -1287,23 +1286,23 @@
       <c r="B7" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="5">
-        <v>1294.909090909091</v>
-      </c>
-      <c r="E7" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F9</f>
+      <c r="C7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="4">
         <v>1460.3333333333333</v>
       </c>
-      <c r="F7" s="7">
-        <f>'[1]DESV. VTS BY SKU'!G9</f>
-        <v>0.12774969577833928</v>
-      </c>
-      <c r="G7" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H9</f>
-        <v>SUBIÓ</v>
+      <c r="E7" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
+        <v>785</v>
+      </c>
+      <c r="F7" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
+        <v>-0.46245149509244465</v>
+      </c>
+      <c r="G7" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
+        <v>BAJO</v>
       </c>
       <c r="H7">
         <v>0.63</v>
@@ -1316,23 +1315,23 @@
       <c r="B8" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8" s="5">
-        <v>122.18181818181819</v>
-      </c>
-      <c r="E8" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F10</f>
+      <c r="C8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="4">
         <v>150.38095238095238</v>
       </c>
-      <c r="F8" s="6">
-        <f>'[1]DESV. VTS BY SKU'!G10</f>
-        <v>0.2307964852607709</v>
-      </c>
-      <c r="G8" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H10</f>
-        <v>SUBIÓ</v>
+      <c r="E8" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
+        <v>90.5</v>
+      </c>
+      <c r="F8" s="5">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
+        <v>-0.39819506016466122</v>
+      </c>
+      <c r="G8" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
+        <v>BAJO</v>
       </c>
       <c r="H8">
         <v>0.63</v>
@@ -1345,23 +1344,23 @@
       <c r="B9" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D9" s="5">
-        <v>303.72727272727275</v>
-      </c>
-      <c r="E9" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F11</f>
+      <c r="C9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="4">
         <v>343.57142857142856</v>
       </c>
-      <c r="F9" s="7">
-        <f>'[1]DESV. VTS BY SKU'!G11</f>
-        <v>0.13118399110617007</v>
-      </c>
-      <c r="G9" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H11</f>
-        <v>SUBIÓ</v>
+      <c r="E9" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
+        <v>181</v>
+      </c>
+      <c r="F9" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
+        <v>-0.47318087318087321</v>
+      </c>
+      <c r="G9" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
+        <v>BAJO</v>
       </c>
       <c r="H9">
         <v>0.63</v>
@@ -1374,23 +1373,23 @@
       <c r="B10" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="5">
-        <v>662</v>
-      </c>
-      <c r="E10" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F12</f>
+      <c r="C10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="4">
         <v>766.19047619047615</v>
       </c>
-      <c r="F10" s="6">
-        <f>'[1]DESV. VTS BY SKU'!G12</f>
-        <v>0.15738742626960134</v>
-      </c>
-      <c r="G10" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H12</f>
-        <v>SUBIÓ</v>
+      <c r="E10" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
+        <v>569.5</v>
+      </c>
+      <c r="F10" s="5">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
+        <v>-0.25671224362958356</v>
+      </c>
+      <c r="G10" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
+        <v>BAJO</v>
       </c>
       <c r="H10">
         <v>1.0900000000000001</v>
@@ -1403,22 +1402,22 @@
       <c r="B11" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="5">
-        <v>405.22727272727275</v>
-      </c>
-      <c r="E11" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F13</f>
+      <c r="C11" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="4">
         <v>362.8095238095238</v>
       </c>
-      <c r="F11" s="7">
-        <f>'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.10467644152445055</v>
-      </c>
-      <c r="G11" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H13</f>
+      <c r="E11" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
+        <v>228</v>
+      </c>
+      <c r="F11" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
+        <v>-0.37157107231920194</v>
+      </c>
+      <c r="G11" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
         <v>BAJO</v>
       </c>
       <c r="H11">
@@ -1432,23 +1431,23 @@
       <c r="B12" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" s="5">
-        <v>3250.0454545454545</v>
-      </c>
-      <c r="E12" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F14</f>
+      <c r="C12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="4">
         <v>3521.5238095238096</v>
       </c>
-      <c r="F12" s="6">
-        <f>'[1]DESV. VTS BY SKU'!G14</f>
-        <v>8.3530633271196475E-2</v>
-      </c>
-      <c r="G12" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H14</f>
-        <v>SUBIÓ</v>
+      <c r="E12" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
+        <v>2041</v>
+      </c>
+      <c r="F12" s="5">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
+        <v>-0.42042135439203809</v>
+      </c>
+      <c r="G12" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
+        <v>BAJO</v>
       </c>
       <c r="H12">
         <v>1.1599999999999999</v>
@@ -1461,23 +1460,23 @@
       <c r="B13" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="5">
-        <v>2178.5454545454545</v>
-      </c>
-      <c r="E13" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F15</f>
+      <c r="C13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="4">
         <v>2305</v>
       </c>
-      <c r="F13" s="7">
-        <f>'[1]DESV. VTS BY SKU'!G15</f>
-        <v>5.8045401435486532E-2</v>
-      </c>
-      <c r="G13" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H15</f>
-        <v>SUBIÓ</v>
+      <c r="E13" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
+        <v>1292</v>
+      </c>
+      <c r="F13" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
+        <v>-0.4394793926247289</v>
+      </c>
+      <c r="G13" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
+        <v>BAJO</v>
       </c>
       <c r="H13">
         <v>1.1599999999999999</v>
@@ -1490,23 +1489,23 @@
       <c r="B14" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="5">
-        <v>2162.5454545454545</v>
-      </c>
-      <c r="E14" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F16</f>
+      <c r="C14" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="4">
         <v>2266.4761904761904</v>
       </c>
-      <c r="F14" s="6">
-        <f>'[1]DESV. VTS BY SKU'!G16</f>
-        <v>4.8059445738948048E-2</v>
-      </c>
-      <c r="G14" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H16</f>
-        <v>SUBIÓ</v>
+      <c r="E14" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
+        <v>1316</v>
+      </c>
+      <c r="F14" s="5">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
+        <v>-0.41936297167829228</v>
+      </c>
+      <c r="G14" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
+        <v>BAJO</v>
       </c>
       <c r="H14">
         <v>1.1599999999999999</v>
@@ -1519,23 +1518,23 @@
       <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="5">
-        <v>2404.681818181818</v>
-      </c>
-      <c r="E15" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F17</f>
+      <c r="C15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="4">
         <v>2674</v>
       </c>
-      <c r="F15" s="7">
-        <f>'[1]DESV. VTS BY SKU'!G17</f>
-        <v>0.11199742925732004</v>
-      </c>
-      <c r="G15" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H17</f>
-        <v>SUBIÓ</v>
+      <c r="E15" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
+        <v>1592</v>
+      </c>
+      <c r="F15" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
+        <v>-0.40463724756918473</v>
+      </c>
+      <c r="G15" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
+        <v>BAJO</v>
       </c>
       <c r="H15">
         <v>1.1599999999999999</v>
@@ -1543,28 +1542,28 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>130156</v>
+        <v>130157</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" s="5">
-        <v>133.13636363636363</v>
-      </c>
-      <c r="E16" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F18</f>
-        <v>11.666666666666666</v>
+        <v>60</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="4">
+        <v>389.1904761904762</v>
+      </c>
+      <c r="E16" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
+        <v>528</v>
       </c>
       <c r="F16" s="6">
-        <f>'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.91237054739956758</v>
-      </c>
-      <c r="G16" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H18</f>
-        <v>BAJO</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
+        <v>0.35666218034993258</v>
+      </c>
+      <c r="G16" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
+        <v>SUBIÓ</v>
       </c>
       <c r="H16">
         <v>1.1599999999999999</v>
@@ -1572,143 +1571,143 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>130700</v>
+        <v>130158</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="5">
-        <v>225.86363636363637</v>
-      </c>
-      <c r="E17" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F19</f>
-        <v>242</v>
-      </c>
-      <c r="F17" s="7">
-        <f>'[1]DESV. VTS BY SKU'!G19</f>
-        <v>7.1442946266854435E-2</v>
-      </c>
-      <c r="G17" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H19</f>
+        <v>61</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="4">
+        <v>428.38095238095241</v>
+      </c>
+      <c r="E17" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
+        <v>683</v>
+      </c>
+      <c r="F17" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
+        <v>0.59437527790128941</v>
+      </c>
+      <c r="G17" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H17">
-        <v>3.68</v>
+        <v>1.1599999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>130701</v>
+        <v>130159</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="5">
-        <v>147.90909090909091</v>
-      </c>
-      <c r="E18" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F20</f>
-        <v>142.1904761904762</v>
+        <v>62</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="4">
+        <v>390.76190476190476</v>
+      </c>
+      <c r="E18" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
+        <v>695.5</v>
       </c>
       <c r="F18" s="6">
-        <f>'[1]DESV. VTS BY SKU'!G20</f>
-        <v>-3.8663037433781078E-2</v>
-      </c>
-      <c r="G18" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H20</f>
-        <v>BAJO</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
+        <v>0.7798562027784548</v>
+      </c>
+      <c r="G18" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
+        <v>SUBIÓ</v>
       </c>
       <c r="H18">
-        <v>3.68</v>
+        <v>1.1599999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>130702</v>
+        <v>130700</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="5">
-        <v>486.59090909090907</v>
-      </c>
-      <c r="E19" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F21</f>
-        <v>513.09523809523807</v>
-      </c>
-      <c r="F19" s="7">
-        <f>'[1]DESV. VTS BY SKU'!G21</f>
-        <v>5.4469429060741481E-2</v>
-      </c>
-      <c r="G19" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H21</f>
-        <v>SUBIÓ</v>
+        <v>18</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="4">
+        <v>242</v>
+      </c>
+      <c r="E19" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
+        <v>189.5</v>
+      </c>
+      <c r="F19" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
+        <v>-0.21694214876033058</v>
+      </c>
+      <c r="G19" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
+        <v>BAJO</v>
       </c>
       <c r="H19">
-        <v>4.1500000000000004</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>130703</v>
+        <v>130701</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="5">
-        <v>796.40909090909088</v>
-      </c>
-      <c r="E20" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F22</f>
-        <v>811.38095238095241</v>
-      </c>
-      <c r="F20" s="6">
-        <f>'[1]DESV. VTS BY SKU'!G22</f>
-        <v>1.8799209655895988E-2</v>
-      </c>
-      <c r="G20" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H22</f>
-        <v>SUBIÓ</v>
+        <v>19</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="4">
+        <v>142.1904761904762</v>
+      </c>
+      <c r="E20" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
+        <v>99.5</v>
+      </c>
+      <c r="F20" s="5">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
+        <v>-0.30023442732752859</v>
+      </c>
+      <c r="G20" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
+        <v>BAJO</v>
       </c>
       <c r="H20">
-        <v>4.1500000000000004</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>130704</v>
+        <v>130702</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21" s="5">
-        <v>5</v>
-      </c>
-      <c r="E21" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F23</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="7">
-        <f>'[1]DESV. VTS BY SKU'!G23</f>
-        <v>-1</v>
-      </c>
-      <c r="G21" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H23</f>
+        <v>20</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="4">
+        <v>513.09523809523807</v>
+      </c>
+      <c r="E21" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
+        <v>380</v>
+      </c>
+      <c r="F21" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
+        <v>-0.25939675174013921</v>
+      </c>
+      <c r="G21" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
         <v>BAJO</v>
       </c>
       <c r="H21">
@@ -1717,28 +1716,28 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>130707</v>
+        <v>130703</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22" s="5">
-        <v>49.18181818181818</v>
-      </c>
-      <c r="E22" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F24</f>
-        <v>74.952380952380949</v>
-      </c>
-      <c r="F22" s="6">
-        <f>'[1]DESV. VTS BY SKU'!G24</f>
-        <v>0.52398556465099899</v>
-      </c>
-      <c r="G22" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H24</f>
-        <v>SUBIÓ</v>
+        <v>21</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="4">
+        <v>811.38095238095241</v>
+      </c>
+      <c r="E22" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
+        <v>628</v>
+      </c>
+      <c r="F22" s="5">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
+        <v>-0.22601091613357593</v>
+      </c>
+      <c r="G22" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
+        <v>BAJO</v>
       </c>
       <c r="H22">
         <v>4.1500000000000004</v>
@@ -1746,57 +1745,57 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>131150</v>
+        <v>130707</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" s="5">
-        <v>684.72727272727275</v>
-      </c>
-      <c r="E23" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F25</f>
-        <v>787.95238095238096</v>
-      </c>
-      <c r="F23" s="7">
-        <f>'[1]DESV. VTS BY SKU'!G25</f>
-        <v>0.15075360999418352</v>
-      </c>
-      <c r="G23" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H25</f>
-        <v>SUBIÓ</v>
+        <v>22</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="4">
+        <v>74.952380952380949</v>
+      </c>
+      <c r="E23" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
+        <v>10</v>
+      </c>
+      <c r="F23" s="5">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
+        <v>-0.8665819567979669</v>
+      </c>
+      <c r="G23" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
+        <v>BAJO</v>
       </c>
       <c r="H23">
-        <v>1.63</v>
+        <v>4.1500000000000004</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>131151</v>
+        <v>131150</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D24" s="5">
-        <v>1109.590909090909</v>
-      </c>
-      <c r="E24" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F26</f>
-        <v>1273.7142857142858</v>
+        <v>23</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="4">
+        <v>787.95238095238096</v>
+      </c>
+      <c r="E24" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
+        <v>343.5</v>
       </c>
       <c r="F24" s="6">
-        <f>'[1]DESV. VTS BY SKU'!G26</f>
-        <v>0.14791341140118353</v>
-      </c>
-      <c r="G24" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H26</f>
-        <v>SUBIÓ</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
+        <v>-0.56405995044418922</v>
+      </c>
+      <c r="G24" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
+        <v>BAJO</v>
       </c>
       <c r="H24">
         <v>1.63</v>
@@ -1804,28 +1803,28 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>131152</v>
+        <v>131151</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D25" s="5">
-        <v>482.90909090909093</v>
-      </c>
-      <c r="E25" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F27</f>
-        <v>529.19047619047615</v>
-      </c>
-      <c r="F25" s="7">
-        <f>'[1]DESV. VTS BY SKU'!G27</f>
-        <v>9.5838711990820169E-2</v>
-      </c>
-      <c r="G25" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H27</f>
-        <v>SUBIÓ</v>
+        <v>24</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="4">
+        <v>1273.7142857142858</v>
+      </c>
+      <c r="E25" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
+        <v>309</v>
+      </c>
+      <c r="F25" s="5">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
+        <v>-0.7574024226110363</v>
+      </c>
+      <c r="G25" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
+        <v>BAJO</v>
       </c>
       <c r="H25">
         <v>1.63</v>
@@ -1833,28 +1832,28 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>131153</v>
+        <v>131152</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="5">
-        <v>366.40909090909093</v>
-      </c>
-      <c r="E26" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F28</f>
-        <v>401.85714285714283</v>
+        <v>25</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="4">
+        <v>529.19047619047615</v>
+      </c>
+      <c r="E26" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
+        <v>388.5</v>
       </c>
       <c r="F26" s="6">
-        <f>'[1]DESV. VTS BY SKU'!G28</f>
-        <v>9.6744466301593057E-2</v>
-      </c>
-      <c r="G26" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H28</f>
-        <v>SUBIÓ</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
+        <v>-0.26585980383334828</v>
+      </c>
+      <c r="G26" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
+        <v>BAJO</v>
       </c>
       <c r="H26">
         <v>1.63</v>
@@ -1862,173 +1861,173 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>131700</v>
+        <v>131153</v>
       </c>
       <c r="B27" t="s">
-        <v>29</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D27" s="5">
-        <v>107.04545454545455</v>
-      </c>
-      <c r="E27" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F29</f>
-        <v>127.85714285714286</v>
-      </c>
-      <c r="F27" s="7">
-        <f>'[1]DESV. VTS BY SKU'!G29</f>
-        <v>0.19441916894146205</v>
-      </c>
-      <c r="G27" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H29</f>
-        <v>SUBIÓ</v>
+        <v>26</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="4">
+        <v>401.85714285714283</v>
+      </c>
+      <c r="E27" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
+        <v>236.5</v>
+      </c>
+      <c r="F27" s="5">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
+        <v>-0.41148240312833273</v>
+      </c>
+      <c r="G27" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
+        <v>BAJO</v>
       </c>
       <c r="H27">
-        <v>6.15</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>131701</v>
+        <v>131154</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
-      </c>
-      <c r="C28" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D28" s="5">
-        <v>122.54545454545455</v>
-      </c>
-      <c r="E28" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F30</f>
-        <v>143.33333333333334</v>
-      </c>
-      <c r="F28" s="6">
-        <f>'[1]DESV. VTS BY SKU'!G30</f>
-        <v>0.16963402571711184</v>
-      </c>
-      <c r="G28" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H30</f>
-        <v>SUBIÓ</v>
+      <c r="C28" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="4">
+        <v>76.095238095238102</v>
+      </c>
+      <c r="E28" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
+        <v>41</v>
+      </c>
+      <c r="F28" s="5">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
+        <v>-0.46120150187734676</v>
+      </c>
+      <c r="G28" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
+        <v>BAJO</v>
       </c>
       <c r="H28">
-        <v>6.15</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>132150</v>
+        <v>131155</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D29" s="5">
-        <v>790.72727272727275</v>
-      </c>
-      <c r="E29" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F31</f>
-        <v>652.19047619047615</v>
-      </c>
-      <c r="F29" s="7">
-        <f>'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-0.17520174314839765</v>
-      </c>
-      <c r="G29" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H31</f>
+      <c r="D29" s="4">
+        <v>72.095238095238102</v>
+      </c>
+      <c r="E29" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
+        <v>70</v>
+      </c>
+      <c r="F29" s="5">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
+        <v>-2.9062087186261687E-2</v>
+      </c>
+      <c r="G29" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
         <v>BAJO</v>
       </c>
       <c r="H29">
-        <v>1.1599999999999999</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>132151</v>
+        <v>131700</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D30" s="5">
-        <v>651.5454545454545</v>
-      </c>
-      <c r="E30" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F32</f>
-        <v>629.04761904761904</v>
+      <c r="D30" s="4">
+        <v>127.85714285714286</v>
+      </c>
+      <c r="E30" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
+        <v>99</v>
       </c>
       <c r="F30" s="6">
-        <f>'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-3.4529955417355929E-2</v>
-      </c>
-      <c r="G30" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H32</f>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
+        <v>-0.22569832402234635</v>
+      </c>
+      <c r="G30" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
         <v>BAJO</v>
       </c>
       <c r="H30">
-        <v>1.1599999999999999</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>132152</v>
+        <v>131701</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C31" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D31" s="5">
-        <v>842.63636363636363</v>
-      </c>
-      <c r="E31" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F33</f>
-        <v>852.19047619047615</v>
-      </c>
-      <c r="F31" s="7">
-        <f>'[1]DESV. VTS BY SKU'!G33</f>
-        <v>1.1338357761920159E-2</v>
-      </c>
-      <c r="G31" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H33</f>
-        <v>SUBIÓ</v>
+      <c r="D31" s="4">
+        <v>143.33333333333334</v>
+      </c>
+      <c r="E31" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
+        <v>66.5</v>
+      </c>
+      <c r="F31" s="5">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
+        <v>-0.53604651162790695</v>
+      </c>
+      <c r="G31" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
+        <v>BAJO</v>
       </c>
       <c r="H31">
-        <v>1.1599999999999999</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>132153</v>
+        <v>132150</v>
       </c>
       <c r="B32" t="s">
-        <v>34</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D32" s="5">
-        <v>572.36363636363637</v>
-      </c>
-      <c r="E32" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F34</f>
-        <v>579</v>
+        <v>29</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" s="4">
+        <v>652.19047619047615</v>
+      </c>
+      <c r="E32" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
+        <v>398.5</v>
       </c>
       <c r="F32" s="6">
-        <f>'[1]DESV. VTS BY SKU'!G34</f>
-        <v>1.1594663278271966E-2</v>
-      </c>
-      <c r="G32" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H34</f>
-        <v>SUBIÓ</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
+        <v>-0.38898218457943923</v>
+      </c>
+      <c r="G32" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
+        <v>BAJO</v>
       </c>
       <c r="H32">
         <v>1.1599999999999999</v>
@@ -2036,27 +2035,27 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>140230</v>
+        <v>132151</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D33" s="5">
-        <v>212.54545454545453</v>
-      </c>
-      <c r="E33" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F35</f>
-        <v>137.14285714285714</v>
-      </c>
-      <c r="F33" s="7">
-        <f>'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-0.3547598680190639</v>
-      </c>
-      <c r="G33" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H35</f>
+        <v>30</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" s="4">
+        <v>629.04761904761904</v>
+      </c>
+      <c r="E33" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
+        <v>327</v>
+      </c>
+      <c r="F33" s="5">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
+        <v>-0.48016654049962149</v>
+      </c>
+      <c r="G33" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
         <v>BAJO</v>
       </c>
       <c r="H33">
@@ -2065,28 +2064,28 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>140231</v>
+        <v>132152</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D34" s="5">
-        <v>291.45454545454544</v>
-      </c>
-      <c r="E34" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F36</f>
-        <v>554.42857142857144</v>
+        <v>31</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D34" s="4">
+        <v>852.19047619047615</v>
+      </c>
+      <c r="E34" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
+        <v>522.5</v>
       </c>
       <c r="F34" s="6">
-        <f>'[1]DESV. VTS BY SKU'!G36</f>
-        <v>0.90228143659210436</v>
-      </c>
-      <c r="G34" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H36</f>
-        <v>SUBIÓ</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
+        <v>-0.38687416182387124</v>
+      </c>
+      <c r="G34" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
+        <v>BAJO</v>
       </c>
       <c r="H34">
         <v>1.1599999999999999</v>
@@ -2094,27 +2093,27 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>140232</v>
+        <v>132153</v>
       </c>
       <c r="B35" t="s">
-        <v>37</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D35" s="5">
-        <v>374.22727272727275</v>
-      </c>
-      <c r="E35" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F37</f>
-        <v>132.8095238095238</v>
-      </c>
-      <c r="F35" s="7">
-        <f>'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.64510998131792507</v>
-      </c>
-      <c r="G35" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H37</f>
+        <v>32</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35" s="4">
+        <v>579</v>
+      </c>
+      <c r="E35" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
+        <v>309.5</v>
+      </c>
+      <c r="F35" s="5">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
+        <v>-0.4654576856649395</v>
+      </c>
+      <c r="G35" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
         <v>BAJO</v>
       </c>
       <c r="H35">
@@ -2122,293 +2121,380 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <v>150360</v>
+      <c r="A36" s="8">
+        <v>134000</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D36" s="5">
-        <v>272.95454545454544</v>
-      </c>
-      <c r="E36" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F38</f>
-        <v>296.14285714285717</v>
+        <v>40</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36" s="4">
+        <v>2.4761904761904763</v>
+      </c>
+      <c r="E36" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
+        <v>4.5</v>
       </c>
       <c r="F36" s="6">
-        <f>'[1]DESV. VTS BY SKU'!G38</f>
-        <v>8.4953015344356064E-2</v>
-      </c>
-      <c r="G36" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H38</f>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
+        <v>0.81730769230769229</v>
+      </c>
+      <c r="G36" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H36">
-        <v>0.81</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>150361</v>
+      <c r="A37" s="8">
+        <v>134001</v>
       </c>
       <c r="B37" t="s">
-        <v>38</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D37" s="5">
-        <v>420.40909090909093</v>
-      </c>
-      <c r="E37" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F39</f>
-        <v>528.71428571428567</v>
-      </c>
-      <c r="F37" s="7">
-        <f>'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.25761858424848993</v>
-      </c>
-      <c r="G37" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H39</f>
+        <v>39</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" s="4">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="E37" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
+        <v>2</v>
+      </c>
+      <c r="F37" s="5">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
+        <v>3.666666666666667</v>
+      </c>
+      <c r="G37" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H37">
-        <v>0.81</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>150362</v>
+        <v>140230</v>
       </c>
       <c r="B38" t="s">
-        <v>39</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D38" s="5">
-        <v>246.45454545454547</v>
-      </c>
-      <c r="E38" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F40</f>
-        <v>305.57142857142856</v>
+        <v>33</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38" s="4">
+        <v>137.14285714285714</v>
+      </c>
+      <c r="E38" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
+        <v>119</v>
       </c>
       <c r="F38" s="6">
-        <f>'[1]DESV. VTS BY SKU'!G40</f>
-        <v>0.2398693154871685</v>
-      </c>
-      <c r="G38" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H40</f>
-        <v>SUBIÓ</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
+        <v>-0.1322916666666667</v>
+      </c>
+      <c r="G38" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
+        <v>BAJO</v>
       </c>
       <c r="H38">
-        <v>0.81</v>
+        <v>1.1599999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>150363</v>
+        <v>140231</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D39" s="5">
-        <v>263.40909090909093</v>
-      </c>
-      <c r="E39" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F41</f>
-        <v>289.90476190476193</v>
-      </c>
-      <c r="F39" s="7">
-        <f>'[1]DESV. VTS BY SKU'!G41</f>
-        <v>0.10058753440979484</v>
-      </c>
-      <c r="G39" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H41</f>
-        <v>SUBIÓ</v>
+        <v>34</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D39" s="4">
+        <v>554.42857142857144</v>
+      </c>
+      <c r="E39" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
+        <v>259</v>
+      </c>
+      <c r="F39" s="5">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
+        <v>-0.53285235763978356</v>
+      </c>
+      <c r="G39" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
+        <v>BAJO</v>
       </c>
       <c r="H39">
-        <v>0.81</v>
+        <v>1.1599999999999999</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>151500</v>
+        <v>140232</v>
       </c>
       <c r="B40" t="s">
-        <v>48</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D40" s="5">
-        <v>49.909090909090907</v>
-      </c>
-      <c r="E40" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F42</f>
-        <v>57.714285714285715</v>
+        <v>35</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D40" s="4">
+        <v>132.8095238095238</v>
+      </c>
+      <c r="E40" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
+        <v>407.5</v>
       </c>
       <c r="F40" s="6">
-        <f>'[1]DESV. VTS BY SKU'!G42</f>
-        <v>0.15638823835545157</v>
-      </c>
-      <c r="G40" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H42</f>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
+        <v>2.0683040516314093</v>
+      </c>
+      <c r="G40" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H40">
-        <v>2.62</v>
+        <v>1.1599999999999999</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>151501</v>
+        <v>150360</v>
       </c>
       <c r="B41" t="s">
-        <v>49</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D41" s="5">
-        <v>79.409090909090907</v>
-      </c>
-      <c r="E41" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F43</f>
-        <v>104.71428571428571</v>
-      </c>
-      <c r="F41" s="7">
-        <f>'[1]DESV. VTS BY SKU'!G43</f>
-        <v>0.31866873824515496</v>
-      </c>
-      <c r="G41" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H43</f>
-        <v>SUBIÓ</v>
+        <v>45</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D41" s="4">
+        <v>296.14285714285717</v>
+      </c>
+      <c r="E41" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
+        <v>117.5</v>
+      </c>
+      <c r="F41" s="5">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
+        <v>-0.60323203087313071</v>
+      </c>
+      <c r="G41" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
+        <v>BAJO</v>
       </c>
       <c r="H41">
-        <v>2.62</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>151502</v>
+        <v>150361</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D42" s="5">
-        <v>34.272727272727273</v>
-      </c>
-      <c r="E42" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F44</f>
-        <v>49.333333333333336</v>
+        <v>36</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D42" s="4">
+        <v>528.71428571428567</v>
+      </c>
+      <c r="E42" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
+        <v>230</v>
       </c>
       <c r="F42" s="6">
-        <f>'[1]DESV. VTS BY SKU'!G44</f>
-        <v>0.43943412908930157</v>
-      </c>
-      <c r="G42" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H44</f>
-        <v>SUBIÓ</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
+        <v>-0.56498243717914076</v>
+      </c>
+      <c r="G42" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
+        <v>BAJO</v>
       </c>
       <c r="H42">
-        <v>2.62</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43">
+        <v>150362</v>
+      </c>
+      <c r="B43" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D43" s="4">
+        <v>305.57142857142856</v>
+      </c>
+      <c r="E43" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
+        <v>119</v>
+      </c>
+      <c r="F43" s="5">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
+        <v>-0.61056568489948571</v>
+      </c>
+      <c r="G43" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
+        <v>BAJO</v>
+      </c>
+      <c r="H43">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>150363</v>
+      </c>
+      <c r="B44" t="s">
+        <v>38</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D44" s="4">
+        <v>289.90476190476193</v>
+      </c>
+      <c r="E44" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
+        <v>144.5</v>
+      </c>
+      <c r="F44" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
+        <v>-0.50156044678055189</v>
+      </c>
+      <c r="G44" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
+        <v>BAJO</v>
+      </c>
+      <c r="H44">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>151500</v>
+      </c>
+      <c r="B45" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D45" s="4">
+        <v>57.714285714285715</v>
+      </c>
+      <c r="E45" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
+        <v>35</v>
+      </c>
+      <c r="F45" s="5">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
+        <v>-0.39356435643564358</v>
+      </c>
+      <c r="G45" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
+        <v>BAJO</v>
+      </c>
+      <c r="H45">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>151501</v>
+      </c>
+      <c r="B46" t="s">
+        <v>47</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D46" s="4">
+        <v>104.71428571428571</v>
+      </c>
+      <c r="E46" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F48</f>
+        <v>51.5</v>
+      </c>
+      <c r="F46" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G48</f>
+        <v>-0.50818553888130968</v>
+      </c>
+      <c r="G46" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H48</f>
+        <v>BAJO</v>
+      </c>
+      <c r="H46">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>151502</v>
+      </c>
+      <c r="B47" t="s">
+        <v>48</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D47" s="4">
+        <v>49.333333333333336</v>
+      </c>
+      <c r="E47" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F49</f>
+        <v>14</v>
+      </c>
+      <c r="F47" s="5">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G49</f>
+        <v>-0.71621621621621623</v>
+      </c>
+      <c r="G47" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H49</f>
+        <v>BAJO</v>
+      </c>
+      <c r="H47">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48">
         <v>151503</v>
       </c>
-      <c r="B43" t="s">
-        <v>51</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D43" s="5">
-        <v>37.5</v>
-      </c>
-      <c r="E43" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F45</f>
+      <c r="B48" t="s">
+        <v>49</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D48" s="4">
         <v>55.333333333333336</v>
       </c>
-      <c r="F43" s="7">
-        <f>'[1]DESV. VTS BY SKU'!G45</f>
-        <v>0.47555555555555551</v>
-      </c>
-      <c r="G43" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H45</f>
-        <v>SUBIÓ</v>
-      </c>
-      <c r="H43">
+      <c r="E48" s="4">
+        <f ca="1">'[1]DESV. VTS BY SKU'!F50</f>
+        <v>17.5</v>
+      </c>
+      <c r="F48" s="6">
+        <f ca="1">'[1]DESV. VTS BY SKU'!G50</f>
+        <v>-0.68373493975903621</v>
+      </c>
+      <c r="G48" s="7" t="str">
+        <f ca="1">'[1]DESV. VTS BY SKU'!H50</f>
+        <v>BAJO</v>
+      </c>
+      <c r="H48">
         <v>2.62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B44" t="s">
-        <v>41</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D44" s="5">
-        <v>0.81818181818181823</v>
-      </c>
-      <c r="E44" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F46</f>
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="F44" s="6">
-        <f>'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-0.47619047619047628</v>
-      </c>
-      <c r="G44" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H46</f>
-        <v>BAJO</v>
-      </c>
-      <c r="H44">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" t="s">
-        <v>42</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D45" s="5">
-        <v>3.2727272727272729</v>
-      </c>
-      <c r="E45" s="5">
-        <f>'[1]DESV. VTS BY SKU'!F47</f>
-        <v>2.4761904761904763</v>
-      </c>
-      <c r="F45" s="7">
-        <f>'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.24338624338624337</v>
-      </c>
-      <c r="G45" s="8" t="str">
-        <f>'[1]DESV. VTS BY SKU'!H47</f>
-        <v>BAJO</v>
-      </c>
-      <c r="H45">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -2426,18 +2512,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0594D04-A4EC-4121-8DE8-47AD5FDB08C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD8C7A46-A3AD-4E3D-9B10-3F8B727C80C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -362,6 +362,7 @@
       <sheetName val="INVENTARIO NACIONAL INICIO"/>
       <sheetName val="INVENTARIO NACIONAL 02-09-2026"/>
       <sheetName val="INVENTARIO NACIONAL 03-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 04-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -374,13 +375,14 @@
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
-      <sheetData sheetId="6">
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7">
         <row r="4">
           <cell r="F4">
-            <v>750.5</v>
+            <v>887</v>
           </cell>
           <cell r="G4">
-            <v>-0.36831663326653308</v>
+            <v>-0.2534268537074148</v>
           </cell>
           <cell r="H4" t="str">
             <v>BAJO</v>
@@ -388,10 +390,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>67.5</v>
+            <v>75.25</v>
           </cell>
           <cell r="G5">
-            <v>-0.11627182044887774</v>
+            <v>-1.4806733167082253E-2</v>
           </cell>
           <cell r="H5" t="str">
             <v>BAJO</v>
@@ -399,10 +401,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>236.5</v>
+            <v>442.5</v>
           </cell>
           <cell r="G6">
-            <v>-0.53579773810636511</v>
+            <v>-0.13146088419478452</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -410,10 +412,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>85.5</v>
+            <v>65.75</v>
           </cell>
           <cell r="G7">
-            <v>-0.12755102040816324</v>
+            <v>-0.32908163265306123</v>
           </cell>
           <cell r="H7" t="str">
             <v>BAJO</v>
@@ -421,10 +423,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>5.5</v>
+            <v>3.5</v>
           </cell>
           <cell r="G8">
-            <v>-0.53984063745019917</v>
+            <v>-0.70717131474103589</v>
           </cell>
           <cell r="H8" t="str">
             <v>BAJO</v>
@@ -432,10 +434,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>785</v>
+            <v>1056.75</v>
           </cell>
           <cell r="G9">
-            <v>-0.46245149509244465</v>
+            <v>-0.27636384387126223</v>
           </cell>
           <cell r="H9" t="str">
             <v>BAJO</v>
@@ -443,10 +445,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>90.5</v>
+            <v>115</v>
           </cell>
           <cell r="G10">
-            <v>-0.39819506016466122</v>
+            <v>-0.23527549081697274</v>
           </cell>
           <cell r="H10" t="str">
             <v>BAJO</v>
@@ -454,10 +456,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>181</v>
+            <v>246.25</v>
           </cell>
           <cell r="G11">
-            <v>-0.47318087318087321</v>
+            <v>-0.28326403326403327</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -465,10 +467,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>569.5</v>
+            <v>688</v>
           </cell>
           <cell r="G12">
-            <v>-0.25671224362958356</v>
+            <v>-0.10205096333126162</v>
           </cell>
           <cell r="H12" t="str">
             <v>BAJO</v>
@@ -476,10 +478,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>228</v>
+            <v>309</v>
           </cell>
           <cell r="G13">
-            <v>-0.37157107231920194</v>
+            <v>-0.14831342695891847</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -487,10 +489,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>2041</v>
+            <v>2618.5</v>
           </cell>
           <cell r="G14">
-            <v>-0.42042135439203809</v>
+            <v>-0.25642984638684552</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -498,10 +500,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>1292</v>
+            <v>1668</v>
           </cell>
           <cell r="G15">
-            <v>-0.4394793926247289</v>
+            <v>-0.27635574837310195</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -509,10 +511,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>1316</v>
+            <v>1671.75</v>
           </cell>
           <cell r="G16">
-            <v>-0.41936297167829228</v>
+            <v>-0.26240125220606769</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -520,10 +522,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>1592</v>
+            <v>1967.25</v>
           </cell>
           <cell r="G17">
-            <v>-0.40463724756918473</v>
+            <v>-0.26430441286462225</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -531,10 +533,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>528</v>
+            <v>585.25</v>
           </cell>
           <cell r="G18">
-            <v>0.35666218034993258</v>
+            <v>0.50376238835189024</v>
           </cell>
           <cell r="H18" t="str">
             <v>SUBIÓ</v>
@@ -542,10 +544,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>683</v>
+            <v>780.5</v>
           </cell>
           <cell r="G19">
-            <v>0.59437527790128941</v>
+            <v>0.82197643397065345</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -553,10 +555,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>695.5</v>
+            <v>766</v>
           </cell>
           <cell r="G20">
-            <v>0.7798562027784548</v>
+            <v>0.96027297099683162</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -564,10 +566,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>189.5</v>
+            <v>183.25</v>
           </cell>
           <cell r="G21">
-            <v>-0.21694214876033058</v>
+            <v>-0.24276859504132231</v>
           </cell>
           <cell r="H21" t="str">
             <v>BAJO</v>
@@ -575,10 +577,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>99.5</v>
+            <v>80.75</v>
           </cell>
           <cell r="G22">
-            <v>-0.30023442732752859</v>
+            <v>-0.43209979906229079</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -586,10 +588,10 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>380</v>
+            <v>426.25</v>
           </cell>
           <cell r="G23">
-            <v>-0.25939675174013921</v>
+            <v>-0.16925754060324827</v>
           </cell>
           <cell r="H23" t="str">
             <v>BAJO</v>
@@ -597,10 +599,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>628</v>
+            <v>693.75</v>
           </cell>
           <cell r="G24">
-            <v>-0.22601091613357593</v>
+            <v>-0.14497623099947188</v>
           </cell>
           <cell r="H24" t="str">
             <v>BAJO</v>
@@ -608,21 +610,21 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>10</v>
+            <v>80</v>
           </cell>
           <cell r="G25">
-            <v>-0.8665819567979669</v>
+            <v>6.7344345616264345E-2</v>
           </cell>
           <cell r="H25" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="26">
           <cell r="F26">
-            <v>343.5</v>
+            <v>457.75</v>
           </cell>
           <cell r="G26">
-            <v>-0.56405995044418922</v>
+            <v>-0.41906387864869765</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -630,10 +632,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>309</v>
+            <v>427</v>
           </cell>
           <cell r="G27">
-            <v>-0.7574024226110363</v>
+            <v>-0.66475998205473308</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -641,10 +643,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>388.5</v>
+            <v>444</v>
           </cell>
           <cell r="G28">
-            <v>-0.26585980383334828</v>
+            <v>-0.16098263295239801</v>
           </cell>
           <cell r="H28" t="str">
             <v>BAJO</v>
@@ -652,10 +654,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>236.5</v>
+            <v>288.25</v>
           </cell>
           <cell r="G29">
-            <v>-0.41148240312833273</v>
+            <v>-0.282705296836118</v>
           </cell>
           <cell r="H29" t="str">
             <v>BAJO</v>
@@ -663,32 +665,32 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>41</v>
+            <v>211.5</v>
           </cell>
           <cell r="G30">
-            <v>-0.46120150187734676</v>
+            <v>1.7794117647058822</v>
           </cell>
           <cell r="H30" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="31">
           <cell r="F31">
-            <v>70</v>
+            <v>231.75</v>
           </cell>
           <cell r="G31">
-            <v>-2.9062087186261687E-2</v>
+            <v>2.214498018494055</v>
           </cell>
           <cell r="H31" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="32">
           <cell r="F32">
-            <v>99</v>
+            <v>101.75</v>
           </cell>
           <cell r="G32">
-            <v>-0.22569832402234635</v>
+            <v>-0.20418994413407821</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -696,10 +698,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>66.5</v>
+            <v>97.75</v>
           </cell>
           <cell r="G33">
-            <v>-0.53604651162790695</v>
+            <v>-0.31802325581395352</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -707,10 +709,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>398.5</v>
+            <v>567.5</v>
           </cell>
           <cell r="G34">
-            <v>-0.38898218457943923</v>
+            <v>-0.12985543224299056</v>
           </cell>
           <cell r="H34" t="str">
             <v>BAJO</v>
@@ -718,10 +720,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>327</v>
+            <v>449.25</v>
           </cell>
           <cell r="G35">
-            <v>-0.48016654049962149</v>
+            <v>-0.28582513247539743</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -729,10 +731,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>522.5</v>
+            <v>598.25</v>
           </cell>
           <cell r="G36">
-            <v>-0.38687416182387124</v>
+            <v>-0.29798558337058556</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -740,10 +742,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>309.5</v>
+            <v>330.5</v>
           </cell>
           <cell r="G37">
-            <v>-0.4654576856649395</v>
+            <v>-0.42918825561312612</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -751,10 +753,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>4.5</v>
+            <v>4</v>
           </cell>
           <cell r="G38">
-            <v>0.81730769230769229</v>
+            <v>0.61538461538461542</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -762,10 +764,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>2</v>
+            <v>1.25</v>
           </cell>
           <cell r="G39">
-            <v>3.666666666666667</v>
+            <v>1.916666666666667</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -773,10 +775,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>119</v>
+            <v>88.5</v>
           </cell>
           <cell r="G40">
-            <v>-0.1322916666666667</v>
+            <v>-0.35468749999999993</v>
           </cell>
           <cell r="H40" t="str">
             <v>BAJO</v>
@@ -784,10 +786,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>259</v>
+            <v>383</v>
           </cell>
           <cell r="G41">
-            <v>-0.53285235763978356</v>
+            <v>-0.30919866013913944</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -795,10 +797,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>407.5</v>
+            <v>400.75</v>
           </cell>
           <cell r="G42">
-            <v>2.0683040516314093</v>
+            <v>2.0174793832915028</v>
           </cell>
           <cell r="H42" t="str">
             <v>SUBIÓ</v>
@@ -806,10 +808,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>117.5</v>
+            <v>161</v>
           </cell>
           <cell r="G43">
-            <v>-0.60323203087313071</v>
+            <v>-0.45634346357935363</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -817,10 +819,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>230</v>
+            <v>262.75</v>
           </cell>
           <cell r="G44">
-            <v>-0.56498243717914076</v>
+            <v>-0.50303971899486621</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -828,10 +830,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>119</v>
+            <v>198.5</v>
           </cell>
           <cell r="G45">
-            <v>-0.61056568489948571</v>
+            <v>-0.35039738195418413</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -839,10 +841,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>144.5</v>
+            <v>212.5</v>
           </cell>
           <cell r="G46">
-            <v>-0.50156044678055189</v>
+            <v>-0.26700065703022346</v>
           </cell>
           <cell r="H46" t="str">
             <v>BAJO</v>
@@ -850,10 +852,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>35</v>
+            <v>33.25</v>
           </cell>
           <cell r="G47">
-            <v>-0.39356435643564358</v>
+            <v>-0.42388613861386137</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -861,10 +863,10 @@
         </row>
         <row r="48">
           <cell r="F48">
-            <v>51.5</v>
+            <v>51</v>
           </cell>
           <cell r="G48">
-            <v>-0.50818553888130968</v>
+            <v>-0.51296043656207368</v>
           </cell>
           <cell r="H48" t="str">
             <v>BAJO</v>
@@ -872,10 +874,10 @@
         </row>
         <row r="49">
           <cell r="F49">
-            <v>14</v>
+            <v>20.75</v>
           </cell>
           <cell r="G49">
-            <v>-0.71621621621621623</v>
+            <v>-0.57939189189189189</v>
           </cell>
           <cell r="H49" t="str">
             <v>BAJO</v>
@@ -883,10 +885,10 @@
         </row>
         <row r="50">
           <cell r="F50">
-            <v>17.5</v>
+            <v>31.5</v>
           </cell>
           <cell r="G50">
-            <v>-0.68373493975903621</v>
+            <v>-0.43072289156626509</v>
           </cell>
           <cell r="H50" t="str">
             <v>BAJO</v>
@@ -1149,11 +1151,11 @@
       </c>
       <c r="E2" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>750.5</v>
+        <v>887</v>
       </c>
       <c r="F2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>-0.36831663326653308</v>
+        <v>-0.2534268537074148</v>
       </c>
       <c r="G2" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1178,11 +1180,11 @@
       </c>
       <c r="E3" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>67.5</v>
+        <v>75.25</v>
       </c>
       <c r="F3" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-0.11627182044887774</v>
+        <v>-1.4806733167082253E-2</v>
       </c>
       <c r="G3" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1207,11 +1209,11 @@
       </c>
       <c r="E4" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>236.5</v>
+        <v>442.5</v>
       </c>
       <c r="F4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-0.53579773810636511</v>
+        <v>-0.13146088419478452</v>
       </c>
       <c r="G4" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1236,11 +1238,11 @@
       </c>
       <c r="E5" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>85.5</v>
+        <v>65.75</v>
       </c>
       <c r="F5" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>-0.12755102040816324</v>
+        <v>-0.32908163265306123</v>
       </c>
       <c r="G5" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1265,11 +1267,11 @@
       </c>
       <c r="E6" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="F6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>-0.53984063745019917</v>
+        <v>-0.70717131474103589</v>
       </c>
       <c r="G6" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1294,11 +1296,11 @@
       </c>
       <c r="E7" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>785</v>
+        <v>1056.75</v>
       </c>
       <c r="F7" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-0.46245149509244465</v>
+        <v>-0.27636384387126223</v>
       </c>
       <c r="G7" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1323,11 +1325,11 @@
       </c>
       <c r="E8" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>90.5</v>
+        <v>115</v>
       </c>
       <c r="F8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-0.39819506016466122</v>
+        <v>-0.23527549081697274</v>
       </c>
       <c r="G8" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1352,11 +1354,11 @@
       </c>
       <c r="E9" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>181</v>
+        <v>246.25</v>
       </c>
       <c r="F9" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-0.47318087318087321</v>
+        <v>-0.28326403326403327</v>
       </c>
       <c r="G9" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1381,11 +1383,11 @@
       </c>
       <c r="E10" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>569.5</v>
+        <v>688</v>
       </c>
       <c r="F10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-0.25671224362958356</v>
+        <v>-0.10205096333126162</v>
       </c>
       <c r="G10" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1410,11 +1412,11 @@
       </c>
       <c r="E11" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>228</v>
+        <v>309</v>
       </c>
       <c r="F11" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.37157107231920194</v>
+        <v>-0.14831342695891847</v>
       </c>
       <c r="G11" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1439,11 +1441,11 @@
       </c>
       <c r="E12" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>2041</v>
+        <v>2618.5</v>
       </c>
       <c r="F12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-0.42042135439203809</v>
+        <v>-0.25642984638684552</v>
       </c>
       <c r="G12" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1468,11 +1470,11 @@
       </c>
       <c r="E13" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>1292</v>
+        <v>1668</v>
       </c>
       <c r="F13" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-0.4394793926247289</v>
+        <v>-0.27635574837310195</v>
       </c>
       <c r="G13" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1497,11 +1499,11 @@
       </c>
       <c r="E14" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>1316</v>
+        <v>1671.75</v>
       </c>
       <c r="F14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-0.41936297167829228</v>
+        <v>-0.26240125220606769</v>
       </c>
       <c r="G14" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1526,11 +1528,11 @@
       </c>
       <c r="E15" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>1592</v>
+        <v>1967.25</v>
       </c>
       <c r="F15" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-0.40463724756918473</v>
+        <v>-0.26430441286462225</v>
       </c>
       <c r="G15" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1555,11 +1557,11 @@
       </c>
       <c r="E16" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>528</v>
+        <v>585.25</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>0.35666218034993258</v>
+        <v>0.50376238835189024</v>
       </c>
       <c r="G16" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1584,11 +1586,11 @@
       </c>
       <c r="E17" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>683</v>
+        <v>780.5</v>
       </c>
       <c r="F17" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>0.59437527790128941</v>
+        <v>0.82197643397065345</v>
       </c>
       <c r="G17" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1613,11 +1615,11 @@
       </c>
       <c r="E18" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>695.5</v>
+        <v>766</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>0.7798562027784548</v>
+        <v>0.96027297099683162</v>
       </c>
       <c r="G18" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1642,11 +1644,11 @@
       </c>
       <c r="E19" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>189.5</v>
+        <v>183.25</v>
       </c>
       <c r="F19" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>-0.21694214876033058</v>
+        <v>-0.24276859504132231</v>
       </c>
       <c r="G19" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1671,11 +1673,11 @@
       </c>
       <c r="E20" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>99.5</v>
+        <v>80.75</v>
       </c>
       <c r="F20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-0.30023442732752859</v>
+        <v>-0.43209979906229079</v>
       </c>
       <c r="G20" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1700,11 +1702,11 @@
       </c>
       <c r="E21" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>380</v>
+        <v>426.25</v>
       </c>
       <c r="F21" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>-0.25939675174013921</v>
+        <v>-0.16925754060324827</v>
       </c>
       <c r="G21" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
@@ -1729,11 +1731,11 @@
       </c>
       <c r="E22" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>628</v>
+        <v>693.75</v>
       </c>
       <c r="F22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>-0.22601091613357593</v>
+        <v>-0.14497623099947188</v>
       </c>
       <c r="G22" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1758,15 +1760,15 @@
       </c>
       <c r="E23" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="F23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-0.8665819567979669</v>
+        <v>6.7344345616264345E-2</v>
       </c>
       <c r="G23" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H23">
         <v>4.1500000000000004</v>
@@ -1787,11 +1789,11 @@
       </c>
       <c r="E24" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>343.5</v>
+        <v>457.75</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.56405995044418922</v>
+        <v>-0.41906387864869765</v>
       </c>
       <c r="G24" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1816,11 +1818,11 @@
       </c>
       <c r="E25" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>309</v>
+        <v>427</v>
       </c>
       <c r="F25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.7574024226110363</v>
+        <v>-0.66475998205473308</v>
       </c>
       <c r="G25" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1845,11 +1847,11 @@
       </c>
       <c r="E26" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>388.5</v>
+        <v>444</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-0.26585980383334828</v>
+        <v>-0.16098263295239801</v>
       </c>
       <c r="G26" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1874,11 +1876,11 @@
       </c>
       <c r="E27" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>236.5</v>
+        <v>288.25</v>
       </c>
       <c r="F27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>-0.41148240312833273</v>
+        <v>-0.282705296836118</v>
       </c>
       <c r="G27" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1903,15 +1905,15 @@
       </c>
       <c r="E28" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>41</v>
+        <v>211.5</v>
       </c>
       <c r="F28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>-0.46120150187734676</v>
+        <v>1.7794117647058822</v>
       </c>
       <c r="G28" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H28">
         <v>1.63</v>
@@ -1932,15 +1934,15 @@
       </c>
       <c r="E29" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>70</v>
+        <v>231.75</v>
       </c>
       <c r="F29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-2.9062087186261687E-2</v>
+        <v>2.214498018494055</v>
       </c>
       <c r="G29" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H29">
         <v>1.63</v>
@@ -1961,11 +1963,11 @@
       </c>
       <c r="E30" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>99</v>
+        <v>101.75</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-0.22569832402234635</v>
+        <v>-0.20418994413407821</v>
       </c>
       <c r="G30" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1990,11 +1992,11 @@
       </c>
       <c r="E31" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>66.5</v>
+        <v>97.75</v>
       </c>
       <c r="F31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-0.53604651162790695</v>
+        <v>-0.31802325581395352</v>
       </c>
       <c r="G31" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2019,11 +2021,11 @@
       </c>
       <c r="E32" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>398.5</v>
+        <v>567.5</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-0.38898218457943923</v>
+        <v>-0.12985543224299056</v>
       </c>
       <c r="G32" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2048,11 +2050,11 @@
       </c>
       <c r="E33" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>327</v>
+        <v>449.25</v>
       </c>
       <c r="F33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-0.48016654049962149</v>
+        <v>-0.28582513247539743</v>
       </c>
       <c r="G33" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2077,11 +2079,11 @@
       </c>
       <c r="E34" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>522.5</v>
+        <v>598.25</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-0.38687416182387124</v>
+        <v>-0.29798558337058556</v>
       </c>
       <c r="G34" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2106,11 +2108,11 @@
       </c>
       <c r="E35" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>309.5</v>
+        <v>330.5</v>
       </c>
       <c r="F35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.4654576856649395</v>
+        <v>-0.42918825561312612</v>
       </c>
       <c r="G35" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2135,11 +2137,11 @@
       </c>
       <c r="E36" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>0.81730769230769229</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="G36" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2164,11 +2166,11 @@
       </c>
       <c r="E37" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="F37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>3.666666666666667</v>
+        <v>1.916666666666667</v>
       </c>
       <c r="G37" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2193,11 +2195,11 @@
       </c>
       <c r="E38" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>119</v>
+        <v>88.5</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>-0.1322916666666667</v>
+        <v>-0.35468749999999993</v>
       </c>
       <c r="G38" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2222,11 +2224,11 @@
       </c>
       <c r="E39" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>259</v>
+        <v>383</v>
       </c>
       <c r="F39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-0.53285235763978356</v>
+        <v>-0.30919866013913944</v>
       </c>
       <c r="G39" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2251,11 +2253,11 @@
       </c>
       <c r="E40" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>407.5</v>
+        <v>400.75</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>2.0683040516314093</v>
+        <v>2.0174793832915028</v>
       </c>
       <c r="G40" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2280,11 +2282,11 @@
       </c>
       <c r="E41" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>117.5</v>
+        <v>161</v>
       </c>
       <c r="F41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.60323203087313071</v>
+        <v>-0.45634346357935363</v>
       </c>
       <c r="G41" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2309,11 +2311,11 @@
       </c>
       <c r="E42" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>230</v>
+        <v>262.75</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-0.56498243717914076</v>
+        <v>-0.50303971899486621</v>
       </c>
       <c r="G42" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2338,11 +2340,11 @@
       </c>
       <c r="E43" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>119</v>
+        <v>198.5</v>
       </c>
       <c r="F43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-0.61056568489948571</v>
+        <v>-0.35039738195418413</v>
       </c>
       <c r="G43" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2367,11 +2369,11 @@
       </c>
       <c r="E44" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>144.5</v>
+        <v>212.5</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-0.50156044678055189</v>
+        <v>-0.26700065703022346</v>
       </c>
       <c r="G44" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
@@ -2396,11 +2398,11 @@
       </c>
       <c r="E45" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>35</v>
+        <v>33.25</v>
       </c>
       <c r="F45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.39356435643564358</v>
+        <v>-0.42388613861386137</v>
       </c>
       <c r="G45" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
@@ -2425,11 +2427,11 @@
       </c>
       <c r="E46" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F48</f>
-        <v>51.5</v>
+        <v>51</v>
       </c>
       <c r="F46" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G48</f>
-        <v>-0.50818553888130968</v>
+        <v>-0.51296043656207368</v>
       </c>
       <c r="G46" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H48</f>
@@ -2454,11 +2456,11 @@
       </c>
       <c r="E47" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F49</f>
-        <v>14</v>
+        <v>20.75</v>
       </c>
       <c r="F47" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G49</f>
-        <v>-0.71621621621621623</v>
+        <v>-0.57939189189189189</v>
       </c>
       <c r="G47" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H49</f>
@@ -2483,11 +2485,11 @@
       </c>
       <c r="E48" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F50</f>
-        <v>17.5</v>
+        <v>31.5</v>
       </c>
       <c r="F48" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G50</f>
-        <v>-0.68373493975903621</v>
+        <v>-0.43072289156626509</v>
       </c>
       <c r="G48" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H50</f>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD8C7A46-A3AD-4E3D-9B10-3F8B727C80C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E324EF51-1007-48B8-99C8-2160D62C1169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -363,6 +363,7 @@
       <sheetName val="INVENTARIO NACIONAL 02-09-2026"/>
       <sheetName val="INVENTARIO NACIONAL 03-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 04-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 08-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -376,13 +377,14 @@
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
-      <sheetData sheetId="7">
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8">
         <row r="4">
           <cell r="F4">
-            <v>887</v>
+            <v>987.4</v>
           </cell>
           <cell r="G4">
-            <v>-0.2534268537074148</v>
+            <v>-0.16892184368737473</v>
           </cell>
           <cell r="H4" t="str">
             <v>BAJO</v>
@@ -390,21 +392,21 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>75.25</v>
+            <v>83.8</v>
           </cell>
           <cell r="G5">
-            <v>-1.4806733167082253E-2</v>
+            <v>9.7132169576059857E-2</v>
           </cell>
           <cell r="H5" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="6">
           <cell r="F6">
-            <v>442.5</v>
+            <v>489</v>
           </cell>
           <cell r="G6">
-            <v>-0.13146088419478452</v>
+            <v>-4.0190672025422924E-2</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -412,10 +414,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>65.75</v>
+            <v>75.2</v>
           </cell>
           <cell r="G7">
-            <v>-0.32908163265306123</v>
+            <v>-0.23265306122448981</v>
           </cell>
           <cell r="H7" t="str">
             <v>BAJO</v>
@@ -423,10 +425,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>3.5</v>
+            <v>6.2</v>
           </cell>
           <cell r="G8">
-            <v>-0.70717131474103589</v>
+            <v>-0.48127490039840637</v>
           </cell>
           <cell r="H8" t="str">
             <v>BAJO</v>
@@ -434,10 +436,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1056.75</v>
+            <v>1339</v>
           </cell>
           <cell r="G9">
-            <v>-0.27636384387126223</v>
+            <v>-8.308605341246289E-2</v>
           </cell>
           <cell r="H9" t="str">
             <v>BAJO</v>
@@ -445,10 +447,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>115</v>
+            <v>113</v>
           </cell>
           <cell r="G10">
-            <v>-0.23527549081697274</v>
+            <v>-0.24857504749841675</v>
           </cell>
           <cell r="H10" t="str">
             <v>BAJO</v>
@@ -456,10 +458,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>246.25</v>
+            <v>235.6</v>
           </cell>
           <cell r="G11">
-            <v>-0.28326403326403327</v>
+            <v>-0.31426195426195425</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -467,10 +469,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>688</v>
+            <v>665.8</v>
           </cell>
           <cell r="G12">
-            <v>-0.10205096333126162</v>
+            <v>-0.13102548166563088</v>
           </cell>
           <cell r="H12" t="str">
             <v>BAJO</v>
@@ -478,10 +480,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>309</v>
+            <v>290.60000000000002</v>
           </cell>
           <cell r="G13">
-            <v>-0.14831342695891847</v>
+            <v>-0.19902874392964942</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -489,10 +491,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>2618.5</v>
+            <v>3103.6</v>
           </cell>
           <cell r="G14">
-            <v>-0.25642984638684552</v>
+            <v>-0.11867697966248381</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -500,10 +502,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>1668</v>
+            <v>1883.2</v>
           </cell>
           <cell r="G15">
-            <v>-0.27635574837310195</v>
+            <v>-0.18299349240780904</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -511,10 +513,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>1671.75</v>
+            <v>1997.6</v>
           </cell>
           <cell r="G16">
-            <v>-0.26240125220606769</v>
+            <v>-0.11863181779981513</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -522,10 +524,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>1967.25</v>
+            <v>2303</v>
           </cell>
           <cell r="G17">
-            <v>-0.26430441286462225</v>
+            <v>-0.13874345549738221</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -533,10 +535,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>585.25</v>
+            <v>578.6</v>
           </cell>
           <cell r="G18">
-            <v>0.50376238835189024</v>
+            <v>0.48667563930013458</v>
           </cell>
           <cell r="H18" t="str">
             <v>SUBIÓ</v>
@@ -544,10 +546,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>780.5</v>
+            <v>760.4</v>
           </cell>
           <cell r="G19">
-            <v>0.82197643397065345</v>
+            <v>0.77505558025789223</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -555,10 +557,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>766</v>
+            <v>752</v>
           </cell>
           <cell r="G20">
-            <v>0.96027297099683162</v>
+            <v>0.92444552766268595</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -566,10 +568,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>183.25</v>
+            <v>196</v>
           </cell>
           <cell r="G21">
-            <v>-0.24276859504132231</v>
+            <v>-0.19008264462809921</v>
           </cell>
           <cell r="H21" t="str">
             <v>BAJO</v>
@@ -577,10 +579,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>80.75</v>
+            <v>85.8</v>
           </cell>
           <cell r="G22">
-            <v>-0.43209979906229079</v>
+            <v>-0.3965840589417281</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -588,10 +590,10 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>426.25</v>
+            <v>436.2</v>
           </cell>
           <cell r="G23">
-            <v>-0.16925754060324827</v>
+            <v>-0.14986542923433877</v>
           </cell>
           <cell r="H23" t="str">
             <v>BAJO</v>
@@ -599,10 +601,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>693.75</v>
+            <v>696.4</v>
           </cell>
           <cell r="G24">
-            <v>-0.14497623099947188</v>
+            <v>-0.14171019426022657</v>
           </cell>
           <cell r="H24" t="str">
             <v>BAJO</v>
@@ -610,21 +612,21 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>80</v>
+            <v>64</v>
           </cell>
           <cell r="G25">
-            <v>6.7344345616264345E-2</v>
+            <v>-0.14612452350698857</v>
           </cell>
           <cell r="H25" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="26">
           <cell r="F26">
-            <v>457.75</v>
+            <v>612.20000000000005</v>
           </cell>
           <cell r="G26">
-            <v>-0.41906387864869765</v>
+            <v>-0.22304949537680541</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -632,10 +634,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>427</v>
+            <v>830.8</v>
           </cell>
           <cell r="G27">
-            <v>-0.66475998205473308</v>
+            <v>-0.34773441004934957</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -643,10 +645,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>444</v>
+            <v>430</v>
           </cell>
           <cell r="G28">
-            <v>-0.16098263295239801</v>
+            <v>-0.18743813551696209</v>
           </cell>
           <cell r="H28" t="str">
             <v>BAJO</v>
@@ -654,10 +656,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>288.25</v>
+            <v>290.60000000000002</v>
           </cell>
           <cell r="G29">
-            <v>-0.282705296836118</v>
+            <v>-0.27685744756487729</v>
           </cell>
           <cell r="H29" t="str">
             <v>BAJO</v>
@@ -665,10 +667,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>211.5</v>
+            <v>225</v>
           </cell>
           <cell r="G30">
-            <v>1.7794117647058822</v>
+            <v>1.9568210262828534</v>
           </cell>
           <cell r="H30" t="str">
             <v>SUBIÓ</v>
@@ -676,10 +678,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>231.75</v>
+            <v>280.39999999999998</v>
           </cell>
           <cell r="G31">
-            <v>2.214498018494055</v>
+            <v>2.8892998678996031</v>
           </cell>
           <cell r="H31" t="str">
             <v>SUBIÓ</v>
@@ -687,10 +689,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>101.75</v>
+            <v>104</v>
           </cell>
           <cell r="G32">
-            <v>-0.20418994413407821</v>
+            <v>-0.1865921787709498</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -698,10 +700,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>97.75</v>
+            <v>99.2</v>
           </cell>
           <cell r="G33">
-            <v>-0.31802325581395352</v>
+            <v>-0.3079069767441861</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -709,10 +711,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>567.5</v>
+            <v>606</v>
           </cell>
           <cell r="G34">
-            <v>-0.12985543224299056</v>
+            <v>-7.0823598130841048E-2</v>
           </cell>
           <cell r="H34" t="str">
             <v>BAJO</v>
@@ -720,10 +722,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>449.25</v>
+            <v>475.6</v>
           </cell>
           <cell r="G35">
-            <v>-0.28582513247539743</v>
+            <v>-0.24393641180923542</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -731,10 +733,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>598.25</v>
+            <v>635.20000000000005</v>
           </cell>
           <cell r="G36">
-            <v>-0.29798558337058556</v>
+            <v>-0.25462673223066601</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -742,10 +744,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>330.5</v>
+            <v>358.8</v>
           </cell>
           <cell r="G37">
-            <v>-0.42918825561312612</v>
+            <v>-0.38031088082901554</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -764,10 +766,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>1.25</v>
+            <v>1.2</v>
           </cell>
           <cell r="G39">
-            <v>1.916666666666667</v>
+            <v>1.8000000000000003</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -775,10 +777,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>88.5</v>
+            <v>96.6</v>
           </cell>
           <cell r="G40">
-            <v>-0.35468749999999993</v>
+            <v>-0.29562500000000003</v>
           </cell>
           <cell r="H40" t="str">
             <v>BAJO</v>
@@ -786,10 +788,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>383</v>
+            <v>408</v>
           </cell>
           <cell r="G41">
-            <v>-0.30919866013913944</v>
+            <v>-0.26410718886884821</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -797,10 +799,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>400.75</v>
+            <v>392.8</v>
           </cell>
           <cell r="G42">
-            <v>2.0174793832915028</v>
+            <v>1.9576192183578347</v>
           </cell>
           <cell r="H42" t="str">
             <v>SUBIÓ</v>
@@ -808,10 +810,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>161</v>
+            <v>140.6</v>
           </cell>
           <cell r="G43">
-            <v>-0.45634346357935363</v>
+            <v>-0.52522913651712499</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -819,10 +821,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>262.75</v>
+            <v>249.6</v>
           </cell>
           <cell r="G44">
-            <v>-0.50303971899486621</v>
+            <v>-0.52791137530397192</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -830,10 +832,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>198.5</v>
+            <v>192.6</v>
           </cell>
           <cell r="G45">
-            <v>-0.35039738195418413</v>
+            <v>-0.36970546984572228</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -841,10 +843,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>212.5</v>
+            <v>210.2</v>
           </cell>
           <cell r="G46">
-            <v>-0.26700065703022346</v>
+            <v>-0.27493429697766103</v>
           </cell>
           <cell r="H46" t="str">
             <v>BAJO</v>
@@ -852,10 +854,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>33.25</v>
+            <v>28.8</v>
           </cell>
           <cell r="G47">
-            <v>-0.42388613861386137</v>
+            <v>-0.50099009900990099</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -863,10 +865,10 @@
         </row>
         <row r="48">
           <cell r="F48">
-            <v>51</v>
+            <v>69.2</v>
           </cell>
           <cell r="G48">
-            <v>-0.51296043656207368</v>
+            <v>-0.33915416098226459</v>
           </cell>
           <cell r="H48" t="str">
             <v>BAJO</v>
@@ -874,10 +876,10 @@
         </row>
         <row r="49">
           <cell r="F49">
-            <v>20.75</v>
+            <v>22.6</v>
           </cell>
           <cell r="G49">
-            <v>-0.57939189189189189</v>
+            <v>-0.54189189189189191</v>
           </cell>
           <cell r="H49" t="str">
             <v>BAJO</v>
@@ -885,10 +887,10 @@
         </row>
         <row r="50">
           <cell r="F50">
-            <v>31.5</v>
+            <v>29.8</v>
           </cell>
           <cell r="G50">
-            <v>-0.43072289156626509</v>
+            <v>-0.46144578313253015</v>
           </cell>
           <cell r="H50" t="str">
             <v>BAJO</v>
@@ -1151,11 +1153,11 @@
       </c>
       <c r="E2" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>887</v>
+        <v>987.4</v>
       </c>
       <c r="F2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>-0.2534268537074148</v>
+        <v>-0.16892184368737473</v>
       </c>
       <c r="G2" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1180,15 +1182,15 @@
       </c>
       <c r="E3" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>75.25</v>
+        <v>83.8</v>
       </c>
       <c r="F3" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-1.4806733167082253E-2</v>
+        <v>9.7132169576059857E-2</v>
       </c>
       <c r="G3" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H3">
         <v>1.59</v>
@@ -1209,11 +1211,11 @@
       </c>
       <c r="E4" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>442.5</v>
+        <v>489</v>
       </c>
       <c r="F4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-0.13146088419478452</v>
+        <v>-4.0190672025422924E-2</v>
       </c>
       <c r="G4" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1238,11 +1240,11 @@
       </c>
       <c r="E5" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>65.75</v>
+        <v>75.2</v>
       </c>
       <c r="F5" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>-0.32908163265306123</v>
+        <v>-0.23265306122448981</v>
       </c>
       <c r="G5" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1267,11 +1269,11 @@
       </c>
       <c r="E6" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="F6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>-0.70717131474103589</v>
+        <v>-0.48127490039840637</v>
       </c>
       <c r="G6" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1296,11 +1298,11 @@
       </c>
       <c r="E7" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1056.75</v>
+        <v>1339</v>
       </c>
       <c r="F7" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-0.27636384387126223</v>
+        <v>-8.308605341246289E-2</v>
       </c>
       <c r="G7" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1325,11 +1327,11 @@
       </c>
       <c r="E8" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-0.23527549081697274</v>
+        <v>-0.24857504749841675</v>
       </c>
       <c r="G8" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1354,11 +1356,11 @@
       </c>
       <c r="E9" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>246.25</v>
+        <v>235.6</v>
       </c>
       <c r="F9" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-0.28326403326403327</v>
+        <v>-0.31426195426195425</v>
       </c>
       <c r="G9" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1383,11 +1385,11 @@
       </c>
       <c r="E10" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>688</v>
+        <v>665.8</v>
       </c>
       <c r="F10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-0.10205096333126162</v>
+        <v>-0.13102548166563088</v>
       </c>
       <c r="G10" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1412,11 +1414,11 @@
       </c>
       <c r="E11" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>309</v>
+        <v>290.60000000000002</v>
       </c>
       <c r="F11" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.14831342695891847</v>
+        <v>-0.19902874392964942</v>
       </c>
       <c r="G11" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1441,11 +1443,11 @@
       </c>
       <c r="E12" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>2618.5</v>
+        <v>3103.6</v>
       </c>
       <c r="F12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-0.25642984638684552</v>
+        <v>-0.11867697966248381</v>
       </c>
       <c r="G12" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1470,11 +1472,11 @@
       </c>
       <c r="E13" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>1668</v>
+        <v>1883.2</v>
       </c>
       <c r="F13" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-0.27635574837310195</v>
+        <v>-0.18299349240780904</v>
       </c>
       <c r="G13" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1499,11 +1501,11 @@
       </c>
       <c r="E14" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>1671.75</v>
+        <v>1997.6</v>
       </c>
       <c r="F14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-0.26240125220606769</v>
+        <v>-0.11863181779981513</v>
       </c>
       <c r="G14" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1528,11 +1530,11 @@
       </c>
       <c r="E15" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>1967.25</v>
+        <v>2303</v>
       </c>
       <c r="F15" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-0.26430441286462225</v>
+        <v>-0.13874345549738221</v>
       </c>
       <c r="G15" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1557,11 +1559,11 @@
       </c>
       <c r="E16" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>585.25</v>
+        <v>578.6</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>0.50376238835189024</v>
+        <v>0.48667563930013458</v>
       </c>
       <c r="G16" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1586,11 +1588,11 @@
       </c>
       <c r="E17" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>780.5</v>
+        <v>760.4</v>
       </c>
       <c r="F17" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>0.82197643397065345</v>
+        <v>0.77505558025789223</v>
       </c>
       <c r="G17" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1615,11 +1617,11 @@
       </c>
       <c r="E18" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>766</v>
+        <v>752</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>0.96027297099683162</v>
+        <v>0.92444552766268595</v>
       </c>
       <c r="G18" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1644,11 +1646,11 @@
       </c>
       <c r="E19" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>183.25</v>
+        <v>196</v>
       </c>
       <c r="F19" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>-0.24276859504132231</v>
+        <v>-0.19008264462809921</v>
       </c>
       <c r="G19" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1673,11 +1675,11 @@
       </c>
       <c r="E20" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>80.75</v>
+        <v>85.8</v>
       </c>
       <c r="F20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-0.43209979906229079</v>
+        <v>-0.3965840589417281</v>
       </c>
       <c r="G20" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1702,11 +1704,11 @@
       </c>
       <c r="E21" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>426.25</v>
+        <v>436.2</v>
       </c>
       <c r="F21" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>-0.16925754060324827</v>
+        <v>-0.14986542923433877</v>
       </c>
       <c r="G21" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
@@ -1731,11 +1733,11 @@
       </c>
       <c r="E22" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>693.75</v>
+        <v>696.4</v>
       </c>
       <c r="F22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>-0.14497623099947188</v>
+        <v>-0.14171019426022657</v>
       </c>
       <c r="G22" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1760,15 +1762,15 @@
       </c>
       <c r="E23" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="F23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>6.7344345616264345E-2</v>
+        <v>-0.14612452350698857</v>
       </c>
       <c r="G23" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H23">
         <v>4.1500000000000004</v>
@@ -1789,11 +1791,11 @@
       </c>
       <c r="E24" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>457.75</v>
+        <v>612.20000000000005</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.41906387864869765</v>
+        <v>-0.22304949537680541</v>
       </c>
       <c r="G24" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1818,11 +1820,11 @@
       </c>
       <c r="E25" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>427</v>
+        <v>830.8</v>
       </c>
       <c r="F25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.66475998205473308</v>
+        <v>-0.34773441004934957</v>
       </c>
       <c r="G25" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1847,11 +1849,11 @@
       </c>
       <c r="E26" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-0.16098263295239801</v>
+        <v>-0.18743813551696209</v>
       </c>
       <c r="G26" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1876,11 +1878,11 @@
       </c>
       <c r="E27" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>288.25</v>
+        <v>290.60000000000002</v>
       </c>
       <c r="F27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>-0.282705296836118</v>
+        <v>-0.27685744756487729</v>
       </c>
       <c r="G27" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1905,11 +1907,11 @@
       </c>
       <c r="E28" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>211.5</v>
+        <v>225</v>
       </c>
       <c r="F28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>1.7794117647058822</v>
+        <v>1.9568210262828534</v>
       </c>
       <c r="G28" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1934,11 +1936,11 @@
       </c>
       <c r="E29" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>231.75</v>
+        <v>280.39999999999998</v>
       </c>
       <c r="F29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>2.214498018494055</v>
+        <v>2.8892998678996031</v>
       </c>
       <c r="G29" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1963,11 +1965,11 @@
       </c>
       <c r="E30" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>101.75</v>
+        <v>104</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-0.20418994413407821</v>
+        <v>-0.1865921787709498</v>
       </c>
       <c r="G30" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1992,11 +1994,11 @@
       </c>
       <c r="E31" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>97.75</v>
+        <v>99.2</v>
       </c>
       <c r="F31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-0.31802325581395352</v>
+        <v>-0.3079069767441861</v>
       </c>
       <c r="G31" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2021,11 +2023,11 @@
       </c>
       <c r="E32" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>567.5</v>
+        <v>606</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-0.12985543224299056</v>
+        <v>-7.0823598130841048E-2</v>
       </c>
       <c r="G32" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2050,11 +2052,11 @@
       </c>
       <c r="E33" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>449.25</v>
+        <v>475.6</v>
       </c>
       <c r="F33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-0.28582513247539743</v>
+        <v>-0.24393641180923542</v>
       </c>
       <c r="G33" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2079,11 +2081,11 @@
       </c>
       <c r="E34" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>598.25</v>
+        <v>635.20000000000005</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-0.29798558337058556</v>
+        <v>-0.25462673223066601</v>
       </c>
       <c r="G34" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2108,11 +2110,11 @@
       </c>
       <c r="E35" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>330.5</v>
+        <v>358.8</v>
       </c>
       <c r="F35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.42918825561312612</v>
+        <v>-0.38031088082901554</v>
       </c>
       <c r="G35" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2166,11 +2168,11 @@
       </c>
       <c r="E37" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="F37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>1.916666666666667</v>
+        <v>1.8000000000000003</v>
       </c>
       <c r="G37" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2195,11 +2197,11 @@
       </c>
       <c r="E38" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>88.5</v>
+        <v>96.6</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>-0.35468749999999993</v>
+        <v>-0.29562500000000003</v>
       </c>
       <c r="G38" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2224,11 +2226,11 @@
       </c>
       <c r="E39" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="F39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-0.30919866013913944</v>
+        <v>-0.26410718886884821</v>
       </c>
       <c r="G39" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2253,11 +2255,11 @@
       </c>
       <c r="E40" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>400.75</v>
+        <v>392.8</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>2.0174793832915028</v>
+        <v>1.9576192183578347</v>
       </c>
       <c r="G40" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2282,11 +2284,11 @@
       </c>
       <c r="E41" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>161</v>
+        <v>140.6</v>
       </c>
       <c r="F41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.45634346357935363</v>
+        <v>-0.52522913651712499</v>
       </c>
       <c r="G41" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2311,11 +2313,11 @@
       </c>
       <c r="E42" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>262.75</v>
+        <v>249.6</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-0.50303971899486621</v>
+        <v>-0.52791137530397192</v>
       </c>
       <c r="G42" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2340,11 +2342,11 @@
       </c>
       <c r="E43" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>198.5</v>
+        <v>192.6</v>
       </c>
       <c r="F43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-0.35039738195418413</v>
+        <v>-0.36970546984572228</v>
       </c>
       <c r="G43" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2369,11 +2371,11 @@
       </c>
       <c r="E44" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>212.5</v>
+        <v>210.2</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-0.26700065703022346</v>
+        <v>-0.27493429697766103</v>
       </c>
       <c r="G44" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
@@ -2398,11 +2400,11 @@
       </c>
       <c r="E45" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>33.25</v>
+        <v>28.8</v>
       </c>
       <c r="F45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.42388613861386137</v>
+        <v>-0.50099009900990099</v>
       </c>
       <c r="G45" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
@@ -2427,11 +2429,11 @@
       </c>
       <c r="E46" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F48</f>
-        <v>51</v>
+        <v>69.2</v>
       </c>
       <c r="F46" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G48</f>
-        <v>-0.51296043656207368</v>
+        <v>-0.33915416098226459</v>
       </c>
       <c r="G46" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H48</f>
@@ -2456,11 +2458,11 @@
       </c>
       <c r="E47" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F49</f>
-        <v>20.75</v>
+        <v>22.6</v>
       </c>
       <c r="F47" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G49</f>
-        <v>-0.57939189189189189</v>
+        <v>-0.54189189189189191</v>
       </c>
       <c r="G47" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H49</f>
@@ -2485,11 +2487,11 @@
       </c>
       <c r="E48" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F50</f>
-        <v>31.5</v>
+        <v>29.8</v>
       </c>
       <c r="F48" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G50</f>
-        <v>-0.43072289156626509</v>
+        <v>-0.46144578313253015</v>
       </c>
       <c r="G48" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H50</f>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E324EF51-1007-48B8-99C8-2160D62C1169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9994C4E4-49CF-44FB-8A91-FD8B93039271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -364,6 +364,7 @@
       <sheetName val="INVENTARIO NACIONAL 03-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 04-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 08-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 09-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -378,13 +379,14 @@
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
-      <sheetData sheetId="8">
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9">
         <row r="4">
           <cell r="F4">
-            <v>987.4</v>
+            <v>1008.3333333333334</v>
           </cell>
           <cell r="G4">
-            <v>-0.16892184368737473</v>
+            <v>-0.15130260521042083</v>
           </cell>
           <cell r="H4" t="str">
             <v>BAJO</v>
@@ -392,10 +394,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>83.8</v>
+            <v>88.833333333333329</v>
           </cell>
           <cell r="G5">
-            <v>9.7132169576059857E-2</v>
+            <v>0.16302992518703241</v>
           </cell>
           <cell r="H5" t="str">
             <v>SUBIÓ</v>
@@ -403,10 +405,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>489</v>
+            <v>429.83333333333331</v>
           </cell>
           <cell r="G6">
-            <v>-4.0190672025422924E-2</v>
+            <v>-0.15632302084306948</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -414,10 +416,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>75.2</v>
+            <v>72.166666666666671</v>
           </cell>
           <cell r="G7">
-            <v>-0.23265306122448981</v>
+            <v>-0.26360544217687065</v>
           </cell>
           <cell r="H7" t="str">
             <v>BAJO</v>
@@ -425,10 +427,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>6.2</v>
+            <v>8.8333333333333339</v>
           </cell>
           <cell r="G8">
-            <v>-0.48127490039840637</v>
+            <v>-0.26095617529880477</v>
           </cell>
           <cell r="H8" t="str">
             <v>BAJO</v>
@@ -436,10 +438,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1339</v>
+            <v>1312.6666666666667</v>
           </cell>
           <cell r="G9">
-            <v>-8.308605341246289E-2</v>
+            <v>-0.10111846610362918</v>
           </cell>
           <cell r="H9" t="str">
             <v>BAJO</v>
@@ -447,10 +449,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>113</v>
+            <v>119.83333333333333</v>
           </cell>
           <cell r="G10">
-            <v>-0.24857504749841675</v>
+            <v>-0.20313489550348329</v>
           </cell>
           <cell r="H10" t="str">
             <v>BAJO</v>
@@ -458,10 +460,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>235.6</v>
+            <v>240</v>
           </cell>
           <cell r="G11">
-            <v>-0.31426195426195425</v>
+            <v>-0.30145530145530142</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -469,10 +471,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>665.8</v>
+            <v>688.66666666666663</v>
           </cell>
           <cell r="G12">
-            <v>-0.13102548166563088</v>
+            <v>-0.10118085767557494</v>
           </cell>
           <cell r="H12" t="str">
             <v>BAJO</v>
@@ -480,10 +482,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>290.60000000000002</v>
+            <v>302</v>
           </cell>
           <cell r="G13">
-            <v>-0.19902874392964942</v>
+            <v>-0.16760729754560966</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -491,10 +493,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3103.6</v>
+            <v>3130</v>
           </cell>
           <cell r="G14">
-            <v>-0.11867697966248381</v>
+            <v>-0.11118022501081781</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -502,10 +504,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>1883.2</v>
+            <v>1931.1666666666667</v>
           </cell>
           <cell r="G15">
-            <v>-0.18299349240780904</v>
+            <v>-0.16218365871294282</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -513,10 +515,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>1997.6</v>
+            <v>2100.6666666666665</v>
           </cell>
           <cell r="G16">
-            <v>-0.11863181779981513</v>
+            <v>-7.3157408185561823E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -524,10 +526,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2303</v>
+            <v>2349.1666666666665</v>
           </cell>
           <cell r="G17">
-            <v>-0.13874345549738221</v>
+            <v>-0.12147843430565952</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -535,10 +537,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>578.6</v>
+            <v>634</v>
           </cell>
           <cell r="G18">
-            <v>0.48667563930013458</v>
+            <v>0.62902239079897226</v>
           </cell>
           <cell r="H18" t="str">
             <v>SUBIÓ</v>
@@ -546,10 +548,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>760.4</v>
+            <v>789.83333333333337</v>
           </cell>
           <cell r="G19">
-            <v>0.77505558025789223</v>
+            <v>0.84376389506447302</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -557,10 +559,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>752</v>
+            <v>781.5</v>
           </cell>
           <cell r="G20">
-            <v>0.92444552766268595</v>
+            <v>0.9999390689739216</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -568,10 +570,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>196</v>
+            <v>213.33333333333334</v>
           </cell>
           <cell r="G21">
-            <v>-0.19008264462809921</v>
+            <v>-0.11845730027548207</v>
           </cell>
           <cell r="H21" t="str">
             <v>BAJO</v>
@@ -579,10 +581,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>85.8</v>
+            <v>94.666666666666671</v>
           </cell>
           <cell r="G22">
-            <v>-0.3965840589417281</v>
+            <v>-0.33422638981915609</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -590,10 +592,10 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>436.2</v>
+            <v>462.66666666666669</v>
           </cell>
           <cell r="G23">
-            <v>-0.14986542923433877</v>
+            <v>-9.8283062645011521E-2</v>
           </cell>
           <cell r="H23" t="str">
             <v>BAJO</v>
@@ -601,10 +603,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>696.4</v>
+            <v>758.33333333333337</v>
           </cell>
           <cell r="G24">
-            <v>-0.14171019426022657</v>
+            <v>-6.5379423675098303E-2</v>
           </cell>
           <cell r="H24" t="str">
             <v>BAJO</v>
@@ -612,10 +614,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>64</v>
+            <v>55</v>
           </cell>
           <cell r="G25">
-            <v>-0.14612452350698857</v>
+            <v>-0.26620076238881829</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -623,10 +625,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>612.20000000000005</v>
+            <v>604.33333333333337</v>
           </cell>
           <cell r="G26">
-            <v>-0.22304949537680541</v>
+            <v>-0.23303317821961678</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -634,10 +636,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>830.8</v>
+            <v>878.83333333333337</v>
           </cell>
           <cell r="G27">
-            <v>-0.34773441004934957</v>
+            <v>-0.31002317930312551</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -645,10 +647,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>430</v>
+            <v>418.83333333333331</v>
           </cell>
           <cell r="G28">
-            <v>-0.18743813551696209</v>
+            <v>-0.20853954827679289</v>
           </cell>
           <cell r="H28" t="str">
             <v>BAJO</v>
@@ -656,10 +658,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>290.60000000000002</v>
+            <v>302.16666666666669</v>
           </cell>
           <cell r="G29">
-            <v>-0.27685744756487729</v>
+            <v>-0.24807441640004735</v>
           </cell>
           <cell r="H29" t="str">
             <v>BAJO</v>
@@ -667,10 +669,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>225</v>
+            <v>224</v>
           </cell>
           <cell r="G30">
-            <v>1.9568210262828534</v>
+            <v>1.9436795994993741</v>
           </cell>
           <cell r="H30" t="str">
             <v>SUBIÓ</v>
@@ -678,10 +680,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>280.39999999999998</v>
+            <v>266.66666666666669</v>
           </cell>
           <cell r="G31">
-            <v>2.8892998678996031</v>
+            <v>2.6988110964332894</v>
           </cell>
           <cell r="H31" t="str">
             <v>SUBIÓ</v>
@@ -689,10 +691,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>104</v>
+            <v>110.16666666666667</v>
           </cell>
           <cell r="G32">
-            <v>-0.1865921787709498</v>
+            <v>-0.13836126629422718</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -700,10 +702,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>99.2</v>
+            <v>105.66666666666667</v>
           </cell>
           <cell r="G33">
-            <v>-0.3079069767441861</v>
+            <v>-0.26279069767441865</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -711,10 +713,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>606</v>
+            <v>633.66666666666663</v>
           </cell>
           <cell r="G34">
-            <v>-7.0823598130841048E-2</v>
+            <v>-2.8402453271028083E-2</v>
           </cell>
           <cell r="H34" t="str">
             <v>BAJO</v>
@@ -722,10 +724,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>475.6</v>
+            <v>516.83333333333337</v>
           </cell>
           <cell r="G35">
-            <v>-0.24393641180923542</v>
+            <v>-0.17838758516275544</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -733,10 +735,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>635.20000000000005</v>
+            <v>677.66666666666663</v>
           </cell>
           <cell r="G36">
-            <v>-0.25462673223066601</v>
+            <v>-0.20479436745641488</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -744,10 +746,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>358.8</v>
+            <v>390.66666666666669</v>
           </cell>
           <cell r="G37">
-            <v>-0.38031088082901554</v>
+            <v>-0.32527345998848589</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -755,10 +757,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>4</v>
+            <v>3.5</v>
           </cell>
           <cell r="G38">
-            <v>0.61538461538461542</v>
+            <v>0.41346153846153832</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -766,10 +768,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>1.2</v>
+            <v>1</v>
           </cell>
           <cell r="G39">
-            <v>1.8000000000000003</v>
+            <v>1.3333333333333335</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -777,10 +779,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>96.6</v>
+            <v>103.5</v>
           </cell>
           <cell r="G40">
-            <v>-0.29562500000000003</v>
+            <v>-0.24531249999999993</v>
           </cell>
           <cell r="H40" t="str">
             <v>BAJO</v>
@@ -788,10 +790,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>408</v>
+            <v>435</v>
           </cell>
           <cell r="G41">
-            <v>-0.26410718886884821</v>
+            <v>-0.21540839989693383</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -799,10 +801,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>392.8</v>
+            <v>396.16666666666669</v>
           </cell>
           <cell r="G42">
-            <v>1.9576192183578347</v>
+            <v>1.9829688060236648</v>
           </cell>
           <cell r="H42" t="str">
             <v>SUBIÓ</v>
@@ -810,10 +812,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>140.6</v>
+            <v>146.33333333333334</v>
           </cell>
           <cell r="G43">
-            <v>-0.52522913651712499</v>
+            <v>-0.50586911078951602</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -821,10 +823,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>249.6</v>
+            <v>274.5</v>
           </cell>
           <cell r="G44">
-            <v>-0.52791137530397192</v>
+            <v>-0.48081599567684408</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -832,10 +834,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>192.6</v>
+            <v>193</v>
           </cell>
           <cell r="G45">
-            <v>-0.36970546984572228</v>
+            <v>-0.36839644693782136</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -843,10 +845,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>210.2</v>
+            <v>225.16666666666666</v>
           </cell>
           <cell r="G46">
-            <v>-0.27493429697766103</v>
+            <v>-0.2233081471747701</v>
           </cell>
           <cell r="H46" t="str">
             <v>BAJO</v>
@@ -854,10 +856,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>28.8</v>
+            <v>32</v>
           </cell>
           <cell r="G47">
-            <v>-0.50099009900990099</v>
+            <v>-0.44554455445544561</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -865,10 +867,10 @@
         </row>
         <row r="48">
           <cell r="F48">
-            <v>69.2</v>
+            <v>76.833333333333329</v>
           </cell>
           <cell r="G48">
-            <v>-0.33915416098226459</v>
+            <v>-0.26625738972260116</v>
           </cell>
           <cell r="H48" t="str">
             <v>BAJO</v>
@@ -876,10 +878,10 @@
         </row>
         <row r="49">
           <cell r="F49">
-            <v>22.6</v>
+            <v>28</v>
           </cell>
           <cell r="G49">
-            <v>-0.54189189189189191</v>
+            <v>-0.43243243243243246</v>
           </cell>
           <cell r="H49" t="str">
             <v>BAJO</v>
@@ -887,10 +889,10 @@
         </row>
         <row r="50">
           <cell r="F50">
-            <v>29.8</v>
+            <v>34.666666666666664</v>
           </cell>
           <cell r="G50">
-            <v>-0.46144578313253015</v>
+            <v>-0.37349397590361455</v>
           </cell>
           <cell r="H50" t="str">
             <v>BAJO</v>
@@ -1153,11 +1155,11 @@
       </c>
       <c r="E2" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>987.4</v>
+        <v>1008.3333333333334</v>
       </c>
       <c r="F2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>-0.16892184368737473</v>
+        <v>-0.15130260521042083</v>
       </c>
       <c r="G2" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1182,11 +1184,11 @@
       </c>
       <c r="E3" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>83.8</v>
+        <v>88.833333333333329</v>
       </c>
       <c r="F3" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>9.7132169576059857E-2</v>
+        <v>0.16302992518703241</v>
       </c>
       <c r="G3" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1211,11 +1213,11 @@
       </c>
       <c r="E4" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>489</v>
+        <v>429.83333333333331</v>
       </c>
       <c r="F4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-4.0190672025422924E-2</v>
+        <v>-0.15632302084306948</v>
       </c>
       <c r="G4" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1240,11 +1242,11 @@
       </c>
       <c r="E5" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>75.2</v>
+        <v>72.166666666666671</v>
       </c>
       <c r="F5" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>-0.23265306122448981</v>
+        <v>-0.26360544217687065</v>
       </c>
       <c r="G5" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1269,11 +1271,11 @@
       </c>
       <c r="E6" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>6.2</v>
+        <v>8.8333333333333339</v>
       </c>
       <c r="F6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>-0.48127490039840637</v>
+        <v>-0.26095617529880477</v>
       </c>
       <c r="G6" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1298,11 +1300,11 @@
       </c>
       <c r="E7" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1339</v>
+        <v>1312.6666666666667</v>
       </c>
       <c r="F7" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-8.308605341246289E-2</v>
+        <v>-0.10111846610362918</v>
       </c>
       <c r="G7" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1327,11 +1329,11 @@
       </c>
       <c r="E8" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>113</v>
+        <v>119.83333333333333</v>
       </c>
       <c r="F8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-0.24857504749841675</v>
+        <v>-0.20313489550348329</v>
       </c>
       <c r="G8" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1356,11 +1358,11 @@
       </c>
       <c r="E9" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>235.6</v>
+        <v>240</v>
       </c>
       <c r="F9" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-0.31426195426195425</v>
+        <v>-0.30145530145530142</v>
       </c>
       <c r="G9" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1385,11 +1387,11 @@
       </c>
       <c r="E10" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>665.8</v>
+        <v>688.66666666666663</v>
       </c>
       <c r="F10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-0.13102548166563088</v>
+        <v>-0.10118085767557494</v>
       </c>
       <c r="G10" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1414,11 +1416,11 @@
       </c>
       <c r="E11" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>290.60000000000002</v>
+        <v>302</v>
       </c>
       <c r="F11" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.19902874392964942</v>
+        <v>-0.16760729754560966</v>
       </c>
       <c r="G11" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1443,11 +1445,11 @@
       </c>
       <c r="E12" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3103.6</v>
+        <v>3130</v>
       </c>
       <c r="F12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-0.11867697966248381</v>
+        <v>-0.11118022501081781</v>
       </c>
       <c r="G12" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1472,11 +1474,11 @@
       </c>
       <c r="E13" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>1883.2</v>
+        <v>1931.1666666666667</v>
       </c>
       <c r="F13" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-0.18299349240780904</v>
+        <v>-0.16218365871294282</v>
       </c>
       <c r="G13" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1501,11 +1503,11 @@
       </c>
       <c r="E14" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>1997.6</v>
+        <v>2100.6666666666665</v>
       </c>
       <c r="F14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-0.11863181779981513</v>
+        <v>-7.3157408185561823E-2</v>
       </c>
       <c r="G14" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1530,11 +1532,11 @@
       </c>
       <c r="E15" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2303</v>
+        <v>2349.1666666666665</v>
       </c>
       <c r="F15" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-0.13874345549738221</v>
+        <v>-0.12147843430565952</v>
       </c>
       <c r="G15" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1559,11 +1561,11 @@
       </c>
       <c r="E16" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>578.6</v>
+        <v>634</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>0.48667563930013458</v>
+        <v>0.62902239079897226</v>
       </c>
       <c r="G16" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1588,11 +1590,11 @@
       </c>
       <c r="E17" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>760.4</v>
+        <v>789.83333333333337</v>
       </c>
       <c r="F17" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>0.77505558025789223</v>
+        <v>0.84376389506447302</v>
       </c>
       <c r="G17" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1617,11 +1619,11 @@
       </c>
       <c r="E18" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>752</v>
+        <v>781.5</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>0.92444552766268595</v>
+        <v>0.9999390689739216</v>
       </c>
       <c r="G18" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1646,11 +1648,11 @@
       </c>
       <c r="E19" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>196</v>
+        <v>213.33333333333334</v>
       </c>
       <c r="F19" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>-0.19008264462809921</v>
+        <v>-0.11845730027548207</v>
       </c>
       <c r="G19" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1675,11 +1677,11 @@
       </c>
       <c r="E20" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>85.8</v>
+        <v>94.666666666666671</v>
       </c>
       <c r="F20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-0.3965840589417281</v>
+        <v>-0.33422638981915609</v>
       </c>
       <c r="G20" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1704,11 +1706,11 @@
       </c>
       <c r="E21" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>436.2</v>
+        <v>462.66666666666669</v>
       </c>
       <c r="F21" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>-0.14986542923433877</v>
+        <v>-9.8283062645011521E-2</v>
       </c>
       <c r="G21" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
@@ -1733,11 +1735,11 @@
       </c>
       <c r="E22" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>696.4</v>
+        <v>758.33333333333337</v>
       </c>
       <c r="F22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>-0.14171019426022657</v>
+        <v>-6.5379423675098303E-2</v>
       </c>
       <c r="G22" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1762,11 +1764,11 @@
       </c>
       <c r="E23" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-0.14612452350698857</v>
+        <v>-0.26620076238881829</v>
       </c>
       <c r="G23" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1791,11 +1793,11 @@
       </c>
       <c r="E24" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>612.20000000000005</v>
+        <v>604.33333333333337</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.22304949537680541</v>
+        <v>-0.23303317821961678</v>
       </c>
       <c r="G24" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1820,11 +1822,11 @@
       </c>
       <c r="E25" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>830.8</v>
+        <v>878.83333333333337</v>
       </c>
       <c r="F25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.34773441004934957</v>
+        <v>-0.31002317930312551</v>
       </c>
       <c r="G25" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1849,11 +1851,11 @@
       </c>
       <c r="E26" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>430</v>
+        <v>418.83333333333331</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-0.18743813551696209</v>
+        <v>-0.20853954827679289</v>
       </c>
       <c r="G26" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1878,11 +1880,11 @@
       </c>
       <c r="E27" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>290.60000000000002</v>
+        <v>302.16666666666669</v>
       </c>
       <c r="F27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>-0.27685744756487729</v>
+        <v>-0.24807441640004735</v>
       </c>
       <c r="G27" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1907,11 +1909,11 @@
       </c>
       <c r="E28" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>1.9568210262828534</v>
+        <v>1.9436795994993741</v>
       </c>
       <c r="G28" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1936,11 +1938,11 @@
       </c>
       <c r="E29" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>280.39999999999998</v>
+        <v>266.66666666666669</v>
       </c>
       <c r="F29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>2.8892998678996031</v>
+        <v>2.6988110964332894</v>
       </c>
       <c r="G29" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1965,11 +1967,11 @@
       </c>
       <c r="E30" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>104</v>
+        <v>110.16666666666667</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-0.1865921787709498</v>
+        <v>-0.13836126629422718</v>
       </c>
       <c r="G30" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1994,11 +1996,11 @@
       </c>
       <c r="E31" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>99.2</v>
+        <v>105.66666666666667</v>
       </c>
       <c r="F31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-0.3079069767441861</v>
+        <v>-0.26279069767441865</v>
       </c>
       <c r="G31" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2023,11 +2025,11 @@
       </c>
       <c r="E32" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>606</v>
+        <v>633.66666666666663</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-7.0823598130841048E-2</v>
+        <v>-2.8402453271028083E-2</v>
       </c>
       <c r="G32" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2052,11 +2054,11 @@
       </c>
       <c r="E33" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>475.6</v>
+        <v>516.83333333333337</v>
       </c>
       <c r="F33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-0.24393641180923542</v>
+        <v>-0.17838758516275544</v>
       </c>
       <c r="G33" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2081,11 +2083,11 @@
       </c>
       <c r="E34" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>635.20000000000005</v>
+        <v>677.66666666666663</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-0.25462673223066601</v>
+        <v>-0.20479436745641488</v>
       </c>
       <c r="G34" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2110,11 +2112,11 @@
       </c>
       <c r="E35" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>358.8</v>
+        <v>390.66666666666669</v>
       </c>
       <c r="F35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.38031088082901554</v>
+        <v>-0.32527345998848589</v>
       </c>
       <c r="G35" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2139,11 +2141,11 @@
       </c>
       <c r="E36" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>0.61538461538461542</v>
+        <v>0.41346153846153832</v>
       </c>
       <c r="G36" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2168,11 +2170,11 @@
       </c>
       <c r="E37" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>1.8000000000000003</v>
+        <v>1.3333333333333335</v>
       </c>
       <c r="G37" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2197,11 +2199,11 @@
       </c>
       <c r="E38" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>96.6</v>
+        <v>103.5</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>-0.29562500000000003</v>
+        <v>-0.24531249999999993</v>
       </c>
       <c r="G38" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2226,11 +2228,11 @@
       </c>
       <c r="E39" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>408</v>
+        <v>435</v>
       </c>
       <c r="F39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-0.26410718886884821</v>
+        <v>-0.21540839989693383</v>
       </c>
       <c r="G39" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2255,11 +2257,11 @@
       </c>
       <c r="E40" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>392.8</v>
+        <v>396.16666666666669</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>1.9576192183578347</v>
+        <v>1.9829688060236648</v>
       </c>
       <c r="G40" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2284,11 +2286,11 @@
       </c>
       <c r="E41" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>140.6</v>
+        <v>146.33333333333334</v>
       </c>
       <c r="F41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.52522913651712499</v>
+        <v>-0.50586911078951602</v>
       </c>
       <c r="G41" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2313,11 +2315,11 @@
       </c>
       <c r="E42" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>249.6</v>
+        <v>274.5</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-0.52791137530397192</v>
+        <v>-0.48081599567684408</v>
       </c>
       <c r="G42" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2342,11 +2344,11 @@
       </c>
       <c r="E43" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>192.6</v>
+        <v>193</v>
       </c>
       <c r="F43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-0.36970546984572228</v>
+        <v>-0.36839644693782136</v>
       </c>
       <c r="G43" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2371,11 +2373,11 @@
       </c>
       <c r="E44" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>210.2</v>
+        <v>225.16666666666666</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-0.27493429697766103</v>
+        <v>-0.2233081471747701</v>
       </c>
       <c r="G44" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
@@ -2400,11 +2402,11 @@
       </c>
       <c r="E45" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>28.8</v>
+        <v>32</v>
       </c>
       <c r="F45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.50099009900990099</v>
+        <v>-0.44554455445544561</v>
       </c>
       <c r="G45" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
@@ -2429,11 +2431,11 @@
       </c>
       <c r="E46" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F48</f>
-        <v>69.2</v>
+        <v>76.833333333333329</v>
       </c>
       <c r="F46" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G48</f>
-        <v>-0.33915416098226459</v>
+        <v>-0.26625738972260116</v>
       </c>
       <c r="G46" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H48</f>
@@ -2458,11 +2460,11 @@
       </c>
       <c r="E47" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F49</f>
-        <v>22.6</v>
+        <v>28</v>
       </c>
       <c r="F47" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G49</f>
-        <v>-0.54189189189189191</v>
+        <v>-0.43243243243243246</v>
       </c>
       <c r="G47" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H49</f>
@@ -2487,11 +2489,11 @@
       </c>
       <c r="E48" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F50</f>
-        <v>29.8</v>
+        <v>34.666666666666664</v>
       </c>
       <c r="F48" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G50</f>
-        <v>-0.46144578313253015</v>
+        <v>-0.37349397590361455</v>
       </c>
       <c r="G48" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H50</f>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9994C4E4-49CF-44FB-8A91-FD8B93039271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B311016-929B-4393-A4FB-09ACA535C6CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -383,10 +383,10 @@
       <sheetData sheetId="9">
         <row r="4">
           <cell r="F4">
-            <v>1008.3333333333334</v>
+            <v>1115</v>
           </cell>
           <cell r="G4">
-            <v>-0.15130260521042083</v>
+            <v>-6.1523046092184397E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>BAJO</v>
@@ -394,10 +394,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>88.833333333333329</v>
+            <v>87.285714285714292</v>
           </cell>
           <cell r="G5">
-            <v>0.16302992518703241</v>
+            <v>0.14276807980049888</v>
           </cell>
           <cell r="H5" t="str">
             <v>SUBIÓ</v>
@@ -405,10 +405,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>429.83333333333331</v>
+            <v>447.14285714285717</v>
           </cell>
           <cell r="G6">
-            <v>-0.15632302084306948</v>
+            <v>-0.12234788297971766</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -416,32 +416,32 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>72.166666666666671</v>
+            <v>104.71428571428571</v>
           </cell>
           <cell r="G7">
-            <v>-0.26360544217687065</v>
+            <v>6.8513119533527567E-2</v>
           </cell>
           <cell r="H7" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="8">
           <cell r="F8">
-            <v>8.8333333333333339</v>
+            <v>15</v>
           </cell>
           <cell r="G8">
-            <v>-0.26095617529880477</v>
+            <v>0.2549800796812749</v>
           </cell>
           <cell r="H8" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1312.6666666666667</v>
+            <v>1298.4285714285713</v>
           </cell>
           <cell r="G9">
-            <v>-0.10111846610362918</v>
+            <v>-0.11086836012652035</v>
           </cell>
           <cell r="H9" t="str">
             <v>BAJO</v>
@@ -449,10 +449,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>119.83333333333333</v>
+            <v>133.85714285714286</v>
           </cell>
           <cell r="G10">
-            <v>-0.20313489550348329</v>
+            <v>-0.10987967067764404</v>
           </cell>
           <cell r="H10" t="str">
             <v>BAJO</v>
@@ -460,10 +460,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>240</v>
+            <v>279.28571428571428</v>
           </cell>
           <cell r="G11">
-            <v>-0.30145530145530142</v>
+            <v>-0.18711018711018712</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -471,10 +471,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>688.66666666666663</v>
+            <v>727.57142857142856</v>
           </cell>
           <cell r="G12">
-            <v>-0.10118085767557494</v>
+            <v>-5.0403977625854579E-2</v>
           </cell>
           <cell r="H12" t="str">
             <v>BAJO</v>
@@ -482,10 +482,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>302</v>
+            <v>324.42857142857144</v>
           </cell>
           <cell r="G13">
-            <v>-0.16760729754560966</v>
+            <v>-0.10578816117600731</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -493,10 +493,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3130</v>
+            <v>3259.5714285714284</v>
           </cell>
           <cell r="G14">
-            <v>-0.11118022501081781</v>
+            <v>-7.4386088273474704E-2</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -504,10 +504,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>1931.1666666666667</v>
+            <v>1977.5714285714287</v>
           </cell>
           <cell r="G15">
-            <v>-0.16218365871294282</v>
+            <v>-0.14205144096684219</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -515,10 +515,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2100.6666666666665</v>
+            <v>2131.7142857142858</v>
           </cell>
           <cell r="G16">
-            <v>-7.3157408185561823E-2</v>
+            <v>-5.9458778048575467E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -526,10 +526,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2349.1666666666665</v>
+            <v>2522.8571428571427</v>
           </cell>
           <cell r="G17">
-            <v>-0.12147843430565952</v>
+            <v>-5.6523132813334875E-2</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -537,10 +537,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>634</v>
+            <v>687.71428571428567</v>
           </cell>
           <cell r="G18">
-            <v>0.62902239079897226</v>
+            <v>0.76703780741465777</v>
           </cell>
           <cell r="H18" t="str">
             <v>SUBIÓ</v>
@@ -548,10 +548,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>789.83333333333337</v>
+            <v>815.71428571428567</v>
           </cell>
           <cell r="G19">
-            <v>0.84376389506447302</v>
+            <v>0.9041796353935081</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -559,10 +559,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>781.5</v>
+            <v>804</v>
           </cell>
           <cell r="G20">
-            <v>0.9999390689739216</v>
+            <v>1.0575188886180844</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -570,21 +570,21 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>213.33333333333334</v>
+            <v>247.14285714285714</v>
           </cell>
           <cell r="G21">
-            <v>-0.11845730027548207</v>
+            <v>2.125147579693043E-2</v>
           </cell>
           <cell r="H21" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="22">
           <cell r="F22">
-            <v>94.666666666666671</v>
+            <v>112.14285714285714</v>
           </cell>
           <cell r="G22">
-            <v>-0.33422638981915609</v>
+            <v>-0.21131949095780322</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -592,43 +592,43 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>462.66666666666669</v>
+            <v>517.85714285714289</v>
           </cell>
           <cell r="G23">
-            <v>-9.8283062645011521E-2</v>
+            <v>9.2807424593968069E-3</v>
           </cell>
           <cell r="H23" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="24">
           <cell r="F24">
-            <v>758.33333333333337</v>
+            <v>837.85714285714289</v>
           </cell>
           <cell r="G24">
-            <v>-6.5379423675098303E-2</v>
+            <v>3.2631022947356092E-2</v>
           </cell>
           <cell r="H24" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="25">
           <cell r="F25">
-            <v>55</v>
+            <v>85.571428571428569</v>
           </cell>
           <cell r="G25">
-            <v>-0.26620076238881829</v>
+            <v>0.14167725540025411</v>
           </cell>
           <cell r="H25" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="26">
           <cell r="F26">
-            <v>604.33333333333337</v>
+            <v>633.14285714285711</v>
           </cell>
           <cell r="G26">
-            <v>-0.23303317821961678</v>
+            <v>-0.1964706593340183</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -636,10 +636,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>878.83333333333337</v>
+            <v>916.14285714285711</v>
           </cell>
           <cell r="G27">
-            <v>-0.31002317930312551</v>
+            <v>-0.28073126962763573</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -647,10 +647,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>418.83333333333331</v>
+            <v>480.85714285714283</v>
           </cell>
           <cell r="G28">
-            <v>-0.20853954827679289</v>
+            <v>-9.1334473139566219E-2</v>
           </cell>
           <cell r="H28" t="str">
             <v>BAJO</v>
@@ -658,10 +658,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>302.16666666666669</v>
+            <v>329</v>
           </cell>
           <cell r="G29">
-            <v>-0.24807441640004735</v>
+            <v>-0.18130110202630634</v>
           </cell>
           <cell r="H29" t="str">
             <v>BAJO</v>
@@ -669,10 +669,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>224</v>
+            <v>218.14285714285714</v>
           </cell>
           <cell r="G30">
-            <v>1.9436795994993741</v>
+            <v>1.8667083854818518</v>
           </cell>
           <cell r="H30" t="str">
             <v>SUBIÓ</v>
@@ -680,10 +680,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>266.66666666666669</v>
+            <v>253.85714285714286</v>
           </cell>
           <cell r="G31">
-            <v>2.6988110964332894</v>
+            <v>2.5211360634081901</v>
           </cell>
           <cell r="H31" t="str">
             <v>SUBIÓ</v>
@@ -691,10 +691,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>110.16666666666667</v>
+            <v>118.57142857142857</v>
           </cell>
           <cell r="G32">
-            <v>-0.13836126629422718</v>
+            <v>-7.2625698324022436E-2</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -702,10 +702,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>105.66666666666667</v>
+            <v>119</v>
           </cell>
           <cell r="G33">
-            <v>-0.26279069767441865</v>
+            <v>-0.16976744186046522</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -713,21 +713,21 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>633.66666666666663</v>
+            <v>727.42857142857144</v>
           </cell>
           <cell r="G34">
-            <v>-2.8402453271028083E-2</v>
+            <v>0.1153621495327104</v>
           </cell>
           <cell r="H34" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="35">
           <cell r="F35">
-            <v>516.83333333333337</v>
+            <v>579.57142857142856</v>
           </cell>
           <cell r="G35">
-            <v>-0.17838758516275544</v>
+            <v>-7.8652535957607905E-2</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -735,10 +735,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>677.66666666666663</v>
+            <v>766.14285714285711</v>
           </cell>
           <cell r="G36">
-            <v>-0.20479436745641488</v>
+            <v>-0.10097228430934291</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -746,10 +746,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>390.66666666666669</v>
+            <v>450.42857142857144</v>
           </cell>
           <cell r="G37">
-            <v>-0.32527345998848589</v>
+            <v>-0.22205773501110282</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -757,10 +757,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>3.5</v>
+            <v>4</v>
           </cell>
           <cell r="G38">
-            <v>0.41346153846153832</v>
+            <v>0.61538461538461542</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -768,10 +768,10 @@
         </row>
         <row r="39">
           <cell r="F39">
+            <v>0.8571428571428571</v>
+          </cell>
+          <cell r="G39">
             <v>1</v>
-          </cell>
-          <cell r="G39">
-            <v>1.3333333333333335</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -779,10 +779,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>103.5</v>
+            <v>132.57142857142858</v>
           </cell>
           <cell r="G40">
-            <v>-0.24531249999999993</v>
+            <v>-3.3333333333333215E-2</v>
           </cell>
           <cell r="H40" t="str">
             <v>BAJO</v>
@@ -790,10 +790,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>435</v>
+            <v>494.14285714285717</v>
           </cell>
           <cell r="G41">
-            <v>-0.21540839989693383</v>
+            <v>-0.10873486214893069</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -801,10 +801,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>396.16666666666669</v>
+            <v>425.42857142857144</v>
           </cell>
           <cell r="G42">
-            <v>1.9829688060236648</v>
+            <v>2.2032986733596274</v>
           </cell>
           <cell r="H42" t="str">
             <v>SUBIÓ</v>
@@ -812,10 +812,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>146.33333333333334</v>
+            <v>142.42857142857142</v>
           </cell>
           <cell r="G43">
-            <v>-0.50586911078951602</v>
+            <v>-0.51905451037144246</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -823,10 +823,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>274.5</v>
+            <v>286.14285714285717</v>
           </cell>
           <cell r="G44">
-            <v>-0.48081599567684408</v>
+            <v>-0.4587949202918129</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -834,10 +834,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>193</v>
+            <v>190.71428571428572</v>
           </cell>
           <cell r="G45">
-            <v>-0.36839644693782136</v>
+            <v>-0.37587657784011219</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -845,10 +845,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>225.16666666666666</v>
+            <v>218.28571428571428</v>
           </cell>
           <cell r="G46">
-            <v>-0.2233081471747701</v>
+            <v>-0.2470433639947438</v>
           </cell>
           <cell r="H46" t="str">
             <v>BAJO</v>
@@ -856,10 +856,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>32</v>
+            <v>30.857142857142858</v>
           </cell>
           <cell r="G47">
-            <v>-0.44554455445544561</v>
+            <v>-0.46534653465346532</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -867,10 +867,10 @@
         </row>
         <row r="48">
           <cell r="F48">
-            <v>76.833333333333329</v>
+            <v>74.428571428571431</v>
           </cell>
           <cell r="G48">
-            <v>-0.26625738972260116</v>
+            <v>-0.28922237380627547</v>
           </cell>
           <cell r="H48" t="str">
             <v>BAJO</v>
@@ -878,10 +878,10 @@
         </row>
         <row r="49">
           <cell r="F49">
-            <v>28</v>
+            <v>26</v>
           </cell>
           <cell r="G49">
-            <v>-0.43243243243243246</v>
+            <v>-0.47297297297297303</v>
           </cell>
           <cell r="H49" t="str">
             <v>BAJO</v>
@@ -889,10 +889,10 @@
         </row>
         <row r="50">
           <cell r="F50">
-            <v>34.666666666666664</v>
+            <v>33.857142857142854</v>
           </cell>
           <cell r="G50">
-            <v>-0.37349397590361455</v>
+            <v>-0.38812392426850262</v>
           </cell>
           <cell r="H50" t="str">
             <v>BAJO</v>
@@ -1155,11 +1155,11 @@
       </c>
       <c r="E2" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1008.3333333333334</v>
+        <v>1115</v>
       </c>
       <c r="F2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>-0.15130260521042083</v>
+        <v>-6.1523046092184397E-2</v>
       </c>
       <c r="G2" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1184,11 +1184,11 @@
       </c>
       <c r="E3" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>88.833333333333329</v>
+        <v>87.285714285714292</v>
       </c>
       <c r="F3" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>0.16302992518703241</v>
+        <v>0.14276807980049888</v>
       </c>
       <c r="G3" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1213,11 +1213,11 @@
       </c>
       <c r="E4" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>429.83333333333331</v>
+        <v>447.14285714285717</v>
       </c>
       <c r="F4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-0.15632302084306948</v>
+        <v>-0.12234788297971766</v>
       </c>
       <c r="G4" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1242,15 +1242,15 @@
       </c>
       <c r="E5" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>72.166666666666671</v>
+        <v>104.71428571428571</v>
       </c>
       <c r="F5" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>-0.26360544217687065</v>
+        <v>6.8513119533527567E-2</v>
       </c>
       <c r="G5" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H5">
         <v>3.61</v>
@@ -1271,15 +1271,15 @@
       </c>
       <c r="E6" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>8.8333333333333339</v>
+        <v>15</v>
       </c>
       <c r="F6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>-0.26095617529880477</v>
+        <v>0.2549800796812749</v>
       </c>
       <c r="G6" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H6">
         <v>8.7799999999999994</v>
@@ -1300,11 +1300,11 @@
       </c>
       <c r="E7" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1312.6666666666667</v>
+        <v>1298.4285714285713</v>
       </c>
       <c r="F7" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-0.10111846610362918</v>
+        <v>-0.11086836012652035</v>
       </c>
       <c r="G7" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1329,11 +1329,11 @@
       </c>
       <c r="E8" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>119.83333333333333</v>
+        <v>133.85714285714286</v>
       </c>
       <c r="F8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-0.20313489550348329</v>
+        <v>-0.10987967067764404</v>
       </c>
       <c r="G8" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1358,11 +1358,11 @@
       </c>
       <c r="E9" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>240</v>
+        <v>279.28571428571428</v>
       </c>
       <c r="F9" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-0.30145530145530142</v>
+        <v>-0.18711018711018712</v>
       </c>
       <c r="G9" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1387,11 +1387,11 @@
       </c>
       <c r="E10" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>688.66666666666663</v>
+        <v>727.57142857142856</v>
       </c>
       <c r="F10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-0.10118085767557494</v>
+        <v>-5.0403977625854579E-2</v>
       </c>
       <c r="G10" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1416,11 +1416,11 @@
       </c>
       <c r="E11" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>302</v>
+        <v>324.42857142857144</v>
       </c>
       <c r="F11" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.16760729754560966</v>
+        <v>-0.10578816117600731</v>
       </c>
       <c r="G11" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1445,11 +1445,11 @@
       </c>
       <c r="E12" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3130</v>
+        <v>3259.5714285714284</v>
       </c>
       <c r="F12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-0.11118022501081781</v>
+        <v>-7.4386088273474704E-2</v>
       </c>
       <c r="G12" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1474,11 +1474,11 @@
       </c>
       <c r="E13" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>1931.1666666666667</v>
+        <v>1977.5714285714287</v>
       </c>
       <c r="F13" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-0.16218365871294282</v>
+        <v>-0.14205144096684219</v>
       </c>
       <c r="G13" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1503,11 +1503,11 @@
       </c>
       <c r="E14" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2100.6666666666665</v>
+        <v>2131.7142857142858</v>
       </c>
       <c r="F14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-7.3157408185561823E-2</v>
+        <v>-5.9458778048575467E-2</v>
       </c>
       <c r="G14" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1532,11 +1532,11 @@
       </c>
       <c r="E15" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2349.1666666666665</v>
+        <v>2522.8571428571427</v>
       </c>
       <c r="F15" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-0.12147843430565952</v>
+        <v>-5.6523132813334875E-2</v>
       </c>
       <c r="G15" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1561,11 +1561,11 @@
       </c>
       <c r="E16" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>634</v>
+        <v>687.71428571428567</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>0.62902239079897226</v>
+        <v>0.76703780741465777</v>
       </c>
       <c r="G16" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1590,11 +1590,11 @@
       </c>
       <c r="E17" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>789.83333333333337</v>
+        <v>815.71428571428567</v>
       </c>
       <c r="F17" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>0.84376389506447302</v>
+        <v>0.9041796353935081</v>
       </c>
       <c r="G17" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1619,11 +1619,11 @@
       </c>
       <c r="E18" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>781.5</v>
+        <v>804</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>0.9999390689739216</v>
+        <v>1.0575188886180844</v>
       </c>
       <c r="G18" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1648,15 +1648,15 @@
       </c>
       <c r="E19" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>213.33333333333334</v>
+        <v>247.14285714285714</v>
       </c>
       <c r="F19" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>-0.11845730027548207</v>
+        <v>2.125147579693043E-2</v>
       </c>
       <c r="G19" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H19">
         <v>3.68</v>
@@ -1677,11 +1677,11 @@
       </c>
       <c r="E20" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>94.666666666666671</v>
+        <v>112.14285714285714</v>
       </c>
       <c r="F20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-0.33422638981915609</v>
+        <v>-0.21131949095780322</v>
       </c>
       <c r="G20" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1706,15 +1706,15 @@
       </c>
       <c r="E21" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>462.66666666666669</v>
+        <v>517.85714285714289</v>
       </c>
       <c r="F21" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>-9.8283062645011521E-2</v>
+        <v>9.2807424593968069E-3</v>
       </c>
       <c r="G21" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H21">
         <v>4.1500000000000004</v>
@@ -1735,15 +1735,15 @@
       </c>
       <c r="E22" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>758.33333333333337</v>
+        <v>837.85714285714289</v>
       </c>
       <c r="F22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>-6.5379423675098303E-2</v>
+        <v>3.2631022947356092E-2</v>
       </c>
       <c r="G22" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H22">
         <v>4.1500000000000004</v>
@@ -1764,15 +1764,15 @@
       </c>
       <c r="E23" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>55</v>
+        <v>85.571428571428569</v>
       </c>
       <c r="F23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-0.26620076238881829</v>
+        <v>0.14167725540025411</v>
       </c>
       <c r="G23" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H23">
         <v>4.1500000000000004</v>
@@ -1793,11 +1793,11 @@
       </c>
       <c r="E24" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>604.33333333333337</v>
+        <v>633.14285714285711</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.23303317821961678</v>
+        <v>-0.1964706593340183</v>
       </c>
       <c r="G24" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1822,11 +1822,11 @@
       </c>
       <c r="E25" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>878.83333333333337</v>
+        <v>916.14285714285711</v>
       </c>
       <c r="F25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.31002317930312551</v>
+        <v>-0.28073126962763573</v>
       </c>
       <c r="G25" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1851,11 +1851,11 @@
       </c>
       <c r="E26" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>418.83333333333331</v>
+        <v>480.85714285714283</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-0.20853954827679289</v>
+        <v>-9.1334473139566219E-2</v>
       </c>
       <c r="G26" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1880,11 +1880,11 @@
       </c>
       <c r="E27" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>302.16666666666669</v>
+        <v>329</v>
       </c>
       <c r="F27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>-0.24807441640004735</v>
+        <v>-0.18130110202630634</v>
       </c>
       <c r="G27" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1909,11 +1909,11 @@
       </c>
       <c r="E28" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>224</v>
+        <v>218.14285714285714</v>
       </c>
       <c r="F28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>1.9436795994993741</v>
+        <v>1.8667083854818518</v>
       </c>
       <c r="G28" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1938,11 +1938,11 @@
       </c>
       <c r="E29" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>266.66666666666669</v>
+        <v>253.85714285714286</v>
       </c>
       <c r="F29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>2.6988110964332894</v>
+        <v>2.5211360634081901</v>
       </c>
       <c r="G29" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1967,11 +1967,11 @@
       </c>
       <c r="E30" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>110.16666666666667</v>
+        <v>118.57142857142857</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-0.13836126629422718</v>
+        <v>-7.2625698324022436E-2</v>
       </c>
       <c r="G30" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1996,11 +1996,11 @@
       </c>
       <c r="E31" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>105.66666666666667</v>
+        <v>119</v>
       </c>
       <c r="F31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-0.26279069767441865</v>
+        <v>-0.16976744186046522</v>
       </c>
       <c r="G31" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2025,15 +2025,15 @@
       </c>
       <c r="E32" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>633.66666666666663</v>
+        <v>727.42857142857144</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-2.8402453271028083E-2</v>
+        <v>0.1153621495327104</v>
       </c>
       <c r="G32" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H32">
         <v>1.1599999999999999</v>
@@ -2054,11 +2054,11 @@
       </c>
       <c r="E33" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>516.83333333333337</v>
+        <v>579.57142857142856</v>
       </c>
       <c r="F33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-0.17838758516275544</v>
+        <v>-7.8652535957607905E-2</v>
       </c>
       <c r="G33" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2083,11 +2083,11 @@
       </c>
       <c r="E34" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>677.66666666666663</v>
+        <v>766.14285714285711</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-0.20479436745641488</v>
+        <v>-0.10097228430934291</v>
       </c>
       <c r="G34" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2112,11 +2112,11 @@
       </c>
       <c r="E35" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>390.66666666666669</v>
+        <v>450.42857142857144</v>
       </c>
       <c r="F35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.32527345998848589</v>
+        <v>-0.22205773501110282</v>
       </c>
       <c r="G35" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2141,11 +2141,11 @@
       </c>
       <c r="E36" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>0.41346153846153832</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="G36" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2170,11 +2170,11 @@
       </c>
       <c r="E37" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="F37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>1.3333333333333335</v>
+        <v>1</v>
       </c>
       <c r="G37" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="E38" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>103.5</v>
+        <v>132.57142857142858</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>-0.24531249999999993</v>
+        <v>-3.3333333333333215E-2</v>
       </c>
       <c r="G38" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2228,11 +2228,11 @@
       </c>
       <c r="E39" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>435</v>
+        <v>494.14285714285717</v>
       </c>
       <c r="F39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-0.21540839989693383</v>
+        <v>-0.10873486214893069</v>
       </c>
       <c r="G39" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2257,11 +2257,11 @@
       </c>
       <c r="E40" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>396.16666666666669</v>
+        <v>425.42857142857144</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>1.9829688060236648</v>
+        <v>2.2032986733596274</v>
       </c>
       <c r="G40" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2286,11 +2286,11 @@
       </c>
       <c r="E41" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>146.33333333333334</v>
+        <v>142.42857142857142</v>
       </c>
       <c r="F41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.50586911078951602</v>
+        <v>-0.51905451037144246</v>
       </c>
       <c r="G41" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2315,11 +2315,11 @@
       </c>
       <c r="E42" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>274.5</v>
+        <v>286.14285714285717</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-0.48081599567684408</v>
+        <v>-0.4587949202918129</v>
       </c>
       <c r="G42" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2344,11 +2344,11 @@
       </c>
       <c r="E43" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>193</v>
+        <v>190.71428571428572</v>
       </c>
       <c r="F43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-0.36839644693782136</v>
+        <v>-0.37587657784011219</v>
       </c>
       <c r="G43" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2373,11 +2373,11 @@
       </c>
       <c r="E44" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>225.16666666666666</v>
+        <v>218.28571428571428</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-0.2233081471747701</v>
+        <v>-0.2470433639947438</v>
       </c>
       <c r="G44" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
@@ -2402,11 +2402,11 @@
       </c>
       <c r="E45" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>32</v>
+        <v>30.857142857142858</v>
       </c>
       <c r="F45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.44554455445544561</v>
+        <v>-0.46534653465346532</v>
       </c>
       <c r="G45" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
@@ -2431,11 +2431,11 @@
       </c>
       <c r="E46" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F48</f>
-        <v>76.833333333333329</v>
+        <v>74.428571428571431</v>
       </c>
       <c r="F46" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G48</f>
-        <v>-0.26625738972260116</v>
+        <v>-0.28922237380627547</v>
       </c>
       <c r="G46" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H48</f>
@@ -2460,11 +2460,11 @@
       </c>
       <c r="E47" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F49</f>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F47" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G49</f>
-        <v>-0.43243243243243246</v>
+        <v>-0.47297297297297303</v>
       </c>
       <c r="G47" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H49</f>
@@ -2489,11 +2489,11 @@
       </c>
       <c r="E48" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F50</f>
-        <v>34.666666666666664</v>
+        <v>33.857142857142854</v>
       </c>
       <c r="F48" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G50</f>
-        <v>-0.37349397590361455</v>
+        <v>-0.38812392426850262</v>
       </c>
       <c r="G48" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H50</f>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B311016-929B-4393-A4FB-09ACA535C6CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FA624A2-FFA4-4047-9C68-EACBAF9F75F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -365,6 +365,7 @@
       <sheetName val="INVENTARIO NACIONAL 04-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 08-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 09-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 10-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -380,13 +381,14 @@
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
-      <sheetData sheetId="9">
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10">
         <row r="4">
           <cell r="F4">
-            <v>1115</v>
+            <v>975.625</v>
           </cell>
           <cell r="G4">
-            <v>-6.1523046092184397E-2</v>
+            <v>-0.17883266533066133</v>
           </cell>
           <cell r="H4" t="str">
             <v>BAJO</v>
@@ -394,21 +396,21 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>87.285714285714292</v>
+            <v>76.375</v>
           </cell>
           <cell r="G5">
-            <v>0.14276807980049888</v>
+            <v>-7.7930174563589638E-5</v>
           </cell>
           <cell r="H5" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="6">
           <cell r="F6">
-            <v>447.14285714285717</v>
+            <v>391.25</v>
           </cell>
           <cell r="G6">
-            <v>-0.12234788297971766</v>
+            <v>-0.23205439760725299</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -416,21 +418,21 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>104.71428571428571</v>
+            <v>91.625</v>
           </cell>
           <cell r="G7">
-            <v>6.8513119533527567E-2</v>
+            <v>-6.505102040816324E-2</v>
           </cell>
           <cell r="H7" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="8">
           <cell r="F8">
-            <v>15</v>
+            <v>13.125</v>
           </cell>
           <cell r="G8">
-            <v>0.2549800796812749</v>
+            <v>9.8107569721115562E-2</v>
           </cell>
           <cell r="H8" t="str">
             <v>SUBIÓ</v>
@@ -438,10 +440,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1298.4285714285713</v>
+            <v>1136.125</v>
           </cell>
           <cell r="G9">
-            <v>-0.11086836012652035</v>
+            <v>-0.22200981511070528</v>
           </cell>
           <cell r="H9" t="str">
             <v>BAJO</v>
@@ -449,10 +451,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>133.85714285714286</v>
+            <v>117.125</v>
           </cell>
           <cell r="G10">
-            <v>-0.10987967067764404</v>
+            <v>-0.2211447118429386</v>
           </cell>
           <cell r="H10" t="str">
             <v>BAJO</v>
@@ -460,10 +462,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>279.28571428571428</v>
+            <v>244.375</v>
           </cell>
           <cell r="G11">
-            <v>-0.18711018711018712</v>
+            <v>-0.28872141372141369</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -471,10 +473,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>727.57142857142856</v>
+            <v>636.625</v>
           </cell>
           <cell r="G12">
-            <v>-5.0403977625854579E-2</v>
+            <v>-0.16910348042262269</v>
           </cell>
           <cell r="H12" t="str">
             <v>BAJO</v>
@@ -482,10 +484,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>324.42857142857144</v>
+            <v>283.875</v>
           </cell>
           <cell r="G13">
-            <v>-0.10578816117600731</v>
+            <v>-0.21756464102900641</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -493,10 +495,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3259.5714285714284</v>
+            <v>2852.125</v>
           </cell>
           <cell r="G14">
-            <v>-7.4386088273474704E-2</v>
+            <v>-0.19008782723929041</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -504,10 +506,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>1977.5714285714287</v>
+            <v>1730.375</v>
           </cell>
           <cell r="G15">
-            <v>-0.14205144096684219</v>
+            <v>-0.24929501084598693</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -515,10 +517,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2131.7142857142858</v>
+            <v>1865.25</v>
           </cell>
           <cell r="G16">
-            <v>-5.9458778048575467E-2</v>
+            <v>-0.17702643079250358</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -526,10 +528,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2522.8571428571427</v>
+            <v>2207.5</v>
           </cell>
           <cell r="G17">
-            <v>-5.6523132813334875E-2</v>
+            <v>-0.1744577412116679</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -537,10 +539,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>687.71428571428567</v>
+            <v>601.75</v>
           </cell>
           <cell r="G18">
-            <v>0.76703780741465777</v>
+            <v>0.54615808148782574</v>
           </cell>
           <cell r="H18" t="str">
             <v>SUBIÓ</v>
@@ -548,10 +550,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>815.71428571428567</v>
+            <v>713.75</v>
           </cell>
           <cell r="G19">
-            <v>0.9041796353935081</v>
+            <v>0.66615718096931964</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -559,10 +561,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>804</v>
+            <v>703.5</v>
           </cell>
           <cell r="G20">
-            <v>1.0575188886180844</v>
+            <v>0.80032902754082369</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -570,21 +572,21 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>247.14285714285714</v>
+            <v>216.25</v>
           </cell>
           <cell r="G21">
-            <v>2.125147579693043E-2</v>
+            <v>-0.10640495867768596</v>
           </cell>
           <cell r="H21" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="22">
           <cell r="F22">
-            <v>112.14285714285714</v>
+            <v>98.125</v>
           </cell>
           <cell r="G22">
-            <v>-0.21131949095780322</v>
+            <v>-0.30990455458807775</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -592,43 +594,43 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>517.85714285714289</v>
+            <v>453.125</v>
           </cell>
           <cell r="G23">
-            <v>9.2807424593968069E-3</v>
+            <v>-0.11687935034802777</v>
           </cell>
           <cell r="H23" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="24">
           <cell r="F24">
-            <v>837.85714285714289</v>
+            <v>733.125</v>
           </cell>
           <cell r="G24">
-            <v>3.2631022947356092E-2</v>
+            <v>-9.6447854921063447E-2</v>
           </cell>
           <cell r="H24" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="25">
           <cell r="F25">
-            <v>85.571428571428569</v>
+            <v>74.875</v>
           </cell>
           <cell r="G25">
-            <v>0.14167725540025411</v>
+            <v>-1.0324015247775709E-3</v>
           </cell>
           <cell r="H25" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="26">
           <cell r="F26">
-            <v>633.14285714285711</v>
+            <v>554</v>
           </cell>
           <cell r="G26">
-            <v>-0.1964706593340183</v>
+            <v>-0.29691182691726603</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -636,10 +638,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>916.14285714285711</v>
+            <v>801.625</v>
           </cell>
           <cell r="G27">
-            <v>-0.28073126962763573</v>
+            <v>-0.37063986092418133</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -647,10 +649,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>480.85714285714283</v>
+            <v>420.75</v>
           </cell>
           <cell r="G28">
-            <v>-9.1334473139566219E-2</v>
+            <v>-0.20491766399712041</v>
           </cell>
           <cell r="H28" t="str">
             <v>BAJO</v>
@@ -658,10 +660,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>329</v>
+            <v>287.875</v>
           </cell>
           <cell r="G29">
-            <v>-0.18130110202630634</v>
+            <v>-0.28363846427301809</v>
           </cell>
           <cell r="H29" t="str">
             <v>BAJO</v>
@@ -669,10 +671,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>218.14285714285714</v>
+            <v>190.875</v>
           </cell>
           <cell r="G30">
-            <v>1.8667083854818518</v>
+            <v>1.5083698372966206</v>
           </cell>
           <cell r="H30" t="str">
             <v>SUBIÓ</v>
@@ -680,10 +682,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>253.85714285714286</v>
+            <v>222.125</v>
           </cell>
           <cell r="G31">
-            <v>2.5211360634081901</v>
+            <v>2.080994055482166</v>
           </cell>
           <cell r="H31" t="str">
             <v>SUBIÓ</v>
@@ -691,10 +693,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>118.57142857142857</v>
+            <v>103.75</v>
           </cell>
           <cell r="G32">
-            <v>-7.2625698324022436E-2</v>
+            <v>-0.18854748603351956</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -702,10 +704,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>119</v>
+            <v>104.125</v>
           </cell>
           <cell r="G33">
-            <v>-0.16976744186046522</v>
+            <v>-0.273546511627907</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -713,21 +715,21 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>727.42857142857144</v>
+            <v>636.5</v>
           </cell>
           <cell r="G34">
-            <v>0.1153621495327104</v>
+            <v>-2.4058119158878455E-2</v>
           </cell>
           <cell r="H34" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="35">
           <cell r="F35">
-            <v>579.57142857142856</v>
+            <v>507.125</v>
           </cell>
           <cell r="G35">
-            <v>-7.8652535957607905E-2</v>
+            <v>-0.1938209689629069</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -735,10 +737,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>766.14285714285711</v>
+            <v>670.375</v>
           </cell>
           <cell r="G36">
-            <v>-0.10097228430934291</v>
+            <v>-0.21335074877067495</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -746,10 +748,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>450.42857142857144</v>
+            <v>394.125</v>
           </cell>
           <cell r="G37">
-            <v>-0.22205773501110282</v>
+            <v>-0.31930051813471505</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -757,10 +759,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>4</v>
+            <v>3.5</v>
           </cell>
           <cell r="G38">
-            <v>0.61538461538461542</v>
+            <v>0.41346153846153832</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -768,10 +770,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>0.8571428571428571</v>
+            <v>0.75</v>
           </cell>
           <cell r="G39">
-            <v>1</v>
+            <v>0.75</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -779,10 +781,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>132.57142857142858</v>
+            <v>116</v>
           </cell>
           <cell r="G40">
-            <v>-3.3333333333333215E-2</v>
+            <v>-0.15416666666666667</v>
           </cell>
           <cell r="H40" t="str">
             <v>BAJO</v>
@@ -790,10 +792,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>494.14285714285717</v>
+            <v>432.375</v>
           </cell>
           <cell r="G41">
-            <v>-0.10873486214893069</v>
+            <v>-0.22014300438031442</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -801,10 +803,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>425.42857142857144</v>
+            <v>372.25</v>
           </cell>
           <cell r="G42">
-            <v>2.2032986733596274</v>
+            <v>1.8028863391896741</v>
           </cell>
           <cell r="H42" t="str">
             <v>SUBIÓ</v>
@@ -812,10 +814,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>142.42857142857142</v>
+            <v>124.625</v>
           </cell>
           <cell r="G43">
-            <v>-0.51905451037144246</v>
+            <v>-0.57917269657501214</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -823,10 +825,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>286.14285714285717</v>
+            <v>250.375</v>
           </cell>
           <cell r="G44">
-            <v>-0.4587949202918129</v>
+            <v>-0.52644555525533643</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -834,10 +836,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>190.71428571428572</v>
+            <v>166.875</v>
           </cell>
           <cell r="G45">
-            <v>-0.37587657784011219</v>
+            <v>-0.45389200561009813</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -845,10 +847,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>218.28571428571428</v>
+            <v>191</v>
           </cell>
           <cell r="G46">
-            <v>-0.2470433639947438</v>
+            <v>-0.34116294349540088</v>
           </cell>
           <cell r="H46" t="str">
             <v>BAJO</v>
@@ -856,10 +858,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>30.857142857142858</v>
+            <v>27</v>
           </cell>
           <cell r="G47">
-            <v>-0.46534653465346532</v>
+            <v>-0.53217821782178221</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -867,10 +869,10 @@
         </row>
         <row r="48">
           <cell r="F48">
-            <v>74.428571428571431</v>
+            <v>65.125</v>
           </cell>
           <cell r="G48">
-            <v>-0.28922237380627547</v>
+            <v>-0.37806957708049105</v>
           </cell>
           <cell r="H48" t="str">
             <v>BAJO</v>
@@ -878,10 +880,10 @@
         </row>
         <row r="49">
           <cell r="F49">
-            <v>26</v>
+            <v>22.75</v>
           </cell>
           <cell r="G49">
-            <v>-0.47297297297297303</v>
+            <v>-0.53885135135135132</v>
           </cell>
           <cell r="H49" t="str">
             <v>BAJO</v>
@@ -889,10 +891,10 @@
         </row>
         <row r="50">
           <cell r="F50">
-            <v>33.857142857142854</v>
+            <v>29.625</v>
           </cell>
           <cell r="G50">
-            <v>-0.38812392426850262</v>
+            <v>-0.46460843373493976</v>
           </cell>
           <cell r="H50" t="str">
             <v>BAJO</v>
@@ -1155,11 +1157,11 @@
       </c>
       <c r="E2" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1115</v>
+        <v>975.625</v>
       </c>
       <c r="F2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>-6.1523046092184397E-2</v>
+        <v>-0.17883266533066133</v>
       </c>
       <c r="G2" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1184,15 +1186,15 @@
       </c>
       <c r="E3" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>87.285714285714292</v>
+        <v>76.375</v>
       </c>
       <c r="F3" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>0.14276807980049888</v>
+        <v>-7.7930174563589638E-5</v>
       </c>
       <c r="G3" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H3">
         <v>1.59</v>
@@ -1213,11 +1215,11 @@
       </c>
       <c r="E4" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>447.14285714285717</v>
+        <v>391.25</v>
       </c>
       <c r="F4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-0.12234788297971766</v>
+        <v>-0.23205439760725299</v>
       </c>
       <c r="G4" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1242,15 +1244,15 @@
       </c>
       <c r="E5" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>104.71428571428571</v>
+        <v>91.625</v>
       </c>
       <c r="F5" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>6.8513119533527567E-2</v>
+        <v>-6.505102040816324E-2</v>
       </c>
       <c r="G5" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H5">
         <v>3.61</v>
@@ -1271,11 +1273,11 @@
       </c>
       <c r="E6" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>15</v>
+        <v>13.125</v>
       </c>
       <c r="F6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>0.2549800796812749</v>
+        <v>9.8107569721115562E-2</v>
       </c>
       <c r="G6" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1300,11 +1302,11 @@
       </c>
       <c r="E7" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1298.4285714285713</v>
+        <v>1136.125</v>
       </c>
       <c r="F7" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-0.11086836012652035</v>
+        <v>-0.22200981511070528</v>
       </c>
       <c r="G7" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1329,11 +1331,11 @@
       </c>
       <c r="E8" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>133.85714285714286</v>
+        <v>117.125</v>
       </c>
       <c r="F8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-0.10987967067764404</v>
+        <v>-0.2211447118429386</v>
       </c>
       <c r="G8" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1358,11 +1360,11 @@
       </c>
       <c r="E9" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>279.28571428571428</v>
+        <v>244.375</v>
       </c>
       <c r="F9" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-0.18711018711018712</v>
+        <v>-0.28872141372141369</v>
       </c>
       <c r="G9" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1387,11 +1389,11 @@
       </c>
       <c r="E10" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>727.57142857142856</v>
+        <v>636.625</v>
       </c>
       <c r="F10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-5.0403977625854579E-2</v>
+        <v>-0.16910348042262269</v>
       </c>
       <c r="G10" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1416,11 +1418,11 @@
       </c>
       <c r="E11" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>324.42857142857144</v>
+        <v>283.875</v>
       </c>
       <c r="F11" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.10578816117600731</v>
+        <v>-0.21756464102900641</v>
       </c>
       <c r="G11" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1445,11 +1447,11 @@
       </c>
       <c r="E12" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3259.5714285714284</v>
+        <v>2852.125</v>
       </c>
       <c r="F12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-7.4386088273474704E-2</v>
+        <v>-0.19008782723929041</v>
       </c>
       <c r="G12" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1474,11 +1476,11 @@
       </c>
       <c r="E13" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>1977.5714285714287</v>
+        <v>1730.375</v>
       </c>
       <c r="F13" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-0.14205144096684219</v>
+        <v>-0.24929501084598693</v>
       </c>
       <c r="G13" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1503,11 +1505,11 @@
       </c>
       <c r="E14" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2131.7142857142858</v>
+        <v>1865.25</v>
       </c>
       <c r="F14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-5.9458778048575467E-2</v>
+        <v>-0.17702643079250358</v>
       </c>
       <c r="G14" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1532,11 +1534,11 @@
       </c>
       <c r="E15" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2522.8571428571427</v>
+        <v>2207.5</v>
       </c>
       <c r="F15" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-5.6523132813334875E-2</v>
+        <v>-0.1744577412116679</v>
       </c>
       <c r="G15" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1561,11 +1563,11 @@
       </c>
       <c r="E16" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>687.71428571428567</v>
+        <v>601.75</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>0.76703780741465777</v>
+        <v>0.54615808148782574</v>
       </c>
       <c r="G16" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1590,11 +1592,11 @@
       </c>
       <c r="E17" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>815.71428571428567</v>
+        <v>713.75</v>
       </c>
       <c r="F17" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>0.9041796353935081</v>
+        <v>0.66615718096931964</v>
       </c>
       <c r="G17" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1619,11 +1621,11 @@
       </c>
       <c r="E18" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>804</v>
+        <v>703.5</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>1.0575188886180844</v>
+        <v>0.80032902754082369</v>
       </c>
       <c r="G18" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1648,15 +1650,15 @@
       </c>
       <c r="E19" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>247.14285714285714</v>
+        <v>216.25</v>
       </c>
       <c r="F19" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>2.125147579693043E-2</v>
+        <v>-0.10640495867768596</v>
       </c>
       <c r="G19" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H19">
         <v>3.68</v>
@@ -1677,11 +1679,11 @@
       </c>
       <c r="E20" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>112.14285714285714</v>
+        <v>98.125</v>
       </c>
       <c r="F20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-0.21131949095780322</v>
+        <v>-0.30990455458807775</v>
       </c>
       <c r="G20" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1706,15 +1708,15 @@
       </c>
       <c r="E21" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>517.85714285714289</v>
+        <v>453.125</v>
       </c>
       <c r="F21" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>9.2807424593968069E-3</v>
+        <v>-0.11687935034802777</v>
       </c>
       <c r="G21" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H21">
         <v>4.1500000000000004</v>
@@ -1735,15 +1737,15 @@
       </c>
       <c r="E22" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>837.85714285714289</v>
+        <v>733.125</v>
       </c>
       <c r="F22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>3.2631022947356092E-2</v>
+        <v>-9.6447854921063447E-2</v>
       </c>
       <c r="G22" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H22">
         <v>4.1500000000000004</v>
@@ -1764,15 +1766,15 @@
       </c>
       <c r="E23" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>85.571428571428569</v>
+        <v>74.875</v>
       </c>
       <c r="F23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>0.14167725540025411</v>
+        <v>-1.0324015247775709E-3</v>
       </c>
       <c r="G23" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H23">
         <v>4.1500000000000004</v>
@@ -1793,11 +1795,11 @@
       </c>
       <c r="E24" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>633.14285714285711</v>
+        <v>554</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.1964706593340183</v>
+        <v>-0.29691182691726603</v>
       </c>
       <c r="G24" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1822,11 +1824,11 @@
       </c>
       <c r="E25" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>916.14285714285711</v>
+        <v>801.625</v>
       </c>
       <c r="F25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.28073126962763573</v>
+        <v>-0.37063986092418133</v>
       </c>
       <c r="G25" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1851,11 +1853,11 @@
       </c>
       <c r="E26" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>480.85714285714283</v>
+        <v>420.75</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-9.1334473139566219E-2</v>
+        <v>-0.20491766399712041</v>
       </c>
       <c r="G26" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1880,11 +1882,11 @@
       </c>
       <c r="E27" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>329</v>
+        <v>287.875</v>
       </c>
       <c r="F27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>-0.18130110202630634</v>
+        <v>-0.28363846427301809</v>
       </c>
       <c r="G27" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1909,11 +1911,11 @@
       </c>
       <c r="E28" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>218.14285714285714</v>
+        <v>190.875</v>
       </c>
       <c r="F28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>1.8667083854818518</v>
+        <v>1.5083698372966206</v>
       </c>
       <c r="G28" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1938,11 +1940,11 @@
       </c>
       <c r="E29" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>253.85714285714286</v>
+        <v>222.125</v>
       </c>
       <c r="F29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>2.5211360634081901</v>
+        <v>2.080994055482166</v>
       </c>
       <c r="G29" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1967,11 +1969,11 @@
       </c>
       <c r="E30" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>118.57142857142857</v>
+        <v>103.75</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-7.2625698324022436E-2</v>
+        <v>-0.18854748603351956</v>
       </c>
       <c r="G30" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1996,11 +1998,11 @@
       </c>
       <c r="E31" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>119</v>
+        <v>104.125</v>
       </c>
       <c r="F31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-0.16976744186046522</v>
+        <v>-0.273546511627907</v>
       </c>
       <c r="G31" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2025,15 +2027,15 @@
       </c>
       <c r="E32" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>727.42857142857144</v>
+        <v>636.5</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>0.1153621495327104</v>
+        <v>-2.4058119158878455E-2</v>
       </c>
       <c r="G32" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H32">
         <v>1.1599999999999999</v>
@@ -2054,11 +2056,11 @@
       </c>
       <c r="E33" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>579.57142857142856</v>
+        <v>507.125</v>
       </c>
       <c r="F33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-7.8652535957607905E-2</v>
+        <v>-0.1938209689629069</v>
       </c>
       <c r="G33" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2083,11 +2085,11 @@
       </c>
       <c r="E34" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>766.14285714285711</v>
+        <v>670.375</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-0.10097228430934291</v>
+        <v>-0.21335074877067495</v>
       </c>
       <c r="G34" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2112,11 +2114,11 @@
       </c>
       <c r="E35" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>450.42857142857144</v>
+        <v>394.125</v>
       </c>
       <c r="F35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.22205773501110282</v>
+        <v>-0.31930051813471505</v>
       </c>
       <c r="G35" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2141,11 +2143,11 @@
       </c>
       <c r="E36" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>0.61538461538461542</v>
+        <v>0.41346153846153832</v>
       </c>
       <c r="G36" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2170,11 +2172,11 @@
       </c>
       <c r="E37" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>0.8571428571428571</v>
+        <v>0.75</v>
       </c>
       <c r="F37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G37" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2199,11 +2201,11 @@
       </c>
       <c r="E38" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>132.57142857142858</v>
+        <v>116</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>-3.3333333333333215E-2</v>
+        <v>-0.15416666666666667</v>
       </c>
       <c r="G38" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2228,11 +2230,11 @@
       </c>
       <c r="E39" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>494.14285714285717</v>
+        <v>432.375</v>
       </c>
       <c r="F39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-0.10873486214893069</v>
+        <v>-0.22014300438031442</v>
       </c>
       <c r="G39" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2257,11 +2259,11 @@
       </c>
       <c r="E40" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>425.42857142857144</v>
+        <v>372.25</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>2.2032986733596274</v>
+        <v>1.8028863391896741</v>
       </c>
       <c r="G40" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2286,11 +2288,11 @@
       </c>
       <c r="E41" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>142.42857142857142</v>
+        <v>124.625</v>
       </c>
       <c r="F41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.51905451037144246</v>
+        <v>-0.57917269657501214</v>
       </c>
       <c r="G41" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2315,11 +2317,11 @@
       </c>
       <c r="E42" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>286.14285714285717</v>
+        <v>250.375</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-0.4587949202918129</v>
+        <v>-0.52644555525533643</v>
       </c>
       <c r="G42" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2344,11 +2346,11 @@
       </c>
       <c r="E43" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>190.71428571428572</v>
+        <v>166.875</v>
       </c>
       <c r="F43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-0.37587657784011219</v>
+        <v>-0.45389200561009813</v>
       </c>
       <c r="G43" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2373,11 +2375,11 @@
       </c>
       <c r="E44" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>218.28571428571428</v>
+        <v>191</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-0.2470433639947438</v>
+        <v>-0.34116294349540088</v>
       </c>
       <c r="G44" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
@@ -2402,11 +2404,11 @@
       </c>
       <c r="E45" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>30.857142857142858</v>
+        <v>27</v>
       </c>
       <c r="F45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.46534653465346532</v>
+        <v>-0.53217821782178221</v>
       </c>
       <c r="G45" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
@@ -2431,11 +2433,11 @@
       </c>
       <c r="E46" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F48</f>
-        <v>74.428571428571431</v>
+        <v>65.125</v>
       </c>
       <c r="F46" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G48</f>
-        <v>-0.28922237380627547</v>
+        <v>-0.37806957708049105</v>
       </c>
       <c r="G46" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H48</f>
@@ -2460,11 +2462,11 @@
       </c>
       <c r="E47" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F49</f>
-        <v>26</v>
+        <v>22.75</v>
       </c>
       <c r="F47" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G49</f>
-        <v>-0.47297297297297303</v>
+        <v>-0.53885135135135132</v>
       </c>
       <c r="G47" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H49</f>
@@ -2489,11 +2491,11 @@
       </c>
       <c r="E48" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F50</f>
-        <v>33.857142857142854</v>
+        <v>29.625</v>
       </c>
       <c r="F48" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G50</f>
-        <v>-0.38812392426850262</v>
+        <v>-0.46460843373493976</v>
       </c>
       <c r="G48" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H50</f>
